--- a/goldStandard/_Index.xlsx
+++ b/goldStandard/_Index.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3DFF11-BAED-4F69-BE87-8051C588F506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A645F18-FB62-4283-832A-F711B021F64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22046" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
   </bookViews>
   <sheets>
     <sheet name="In" sheetId="1" r:id="rId1"/>
     <sheet name="Out" sheetId="2" r:id="rId2"/>
+    <sheet name="Possible" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="260">
   <si>
     <t>ID</t>
   </si>
@@ -208,9 +209,6 @@
     <t>DOI: 10.1021/ACS.JPROTEOME.3C00677</t>
   </si>
   <si>
-    <t>spectral count todo?</t>
-  </si>
-  <si>
     <t>PXD058626</t>
   </si>
   <si>
@@ -220,9 +218,6 @@
     <t>Lung tissue</t>
   </si>
   <si>
-    <t>Control;IPF</t>
-  </si>
-  <si>
     <t>DOI: 10.1172/JCI.INSIGHT.189636</t>
   </si>
   <si>
@@ -347,6 +342,471 @@
   </si>
   <si>
     <t>From meta-analysis 944 (searching there corresponce between group - samples)</t>
+  </si>
+  <si>
+    <t>Quedan poucas proteínas e teñen formas raras nas gráficas de evaluación… mais que raras, sin forma. Quizás hai que eliminar</t>
+  </si>
+  <si>
+    <t>Control;IPF X Alveoli;Airway;</t>
+  </si>
+  <si>
+    <t>PXD022614</t>
+  </si>
+  <si>
+    <t>LTQ Orbitrap;Q Exactive</t>
+  </si>
+  <si>
+    <t>Adult;Adult+Sperm;Young</t>
+  </si>
+  <si>
+    <t>PXD019504</t>
+  </si>
+  <si>
+    <t>Colon</t>
+  </si>
+  <si>
+    <t>C;T</t>
+  </si>
+  <si>
+    <t>DOI: 10.18632/oncotarget.27491</t>
+  </si>
+  <si>
+    <t>PXD054553</t>
+  </si>
+  <si>
+    <t>Blood</t>
+  </si>
+  <si>
+    <t>BJAB;MEC-1</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/J.JBC.2025.108386</t>
+  </si>
+  <si>
+    <t>PXD054636</t>
+  </si>
+  <si>
+    <t>Con;VEGFA;BRK</t>
+  </si>
+  <si>
+    <t>PXD054712 for the same author, same illness</t>
+  </si>
+  <si>
+    <t>PXD054817</t>
+  </si>
+  <si>
+    <t>Q Exactive</t>
+  </si>
+  <si>
+    <t>ARIDA;IgG</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/1878-0261.70019</t>
+  </si>
+  <si>
+    <t>Experiment 1</t>
+  </si>
+  <si>
+    <t>Experiment 2</t>
+  </si>
+  <si>
+    <t>Cntl;IPL</t>
+  </si>
+  <si>
+    <t>PXD054817.2</t>
+  </si>
+  <si>
+    <t>PXD046983</t>
+  </si>
+  <si>
+    <t>ZenoTOF 7600</t>
+  </si>
+  <si>
+    <t>DIANN</t>
+  </si>
+  <si>
+    <t>Retina</t>
+  </si>
+  <si>
+    <t>Ctl;LIM</t>
+  </si>
+  <si>
+    <t>TSV: sample info PXD046983.sdrf.tsv</t>
+  </si>
+  <si>
+    <t>PXD050996</t>
+  </si>
+  <si>
+    <t>Heart</t>
+  </si>
+  <si>
+    <t>CA;CP;MA;MP</t>
+  </si>
+  <si>
+    <t>Group info from sample name | PXD050990 from same research</t>
+  </si>
+  <si>
+    <t>PXD052720</t>
+  </si>
+  <si>
+    <t>Dengue;Control</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/jmv.29775</t>
+  </si>
+  <si>
+    <t>PXD062678</t>
+  </si>
+  <si>
+    <t>timsTOF Pro 2</t>
+  </si>
+  <si>
+    <t>Saliva</t>
+  </si>
+  <si>
+    <t>Control;OSCC;Premalignant</t>
+  </si>
+  <si>
+    <t>PXD063236</t>
+  </si>
+  <si>
+    <t>Control;Moyamoya</t>
+  </si>
+  <si>
+    <t>PXD063383</t>
+  </si>
+  <si>
+    <t>BV2;EMPTY;SCR;SPI1KD;SPI1OE</t>
+  </si>
+  <si>
+    <t>PXD063923</t>
+  </si>
+  <si>
+    <t>WT;IT;RX</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/J.MCPRO.2025.101462</t>
+  </si>
+  <si>
+    <t>PXD058791</t>
+  </si>
+  <si>
+    <t>Myc.M.aMum1.;Myc.M.IgG.;Myc.M.aMvc.;Vec.a.MVC.</t>
+  </si>
+  <si>
+    <t>PXD058655</t>
+  </si>
+  <si>
+    <t>Orbitrap Eclipse</t>
+  </si>
+  <si>
+    <t>0h;12h;24h</t>
+  </si>
+  <si>
+    <t>DOI: 10.1101/2023.09.16.558067</t>
+  </si>
+  <si>
+    <t>PXD051732</t>
+  </si>
+  <si>
+    <t>Escherichia coli</t>
+  </si>
+  <si>
+    <t>maXis</t>
+  </si>
+  <si>
+    <t>CI3_M5;CI3_WT;CI23_M3;CI23_WT;CI39_M3;CI39_WT</t>
+  </si>
+  <si>
+    <t>DOI: 10.1038/S44259-024-00050-7</t>
+  </si>
+  <si>
+    <t>PXD047566</t>
+  </si>
+  <si>
+    <t>Same paper PXD051732</t>
+  </si>
+  <si>
+    <t>WT;M3;M6;M8;WT_T;M3_T;M6_T;M8_T</t>
+  </si>
+  <si>
+    <t>PXD055964</t>
+  </si>
+  <si>
+    <t>Aortic tissue</t>
+  </si>
+  <si>
+    <t>WT_No;fl/fl_No;WT_Yes;fl/fl_Yes</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.jbc.2025.108400</t>
+  </si>
+  <si>
+    <t>XLSX: PXD055964_Metadata.xlsx</t>
+  </si>
+  <si>
+    <t>PXD060381</t>
+  </si>
+  <si>
+    <t>Orbitrap Astral</t>
+  </si>
+  <si>
+    <t>WT;NT;TS</t>
+  </si>
+  <si>
+    <t>DOI: 10.1007/s12195-025-00843-4</t>
+  </si>
+  <si>
+    <t>PXD056859</t>
+  </si>
+  <si>
+    <t>Oocyte</t>
+  </si>
+  <si>
+    <t>WT;Het;Hom</t>
+  </si>
+  <si>
+    <t>DOI: 10.1093/molehr/gaaf055</t>
+  </si>
+  <si>
+    <t>PXD047128</t>
+  </si>
+  <si>
+    <t>Urine</t>
+  </si>
+  <si>
+    <t>UW;UO;UP</t>
+  </si>
+  <si>
+    <t>PXD064948</t>
+  </si>
+  <si>
+    <t>Unfixed;fixed</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.ocarto.2025.100664</t>
+  </si>
+  <si>
+    <t>Chondrocytes</t>
+  </si>
+  <si>
+    <t>timsTOF HT</t>
+  </si>
+  <si>
+    <t>PXD051201</t>
+  </si>
+  <si>
+    <t>Men;Women</t>
+  </si>
+  <si>
+    <t>TXT: PXD051201_DM.xlsx</t>
+  </si>
+  <si>
+    <t>DM file created from an additional XLSX in PRIDE and Supplementary Material wit group info</t>
+  </si>
+  <si>
+    <t>DOI: 10.1186/s12014-025-09549-1</t>
+  </si>
+  <si>
+    <t>PXD068597</t>
+  </si>
+  <si>
+    <t>Young;OLD</t>
+  </si>
+  <si>
+    <t>DOI: 10.1158/0008-5472.can-25-1904</t>
+  </si>
+  <si>
+    <t>PXD060921</t>
+  </si>
+  <si>
+    <t>timsTOF fleX</t>
+  </si>
+  <si>
+    <t>Neuronal stem cell</t>
+  </si>
+  <si>
+    <t>EV.VH;NI;PBS;ND</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/jex2.70108</t>
+  </si>
+  <si>
+    <t>PXD071471</t>
+  </si>
+  <si>
+    <t>AR_3rdT;AH_6MPP;H_3rdT;H_6MPP</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/J.ARCHORALBIO.2025.106319</t>
+  </si>
+  <si>
+    <t>XLSX: PXD071471_SDRF_pregnancy.xlsx</t>
+  </si>
+  <si>
+    <t>PXD057069</t>
+  </si>
+  <si>
+    <t>WT_CTSB;AD_CTSB;AD_Con;WT_Con</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/acel.70242</t>
+  </si>
+  <si>
+    <t>TXT: PXD057069_HvP_Metadata.txt</t>
+  </si>
+  <si>
+    <t>There are also quantification files for blood and muscle!</t>
+  </si>
+  <si>
+    <t>PXD055158</t>
+  </si>
+  <si>
+    <t>TripleTOF 5600</t>
+  </si>
+  <si>
+    <t>Severe;Mild</t>
+  </si>
+  <si>
+    <t>DOI: 10.1186/s13075-025-03489-9</t>
+  </si>
+  <si>
+    <t>TXT: PXD055158_experiment_annotation.txt</t>
+  </si>
+  <si>
+    <t>PXD045557</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>DC;ARC;PVC</t>
+  </si>
+  <si>
+    <t>DOI: 10.3390/jcm13237287</t>
+  </si>
+  <si>
+    <t>XLSX: PXD045557_KEY_Phaco.xlsx</t>
+  </si>
+  <si>
+    <t>PXD045554</t>
+  </si>
+  <si>
+    <t>Eye</t>
+  </si>
+  <si>
+    <t>XLSX: PXD045554_KEY_AH.xlsx</t>
+  </si>
+  <si>
+    <t>PXD054270</t>
+  </si>
+  <si>
+    <t>RWPE1/KSFM;RWPE1/MEMa;22Rv;LNCaP;PC3"</t>
+  </si>
+  <si>
+    <t>DOI: 10.3390/ANTIOX13111340</t>
+  </si>
+  <si>
+    <t>TXT: PXD054270_DIA_experimental_design_MCF001695.txt</t>
+  </si>
+  <si>
+    <t>PXD040451</t>
+  </si>
+  <si>
+    <t>Rectal cancer cell</t>
+  </si>
+  <si>
+    <t>Responder;Non-Responder</t>
+  </si>
+  <si>
+    <t>DOI: 10.3390/ijms242015412</t>
+  </si>
+  <si>
+    <t>XLSX: PXD040451_Key_30330.xlsx</t>
+  </si>
+  <si>
+    <t>PXD051606</t>
+  </si>
+  <si>
+    <t>Q Exactive HF-X;Orbitrap Exploris 480</t>
+  </si>
+  <si>
+    <t>Plasma</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.molmet.2024.101983</t>
+  </si>
+  <si>
+    <t>PXD043635</t>
+  </si>
+  <si>
+    <t>Veh;Dex;Spi10;Spi1;Dex+Spi10;Dex+Spi1</t>
+  </si>
+  <si>
+    <t>DOI: 10.1007/s00018-023-04900-x</t>
+  </si>
+  <si>
+    <t>TXT: PXD043635_sample_info.txt</t>
+  </si>
+  <si>
+    <t>PXD044220</t>
+  </si>
+  <si>
+    <t>Fibroblast</t>
+  </si>
+  <si>
+    <t>WT_D0;WT_D3;WT_D4;KO_D0;KO_D3;KO_D4</t>
+  </si>
+  <si>
+    <t>DOI: 10.3390/CANCERS15204997</t>
+  </si>
+  <si>
+    <t>XLSX: PXD044220_Dafou_KEY.xlsx</t>
+  </si>
+  <si>
+    <t>PXD054374</t>
+  </si>
+  <si>
+    <t>Vehicle;R1881</t>
+  </si>
+  <si>
+    <t>TXT: PXD054374_DIA_experimental_design_PCF000078.txt</t>
+  </si>
+  <si>
+    <t>PXD047024</t>
+  </si>
+  <si>
+    <t>Control;Mutant</t>
+  </si>
+  <si>
+    <t>XLSX: PXD047024_40485_KEY.xlsx</t>
+  </si>
+  <si>
+    <t>PXD047038</t>
+  </si>
+  <si>
+    <t>Es de Martina Samiotaki, xa teño moitos pero en ultima instancia valería</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>PXD054712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do mesmo autor que PXD054636, pero valería </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PXD051732</t>
+  </si>
+  <si>
+    <t>Do mesmo auto que PXD047566, valería</t>
+  </si>
+  <si>
+    <t>PXD041191</t>
+  </si>
+  <si>
+    <t>Es de Martina Samiotaki, pero é Sacaromyces…</t>
   </si>
 </sst>
 </file>
@@ -426,12 +886,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -758,9 +1219,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" customWidth="1"/>
@@ -782,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -826,7 +1288,7 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -871,7 +1333,7 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
@@ -899,7 +1361,7 @@
         <v>29</v>
       </c>
       <c r="N3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -913,7 +1375,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
@@ -950,7 +1412,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
@@ -989,7 +1451,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
@@ -1019,7 +1481,7 @@
         <v>42</v>
       </c>
       <c r="N6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1033,7 +1495,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
         <v>45</v>
@@ -1064,7 +1526,7 @@
         <v>48</v>
       </c>
       <c r="N7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1078,7 +1540,7 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
         <v>50</v>
@@ -1121,7 +1583,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -1152,7 +1614,7 @@
         <v>54</v>
       </c>
       <c r="N9" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1160,16 +1622,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" t="s">
         <v>61</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" t="s">
-        <v>62</v>
       </c>
       <c r="F10" t="s">
         <v>56</v>
@@ -1178,22 +1640,22 @@
         <v>11</v>
       </c>
       <c r="H10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="K10">
         <v>24</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -1201,16 +1663,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11" t="s">
         <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" t="s">
-        <v>69</v>
       </c>
       <c r="F11" t="s">
         <v>56</v>
@@ -1219,22 +1681,22 @@
         <v>11</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I11">
         <v>2</v>
       </c>
       <c r="J11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K11">
         <v>33</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -1242,16 +1704,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F12" t="s">
         <v>56</v>
@@ -1260,20 +1722,20 @@
         <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I12">
         <v>2</v>
       </c>
       <c r="J12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K12">
         <f>9</f>
         <v>9</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -1281,13 +1743,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
@@ -1299,22 +1761,22 @@
         <v>18</v>
       </c>
       <c r="H13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
       <c r="J13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K13">
         <v>16</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -1322,13 +1784,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
         <v>50</v>
@@ -1340,23 +1802,23 @@
         <v>11</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K14">
         <f>8*4</f>
         <v>32</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -1364,16 +1826,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
@@ -1382,251 +1844,1621 @@
         <v>11</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
       <c r="J15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K15">
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
+      <c r="B16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
       <c r="D16" t="s">
-        <v>100</v>
-      </c>
-      <c r="L16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="E16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+      <c r="J16" t="s">
+        <v>109</v>
+      </c>
+      <c r="K16">
+        <v>9</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
+      <c r="B17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
       <c r="D17" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" t="s">
+        <v>111</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17">
+        <v>46</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
+      <c r="B18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
       <c r="D18" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" t="s">
+        <v>115</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18" t="s">
+        <v>116</v>
+      </c>
+      <c r="K18">
+        <v>6</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
+      <c r="B19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
       <c r="D19" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="J19" t="s">
+        <v>119</v>
+      </c>
+      <c r="K19">
+        <f>I19*4</f>
+        <v>12</v>
+      </c>
+      <c r="L19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
+      <c r="B20" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
       <c r="D20" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="E20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" t="s">
+        <v>39</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K20">
+        <f>6</f>
+        <v>6</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="N20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
+      <c r="B21" t="s">
+        <v>164</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
       <c r="D21" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" t="s">
+        <v>160</v>
+      </c>
+      <c r="H21" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21">
+        <v>8</v>
+      </c>
+      <c r="J21" t="s">
+        <v>166</v>
+      </c>
+      <c r="K21">
+        <f>I21*4</f>
+        <v>32</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="N21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
+      <c r="B22" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
       <c r="D22" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="E22" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22" t="s">
+        <v>131</v>
+      </c>
+      <c r="G22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" t="s">
+        <v>132</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22" t="s">
+        <v>133</v>
+      </c>
+      <c r="K22">
+        <f>I22*11</f>
+        <v>22</v>
+      </c>
+      <c r="L22" t="s">
+        <v>47</v>
+      </c>
+      <c r="M22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
+      <c r="B23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
       <c r="D23" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="E23" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" t="s">
+        <v>136</v>
+      </c>
+      <c r="I23">
+        <v>4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>137</v>
+      </c>
+      <c r="K23">
+        <f>19*2+16*2+1</f>
+        <v>71</v>
+      </c>
+      <c r="L23" t="s">
+        <v>47</v>
+      </c>
+      <c r="N23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
+      <c r="B24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
       <c r="D24" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="E24" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I24">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="J24" t="s">
+        <v>140</v>
+      </c>
+      <c r="K24">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
+      <c r="B25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
       <c r="D25" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="E25" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25" t="s">
+        <v>131</v>
+      </c>
+      <c r="G25" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" t="s">
+        <v>144</v>
+      </c>
+      <c r="I25">
+        <v>3</v>
+      </c>
+      <c r="J25" t="s">
+        <v>145</v>
+      </c>
+      <c r="K25">
+        <v>46</v>
+      </c>
+      <c r="L25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
+      <c r="B26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
       <c r="D26" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="E26" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" t="s">
+        <v>115</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26" t="s">
+        <v>147</v>
+      </c>
+      <c r="K26">
+        <v>22</v>
+      </c>
+      <c r="L26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
+      <c r="B27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
       <c r="D27" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s">
+        <v>131</v>
+      </c>
+      <c r="G27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" t="s">
+        <v>39</v>
+      </c>
+      <c r="I27">
+        <v>5</v>
+      </c>
+      <c r="J27" t="s">
+        <v>149</v>
+      </c>
+      <c r="K27">
+        <f>I27*4</f>
+        <v>20</v>
+      </c>
+      <c r="L27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
+      <c r="B28" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
       <c r="D28" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="E28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" t="s">
+        <v>131</v>
+      </c>
+      <c r="G28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" t="s">
+        <v>132</v>
+      </c>
+      <c r="I28">
+        <v>3</v>
+      </c>
+      <c r="J28" t="s">
+        <v>151</v>
+      </c>
+      <c r="K28">
+        <f>I28*3</f>
+        <v>9</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
+      <c r="B29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
       <c r="D29" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="E29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" t="s">
+        <v>131</v>
+      </c>
+      <c r="G29" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" t="s">
+        <v>39</v>
+      </c>
+      <c r="I29">
+        <v>4</v>
+      </c>
+      <c r="J29" t="s">
+        <v>154</v>
+      </c>
+      <c r="K29">
+        <f>I29*3</f>
+        <v>12</v>
+      </c>
+      <c r="L29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
+      <c r="B30" t="s">
+        <v>155</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
       <c r="D30" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="E30" t="s">
+        <v>156</v>
+      </c>
+      <c r="F30" t="s">
+        <v>131</v>
+      </c>
+      <c r="G30" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" t="s">
+        <v>39</v>
+      </c>
+      <c r="I30">
+        <v>3</v>
+      </c>
+      <c r="J30" t="s">
+        <v>157</v>
+      </c>
+      <c r="K30">
+        <f>I30*4</f>
+        <v>12</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
+      <c r="B31" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
       <c r="D31" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="E31" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" t="s">
+        <v>131</v>
+      </c>
+      <c r="G31" t="s">
+        <v>160</v>
+      </c>
+      <c r="H31" t="s">
+        <v>39</v>
+      </c>
+      <c r="I31">
+        <v>4</v>
+      </c>
+      <c r="J31" t="s">
+        <v>162</v>
+      </c>
+      <c r="K31">
+        <f>I31*4</f>
+        <v>16</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>167</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" t="s">
+        <v>99</v>
+      </c>
+      <c r="E32" t="s">
+        <v>67</v>
+      </c>
+      <c r="F32" t="s">
+        <v>131</v>
+      </c>
+      <c r="G32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" t="s">
+        <v>168</v>
+      </c>
+      <c r="I32">
+        <v>4</v>
+      </c>
+      <c r="J32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K32">
+        <f>I32*4</f>
+        <v>16</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="M32" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" t="s">
+        <v>173</v>
+      </c>
+      <c r="F33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33">
+        <f>3</f>
+        <v>3</v>
+      </c>
+      <c r="J33" t="s">
+        <v>174</v>
+      </c>
+      <c r="K33">
+        <f>I33*3</f>
+        <v>9</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>176</v>
+      </c>
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
+        <v>99</v>
+      </c>
+      <c r="E34" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" t="s">
+        <v>131</v>
+      </c>
+      <c r="G34" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" t="s">
+        <v>177</v>
+      </c>
+      <c r="I34">
+        <v>4</v>
+      </c>
+      <c r="J34" t="s">
+        <v>178</v>
+      </c>
+      <c r="K34">
+        <f>11</f>
+        <v>11</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>180</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>131</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" t="s">
+        <v>181</v>
+      </c>
+      <c r="I35">
+        <v>3</v>
+      </c>
+      <c r="J35" t="s">
+        <v>182</v>
+      </c>
+      <c r="K35">
+        <f>9</f>
+        <v>9</v>
+      </c>
+      <c r="L35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" t="s">
+        <v>187</v>
+      </c>
+      <c r="F36" t="s">
+        <v>131</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" t="s">
+        <v>186</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="J36" t="s">
+        <v>184</v>
+      </c>
+      <c r="K36">
+        <f>8</f>
+        <v>8</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>188</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E37" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37" t="s">
+        <v>131</v>
+      </c>
+      <c r="G37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37" t="s">
+        <v>136</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="J37" t="s">
+        <v>189</v>
+      </c>
+      <c r="K37">
+        <f>25*2</f>
+        <v>50</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="M37" t="s">
+        <v>190</v>
+      </c>
+      <c r="N37" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" t="s">
+        <v>99</v>
+      </c>
+      <c r="E38" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" t="s">
+        <v>131</v>
+      </c>
+      <c r="G38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" t="s">
+        <v>39</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38" t="s">
+        <v>194</v>
+      </c>
+      <c r="K38">
+        <f>6</f>
+        <v>6</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" t="s">
+        <v>197</v>
+      </c>
+      <c r="F39" t="s">
+        <v>131</v>
+      </c>
+      <c r="G39" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" t="s">
+        <v>198</v>
+      </c>
+      <c r="I39">
+        <v>4</v>
+      </c>
+      <c r="J39" t="s">
+        <v>199</v>
+      </c>
+      <c r="K39">
+        <f>I39*3</f>
+        <v>12</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>201</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" t="s">
+        <v>131</v>
+      </c>
+      <c r="G40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" t="s">
+        <v>144</v>
+      </c>
+      <c r="I40">
+        <v>4</v>
+      </c>
+      <c r="J40" t="s">
+        <v>202</v>
+      </c>
+      <c r="K40">
+        <f>I40*10</f>
+        <v>40</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="M40" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>205</v>
+      </c>
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" t="s">
+        <v>99</v>
+      </c>
+      <c r="E41" t="s">
+        <v>67</v>
+      </c>
+      <c r="F41" t="s">
+        <v>131</v>
+      </c>
+      <c r="G41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" t="s">
+        <v>77</v>
+      </c>
+      <c r="I41">
+        <v>4</v>
+      </c>
+      <c r="J41" t="s">
+        <v>206</v>
+      </c>
+      <c r="K41">
+        <f>24</f>
+        <v>24</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="M41" t="s">
+        <v>208</v>
+      </c>
+      <c r="N41" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" t="s">
+        <v>98</v>
+      </c>
+      <c r="E42" t="s">
+        <v>122</v>
+      </c>
+      <c r="F42" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" t="s">
+        <v>39</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42" t="s">
+        <v>127</v>
+      </c>
+      <c r="K42">
+        <f>6</f>
+        <v>6</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="N42" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" t="s">
+        <v>99</v>
+      </c>
+      <c r="E43" t="s">
+        <v>211</v>
+      </c>
+      <c r="F43" t="s">
+        <v>131</v>
+      </c>
+      <c r="G43" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" t="s">
+        <v>115</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+      <c r="J43" t="s">
+        <v>212</v>
+      </c>
+      <c r="K43">
+        <f>35</f>
+        <v>35</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="M43" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>215</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" t="s">
+        <v>99</v>
+      </c>
+      <c r="E44" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" t="s">
+        <v>131</v>
+      </c>
+      <c r="G44" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" t="s">
+        <v>216</v>
+      </c>
+      <c r="I44">
+        <v>3</v>
+      </c>
+      <c r="J44" t="s">
+        <v>217</v>
+      </c>
+      <c r="K44">
+        <v>29</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="M44" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>220</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" t="s">
+        <v>99</v>
+      </c>
+      <c r="E45" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" t="s">
+        <v>131</v>
+      </c>
+      <c r="G45" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" t="s">
+        <v>221</v>
+      </c>
+      <c r="I45">
+        <v>3</v>
+      </c>
+      <c r="J45" t="s">
+        <v>217</v>
+      </c>
+      <c r="K45">
+        <v>28</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="M45" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>223</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" t="s">
+        <v>99</v>
+      </c>
+      <c r="E46" t="s">
+        <v>130</v>
+      </c>
+      <c r="F46" t="s">
+        <v>131</v>
+      </c>
+      <c r="G46" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" t="s">
+        <v>39</v>
+      </c>
+      <c r="I46">
+        <v>6</v>
+      </c>
+      <c r="J46" t="s">
+        <v>224</v>
+      </c>
+      <c r="K46">
+        <f>6*3</f>
+        <v>18</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="M46" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>227</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" t="s">
+        <v>99</v>
+      </c>
+      <c r="E47" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" t="s">
+        <v>131</v>
+      </c>
+      <c r="G47" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" t="s">
+        <v>228</v>
+      </c>
+      <c r="I47">
+        <v>2</v>
+      </c>
+      <c r="J47" t="s">
+        <v>229</v>
+      </c>
+      <c r="K47">
+        <v>21</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="M47" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>232</v>
+      </c>
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" t="s">
+        <v>99</v>
+      </c>
+      <c r="E48" t="s">
+        <v>233</v>
+      </c>
+      <c r="F48" t="s">
+        <v>131</v>
+      </c>
+      <c r="G48" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" t="s">
+        <v>234</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="J48" t="s">
+        <v>74</v>
+      </c>
+      <c r="K48">
+        <v>8</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>236</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" t="s">
+        <v>99</v>
+      </c>
+      <c r="E49" t="s">
+        <v>45</v>
+      </c>
+      <c r="F49" t="s">
+        <v>131</v>
+      </c>
+      <c r="G49" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" t="s">
+        <v>39</v>
+      </c>
+      <c r="I49">
+        <v>6</v>
+      </c>
+      <c r="J49" t="s">
+        <v>237</v>
+      </c>
+      <c r="K49">
+        <f>I49*4</f>
+        <v>24</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="M49" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>240</v>
+      </c>
+      <c r="C50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" t="s">
+        <v>99</v>
+      </c>
+      <c r="E50" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50" t="s">
+        <v>131</v>
+      </c>
+      <c r="G50" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" t="s">
+        <v>241</v>
+      </c>
+      <c r="I50">
+        <f>6</f>
+        <v>6</v>
+      </c>
+      <c r="J50" t="s">
+        <v>242</v>
+      </c>
+      <c r="K50">
+        <f>I50*3</f>
+        <v>18</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="M50" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>245</v>
+      </c>
+      <c r="C51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" t="s">
+        <v>99</v>
+      </c>
+      <c r="E51" t="s">
+        <v>130</v>
+      </c>
+      <c r="F51" t="s">
+        <v>131</v>
+      </c>
+      <c r="G51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H51" t="s">
+        <v>39</v>
+      </c>
+      <c r="I51">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="J51" t="s">
+        <v>246</v>
+      </c>
+      <c r="K51">
+        <f>I51*3</f>
+        <v>6</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="M51" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>248</v>
+      </c>
+      <c r="C52" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" t="s">
+        <v>99</v>
+      </c>
+      <c r="E52" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52" t="s">
+        <v>131</v>
+      </c>
+      <c r="G52" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" t="s">
+        <v>241</v>
+      </c>
+      <c r="I52">
+        <v>2</v>
+      </c>
+      <c r="J52" t="s">
+        <v>249</v>
+      </c>
+      <c r="K52">
+        <v>6</v>
+      </c>
+      <c r="L52" t="s">
+        <v>47</v>
+      </c>
+      <c r="M52" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="C54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="C55" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="C56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="C57" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="C58" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="C59" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="C60" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="C61" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1644,9 +3476,36 @@
     <hyperlink ref="L13" r:id="rId11" location="Sec11" xr:uid="{EAAEE3D5-FD5F-4C5E-BEDE-E149007B61D7}"/>
     <hyperlink ref="L14" r:id="rId12" xr:uid="{1466ACE4-040B-4872-B3E7-CB073BC90CE4}"/>
     <hyperlink ref="L15" r:id="rId13" display="https://doi.org/10.1038/s42255-021-00420-9" xr:uid="{AA76EE2A-3D95-4B26-A3B2-D6961FCAA8B9}"/>
+    <hyperlink ref="L17" r:id="rId14" xr:uid="{73C3C164-1B9E-424D-B497-0A5C1413062E}"/>
+    <hyperlink ref="L18" r:id="rId15" xr:uid="{8E96941A-F27E-446D-BAAB-8817BA69407F}"/>
+    <hyperlink ref="L20" r:id="rId16" xr:uid="{612CAC31-BDF9-4217-882E-04BA9D317851}"/>
+    <hyperlink ref="L42" r:id="rId17" xr:uid="{A0AABACF-D49B-4ADE-969F-34674947E980}"/>
+    <hyperlink ref="L24" r:id="rId18" xr:uid="{45029A78-EC32-4653-B2C0-8A1C6AB739CD}"/>
+    <hyperlink ref="L28" r:id="rId19" xr:uid="{58E39B3E-0FD0-41D5-8918-94CB0DEBE92F}"/>
+    <hyperlink ref="L30" r:id="rId20" xr:uid="{798BD1EC-17B3-4197-8EAE-486722AEADF1}"/>
+    <hyperlink ref="L31" r:id="rId21" xr:uid="{AE40AA44-2798-47B6-B9FB-02DFCD819A98}"/>
+    <hyperlink ref="L21" r:id="rId22" xr:uid="{812AD498-467D-4930-99B1-0BD72991EB74}"/>
+    <hyperlink ref="L32" r:id="rId23" xr:uid="{0A4265F2-3C05-4E25-883C-F8A8F58C6D63}"/>
+    <hyperlink ref="L33" r:id="rId24" xr:uid="{DBE6CDEE-1512-471E-91A3-29DE9DCD40F4}"/>
+    <hyperlink ref="L34" r:id="rId25" xr:uid="{1530F3E7-5FB8-4C45-8815-BC53BEE62E5F}"/>
+    <hyperlink ref="L36" r:id="rId26" xr:uid="{81A03F1A-4A0B-4C2D-947D-86D4D18A30FC}"/>
+    <hyperlink ref="L37" r:id="rId27" xr:uid="{03A7BDDE-DDD3-4CE4-9A6A-3F28026978CD}"/>
+    <hyperlink ref="L38" r:id="rId28" xr:uid="{97D5A0D0-4F73-4447-98D7-176FE36E7E9F}"/>
+    <hyperlink ref="L39" r:id="rId29" xr:uid="{3FDDCA56-CB99-4846-8D3C-3F87979E1526}"/>
+    <hyperlink ref="L40" r:id="rId30" xr:uid="{7859E8C3-2333-43D3-B478-A44FA49BB177}"/>
+    <hyperlink ref="L41" r:id="rId31" xr:uid="{4AAB6572-69BF-4A8C-B9DD-0ECD744015A7}"/>
+    <hyperlink ref="L43" r:id="rId32" xr:uid="{AEFB8F3B-EA1A-47CE-B2E9-52C8FEE30E73}"/>
+    <hyperlink ref="L44" r:id="rId33" xr:uid="{CB2F7DF2-FC97-4B92-86B1-9479DA20F40F}"/>
+    <hyperlink ref="L45" r:id="rId34" xr:uid="{256ADA76-DDF3-43D7-9FF6-3D06B3102F1B}"/>
+    <hyperlink ref="L46" r:id="rId35" xr:uid="{8607D0FC-A3CA-4C2C-B9AF-EA3A5742473F}"/>
+    <hyperlink ref="L47" r:id="rId36" xr:uid="{CC518961-8295-4994-A3DF-84ED80F14808}"/>
+    <hyperlink ref="L48" r:id="rId37" xr:uid="{2FCAA5AF-4D5B-40D6-9710-958A63043040}"/>
+    <hyperlink ref="L49" r:id="rId38" xr:uid="{AE407C0D-97C6-498B-BFB4-71C4936A1365}"/>
+    <hyperlink ref="L50" r:id="rId39" xr:uid="{92FB0A8D-11DB-4567-8F9B-CF523A119E05}"/>
+    <hyperlink ref="L51" r:id="rId40" xr:uid="{207EE6F5-656D-4A38-9817-F2A00ABFCEEE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>
 </worksheet>
 </file>
 
@@ -1666,10 +3525,10 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
@@ -1707,46 +3566,46 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F2" t="s">
         <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J2">
         <v>7</v>
       </c>
       <c r="K2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L2">
         <v>365</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1755,4 +3614,57 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5412E459-6599-4D39-A6E4-9FCCBAA2B3FA}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="65.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/goldStandard/_Index.xlsx
+++ b/goldStandard/_Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A645F18-FB62-4283-832A-F711B021F64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1841AF98-F4E0-4774-BF94-A898247A907F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
+    <workbookView xWindow="26475" yWindow="0" windowWidth="25230" windowHeight="20985" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
   </bookViews>
   <sheets>
     <sheet name="In" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="316">
   <si>
     <t>ID</t>
   </si>
@@ -807,6 +807,174 @@
   </si>
   <si>
     <t>Es de Martina Samiotaki, pero é Sacaromyces…</t>
+  </si>
+  <si>
+    <t>PXD071192</t>
+  </si>
+  <si>
+    <t>ProteinPilot</t>
+  </si>
+  <si>
+    <t>Placenta</t>
+  </si>
+  <si>
+    <t>Control;depressed/no SRI;depressed/SRI</t>
+  </si>
+  <si>
+    <t>DOI: 10.1371/journal.pone.0322090</t>
+  </si>
+  <si>
+    <t>metadata and code in CSV files</t>
+  </si>
+  <si>
+    <t>T_30 remove from df quant, no info in dm matrix. T29 remove from dm matrix, no info in df quant</t>
+  </si>
+  <si>
+    <t>PXD070887</t>
+  </si>
+  <si>
+    <t>Liver</t>
+  </si>
+  <si>
+    <t>WT;HET;SMA</t>
+  </si>
+  <si>
+    <t>DOI: 10.64898/2026.01.08.698518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group identification by supplementary table 6 in paper. </t>
+  </si>
+  <si>
+    <t>PXD070232</t>
+  </si>
+  <si>
+    <t>Spectronaut</t>
+  </si>
+  <si>
+    <t>AD_M;AD_F;Healthy_F;Healthy_M</t>
+  </si>
+  <si>
+    <t>DOI: 10.17912/MICROPUB.BIOLOGY.001922</t>
+  </si>
+  <si>
+    <t>CSV: PXD070232_CombsC_20250305_04_DIA_SampleList.csv</t>
+  </si>
+  <si>
+    <t>PXD036609</t>
+  </si>
+  <si>
+    <t>HC;LTPP</t>
+  </si>
+  <si>
+    <t>Publication pending</t>
+  </si>
+  <si>
+    <t>XLSX x2: metadata_for_HC.xlsx | metadata_for_LTPP.xlsx</t>
+  </si>
+  <si>
+    <t>PXD035942</t>
+  </si>
+  <si>
+    <t>PCA;BPH</t>
+  </si>
+  <si>
+    <t>DOI: 10.1021/acsomega.2c05487</t>
+  </si>
+  <si>
+    <t>A supplementary XLSX from publication with sample basal info and groups</t>
+  </si>
+  <si>
+    <t>PXD031992</t>
+  </si>
+  <si>
+    <t>KO;WT</t>
+  </si>
+  <si>
+    <t>DOI: 10.7554/elife.77937</t>
+  </si>
+  <si>
+    <t>Cl11 line proteomics data is removed because in the FTP only .raw files for Cl31 samples were updated and onlt Cl3.1 was mentioned in the corresponding publication</t>
+  </si>
+  <si>
+    <t>siNC;siPRDX6</t>
+  </si>
+  <si>
+    <t>PXD028772</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.redox.2021.102212</t>
+  </si>
+  <si>
+    <t>XLSX: PXD028772_Annotation.xlsx</t>
+  </si>
+  <si>
+    <t>PXD027817</t>
+  </si>
+  <si>
+    <t>A;D</t>
+  </si>
+  <si>
+    <t>DOI: 10.2147/jhc.s325629</t>
+  </si>
+  <si>
+    <t>Table1 from publciation confirms 2 groups of 48 samples</t>
+  </si>
+  <si>
+    <t>PXD020722</t>
+  </si>
+  <si>
+    <t>DOI: 10.15252/emmm.202013257</t>
+  </si>
+  <si>
+    <t>Table from publication with group information</t>
+  </si>
+  <si>
+    <t>XLSX: PXD015422_44321_2021_BFEMMM202013257_MOESM2_ESM.xlsx</t>
+  </si>
+  <si>
+    <t>PXD020722.2</t>
+  </si>
+  <si>
+    <t>PD-/LRRK2-;PD+/LRRK2-;PD+/LRRK2+;PD-/LRRK2+</t>
+  </si>
+  <si>
+    <t>PXD041168</t>
+  </si>
+  <si>
+    <t>unfed_GFP_Z12;unfed_GRKO_Z12;fed_GFP_Z14;fed_GRKO_Z14;fed_GFP_Z18;fed_GRKO_Z18</t>
+  </si>
+  <si>
+    <t>DOI: 10.1210/endocr/bqad128</t>
+  </si>
+  <si>
+    <t>TXT: PXD041168_experimental_design_.txt</t>
+  </si>
+  <si>
+    <t>PXD054895</t>
+  </si>
+  <si>
+    <t>Chow_Con_Insulin;HFD_612_Insulin;HFD_Con_Basal;HFD_Veh_Insulin;Chow_Con_Basal</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.ejphar.2025.177465</t>
+  </si>
+  <si>
+    <t>CSV: PXD054895_metadata.csv</t>
+  </si>
+  <si>
+    <t>PXD070490</t>
+  </si>
+  <si>
+    <t>Felis chaus</t>
+  </si>
+  <si>
+    <t>ctrl;FCV_BJDX;FCV_BJ616</t>
+  </si>
+  <si>
+    <t>In raw files we found the correspondence between samples and FCV strains</t>
+  </si>
+  <si>
+    <t>https://www.ebi.ac.uk/pride/archive?keyword=spectronaut&amp;sortDirection=DESC&amp;page=1&amp;pageSize=20</t>
   </si>
 </sst>
 </file>
@@ -886,13 +1054,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1219,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
@@ -2050,7 +2217,6 @@
         <v>123</v>
       </c>
       <c r="K20">
-        <f>6</f>
         <v>6</v>
       </c>
       <c r="L20" s="1" t="s">
@@ -3193,7 +3359,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3235,7 +3401,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3278,7 +3444,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3321,7 +3487,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3362,103 +3528,728 @@
         <v>250</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
+      <c r="B53" t="s">
+        <v>260</v>
+      </c>
       <c r="C53" t="s">
         <v>8</v>
       </c>
       <c r="D53" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E53" t="s">
+        <v>211</v>
+      </c>
+      <c r="F53" t="s">
+        <v>261</v>
+      </c>
+      <c r="G53" t="s">
+        <v>11</v>
+      </c>
+      <c r="H53" t="s">
+        <v>262</v>
+      </c>
+      <c r="I53">
+        <v>3</v>
+      </c>
+      <c r="J53" t="s">
+        <v>263</v>
+      </c>
+      <c r="K53">
+        <v>69</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="M53" t="s">
+        <v>265</v>
+      </c>
+      <c r="N53" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
+      <c r="B54" t="s">
+        <v>267</v>
+      </c>
       <c r="C54" t="s">
         <v>8</v>
       </c>
       <c r="D54" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E54" t="s">
+        <v>45</v>
+      </c>
+      <c r="F54" t="s">
+        <v>131</v>
+      </c>
+      <c r="G54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54" t="s">
+        <v>268</v>
+      </c>
+      <c r="I54">
+        <v>3</v>
+      </c>
+      <c r="J54" t="s">
+        <v>269</v>
+      </c>
+      <c r="K54">
+        <f>14</f>
+        <v>14</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="M54" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
+      <c r="B55" t="s">
+        <v>272</v>
+      </c>
       <c r="C55" t="s">
         <v>8</v>
       </c>
       <c r="D55" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E55" t="s">
+        <v>173</v>
+      </c>
+      <c r="F55" t="s">
+        <v>273</v>
+      </c>
+      <c r="G55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H55" t="s">
+        <v>115</v>
+      </c>
+      <c r="I55">
+        <v>4</v>
+      </c>
+      <c r="J55" t="s">
+        <v>274</v>
+      </c>
+      <c r="K55">
+        <f>32</f>
+        <v>32</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="M55" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
+      <c r="B56" t="s">
+        <v>277</v>
+      </c>
       <c r="C56" t="s">
         <v>8</v>
       </c>
       <c r="D56" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E56" t="s">
+        <v>50</v>
+      </c>
+      <c r="F56" t="s">
+        <v>273</v>
+      </c>
+      <c r="G56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56" t="s">
+        <v>115</v>
+      </c>
+      <c r="I56">
+        <v>2</v>
+      </c>
+      <c r="J56" t="s">
+        <v>278</v>
+      </c>
+      <c r="K56">
+        <f>27</f>
+        <v>27</v>
+      </c>
+      <c r="L56" t="s">
+        <v>279</v>
+      </c>
+      <c r="M56" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
+      <c r="B57" t="s">
+        <v>281</v>
+      </c>
       <c r="C57" t="s">
         <v>8</v>
       </c>
       <c r="D57" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E57" t="s">
+        <v>122</v>
+      </c>
+      <c r="F57" t="s">
+        <v>273</v>
+      </c>
+      <c r="G57" t="s">
+        <v>11</v>
+      </c>
+      <c r="H57" t="s">
+        <v>181</v>
+      </c>
+      <c r="I57">
+        <v>2</v>
+      </c>
+      <c r="J57" t="s">
+        <v>282</v>
+      </c>
+      <c r="K57">
+        <f>133</f>
+        <v>133</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="N57" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
+      <c r="B58" t="s">
+        <v>285</v>
+      </c>
       <c r="C58" t="s">
         <v>8</v>
       </c>
       <c r="D58" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E58" t="s">
+        <v>50</v>
+      </c>
+      <c r="F58" t="s">
+        <v>273</v>
+      </c>
+      <c r="G58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" t="s">
+        <v>39</v>
+      </c>
+      <c r="I58">
+        <v>2</v>
+      </c>
+      <c r="J58" t="s">
+        <v>286</v>
+      </c>
+      <c r="K58">
+        <v>10</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="N58" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
+      <c r="B59" t="s">
+        <v>290</v>
+      </c>
       <c r="C59" t="s">
         <v>8</v>
       </c>
       <c r="D59" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E59" t="s">
+        <v>45</v>
+      </c>
+      <c r="F59" t="s">
+        <v>273</v>
+      </c>
+      <c r="G59" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" t="s">
+        <v>39</v>
+      </c>
+      <c r="I59">
+        <v>2</v>
+      </c>
+      <c r="J59" t="s">
+        <v>289</v>
+      </c>
+      <c r="K59">
+        <v>7</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="M59" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
+      <c r="B60" t="s">
+        <v>293</v>
+      </c>
       <c r="C60" t="s">
         <v>8</v>
       </c>
       <c r="D60" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E60" t="s">
+        <v>31</v>
+      </c>
+      <c r="F60" t="s">
+        <v>273</v>
+      </c>
+      <c r="G60" t="s">
+        <v>11</v>
+      </c>
+      <c r="H60" t="s">
+        <v>115</v>
+      </c>
+      <c r="I60">
+        <v>2</v>
+      </c>
+      <c r="J60" t="s">
+        <v>294</v>
+      </c>
+      <c r="K60">
+        <v>48</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="N60" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
+      <c r="B61" t="s">
+        <v>297</v>
+      </c>
       <c r="C61" t="s">
         <v>8</v>
       </c>
       <c r="D61" t="s">
         <v>99</v>
+      </c>
+      <c r="E61" t="s">
+        <v>50</v>
+      </c>
+      <c r="F61" t="s">
+        <v>273</v>
+      </c>
+      <c r="G61" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61" t="s">
+        <v>181</v>
+      </c>
+      <c r="I61">
+        <v>4</v>
+      </c>
+      <c r="J61" t="s">
+        <v>302</v>
+      </c>
+      <c r="K61">
+        <f>63+52</f>
+        <v>115</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="M61" t="s">
+        <v>300</v>
+      </c>
+      <c r="N61" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>301</v>
+      </c>
+      <c r="C62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" t="s">
+        <v>99</v>
+      </c>
+      <c r="E62" t="s">
+        <v>50</v>
+      </c>
+      <c r="F62" t="s">
+        <v>273</v>
+      </c>
+      <c r="G62" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" t="s">
+        <v>181</v>
+      </c>
+      <c r="I62">
+        <v>4</v>
+      </c>
+      <c r="J62" t="s">
+        <v>302</v>
+      </c>
+      <c r="K62">
+        <f>120</f>
+        <v>120</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="M62" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>303</v>
+      </c>
+      <c r="C63" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" t="s">
+        <v>99</v>
+      </c>
+      <c r="E63" t="s">
+        <v>45</v>
+      </c>
+      <c r="F63" t="s">
+        <v>273</v>
+      </c>
+      <c r="G63" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63" t="s">
+        <v>268</v>
+      </c>
+      <c r="I63">
+        <v>6</v>
+      </c>
+      <c r="J63" t="s">
+        <v>304</v>
+      </c>
+      <c r="K63">
+        <v>36</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="M63" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>307</v>
+      </c>
+      <c r="C64" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" t="s">
+        <v>99</v>
+      </c>
+      <c r="E64" t="s">
+        <v>45</v>
+      </c>
+      <c r="F64" t="s">
+        <v>131</v>
+      </c>
+      <c r="G64" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" t="s">
+        <v>268</v>
+      </c>
+      <c r="I64">
+        <v>5</v>
+      </c>
+      <c r="J64" t="s">
+        <v>308</v>
+      </c>
+      <c r="K64">
+        <v>35</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="M64" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>311</v>
+      </c>
+      <c r="C65" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" t="s">
+        <v>99</v>
+      </c>
+      <c r="E65" t="s">
+        <v>50</v>
+      </c>
+      <c r="F65" t="s">
+        <v>273</v>
+      </c>
+      <c r="G65" t="s">
+        <v>312</v>
+      </c>
+      <c r="H65" t="s">
+        <v>57</v>
+      </c>
+      <c r="I65">
+        <v>3</v>
+      </c>
+      <c r="J65" t="s">
+        <v>313</v>
+      </c>
+      <c r="K65">
+        <v>9</v>
+      </c>
+      <c r="L65" t="s">
+        <v>47</v>
+      </c>
+      <c r="N65" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>315</v>
+      </c>
+      <c r="C66" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="C67" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="C68" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="C69" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="C70" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="C71" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="C72" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="C73" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="C74" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="C75" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="C76" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="C77" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="C78" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="C79" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="C80" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="C81" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3503,9 +4294,20 @@
     <hyperlink ref="L49" r:id="rId38" xr:uid="{AE407C0D-97C6-498B-BFB4-71C4936A1365}"/>
     <hyperlink ref="L50" r:id="rId39" xr:uid="{92FB0A8D-11DB-4567-8F9B-CF523A119E05}"/>
     <hyperlink ref="L51" r:id="rId40" xr:uid="{207EE6F5-656D-4A38-9817-F2A00ABFCEEE}"/>
+    <hyperlink ref="L53" r:id="rId41" xr:uid="{E3F0AF35-4EFD-4690-93B1-C3CEFB35EC15}"/>
+    <hyperlink ref="L54" r:id="rId42" xr:uid="{7C683447-D985-423F-B5CD-03B9FB95AD65}"/>
+    <hyperlink ref="L55" r:id="rId43" xr:uid="{BDF4E4E0-765A-4F0B-BD68-C69115F0738F}"/>
+    <hyperlink ref="L57" r:id="rId44" xr:uid="{C0FA8537-4468-48BF-A054-0D7291F65AE0}"/>
+    <hyperlink ref="L58" r:id="rId45" xr:uid="{8D999E26-CBDB-4FE4-ADDB-E6B611D67331}"/>
+    <hyperlink ref="L59" r:id="rId46" xr:uid="{7A24ADCF-B6A2-404E-89EC-C398B7118D79}"/>
+    <hyperlink ref="L60" r:id="rId47" xr:uid="{0B450A65-6781-41DE-9BEF-0479DD4B3225}"/>
+    <hyperlink ref="L61" r:id="rId48" xr:uid="{13A1084D-B36D-4396-A3D3-56FA85A81598}"/>
+    <hyperlink ref="L63" r:id="rId49" xr:uid="{815FAA3B-87CE-4626-94FB-28BB0C9DC865}"/>
+    <hyperlink ref="L64" r:id="rId50" xr:uid="{87332800-52F9-415F-88A8-13B3218E1B95}"/>
+    <hyperlink ref="L62" r:id="rId51" xr:uid="{20655D6D-7A5B-4884-972D-A0B324AF2E09}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId52"/>
 </worksheet>
 </file>
 
@@ -3660,7 +4462,7 @@
       <c r="A5" t="s">
         <v>258</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>259</v>
       </c>
     </row>

--- a/goldStandard/_Index.xlsx
+++ b/goldStandard/_Index.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1841AF98-F4E0-4774-BF94-A898247A907F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9342C580-29F6-45ED-917A-31FFFF31A0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26475" yWindow="0" windowWidth="25230" windowHeight="20985" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
+    <workbookView xWindow="24960" yWindow="0" windowWidth="26745" windowHeight="20985" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
   </bookViews>
   <sheets>
     <sheet name="In" sheetId="1" r:id="rId1"/>
     <sheet name="Out" sheetId="2" r:id="rId2"/>
     <sheet name="Possible" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">In!$A$1:$N$81</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="399">
   <si>
     <t>ID</t>
   </si>
@@ -974,7 +977,256 @@
     <t>In raw files we found the correspondence between samples and FCV strains</t>
   </si>
   <si>
-    <t>https://www.ebi.ac.uk/pride/archive?keyword=spectronaut&amp;sortDirection=DESC&amp;page=1&amp;pageSize=20</t>
+    <t>PXD025359</t>
+  </si>
+  <si>
+    <t>PXD014311</t>
+  </si>
+  <si>
+    <t>Small intestine epithelium</t>
+  </si>
+  <si>
+    <t>Duo_WT;Jej_WT;Ile_WT;Duo_KO;Jej_KO;Ile_KO</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.celrep.2020.107565</t>
+  </si>
+  <si>
+    <t>Non me quedan claros os grupos de comparacion, hai 4 tecidos por animal e cada animal mátase en semanas diferentes. Si fago os grupos tecido x semanas morte hai grupos duas e unha mostra</t>
+  </si>
+  <si>
+    <t>PXD052118</t>
+  </si>
+  <si>
+    <t>Control;KO</t>
+  </si>
+  <si>
+    <t>XLSX: Samples_conditions_files.xlsx</t>
+  </si>
+  <si>
+    <t>PXD050249</t>
+  </si>
+  <si>
+    <t>Saccharomyces cerevisiae</t>
+  </si>
+  <si>
+    <t>MCY1441, MCY1444 strains</t>
+  </si>
+  <si>
+    <t>Minus;Plus</t>
+  </si>
+  <si>
+    <t>DOI: 10.1093/nar/gkae1321</t>
+  </si>
+  <si>
+    <t>PXD051789</t>
+  </si>
+  <si>
+    <t>Skyline</t>
+  </si>
+  <si>
+    <t>Cancer;Control</t>
+  </si>
+  <si>
+    <t>DOI:10.1039/d4mo00112e</t>
+  </si>
+  <si>
+    <t>PXD012431</t>
+  </si>
+  <si>
+    <t>Breast tissues</t>
+  </si>
+  <si>
+    <t>axillary metastatic lymph nodes tissues;primary breast tumor tissues;adjacent breast tissues;non-tumor contralateral breast tissues</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.dib.2019.104125</t>
+  </si>
+  <si>
+    <t>LTQ Orbitrap XL ETD</t>
+  </si>
+  <si>
+    <t>TSV: sdrf.tsv with sample annotations</t>
+  </si>
+  <si>
+    <t>PXD048564</t>
+  </si>
+  <si>
+    <t>TripleTOF 6600</t>
+  </si>
+  <si>
+    <t>Rattus norvegicus</t>
+  </si>
+  <si>
+    <t>Sham;SNx</t>
+  </si>
+  <si>
+    <t>DOI: 10.1038/S41598-025-93894-6</t>
+  </si>
+  <si>
+    <t>Fig 2 B from publication group asignation</t>
+  </si>
+  <si>
+    <t>Urine and kidney available</t>
+  </si>
+  <si>
+    <t>PXD045168</t>
+  </si>
+  <si>
+    <t>timsTOF</t>
+  </si>
+  <si>
+    <t>Microglia</t>
+  </si>
+  <si>
+    <t>HI;HT;S;Si;SiHT</t>
+  </si>
+  <si>
+    <t>DOI: 10.1186/S12974-024-03022-W</t>
+  </si>
+  <si>
+    <t>Fig6 with proteomics representation and groups</t>
+  </si>
+  <si>
+    <t>GABI;SALK;WT</t>
+  </si>
+  <si>
+    <t>PXD043729</t>
+  </si>
+  <si>
+    <t>Arabidopsis thaliana</t>
+  </si>
+  <si>
+    <t>Mitochondria</t>
+  </si>
+  <si>
+    <t>DOI: 10.1126/SCIENCE.ADG0995</t>
+  </si>
+  <si>
+    <t>PXD018900</t>
+  </si>
+  <si>
+    <t>Lung</t>
+  </si>
+  <si>
+    <t>D180_0.5mg;D180_1.5mg;D180_Ctrl;D3_0.5mg;D3_1.5mg;D3_Ctrl;D30_0.5mg;D30_1.5mg;D30_Ctrl;D90_0.5mg;D90_1.5mg;D90_Ctrl</t>
+  </si>
+  <si>
+    <t>DOI: 10.1080/17435390.2020.1851418</t>
+  </si>
+  <si>
+    <t>TXT: PXD018900_experimentalDesignTemplate.txt</t>
+  </si>
+  <si>
+    <t>PXD019296</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.jep.2020.113460</t>
+  </si>
+  <si>
+    <t>MI_D0;MI_D15;SBP_D0;SBP_D15;SOG_D0;SOG_D15</t>
+  </si>
+  <si>
+    <t>PXD016670</t>
+  </si>
+  <si>
+    <t>LTQ Orbitrap</t>
+  </si>
+  <si>
+    <t>MaxQuant </t>
+  </si>
+  <si>
+    <t>Colonies</t>
+  </si>
+  <si>
+    <t>Ctl;psr1psr2;whi2</t>
+  </si>
+  <si>
+    <t>DOI:10.1073/pnas.1922076117</t>
+  </si>
+  <si>
+    <t>CTL;MAN;NACL</t>
+  </si>
+  <si>
+    <t>Root</t>
+  </si>
+  <si>
+    <t>PXD019139</t>
+  </si>
+  <si>
+    <t>DOI: 10.1093/pcp/pcab076</t>
+  </si>
+  <si>
+    <t>PXD019103</t>
+  </si>
+  <si>
+    <t>N;T</t>
+  </si>
+  <si>
+    <t>DOI: 10.3389/fonc.2020.00945</t>
+  </si>
+  <si>
+    <t>PXD029776</t>
+  </si>
+  <si>
+    <t>M0;M1;M2</t>
+  </si>
+  <si>
+    <t>Macrophagues</t>
+  </si>
+  <si>
+    <t>PXD041237</t>
+  </si>
+  <si>
+    <t>Caenorhabditis elegans</t>
+  </si>
+  <si>
+    <t>Whole body</t>
+  </si>
+  <si>
+    <t>MC;MT</t>
+  </si>
+  <si>
+    <t>DOI: 10.1186/s12979-024-00457-w</t>
+  </si>
+  <si>
+    <t>DOI: 10.3390/biomedicines10020239</t>
+  </si>
+  <si>
+    <t>PXD039491</t>
+  </si>
+  <si>
+    <t>DOI: 10.3390/antiox12061153</t>
+  </si>
+  <si>
+    <t>https://www.ebi.ac.uk/pride/archive?keyword=proteinGroups.txt&amp;filter=projectTags%3D%3DBiology%2Fdisease-driven%20human%20proteome%20project%20%28b%2Fd-hpp%29&amp;sortFields=downloadCount&amp;sortDirection=DESC&amp;page=0&amp;pageSize=20</t>
+  </si>
+  <si>
+    <t>PXD040288</t>
+  </si>
+  <si>
+    <t>C;I;L</t>
+  </si>
+  <si>
+    <t>DOI: 10.3389/FIMMU.2023.1162159</t>
+  </si>
+  <si>
+    <t>PXD022038</t>
+  </si>
+  <si>
+    <t>DMSO;OXS008450;OXS008450.OXS008255.1uM;OXS008450.OXS008255.25uM;OXS008450.OXS008255.5uM;OXS008450.Paclitaxel;OXS008483"</t>
+  </si>
+  <si>
+    <t>DOI:10.1016/j.isci.2022.104787</t>
+  </si>
+  <si>
+    <t>PXD007182</t>
+  </si>
+  <si>
+    <t>DOI: 10.1074/jbc.ra117.001058</t>
+  </si>
+  <si>
+    <t>Ctrl;XAV939</t>
   </si>
 </sst>
 </file>
@@ -1386,14 +1638,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}">
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.85546875" customWidth="1"/>
     <col min="10" max="10" width="14.28515625" customWidth="1"/>
     <col min="12" max="12" width="38.28515625" customWidth="1"/>
     <col min="13" max="13" width="40.7109375" customWidth="1"/>
@@ -4078,181 +4330,947 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C66" t="s">
         <v>8</v>
       </c>
       <c r="D66" t="s">
         <v>99</v>
+      </c>
+      <c r="E66" t="s">
+        <v>50</v>
+      </c>
+      <c r="F66" t="s">
+        <v>273</v>
+      </c>
+      <c r="G66" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66" t="s">
+        <v>317</v>
+      </c>
+      <c r="I66">
+        <v>6</v>
+      </c>
+      <c r="J66" t="s">
+        <v>318</v>
+      </c>
+      <c r="K66">
+        <f>I66*3</f>
+        <v>18</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
+      <c r="B67" t="s">
+        <v>321</v>
+      </c>
       <c r="C67" t="s">
         <v>8</v>
       </c>
       <c r="D67" t="s">
         <v>99</v>
+      </c>
+      <c r="E67" t="s">
+        <v>67</v>
+      </c>
+      <c r="F67" t="s">
+        <v>273</v>
+      </c>
+      <c r="G67" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67" t="s">
+        <v>77</v>
+      </c>
+      <c r="I67">
+        <v>2</v>
+      </c>
+      <c r="J67" t="s">
+        <v>322</v>
+      </c>
+      <c r="K67">
+        <f>12</f>
+        <v>12</v>
+      </c>
+      <c r="L67" t="s">
+        <v>47</v>
+      </c>
+      <c r="M67" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
+      <c r="B68" t="s">
+        <v>324</v>
+      </c>
       <c r="C68" t="s">
         <v>8</v>
       </c>
       <c r="D68" t="s">
         <v>99</v>
+      </c>
+      <c r="E68" t="s">
+        <v>67</v>
+      </c>
+      <c r="F68" t="s">
+        <v>9</v>
+      </c>
+      <c r="G68" t="s">
+        <v>325</v>
+      </c>
+      <c r="H68" t="s">
+        <v>326</v>
+      </c>
+      <c r="I68">
+        <v>2</v>
+      </c>
+      <c r="J68" t="s">
+        <v>327</v>
+      </c>
+      <c r="K68">
+        <v>12</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
+      <c r="B69" t="s">
+        <v>329</v>
+      </c>
       <c r="C69" t="s">
         <v>8</v>
       </c>
       <c r="D69" t="s">
         <v>99</v>
+      </c>
+      <c r="E69" t="s">
+        <v>33</v>
+      </c>
+      <c r="F69" t="s">
+        <v>330</v>
+      </c>
+      <c r="G69" t="s">
+        <v>11</v>
+      </c>
+      <c r="H69" t="s">
+        <v>115</v>
+      </c>
+      <c r="I69">
+        <v>2</v>
+      </c>
+      <c r="J69" t="s">
+        <v>331</v>
+      </c>
+      <c r="K69">
+        <f>6</f>
+        <v>6</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
+      <c r="B70" t="s">
+        <v>339</v>
+      </c>
       <c r="C70" t="s">
         <v>8</v>
       </c>
       <c r="D70" t="s">
         <v>99</v>
+      </c>
+      <c r="E70" t="s">
+        <v>340</v>
+      </c>
+      <c r="F70" t="s">
+        <v>131</v>
+      </c>
+      <c r="G70" t="s">
+        <v>341</v>
+      </c>
+      <c r="H70" t="s">
+        <v>234</v>
+      </c>
+      <c r="I70">
+        <v>2</v>
+      </c>
+      <c r="J70" t="s">
+        <v>342</v>
+      </c>
+      <c r="K70">
+        <v>10</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="N70" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
+      <c r="B71" t="s">
+        <v>346</v>
+      </c>
       <c r="C71" t="s">
         <v>8</v>
       </c>
       <c r="D71" t="s">
         <v>99</v>
+      </c>
+      <c r="E71" t="s">
+        <v>347</v>
+      </c>
+      <c r="F71" t="s">
+        <v>131</v>
+      </c>
+      <c r="G71" t="s">
+        <v>341</v>
+      </c>
+      <c r="H71" t="s">
+        <v>348</v>
+      </c>
+      <c r="I71">
+        <v>5</v>
+      </c>
+      <c r="J71" t="s">
+        <v>349</v>
+      </c>
+      <c r="K71">
+        <f>I71*4+4</f>
+        <v>24</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="N71" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
+      <c r="B72" t="s">
+        <v>353</v>
+      </c>
       <c r="C72" t="s">
         <v>8</v>
       </c>
       <c r="D72" t="s">
         <v>99</v>
+      </c>
+      <c r="E72" t="s">
+        <v>20</v>
+      </c>
+      <c r="F72" t="s">
+        <v>131</v>
+      </c>
+      <c r="G72" t="s">
+        <v>354</v>
+      </c>
+      <c r="H72" t="s">
+        <v>355</v>
+      </c>
+      <c r="I72">
+        <v>3</v>
+      </c>
+      <c r="J72" t="s">
+        <v>352</v>
+      </c>
+      <c r="K72">
+        <f>3*4</f>
+        <v>12</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
+      <c r="B73" t="s">
+        <v>333</v>
+      </c>
       <c r="C73" t="s">
         <v>8</v>
       </c>
       <c r="D73" t="s">
         <v>98</v>
+      </c>
+      <c r="E73" t="s">
+        <v>337</v>
+      </c>
+      <c r="F73" t="s">
+        <v>9</v>
+      </c>
+      <c r="G73" t="s">
+        <v>11</v>
+      </c>
+      <c r="H73" t="s">
+        <v>334</v>
+      </c>
+      <c r="I73">
+        <v>4</v>
+      </c>
+      <c r="J73" t="s">
+        <v>335</v>
+      </c>
+      <c r="K73">
+        <v>23</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="M73" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
+      <c r="B74" t="s">
+        <v>357</v>
+      </c>
       <c r="C74" t="s">
         <v>8</v>
       </c>
       <c r="D74" t="s">
         <v>98</v>
+      </c>
+      <c r="E74" t="s">
+        <v>122</v>
+      </c>
+      <c r="F74" t="s">
+        <v>9</v>
+      </c>
+      <c r="G74" t="s">
+        <v>341</v>
+      </c>
+      <c r="H74" t="s">
+        <v>358</v>
+      </c>
+      <c r="I74">
+        <v>12</v>
+      </c>
+      <c r="J74" t="s">
+        <v>359</v>
+      </c>
+      <c r="K74">
+        <f>I74*6</f>
+        <v>72</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="M74" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
+      <c r="B75" t="s">
+        <v>362</v>
+      </c>
       <c r="C75" t="s">
         <v>8</v>
       </c>
       <c r="D75" t="s">
         <v>98</v>
+      </c>
+      <c r="E75" t="s">
+        <v>122</v>
+      </c>
+      <c r="F75" t="s">
+        <v>9</v>
+      </c>
+      <c r="G75" t="s">
+        <v>341</v>
+      </c>
+      <c r="H75" t="s">
+        <v>136</v>
+      </c>
+      <c r="I75">
+        <v>6</v>
+      </c>
+      <c r="J75" t="s">
+        <v>364</v>
+      </c>
+      <c r="K75">
+        <f>6*3</f>
+        <v>18</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
+      <c r="B76" t="s">
+        <v>365</v>
+      </c>
       <c r="C76" t="s">
         <v>8</v>
       </c>
       <c r="D76" t="s">
         <v>98</v>
+      </c>
+      <c r="E76" t="s">
+        <v>366</v>
+      </c>
+      <c r="F76" t="s">
+        <v>367</v>
+      </c>
+      <c r="G76" t="s">
+        <v>325</v>
+      </c>
+      <c r="H76" t="s">
+        <v>368</v>
+      </c>
+      <c r="I76">
+        <v>3</v>
+      </c>
+      <c r="J76" t="s">
+        <v>369</v>
+      </c>
+      <c r="K76">
+        <f>I76*3</f>
+        <v>9</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
+      <c r="B77" t="s">
+        <v>373</v>
+      </c>
       <c r="C77" t="s">
         <v>8</v>
       </c>
       <c r="D77" t="s">
         <v>98</v>
+      </c>
+      <c r="E77" t="s">
+        <v>33</v>
+      </c>
+      <c r="F77" t="s">
+        <v>9</v>
+      </c>
+      <c r="G77" t="s">
+        <v>354</v>
+      </c>
+      <c r="H77" t="s">
+        <v>372</v>
+      </c>
+      <c r="I77">
+        <f>3</f>
+        <v>3</v>
+      </c>
+      <c r="J77" t="s">
+        <v>371</v>
+      </c>
+      <c r="K77">
+        <f>I77*3</f>
+        <v>9</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
+      <c r="B78" t="s">
+        <v>375</v>
+      </c>
       <c r="C78" t="s">
         <v>8</v>
       </c>
       <c r="D78" t="s">
         <v>98</v>
+      </c>
+      <c r="E78" t="s">
+        <v>31</v>
+      </c>
+      <c r="F78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G78" t="s">
+        <v>11</v>
+      </c>
+      <c r="H78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I78">
+        <v>2</v>
+      </c>
+      <c r="J78" t="s">
+        <v>376</v>
+      </c>
+      <c r="K78">
+        <v>15</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
+      <c r="B79" t="s">
+        <v>378</v>
+      </c>
       <c r="C79" t="s">
         <v>8</v>
       </c>
       <c r="D79" t="s">
         <v>98</v>
+      </c>
+      <c r="E79" t="s">
+        <v>50</v>
+      </c>
+      <c r="F79" t="s">
+        <v>9</v>
+      </c>
+      <c r="G79" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" t="s">
+        <v>380</v>
+      </c>
+      <c r="I79">
+        <v>3</v>
+      </c>
+      <c r="J79" t="s">
+        <v>379</v>
+      </c>
+      <c r="K79">
+        <f>9</f>
+        <v>9</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
+      <c r="B80" t="s">
+        <v>381</v>
+      </c>
       <c r="C80" t="s">
         <v>8</v>
       </c>
       <c r="D80" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E80" t="s">
+        <v>33</v>
+      </c>
+      <c r="F80" t="s">
+        <v>9</v>
+      </c>
+      <c r="G80" t="s">
+        <v>382</v>
+      </c>
+      <c r="H80" t="s">
+        <v>383</v>
+      </c>
+      <c r="I80">
+        <v>2</v>
+      </c>
+      <c r="J80" t="s">
+        <v>384</v>
+      </c>
+      <c r="K80">
+        <f>6</f>
+        <v>6</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
+      <c r="B81" t="s">
+        <v>387</v>
+      </c>
       <c r="C81" t="s">
         <v>8</v>
       </c>
       <c r="D81" t="s">
         <v>98</v>
       </c>
+      <c r="E81" t="s">
+        <v>33</v>
+      </c>
+      <c r="F81" t="s">
+        <v>9</v>
+      </c>
+      <c r="G81" t="s">
+        <v>11</v>
+      </c>
+      <c r="H81" t="s">
+        <v>39</v>
+      </c>
+      <c r="I81">
+        <v>2</v>
+      </c>
+      <c r="J81" t="s">
+        <v>286</v>
+      </c>
+      <c r="K81">
+        <v>6</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>390</v>
+      </c>
+      <c r="C82" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" t="s">
+        <v>98</v>
+      </c>
+      <c r="E82" t="s">
+        <v>50</v>
+      </c>
+      <c r="F82" t="s">
+        <v>9</v>
+      </c>
+      <c r="G82" t="s">
+        <v>18</v>
+      </c>
+      <c r="H82" t="s">
+        <v>358</v>
+      </c>
+      <c r="I82">
+        <v>3</v>
+      </c>
+      <c r="J82" t="s">
+        <v>391</v>
+      </c>
+      <c r="K82">
+        <v>9</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>393</v>
+      </c>
+      <c r="C83" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" t="s">
+        <v>98</v>
+      </c>
+      <c r="E83" t="s">
+        <v>122</v>
+      </c>
+      <c r="F83" t="s">
+        <v>9</v>
+      </c>
+      <c r="G83" t="s">
+        <v>11</v>
+      </c>
+      <c r="H83" t="s">
+        <v>39</v>
+      </c>
+      <c r="I83">
+        <v>7</v>
+      </c>
+      <c r="J83" t="s">
+        <v>394</v>
+      </c>
+      <c r="K83">
+        <f>I83*3</f>
+        <v>21</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>396</v>
+      </c>
+      <c r="C84" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" t="s">
+        <v>98</v>
+      </c>
+      <c r="E84" t="s">
+        <v>122</v>
+      </c>
+      <c r="F84" t="s">
+        <v>9</v>
+      </c>
+      <c r="G84" t="s">
+        <v>341</v>
+      </c>
+      <c r="H84" t="s">
+        <v>39</v>
+      </c>
+      <c r="I84">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="J84" t="s">
+        <v>398</v>
+      </c>
+      <c r="K84">
+        <f>6</f>
+        <v>6</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="C85" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="C86" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="C87" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="C88" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="C89" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="C90" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="C91" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="C92" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="C93" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="C94" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="C95" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="C96" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="C97" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="C98" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="C99" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="C100" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="C101" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>389</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N81" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}"/>
   <hyperlinks>
     <hyperlink ref="L4" r:id="rId1" display="https://doi.org/10.1016/j.stemcr.2022.04.003" xr:uid="{A58B2C92-8135-4993-80B6-E01F7C4414D7}"/>
     <hyperlink ref="L2" r:id="rId2" xr:uid="{ECF580C4-849C-4561-A481-5430106E5AFC}"/>
@@ -4305,9 +5323,27 @@
     <hyperlink ref="L63" r:id="rId49" xr:uid="{815FAA3B-87CE-4626-94FB-28BB0C9DC865}"/>
     <hyperlink ref="L64" r:id="rId50" xr:uid="{87332800-52F9-415F-88A8-13B3218E1B95}"/>
     <hyperlink ref="L62" r:id="rId51" xr:uid="{20655D6D-7A5B-4884-972D-A0B324AF2E09}"/>
+    <hyperlink ref="L66" r:id="rId52" xr:uid="{29C9B3AB-C1C5-4CD9-9B61-66EB2F5DB119}"/>
+    <hyperlink ref="L68" r:id="rId53" xr:uid="{A5A57614-CF6E-46F6-B6E8-5F616167FA0D}"/>
+    <hyperlink ref="L69" r:id="rId54" xr:uid="{01DF9558-6F69-4543-A8DD-1581956A8E01}"/>
+    <hyperlink ref="L73" r:id="rId55" xr:uid="{709E7BEA-314C-4B0F-A59A-6BF8CAABD75C}"/>
+    <hyperlink ref="L70" r:id="rId56" xr:uid="{9A7B274C-695B-4B24-B4F1-DD64F89BEC2F}"/>
+    <hyperlink ref="L71" r:id="rId57" xr:uid="{53F78946-D0F1-45CE-80F4-DCEF51325FA5}"/>
+    <hyperlink ref="L72" r:id="rId58" xr:uid="{8853D92F-CF28-4712-9231-7429D3BFBBFB}"/>
+    <hyperlink ref="L74" r:id="rId59" xr:uid="{44AE3EE4-BA3F-4C04-B457-C8BE8762DC83}"/>
+    <hyperlink ref="L75" r:id="rId60" xr:uid="{DB61579F-438D-4DF9-B387-7F2F5EA1AE5D}"/>
+    <hyperlink ref="L76" r:id="rId61" xr:uid="{9C641A84-E07C-4EF1-9FFC-12E3055FF46E}"/>
+    <hyperlink ref="L77" r:id="rId62" xr:uid="{35F7105D-4C78-45B1-8E0C-651E22400B24}"/>
+    <hyperlink ref="L78" r:id="rId63" xr:uid="{76FAEE4C-5466-4FB1-B104-402F652D0F82}"/>
+    <hyperlink ref="L80" r:id="rId64" xr:uid="{B222AC14-18AF-40AE-8D03-B1981FBE28A6}"/>
+    <hyperlink ref="L79" r:id="rId65" xr:uid="{B875AC8B-59AF-4BD2-9A20-40747F088572}"/>
+    <hyperlink ref="L81" r:id="rId66" xr:uid="{612059EE-8652-46E0-8015-99B298BDC96E}"/>
+    <hyperlink ref="L82" r:id="rId67" xr:uid="{2274C7CE-0848-479C-8E48-A92AFCD2DAF3}"/>
+    <hyperlink ref="L83" r:id="rId68" tooltip="Persistent link using digital object identifier" xr:uid="{27BFC4E4-9DCB-4C1D-B672-888C8D8E2732}"/>
+    <hyperlink ref="L84" r:id="rId69" xr:uid="{3593983D-93B4-45AC-8DAA-EEEB7814C6DA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId52"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId70"/>
 </worksheet>
 </file>
 
@@ -4420,7 +5456,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5412E459-6599-4D39-A6E4-9FCCBAA2B3FA}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="65.5703125" bestFit="1" customWidth="1"/>
@@ -4466,6 +5502,22 @@
         <v>259</v>
       </c>
     </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>315</v>
+      </c>
+      <c r="B6" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>339</v>
+      </c>
+      <c r="B7" t="s">
+        <v>345</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/goldStandard/_Index.xlsx
+++ b/goldStandard/_Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9342C580-29F6-45ED-917A-31FFFF31A0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5062FE-6E5A-460F-8B06-332CF3AFEA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24960" yWindow="0" windowWidth="26745" windowHeight="20985" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
+    <workbookView xWindow="-19320" yWindow="-2745" windowWidth="19440" windowHeight="14880" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
   </bookViews>
   <sheets>
     <sheet name="In" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="476">
   <si>
     <t>ID</t>
   </si>
@@ -1199,9 +1199,6 @@
     <t>DOI: 10.3390/antiox12061153</t>
   </si>
   <si>
-    <t>https://www.ebi.ac.uk/pride/archive?keyword=proteinGroups.txt&amp;filter=projectTags%3D%3DBiology%2Fdisease-driven%20human%20proteome%20project%20%28b%2Fd-hpp%29&amp;sortFields=downloadCount&amp;sortDirection=DESC&amp;page=0&amp;pageSize=20</t>
-  </si>
-  <si>
     <t>PXD040288</t>
   </si>
   <si>
@@ -1227,6 +1224,240 @@
   </si>
   <si>
     <t>Ctrl;XAV939</t>
+  </si>
+  <si>
+    <t>PXD042498</t>
+  </si>
+  <si>
+    <t>DMSO_24hr;DMSO_4hr;ERCO_24hr;ERCO_4hr</t>
+  </si>
+  <si>
+    <t>DOI: 10.12688/openreseurope.15973.2</t>
+  </si>
+  <si>
+    <t>Hsp162_Insolubl;Hsp162_Solubl;Hsp17_Insolubl;Hsp17_Solubl;Insolubl;Sip1_Insolubl;Sip1_Solubl;Solubl</t>
+  </si>
+  <si>
+    <t>PXD038019</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/J.JBC.2022.102753</t>
+  </si>
+  <si>
+    <t>PXD069093</t>
+  </si>
+  <si>
+    <t>XLSX: PXD069093_KinomeMetadata.xlsx</t>
+  </si>
+  <si>
+    <t>palbociclib;palbociclib_efficacy;vehicle;vehicle_efficacy</t>
+  </si>
+  <si>
+    <t>Xenografs</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.neo.2025.101266</t>
+  </si>
+  <si>
+    <t>PXD068908</t>
+  </si>
+  <si>
+    <t>3T3L1_Co;3T3L1_Vas;imBA_Co;imBA_Vas</t>
+  </si>
+  <si>
+    <t>DOI: 10.1038/s41467-025-66950-y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bad quality, many missing values and two types of cell cultures that should be independently analyzed </t>
+  </si>
+  <si>
+    <t>PXD068664</t>
+  </si>
+  <si>
+    <t>Cell culture, 3x3 samples</t>
+  </si>
+  <si>
+    <t>PXD004242</t>
+  </si>
+  <si>
+    <t>Only one group: obesity</t>
+  </si>
+  <si>
+    <t>PXD005354</t>
+  </si>
+  <si>
+    <t>Only one group: colorrectal cancer</t>
+  </si>
+  <si>
+    <t>PXD005025</t>
+  </si>
+  <si>
+    <t>Vigna mungo</t>
+  </si>
+  <si>
+    <t>Leaves</t>
+  </si>
+  <si>
+    <t>V2;SV2;V6;SV6;S6;C2;C6;S2</t>
+  </si>
+  <si>
+    <t>DOI: 10.1021/acs.jproteome.6b00211</t>
+  </si>
+  <si>
+    <t>PXD027404</t>
+  </si>
+  <si>
+    <t>Only one group: Adenocarcinoma</t>
+  </si>
+  <si>
+    <t>PXD010785</t>
+  </si>
+  <si>
+    <t>DMSO;xanthohumol C in DMSO;xanthohumol in DMSO</t>
+  </si>
+  <si>
+    <t>DOI: 10.1371/journal.pone.0213469</t>
+  </si>
+  <si>
+    <t>PXD022701</t>
+  </si>
+  <si>
+    <t>Drosophila melanogaster</t>
+  </si>
+  <si>
+    <t>Head</t>
+  </si>
+  <si>
+    <t>C;E</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.jbc.2021.100408</t>
+  </si>
+  <si>
+    <t>HTLV1a;HTLV1c;Mock</t>
+  </si>
+  <si>
+    <t>T-cell</t>
+  </si>
+  <si>
+    <t> PXD030132</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/J.CELL.2025.06.023</t>
+  </si>
+  <si>
+    <t>PXD028841</t>
+  </si>
+  <si>
+    <t>BD;CON;FEP;MDD</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.dib.2021.107495</t>
+  </si>
+  <si>
+    <t>PXD015470</t>
+  </si>
+  <si>
+    <t>Ovary</t>
+  </si>
+  <si>
+    <t>AA;C</t>
+  </si>
+  <si>
+    <t>DOI: 10.1007/s00204-020-02697-3</t>
+  </si>
+  <si>
+    <t>PXD020238</t>
+  </si>
+  <si>
+    <t>Sodium butyrate;Untreated</t>
+  </si>
+  <si>
+    <t>Canis familiaris</t>
+  </si>
+  <si>
+    <t>PXD020245</t>
+  </si>
+  <si>
+    <t>Untreated_Ileum;Untreated_Distal Colon;Untreated_Proximal Colon;Treated_Ileum;Treated_Distal Colon;Treated_Proximal Colon</t>
+  </si>
+  <si>
+    <t>Intestin</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.xphs.2020.11.001</t>
+  </si>
+  <si>
+    <t>PXD062946</t>
+  </si>
+  <si>
+    <t>Crtl_antiFLAG;Crtl_antiGFP;hangover_FLAG;hangover_GFP</t>
+  </si>
+  <si>
+    <t>PXD011804</t>
+  </si>
+  <si>
+    <t>CAA;N;PDF</t>
+  </si>
+  <si>
+    <t>DOI: 10.1021/acs.jproteome.9b00242</t>
+  </si>
+  <si>
+    <t>DOI: 10.1093/nar/gkaf1349</t>
+  </si>
+  <si>
+    <t>Nash;Norm;SS</t>
+  </si>
+  <si>
+    <t>PXD005847</t>
+  </si>
+  <si>
+    <t>LTQ Orbitrap Velos</t>
+  </si>
+  <si>
+    <t>DOI: 10.1186/s12014-018-9186-0</t>
+  </si>
+  <si>
+    <t>Case;Wild Control;Captive Control</t>
+  </si>
+  <si>
+    <t>PXD030595</t>
+  </si>
+  <si>
+    <t>Enhydra lutris nereis</t>
+  </si>
+  <si>
+    <t>APP;KYL;WT</t>
+  </si>
+  <si>
+    <t>PXD056771</t>
+  </si>
+  <si>
+    <t>DOI: 10.1073/PNAS.2420324122</t>
+  </si>
+  <si>
+    <t>XLSX: PXD030595_Table_S1.xlsx</t>
+  </si>
+  <si>
+    <t>TXT: PXD005847_experimentalDesignTemplate.txt</t>
+  </si>
+  <si>
+    <t>TXT: PXD062946_experimentalDesignTemplate.txt</t>
+  </si>
+  <si>
+    <t>TXT: PXD020245_metadata_Mouse.txt</t>
+  </si>
+  <si>
+    <t>TXT: PXD020238_metadata_NaBut.txt</t>
+  </si>
+  <si>
+    <t>XLSX: PXD015470_metadata.xlsx</t>
+  </si>
+  <si>
+    <t>TXT: PXD005025_experimentalDesignTemplate.txt</t>
+  </si>
+  <si>
+    <t>PXD022038_Conditionsassessed.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1306,12 +1537,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1639,20 +1871,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}">
   <dimension ref="A1:N102"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="27.85546875" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" customWidth="1"/>
-    <col min="12" max="12" width="38.28515625" customWidth="1"/>
-    <col min="13" max="13" width="40.7109375" customWidth="1"/>
-    <col min="14" max="14" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.3046875" customWidth="1"/>
+    <col min="5" max="5" width="22.84375" customWidth="1"/>
+    <col min="6" max="6" width="15.3046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.69140625" customWidth="1"/>
+    <col min="8" max="8" width="27.84375" customWidth="1"/>
+    <col min="10" max="10" width="14.3046875" customWidth="1"/>
+    <col min="12" max="12" width="38.3046875" customWidth="1"/>
+    <col min="13" max="13" width="40.69140625" customWidth="1"/>
+    <col min="14" max="14" width="38.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="15.9" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
@@ -1696,7 +1928,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1741,7 +1973,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1783,7 +2015,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1820,7 +2052,7 @@
       </c>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1859,7 +2091,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1903,7 +2135,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1948,7 +2180,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1991,7 +2223,7 @@
       </c>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2036,7 +2268,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2077,7 +2309,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2118,7 +2350,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2157,7 +2389,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2198,7 +2430,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2240,7 +2472,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2281,7 +2513,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2319,7 +2551,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2357,7 +2589,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2395,7 +2627,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2437,7 +2669,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2478,7 +2710,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2520,7 +2752,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2562,7 +2794,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2604,7 +2836,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2644,7 +2876,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2682,7 +2914,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2720,7 +2952,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2759,7 +2991,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2798,7 +3030,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2837,7 +3069,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2876,7 +3108,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2915,7 +3147,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2957,7 +3189,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2997,7 +3229,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3036,7 +3268,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3075,7 +3307,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3114,7 +3346,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3159,7 +3391,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3198,7 +3430,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3237,7 +3469,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3279,7 +3511,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3324,7 +3556,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3366,7 +3598,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3408,7 +3640,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3449,7 +3681,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3490,7 +3722,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3532,7 +3764,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3573,7 +3805,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3611,7 +3843,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3653,7 +3885,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3696,7 +3928,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3739,7 +3971,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3780,7 +4012,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3824,7 +4056,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3866,7 +4098,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3908,7 +4140,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3950,7 +4182,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3992,7 +4224,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4033,7 +4265,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4074,7 +4306,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4115,7 +4347,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4160,7 +4392,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4202,7 +4434,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4243,7 +4475,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4284,7 +4516,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4325,7 +4557,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4364,7 +4596,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4406,7 +4638,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4444,7 +4676,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4483,7 +4715,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4524,7 +4756,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4566,7 +4798,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4605,7 +4837,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4646,7 +4878,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4688,7 +4920,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4727,7 +4959,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4766,7 +4998,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4806,7 +5038,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4844,7 +5076,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4883,7 +5115,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4922,7 +5154,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4960,12 +5192,12 @@
         <v>388</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C82" t="s">
         <v>8</v>
@@ -4989,21 +5221,21 @@
         <v>3</v>
       </c>
       <c r="J82" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K82">
         <v>9</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C83" t="s">
         <v>8</v>
@@ -5027,22 +5259,25 @@
         <v>7</v>
       </c>
       <c r="J83" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K83">
         <f>I83*3</f>
         <v>21</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+      <c r="M83" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C84" t="s">
         <v>8</v>
@@ -5067,207 +5302,706 @@
         <v>2</v>
       </c>
       <c r="J84" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K84">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>84</v>
       </c>
+      <c r="B85" t="s">
+        <v>398</v>
+      </c>
       <c r="C85" t="s">
         <v>8</v>
       </c>
       <c r="D85" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E85" t="s">
+        <v>122</v>
+      </c>
+      <c r="F85" t="s">
+        <v>9</v>
+      </c>
+      <c r="G85" t="s">
+        <v>11</v>
+      </c>
+      <c r="H85" t="s">
+        <v>39</v>
+      </c>
+      <c r="I85">
+        <v>4</v>
+      </c>
+      <c r="J85" t="s">
+        <v>399</v>
+      </c>
+      <c r="K85">
+        <f>4*I85</f>
+        <v>16</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>85</v>
       </c>
+      <c r="B86" t="s">
+        <v>402</v>
+      </c>
       <c r="C86" t="s">
         <v>8</v>
       </c>
       <c r="D86" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E86" t="s">
+        <v>33</v>
+      </c>
+      <c r="F86" t="s">
+        <v>9</v>
+      </c>
+      <c r="G86" t="s">
+        <v>382</v>
+      </c>
+      <c r="H86" t="s">
+        <v>383</v>
+      </c>
+      <c r="I86">
+        <v>8</v>
+      </c>
+      <c r="J86" t="s">
+        <v>401</v>
+      </c>
+      <c r="K86">
+        <f>8*4</f>
+        <v>32</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>86</v>
       </c>
+      <c r="B87" t="s">
+        <v>404</v>
+      </c>
       <c r="C87" t="s">
         <v>8</v>
       </c>
       <c r="D87" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E87" t="s">
+        <v>50</v>
+      </c>
+      <c r="F87" t="s">
+        <v>9</v>
+      </c>
+      <c r="G87" t="s">
+        <v>11</v>
+      </c>
+      <c r="H87" t="s">
+        <v>407</v>
+      </c>
+      <c r="I87">
+        <v>4</v>
+      </c>
+      <c r="J87" t="s">
+        <v>406</v>
+      </c>
+      <c r="K87">
+        <f>4*4</f>
+        <v>16</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="M87" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>87</v>
       </c>
+      <c r="B88" t="s">
+        <v>409</v>
+      </c>
       <c r="C88" t="s">
         <v>8</v>
       </c>
       <c r="D88" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E88" t="s">
+        <v>50</v>
+      </c>
+      <c r="F88" t="s">
+        <v>9</v>
+      </c>
+      <c r="G88" t="s">
+        <v>18</v>
+      </c>
+      <c r="H88" t="s">
+        <v>39</v>
+      </c>
+      <c r="I88">
+        <v>4</v>
+      </c>
+      <c r="J88" t="s">
+        <v>410</v>
+      </c>
+      <c r="K88">
+        <f>4*5</f>
+        <v>20</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="N88" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>88</v>
       </c>
+      <c r="B89" t="s">
+        <v>419</v>
+      </c>
       <c r="C89" t="s">
         <v>8</v>
       </c>
       <c r="D89" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E89" t="s">
+        <v>122</v>
+      </c>
+      <c r="F89" t="s">
+        <v>9</v>
+      </c>
+      <c r="G89" t="s">
+        <v>420</v>
+      </c>
+      <c r="H89" t="s">
+        <v>421</v>
+      </c>
+      <c r="I89">
+        <v>6</v>
+      </c>
+      <c r="J89" t="s">
+        <v>422</v>
+      </c>
+      <c r="K89">
+        <f>6*3</f>
+        <v>18</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="M89" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>89</v>
       </c>
+      <c r="B90" t="s">
+        <v>426</v>
+      </c>
       <c r="C90" t="s">
         <v>8</v>
       </c>
       <c r="D90" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E90" t="s">
+        <v>50</v>
+      </c>
+      <c r="F90" t="s">
+        <v>9</v>
+      </c>
+      <c r="G90" t="s">
+        <v>11</v>
+      </c>
+      <c r="H90" t="s">
+        <v>39</v>
+      </c>
+      <c r="I90">
+        <v>3</v>
+      </c>
+      <c r="J90" t="s">
+        <v>427</v>
+      </c>
+      <c r="K90">
+        <f>3*4</f>
+        <v>12</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>90</v>
       </c>
+      <c r="B91" t="s">
+        <v>429</v>
+      </c>
       <c r="C91" t="s">
         <v>8</v>
       </c>
       <c r="D91" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E91" t="s">
+        <v>122</v>
+      </c>
+      <c r="F91" t="s">
+        <v>9</v>
+      </c>
+      <c r="G91" t="s">
+        <v>430</v>
+      </c>
+      <c r="H91" t="s">
+        <v>431</v>
+      </c>
+      <c r="I91">
+        <v>3</v>
+      </c>
+      <c r="J91" t="s">
+        <v>432</v>
+      </c>
+      <c r="K91">
+        <f>6</f>
+        <v>6</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>91</v>
       </c>
+      <c r="B92" t="s">
+        <v>436</v>
+      </c>
       <c r="C92" t="s">
         <v>8</v>
       </c>
       <c r="D92" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E92" t="s">
+        <v>67</v>
+      </c>
+      <c r="F92" t="s">
+        <v>9</v>
+      </c>
+      <c r="G92" t="s">
+        <v>11</v>
+      </c>
+      <c r="H92" t="s">
+        <v>435</v>
+      </c>
+      <c r="I92">
+        <v>3</v>
+      </c>
+      <c r="J92" t="s">
+        <v>434</v>
+      </c>
+      <c r="K92">
+        <v>13</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>92</v>
       </c>
+      <c r="B93" t="s">
+        <v>438</v>
+      </c>
       <c r="C93" t="s">
         <v>8</v>
       </c>
       <c r="D93" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E93" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" t="s">
+        <v>9</v>
+      </c>
+      <c r="G93" t="s">
+        <v>11</v>
+      </c>
+      <c r="H93" t="s">
+        <v>39</v>
+      </c>
+      <c r="I93">
+        <v>4</v>
+      </c>
+      <c r="J93" t="s">
+        <v>439</v>
+      </c>
+      <c r="K93">
+        <f>158</f>
+        <v>158</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>93</v>
       </c>
+      <c r="B94" t="s">
+        <v>441</v>
+      </c>
       <c r="C94" t="s">
         <v>8</v>
       </c>
       <c r="D94" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E94" t="s">
+        <v>122</v>
+      </c>
+      <c r="F94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G94" t="s">
+        <v>341</v>
+      </c>
+      <c r="H94" t="s">
+        <v>442</v>
+      </c>
+      <c r="I94">
+        <v>2</v>
+      </c>
+      <c r="J94" t="s">
+        <v>443</v>
+      </c>
+      <c r="K94">
+        <f>16</f>
+        <v>16</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="M94" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>94</v>
       </c>
+      <c r="B95" t="s">
+        <v>445</v>
+      </c>
       <c r="C95" t="s">
         <v>8</v>
       </c>
       <c r="D95" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E95" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F95" t="s">
+        <v>9</v>
+      </c>
+      <c r="G95" t="s">
+        <v>447</v>
+      </c>
+      <c r="H95" t="s">
+        <v>39</v>
+      </c>
+      <c r="I95">
+        <v>2</v>
+      </c>
+      <c r="J95" t="s">
+        <v>446</v>
+      </c>
+      <c r="K95">
+        <v>6</v>
+      </c>
+      <c r="L95" t="s">
+        <v>47</v>
+      </c>
+      <c r="M95" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>95</v>
       </c>
+      <c r="B96" s="5" t="s">
+        <v>448</v>
+      </c>
       <c r="C96" t="s">
         <v>8</v>
       </c>
       <c r="D96" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E96" t="s">
+        <v>122</v>
+      </c>
+      <c r="F96" t="s">
+        <v>9</v>
+      </c>
+      <c r="G96" t="s">
+        <v>18</v>
+      </c>
+      <c r="H96" t="s">
+        <v>450</v>
+      </c>
+      <c r="I96">
+        <v>6</v>
+      </c>
+      <c r="J96" t="s">
+        <v>449</v>
+      </c>
+      <c r="K96">
+        <f>6*8</f>
+        <v>48</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="M96" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>96</v>
       </c>
+      <c r="B97" t="s">
+        <v>452</v>
+      </c>
       <c r="C97" t="s">
         <v>8</v>
       </c>
       <c r="D97" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E97" t="s">
+        <v>45</v>
+      </c>
+      <c r="F97" t="s">
+        <v>9</v>
+      </c>
+      <c r="G97" t="s">
+        <v>430</v>
+      </c>
+      <c r="H97" t="s">
+        <v>39</v>
+      </c>
+      <c r="I97">
+        <v>4</v>
+      </c>
+      <c r="J97" t="s">
+        <v>453</v>
+      </c>
+      <c r="K97">
+        <f>4*3</f>
+        <v>12</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="M97" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>97</v>
       </c>
+      <c r="B98" t="s">
+        <v>454</v>
+      </c>
       <c r="C98" t="s">
         <v>8</v>
       </c>
       <c r="D98" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E98" t="s">
+        <v>211</v>
+      </c>
+      <c r="F98" t="s">
+        <v>9</v>
+      </c>
+      <c r="G98" t="s">
+        <v>11</v>
+      </c>
+      <c r="H98" t="s">
+        <v>57</v>
+      </c>
+      <c r="I98">
+        <v>3</v>
+      </c>
+      <c r="J98" t="s">
+        <v>455</v>
+      </c>
+      <c r="K98">
+        <f>30</f>
+        <v>30</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>98</v>
       </c>
+      <c r="B99" t="s">
+        <v>459</v>
+      </c>
       <c r="C99" t="s">
         <v>8</v>
       </c>
       <c r="D99" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E99" t="s">
+        <v>460</v>
+      </c>
+      <c r="F99" t="s">
+        <v>9</v>
+      </c>
+      <c r="G99" t="s">
+        <v>11</v>
+      </c>
+      <c r="H99" t="s">
+        <v>57</v>
+      </c>
+      <c r="I99">
+        <v>3</v>
+      </c>
+      <c r="J99" t="s">
+        <v>458</v>
+      </c>
+      <c r="K99">
+        <f>15</f>
+        <v>15</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="M99" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>99</v>
       </c>
+      <c r="B100" t="s">
+        <v>463</v>
+      </c>
       <c r="C100" t="s">
         <v>8</v>
       </c>
       <c r="D100" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E100" t="s">
+        <v>31</v>
+      </c>
+      <c r="F100" t="s">
+        <v>56</v>
+      </c>
+      <c r="G100" t="s">
+        <v>464</v>
+      </c>
+      <c r="H100" t="s">
+        <v>115</v>
+      </c>
+      <c r="I100">
+        <v>3</v>
+      </c>
+      <c r="J100" t="s">
+        <v>462</v>
+      </c>
+      <c r="K100">
+        <f>60</f>
+        <v>60</v>
+      </c>
+      <c r="L100" t="s">
+        <v>47</v>
+      </c>
+      <c r="M100" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>100</v>
       </c>
+      <c r="B101" t="s">
+        <v>466</v>
+      </c>
       <c r="C101" t="s">
         <v>8</v>
       </c>
       <c r="D101" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B102" t="s">
-        <v>389</v>
-      </c>
+      <c r="E101" t="s">
+        <v>67</v>
+      </c>
+      <c r="F101" t="s">
+        <v>56</v>
+      </c>
+      <c r="G101" t="s">
+        <v>18</v>
+      </c>
+      <c r="H101" t="s">
+        <v>77</v>
+      </c>
+      <c r="I101">
+        <v>3</v>
+      </c>
+      <c r="J101" t="s">
+        <v>465</v>
+      </c>
+      <c r="K101">
+        <f>3*4</f>
+        <v>12</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B102" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N81" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}"/>
@@ -5341,18 +6075,33 @@
     <hyperlink ref="L82" r:id="rId67" xr:uid="{2274C7CE-0848-479C-8E48-A92AFCD2DAF3}"/>
     <hyperlink ref="L83" r:id="rId68" tooltip="Persistent link using digital object identifier" xr:uid="{27BFC4E4-9DCB-4C1D-B672-888C8D8E2732}"/>
     <hyperlink ref="L84" r:id="rId69" xr:uid="{3593983D-93B4-45AC-8DAA-EEEB7814C6DA}"/>
+    <hyperlink ref="L85" r:id="rId70" xr:uid="{EC9CC085-AE00-427A-8A98-D6B7FAC40915}"/>
+    <hyperlink ref="L86" r:id="rId71" xr:uid="{37B11193-AEED-49A8-8DC8-B8B1A4B50E16}"/>
+    <hyperlink ref="L87" r:id="rId72" xr:uid="{A403A46C-980D-45D5-B1F3-6B41994824E5}"/>
+    <hyperlink ref="L88" r:id="rId73" xr:uid="{15C15D05-2BF6-429B-990B-D4D122B2135A}"/>
+    <hyperlink ref="L89" r:id="rId74" display="https://pubs.acs.org/doi/abs/10.1021/acs.jproteome.6b00211" xr:uid="{C8CA3592-D189-4484-9578-3CE6AA7AAAF0}"/>
+    <hyperlink ref="L90" r:id="rId75" xr:uid="{EA5E6D9D-EB0C-4CD0-A732-5E51418702BE}"/>
+    <hyperlink ref="L91" r:id="rId76" display="https://doi.org/10.1016/j.jbc.2021.100408" xr:uid="{B898DC3E-877C-48D3-B8DB-38527442C91C}"/>
+    <hyperlink ref="L92" r:id="rId77" xr:uid="{E631AF55-B593-4564-AD7B-C50AA064B385}"/>
+    <hyperlink ref="L93" r:id="rId78" xr:uid="{B2B70E0C-93B6-4E11-96C1-A5E9EACBC9AA}"/>
+    <hyperlink ref="L94" r:id="rId79" xr:uid="{9AE33C66-89B4-4F2A-8E68-CFB244668468}"/>
+    <hyperlink ref="L96" r:id="rId80" xr:uid="{DE49CA08-17FF-4C18-8C19-DF135E909D8E}"/>
+    <hyperlink ref="L98" r:id="rId81" xr:uid="{8925AE44-1384-4094-9B9F-CDCD372A1CA9}"/>
+    <hyperlink ref="L97" r:id="rId82" xr:uid="{69516E89-6753-4063-B3E0-FCDA495C291D}"/>
+    <hyperlink ref="L99" r:id="rId83" xr:uid="{58BA4A32-0915-4B17-956C-DBF2AC5940FA}"/>
+    <hyperlink ref="L101" r:id="rId84" xr:uid="{74804044-9702-465A-B0D4-A230294D0CE5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId70"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId85"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2087B5-F5A7-4715-8903-807F8D9032AE}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="15.9" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
@@ -5399,7 +6148,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>15</v>
       </c>
@@ -5456,13 +6205,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5412E459-6599-4D39-A6E4-9FCCBAA2B3FA}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="65.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5470,7 +6219,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>251</v>
       </c>
@@ -5478,7 +6227,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>254</v>
       </c>
@@ -5486,7 +6235,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>256</v>
       </c>
@@ -5494,7 +6243,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>258</v>
       </c>
@@ -5502,7 +6251,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>315</v>
       </c>
@@ -5510,12 +6259,44 @@
         <v>320</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>339</v>
       </c>
       <c r="B7" t="s">
         <v>345</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>424</v>
+      </c>
+      <c r="B11" t="s">
+        <v>425</v>
       </c>
     </row>
   </sheetData>

--- a/goldStandard/_Index.xlsx
+++ b/goldStandard/_Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5062FE-6E5A-460F-8B06-332CF3AFEA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97648E71-C17B-4B4C-A4FD-8AE0DC5F8736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19320" yWindow="-2745" windowWidth="19440" windowHeight="14880" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
+    <workbookView xWindow="16260" yWindow="2340" windowWidth="38700" windowHeight="15240" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
   </bookViews>
   <sheets>
     <sheet name="In" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Possible" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">In!$A$1:$N$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">In!$A$1:$N$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="478">
   <si>
     <t>ID</t>
   </si>
@@ -932,9 +932,6 @@
     <t>Table from publication with group information</t>
   </si>
   <si>
-    <t>XLSX: PXD015422_44321_2021_BFEMMM202013257_MOESM2_ESM.xlsx</t>
-  </si>
-  <si>
     <t>PXD020722.2</t>
   </si>
   <si>
@@ -1340,9 +1337,6 @@
     <t>T-cell</t>
   </si>
   <si>
-    <t> PXD030132</t>
-  </si>
-  <si>
     <t>DOI: 10.1016/J.CELL.2025.06.023</t>
   </si>
   <si>
@@ -1458,6 +1452,18 @@
   </si>
   <si>
     <t>PXD022038_Conditionsassessed.xlsx</t>
+  </si>
+  <si>
+    <t>PXD030132</t>
+  </si>
+  <si>
+    <t>XLSX: PXD020722_44321_2021_BFEMMM202013257_MOESM2_ESM.xlsx</t>
+  </si>
+  <si>
+    <t>PXD015422</t>
+  </si>
+  <si>
+    <t>PXD020722  aparecia con ese identificador, por si acaso no futuro hai problemas con estes datasets</t>
   </si>
 </sst>
 </file>
@@ -1537,13 +1543,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1871,20 +1876,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}">
   <dimension ref="A1:N102"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" customWidth="1"/>
-    <col min="5" max="5" width="22.84375" customWidth="1"/>
-    <col min="6" max="6" width="15.3046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.69140625" customWidth="1"/>
-    <col min="8" max="8" width="27.84375" customWidth="1"/>
-    <col min="10" max="10" width="14.3046875" customWidth="1"/>
-    <col min="12" max="12" width="38.3046875" customWidth="1"/>
-    <col min="13" max="13" width="40.69140625" customWidth="1"/>
-    <col min="14" max="14" width="38.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="27.85546875" customWidth="1"/>
+    <col min="10" max="10" width="149.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="38.28515625" customWidth="1"/>
+    <col min="13" max="13" width="40.7109375" customWidth="1"/>
+    <col min="14" max="14" width="38.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
@@ -1928,7 +1933,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1973,7 +1978,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2015,7 +2020,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2052,7 +2057,7 @@
       </c>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2091,7 +2096,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2135,7 +2140,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2180,7 +2185,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2223,7 +2228,7 @@
       </c>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2268,7 +2273,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2309,7 +2314,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2350,7 +2355,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2389,7 +2394,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2430,7 +2435,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2472,7 +2477,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2513,7 +2518,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2551,7 +2556,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2589,7 +2594,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2627,7 +2632,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2669,7 +2674,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2710,7 +2715,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2752,7 +2757,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2794,7 +2799,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2836,7 +2841,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2876,7 +2881,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2914,7 +2919,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2952,7 +2957,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2991,7 +2996,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3030,7 +3035,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3069,7 +3074,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3108,7 +3113,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3147,7 +3152,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3189,7 +3194,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3229,7 +3234,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3268,7 +3273,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3307,7 +3312,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3346,7 +3351,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3391,7 +3396,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3430,7 +3435,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3469,7 +3474,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3511,7 +3516,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3556,7 +3561,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3598,7 +3603,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3640,7 +3645,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3681,7 +3686,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3722,7 +3727,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3764,7 +3769,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3805,7 +3810,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3843,7 +3848,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3885,7 +3890,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3928,7 +3933,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3971,7 +3976,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4012,7 +4017,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4056,7 +4061,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4098,7 +4103,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4140,7 +4145,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4182,7 +4187,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4224,7 +4229,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4265,7 +4270,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4306,7 +4311,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4347,7 +4352,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4376,7 +4381,7 @@
         <v>4</v>
       </c>
       <c r="J61" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K61">
         <f>63+52</f>
@@ -4386,18 +4391,18 @@
         <v>298</v>
       </c>
       <c r="M61" t="s">
-        <v>300</v>
+        <v>475</v>
       </c>
       <c r="N61" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C62" t="s">
         <v>8</v>
@@ -4421,7 +4426,7 @@
         <v>4</v>
       </c>
       <c r="J62" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K62">
         <f>120</f>
@@ -4431,15 +4436,15 @@
         <v>298</v>
       </c>
       <c r="M62" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.4">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C63" t="s">
         <v>8</v>
@@ -4463,24 +4468,24 @@
         <v>6</v>
       </c>
       <c r="J63" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K63">
         <v>36</v>
       </c>
       <c r="L63" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="M63" t="s">
         <v>305</v>
       </c>
-      <c r="M63" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C64" t="s">
         <v>8</v>
@@ -4504,24 +4509,24 @@
         <v>5</v>
       </c>
       <c r="J64" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K64">
         <v>35</v>
       </c>
       <c r="L64" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="M64" t="s">
         <v>309</v>
       </c>
-      <c r="M64" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C65" t="s">
         <v>8</v>
@@ -4536,7 +4541,7 @@
         <v>273</v>
       </c>
       <c r="G65" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H65" t="s">
         <v>57</v>
@@ -4545,7 +4550,7 @@
         <v>3</v>
       </c>
       <c r="J65" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K65">
         <v>9</v>
@@ -4554,15 +4559,15 @@
         <v>47</v>
       </c>
       <c r="N65" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.4">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C66" t="s">
         <v>8</v>
@@ -4580,28 +4585,28 @@
         <v>18</v>
       </c>
       <c r="H66" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I66">
         <v>6</v>
       </c>
       <c r="J66" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="K66">
         <f>I66*3</f>
         <v>18</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.4">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C67" t="s">
         <v>8</v>
@@ -4625,7 +4630,7 @@
         <v>2</v>
       </c>
       <c r="J67" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K67">
         <f>12</f>
@@ -4635,15 +4640,15 @@
         <v>47</v>
       </c>
       <c r="M67" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.4">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C68" t="s">
         <v>8</v>
@@ -4658,30 +4663,30 @@
         <v>9</v>
       </c>
       <c r="G68" t="s">
+        <v>324</v>
+      </c>
+      <c r="H68" t="s">
         <v>325</v>
-      </c>
-      <c r="H68" t="s">
-        <v>326</v>
       </c>
       <c r="I68">
         <v>2</v>
       </c>
       <c r="J68" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K68">
         <v>12</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.4">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C69" t="s">
         <v>8</v>
@@ -4693,7 +4698,7 @@
         <v>33</v>
       </c>
       <c r="F69" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
@@ -4705,22 +4710,22 @@
         <v>2</v>
       </c>
       <c r="J69" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K69">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.4">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C70" t="s">
         <v>8</v>
@@ -4729,13 +4734,13 @@
         <v>99</v>
       </c>
       <c r="E70" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F70" t="s">
         <v>131</v>
       </c>
       <c r="G70" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H70" t="s">
         <v>234</v>
@@ -4744,24 +4749,24 @@
         <v>2</v>
       </c>
       <c r="J70" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K70">
         <v>10</v>
       </c>
       <c r="L70" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="N70" t="s">
         <v>343</v>
       </c>
-      <c r="N70" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C71" t="s">
         <v>8</v>
@@ -4770,40 +4775,40 @@
         <v>99</v>
       </c>
       <c r="E71" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F71" t="s">
         <v>131</v>
       </c>
       <c r="G71" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H71" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I71">
         <v>5</v>
       </c>
       <c r="J71" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K71">
         <f>I71*4+4</f>
         <v>24</v>
       </c>
       <c r="L71" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N71" t="s">
         <v>350</v>
       </c>
-      <c r="N71" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C72" t="s">
         <v>8</v>
@@ -4818,31 +4823,31 @@
         <v>131</v>
       </c>
       <c r="G72" t="s">
+        <v>353</v>
+      </c>
+      <c r="H72" t="s">
         <v>354</v>
-      </c>
-      <c r="H72" t="s">
-        <v>355</v>
       </c>
       <c r="I72">
         <v>3</v>
       </c>
       <c r="J72" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K72">
         <f>3*4</f>
         <v>12</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.4">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C73" t="s">
         <v>8</v>
@@ -4851,7 +4856,7 @@
         <v>98</v>
       </c>
       <c r="E73" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F73" t="s">
         <v>9</v>
@@ -4860,30 +4865,30 @@
         <v>11</v>
       </c>
       <c r="H73" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I73">
         <v>4</v>
       </c>
       <c r="J73" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K73">
         <v>23</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M73" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.4">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C74" t="s">
         <v>8</v>
@@ -4898,34 +4903,34 @@
         <v>9</v>
       </c>
       <c r="G74" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H74" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I74">
         <v>12</v>
       </c>
       <c r="J74" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K74">
         <f>I74*6</f>
         <v>72</v>
       </c>
       <c r="L74" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="M74" t="s">
         <v>360</v>
       </c>
-      <c r="M74" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C75" t="s">
         <v>8</v>
@@ -4940,7 +4945,7 @@
         <v>9</v>
       </c>
       <c r="G75" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H75" t="s">
         <v>136</v>
@@ -4949,22 +4954,22 @@
         <v>6</v>
       </c>
       <c r="J75" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K75">
         <f>6*3</f>
         <v>18</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.4">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C76" t="s">
         <v>8</v>
@@ -4973,37 +4978,37 @@
         <v>98</v>
       </c>
       <c r="E76" t="s">
+        <v>365</v>
+      </c>
+      <c r="F76" t="s">
         <v>366</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
+        <v>324</v>
+      </c>
+      <c r="H76" t="s">
         <v>367</v>
-      </c>
-      <c r="G76" t="s">
-        <v>325</v>
-      </c>
-      <c r="H76" t="s">
-        <v>368</v>
       </c>
       <c r="I76">
         <v>3</v>
       </c>
       <c r="J76" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K76">
         <f>I76*3</f>
         <v>9</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.4">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C77" t="s">
         <v>8</v>
@@ -5018,32 +5023,32 @@
         <v>9</v>
       </c>
       <c r="G77" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H77" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I77">
         <f>3</f>
         <v>3</v>
       </c>
       <c r="J77" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K77">
         <f>I77*3</f>
         <v>9</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.4">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C78" t="s">
         <v>8</v>
@@ -5067,21 +5072,21 @@
         <v>2</v>
       </c>
       <c r="J78" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K78">
         <v>15</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.4">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C79" t="s">
         <v>8</v>
@@ -5099,28 +5104,28 @@
         <v>18</v>
       </c>
       <c r="H79" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I79">
         <v>3</v>
       </c>
       <c r="J79" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K79">
         <f>9</f>
         <v>9</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.4">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C80" t="s">
         <v>8</v>
@@ -5135,31 +5140,31 @@
         <v>9</v>
       </c>
       <c r="G80" t="s">
+        <v>381</v>
+      </c>
+      <c r="H80" t="s">
         <v>382</v>
-      </c>
-      <c r="H80" t="s">
-        <v>383</v>
       </c>
       <c r="I80">
         <v>2</v>
       </c>
       <c r="J80" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K80">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.4">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C81" t="s">
         <v>8</v>
@@ -5189,15 +5194,15 @@
         <v>6</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C82" t="s">
         <v>8</v>
@@ -5215,27 +5220,27 @@
         <v>18</v>
       </c>
       <c r="H82" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I82">
         <v>3</v>
       </c>
       <c r="J82" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K82">
         <v>9</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.4">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C83" t="s">
         <v>8</v>
@@ -5259,25 +5264,25 @@
         <v>7</v>
       </c>
       <c r="J83" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K83">
         <f>I83*3</f>
         <v>21</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="M83" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.4">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C84" t="s">
         <v>8</v>
@@ -5292,7 +5297,7 @@
         <v>9</v>
       </c>
       <c r="G84" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H84" t="s">
         <v>39</v>
@@ -5302,22 +5307,22 @@
         <v>2</v>
       </c>
       <c r="J84" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K84">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.4">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C85" t="s">
         <v>8</v>
@@ -5341,22 +5346,22 @@
         <v>4</v>
       </c>
       <c r="J85" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K85">
         <f>4*I85</f>
         <v>16</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.4">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C86" t="s">
         <v>8</v>
@@ -5371,31 +5376,31 @@
         <v>9</v>
       </c>
       <c r="G86" t="s">
+        <v>381</v>
+      </c>
+      <c r="H86" t="s">
         <v>382</v>
       </c>
-      <c r="H86" t="s">
-        <v>383</v>
-      </c>
       <c r="I86">
         <v>8</v>
       </c>
       <c r="J86" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K86">
         <f>8*4</f>
         <v>32</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.4">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C87" t="s">
         <v>8</v>
@@ -5413,31 +5418,31 @@
         <v>11</v>
       </c>
       <c r="H87" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I87">
         <v>4</v>
       </c>
       <c r="J87" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K87">
         <f>4*4</f>
         <v>16</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="M87" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.4">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C88" t="s">
         <v>8</v>
@@ -5461,25 +5466,25 @@
         <v>4</v>
       </c>
       <c r="J88" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K88">
         <f>4*5</f>
         <v>20</v>
       </c>
       <c r="L88" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="N88" t="s">
         <v>411</v>
       </c>
-      <c r="N88" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C89" t="s">
         <v>8</v>
@@ -5494,34 +5499,34 @@
         <v>9</v>
       </c>
       <c r="G89" t="s">
+        <v>419</v>
+      </c>
+      <c r="H89" t="s">
         <v>420</v>
-      </c>
-      <c r="H89" t="s">
-        <v>421</v>
       </c>
       <c r="I89">
         <v>6</v>
       </c>
       <c r="J89" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K89">
         <f>6*3</f>
         <v>18</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="M89" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.4">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C90" t="s">
         <v>8</v>
@@ -5545,22 +5550,22 @@
         <v>3</v>
       </c>
       <c r="J90" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K90">
         <f>3*4</f>
         <v>12</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.4">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C91" t="s">
         <v>8</v>
@@ -5575,31 +5580,31 @@
         <v>9</v>
       </c>
       <c r="G91" t="s">
+        <v>429</v>
+      </c>
+      <c r="H91" t="s">
         <v>430</v>
-      </c>
-      <c r="H91" t="s">
-        <v>431</v>
       </c>
       <c r="I91">
         <v>3</v>
       </c>
       <c r="J91" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K91">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.4">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>436</v>
+        <v>474</v>
       </c>
       <c r="C92" t="s">
         <v>8</v>
@@ -5617,27 +5622,27 @@
         <v>11</v>
       </c>
       <c r="H92" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I92">
         <v>3</v>
       </c>
       <c r="J92" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K92">
         <v>13</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.4">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C93" t="s">
         <v>8</v>
@@ -5661,22 +5666,22 @@
         <v>4</v>
       </c>
       <c r="J93" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K93">
         <f>158</f>
         <v>158</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.4">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C94" t="s">
         <v>8</v>
@@ -5691,34 +5696,34 @@
         <v>9</v>
       </c>
       <c r="G94" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H94" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I94">
         <v>2</v>
       </c>
       <c r="J94" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="K94">
         <f>16</f>
         <v>16</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="M94" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.4">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C95" t="s">
         <v>8</v>
@@ -5726,14 +5731,14 @@
       <c r="D95" t="s">
         <v>98</v>
       </c>
-      <c r="E95" s="5" t="s">
+      <c r="E95" t="s">
         <v>50</v>
       </c>
       <c r="F95" t="s">
         <v>9</v>
       </c>
       <c r="G95" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H95" t="s">
         <v>39</v>
@@ -5742,7 +5747,7 @@
         <v>2</v>
       </c>
       <c r="J95" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="K95">
         <v>6</v>
@@ -5751,15 +5756,15 @@
         <v>47</v>
       </c>
       <c r="M95" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.4">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
-      <c r="B96" s="5" t="s">
-        <v>448</v>
+      <c r="B96" t="s">
+        <v>446</v>
       </c>
       <c r="C96" t="s">
         <v>8</v>
@@ -5777,31 +5782,31 @@
         <v>18</v>
       </c>
       <c r="H96" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="I96">
         <v>6</v>
       </c>
       <c r="J96" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K96">
         <f>6*8</f>
         <v>48</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="M96" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.4">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C97" t="s">
         <v>8</v>
@@ -5816,7 +5821,7 @@
         <v>9</v>
       </c>
       <c r="G97" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H97" t="s">
         <v>39</v>
@@ -5825,25 +5830,25 @@
         <v>4</v>
       </c>
       <c r="J97" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K97">
         <f>4*3</f>
         <v>12</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="M97" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.4">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C98" t="s">
         <v>8</v>
@@ -5867,22 +5872,22 @@
         <v>3</v>
       </c>
       <c r="J98" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K98">
         <f>30</f>
         <v>30</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.4">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C99" t="s">
         <v>8</v>
@@ -5891,7 +5896,7 @@
         <v>98</v>
       </c>
       <c r="E99" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F99" t="s">
         <v>9</v>
@@ -5906,25 +5911,25 @@
         <v>3</v>
       </c>
       <c r="J99" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K99">
         <f>15</f>
         <v>15</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M99" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.4">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C100" t="s">
         <v>8</v>
@@ -5939,7 +5944,7 @@
         <v>56</v>
       </c>
       <c r="G100" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H100" t="s">
         <v>115</v>
@@ -5948,7 +5953,7 @@
         <v>3</v>
       </c>
       <c r="J100" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K100">
         <f>60</f>
@@ -5958,15 +5963,15 @@
         <v>47</v>
       </c>
       <c r="M100" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.4">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C101" t="s">
         <v>8</v>
@@ -5990,21 +5995,21 @@
         <v>3</v>
       </c>
       <c r="J101" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="K101">
         <f>3*4</f>
         <v>12</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.4">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B102" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N81" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}"/>
+  <autoFilter ref="A1:N101" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}"/>
   <hyperlinks>
     <hyperlink ref="L4" r:id="rId1" display="https://doi.org/10.1016/j.stemcr.2022.04.003" xr:uid="{A58B2C92-8135-4993-80B6-E01F7C4414D7}"/>
     <hyperlink ref="L2" r:id="rId2" xr:uid="{ECF580C4-849C-4561-A481-5430106E5AFC}"/>
@@ -6099,9 +6104,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2087B5-F5A7-4715-8903-807F8D9032AE}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
@@ -6148,7 +6153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>15</v>
       </c>
@@ -6205,13 +6210,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5412E459-6599-4D39-A6E4-9FCCBAA2B3FA}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="65.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6219,7 +6224,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>251</v>
       </c>
@@ -6227,7 +6232,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>254</v>
       </c>
@@ -6235,7 +6240,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>256</v>
       </c>
@@ -6243,7 +6248,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>258</v>
       </c>
@@ -6251,52 +6256,60 @@
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B6" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>412</v>
+      </c>
+      <c r="B8" t="s">
         <v>413</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>415</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>417</v>
       </c>
-      <c r="B10" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>423</v>
+      </c>
+      <c r="B11" t="s">
         <v>424</v>
       </c>
-      <c r="B11" t="s">
-        <v>425</v>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>476</v>
+      </c>
+      <c r="B12" t="s">
+        <v>477</v>
       </c>
     </row>
   </sheetData>

--- a/goldStandard/_Index.xlsx
+++ b/goldStandard/_Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97648E71-C17B-4B4C-A4FD-8AE0DC5F8736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96122E0-18C3-4F99-A61D-5ED559F6C78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16260" yWindow="2340" windowWidth="38700" windowHeight="15240" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
+    <workbookView xWindow="-22046" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
   </bookViews>
   <sheets>
     <sheet name="In" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="Possible" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">In!$A$1:$N$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">In!$A$1:$P$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Out!$B$3:$P$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="533">
   <si>
     <t>ID</t>
   </si>
@@ -77,9 +78,6 @@
     <t>DOI: 10.1016/j.stemcr.2022.04.003 </t>
   </si>
   <si>
-    <t>Neural retina; Pluripotencial stem cells Brain</t>
-  </si>
-  <si>
     <t>DOI: 10.1128/JVI.00790-24</t>
   </si>
   <si>
@@ -89,9 +87,6 @@
     <t>Mus musculus</t>
   </si>
   <si>
-    <t>embrionic fibroblast</t>
-  </si>
-  <si>
     <t>Q Exactive HF-X</t>
   </si>
   <si>
@@ -104,9 +99,6 @@
     <t>PXD058699</t>
   </si>
   <si>
-    <t>Jurkat cell; T cell</t>
-  </si>
-  <si>
     <t>Group names</t>
   </si>
   <si>
@@ -185,9 +177,6 @@
     <t>Q Exactive HF</t>
   </si>
   <si>
-    <t>Bone marrow; macrophage</t>
-  </si>
-  <si>
     <t>wt;ko</t>
   </si>
   <si>
@@ -218,9 +207,6 @@
     <t>timsTOF SCP</t>
   </si>
   <si>
-    <t>Lung tissue</t>
-  </si>
-  <si>
     <t>DOI: 10.1172/JCI.INSIGHT.189636</t>
   </si>
   <si>
@@ -230,9 +216,6 @@
     <t>PXD029547</t>
   </si>
   <si>
-    <t>Blood plasma</t>
-  </si>
-  <si>
     <t>timsTOF Pro</t>
   </si>
   <si>
@@ -251,9 +234,6 @@
     <t>PXD038236</t>
   </si>
   <si>
-    <t>Vascular smooth muscle cells</t>
-  </si>
-  <si>
     <t>WT;KO</t>
   </si>
   <si>
@@ -449,9 +429,6 @@
     <t>Group info from sample name | PXD050990 from same research</t>
   </si>
   <si>
-    <t>PXD052720</t>
-  </si>
-  <si>
     <t>Dengue;Control</t>
   </si>
   <si>
@@ -1250,9 +1227,6 @@
     <t>palbociclib;palbociclib_efficacy;vehicle;vehicle_efficacy</t>
   </si>
   <si>
-    <t>Xenografs</t>
-  </si>
-  <si>
     <t>DOI: 10.1016/j.neo.2025.101266</t>
   </si>
   <si>
@@ -1464,6 +1438,198 @@
   </si>
   <si>
     <t>PXD020722  aparecia con ese identificador, por si acaso no futuro hai problemas con estes datasets</t>
+  </si>
+  <si>
+    <t>Comments during assessment</t>
+  </si>
+  <si>
+    <t>Low correlation (0,45). Pode ser porque hai 3 tecidos diferentes x 2 grupos de estudo (cancer, control), entón entendo que entre cancer ileon e control colon pode haber diferencias.</t>
+  </si>
+  <si>
+    <t>Low correlaction (0,55). CAMBIO?</t>
+  </si>
+  <si>
+    <t>Low correlation (0,45). CAMBIO?</t>
+  </si>
+  <si>
+    <t>MAPLOT RARO. CAMBIO?</t>
+  </si>
+  <si>
+    <t>MAPLOT RARO (parece que hai un Maplot arriba e outro abaixo, quedando a liña do 0 sin nada). CAMBIO?</t>
+  </si>
+  <si>
+    <t>BrainPhys;IDMA;StemCell</t>
+  </si>
+  <si>
+    <t>PXD060778</t>
+  </si>
+  <si>
+    <t>TRPV2;WT</t>
+  </si>
+  <si>
+    <t>DOI: 10.1186/s12964-026-02729-y</t>
+  </si>
+  <si>
+    <t>PXD033095</t>
+  </si>
+  <si>
+    <t>siBPGMcontrol;mockcontrol;siBPGMhyperosm;mockhyperosm</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/apha.14242</t>
+  </si>
+  <si>
+    <t>Maplot raro</t>
+  </si>
+  <si>
+    <t>Tissue (summary)</t>
+  </si>
+  <si>
+    <t>Breast</t>
+  </si>
+  <si>
+    <t>Strains</t>
+  </si>
+  <si>
+    <t>Tissue (specific)</t>
+  </si>
+  <si>
+    <t>Cortical organoids; Stem cells</t>
+  </si>
+  <si>
+    <t>Monocyte</t>
+  </si>
+  <si>
+    <t>Adipocyte</t>
+  </si>
+  <si>
+    <t>Mammary gland epithelial cell</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Inmune</t>
+  </si>
+  <si>
+    <t>Adipose tissue</t>
+  </si>
+  <si>
+    <t>Superior mesenteric artery</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Cerebellar tissue</t>
+  </si>
+  <si>
+    <t>Coronary artery (endothelial cells)</t>
+  </si>
+  <si>
+    <t>Colon (ephitelial cells)</t>
+  </si>
+  <si>
+    <t>Urothelial cell</t>
+  </si>
+  <si>
+    <t>Urinary-related</t>
+  </si>
+  <si>
+    <t>Bacteria</t>
+  </si>
+  <si>
+    <t>Cardiomyocytes;Macrophages</t>
+  </si>
+  <si>
+    <t>Ovarian granulosa cell tumors</t>
+  </si>
+  <si>
+    <t>Ovarian-related</t>
+  </si>
+  <si>
+    <t>Kidney</t>
+  </si>
+  <si>
+    <t>Renal cells</t>
+  </si>
+  <si>
+    <t>Breast tumoral cells</t>
+  </si>
+  <si>
+    <t>Mesenquimal cells</t>
+  </si>
+  <si>
+    <t>Bone marrow</t>
+  </si>
+  <si>
+    <t>Aortic valve</t>
+  </si>
+  <si>
+    <t>Pancreas cells</t>
+  </si>
+  <si>
+    <t>Hippocampus;Muscle;Blood</t>
+  </si>
+  <si>
+    <t>Aqueus humor</t>
+  </si>
+  <si>
+    <t>Prostate (epithelial cells)</t>
+  </si>
+  <si>
+    <t>Prostate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple myeloma cell </t>
+  </si>
+  <si>
+    <t>Chorionic villous tissue</t>
+  </si>
+  <si>
+    <t>Erythrocytes</t>
+  </si>
+  <si>
+    <t>Retinal pigment epithelial cells</t>
+  </si>
+  <si>
+    <t>Mesenchymal hepatocarcinoma cell</t>
+  </si>
+  <si>
+    <t>Leukemia cell</t>
+  </si>
+  <si>
+    <t>Skeletal muscle cells</t>
+  </si>
+  <si>
+    <t>Muscle</t>
+  </si>
+  <si>
+    <t>Uveal Melanoma Cells </t>
+  </si>
+  <si>
+    <t>Ephitelium</t>
+  </si>
+  <si>
+    <t>Osteoblast (xenografts)</t>
+  </si>
+  <si>
+    <t>Bone</t>
+  </si>
+  <si>
+    <t>Adipocytes </t>
+  </si>
+  <si>
+    <t>Breast Cancer Cells</t>
+  </si>
+  <si>
+    <t>Renal</t>
+  </si>
+  <si>
+    <t>S2 cells</t>
+  </si>
+  <si>
+    <t>Hippocampus</t>
   </si>
 </sst>
 </file>
@@ -1563,6 +1729,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF9999"/>
       <color rgb="FF6C8092"/>
       <color rgb="FF03619B"/>
     </mruColors>
@@ -1875,152 +2042,171 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}">
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="27.85546875" customWidth="1"/>
-    <col min="10" max="10" width="149.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="38.28515625" customWidth="1"/>
-    <col min="13" max="13" width="40.7109375" customWidth="1"/>
-    <col min="14" max="14" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="27.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" customWidth="1"/>
+    <col min="9" max="9" width="27.85546875" customWidth="1"/>
+    <col min="11" max="11" width="24.140625" customWidth="1"/>
+    <col min="13" max="13" width="38.28515625" customWidth="1"/>
+    <col min="14" max="14" width="40.7109375" customWidth="1"/>
+    <col min="15" max="15" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="116.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>4</v>
+        <v>486</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2">
+        <v>491</v>
+      </c>
+      <c r="I2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J2">
         <v>2</v>
       </c>
-      <c r="J2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2">
         <f>10</f>
         <v>10</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" t="s">
-        <v>30</v>
+      <c r="M2" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>425</v>
+      </c>
+      <c r="H3" t="s">
+        <v>491</v>
+      </c>
+      <c r="I3" t="s">
+        <v>492</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3">
+      <c r="L3">
         <f>4*5</f>
         <v>20</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2028,4087 +2214,4401 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>487</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4">
+        <v>491</v>
+      </c>
+      <c r="I4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4">
         <v>3</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>475</v>
+      </c>
+      <c r="L4">
         <f>3*3</f>
         <v>9</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5">
+        <v>489</v>
+      </c>
+      <c r="H5" t="s">
+        <v>491</v>
+      </c>
+      <c r="I5" t="s">
+        <v>493</v>
+      </c>
+      <c r="J5">
         <v>6</v>
       </c>
-      <c r="J5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5">
         <f>6*3</f>
         <v>18</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>488</v>
+      </c>
+      <c r="H6" t="s">
+        <v>491</v>
+      </c>
+      <c r="I6" t="s">
+        <v>492</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="L6">
+        <v>16</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="N6" t="s">
         <v>39</v>
       </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6">
-        <v>16</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>490</v>
+      </c>
+      <c r="H7" t="s">
+        <v>491</v>
+      </c>
+      <c r="I7" t="s">
+        <v>484</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7">
+        <f>J7*4</f>
+        <v>16</v>
+      </c>
+      <c r="M7" t="s">
         <v>44</v>
       </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="N7" t="s">
         <v>45</v>
       </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7" t="s">
-        <v>46</v>
-      </c>
-      <c r="K7">
-        <f>I7*4</f>
-        <v>16</v>
-      </c>
-      <c r="L7" t="s">
-        <v>47</v>
-      </c>
-      <c r="M7" t="s">
-        <v>48</v>
-      </c>
-      <c r="N7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>371</v>
       </c>
       <c r="H8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8">
+        <v>491</v>
+      </c>
+      <c r="I8" t="s">
+        <v>492</v>
+      </c>
+      <c r="J8">
         <v>2</v>
       </c>
-      <c r="J8" t="s">
-        <v>52</v>
-      </c>
-      <c r="K8">
+      <c r="K8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8">
         <f>24</f>
         <v>24</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M8" t="s">
-        <v>54</v>
-      </c>
-      <c r="N8" s="4"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9">
+        <v>495</v>
+      </c>
+      <c r="I9" t="s">
+        <v>108</v>
+      </c>
+      <c r="J9">
         <v>3</v>
       </c>
-      <c r="J9" t="s">
-        <v>58</v>
-      </c>
-      <c r="K9">
+      <c r="K9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9">
         <f>29</f>
         <v>29</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="M9" t="s">
-        <v>54</v>
+      <c r="M9" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="N9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="O9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>349</v>
       </c>
       <c r="H10" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10">
+        <v>495</v>
+      </c>
+      <c r="I10" t="s">
+        <v>349</v>
+      </c>
+      <c r="J10">
         <v>7</v>
       </c>
-      <c r="J10" t="s">
-        <v>106</v>
-      </c>
-      <c r="K10">
+      <c r="K10" t="s">
+        <v>99</v>
+      </c>
+      <c r="L10">
         <v>24</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
-      </c>
-      <c r="I11">
+        <v>495</v>
+      </c>
+      <c r="I11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J11">
         <v>2</v>
       </c>
-      <c r="J11" t="s">
-        <v>68</v>
-      </c>
-      <c r="K11">
+      <c r="K11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11">
         <v>33</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="M11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>494</v>
       </c>
       <c r="H12" t="s">
-        <v>73</v>
-      </c>
-      <c r="I12">
+        <v>495</v>
+      </c>
+      <c r="I12" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12">
         <v>2</v>
       </c>
-      <c r="J12" t="s">
-        <v>74</v>
-      </c>
-      <c r="K12">
+      <c r="K12" t="s">
+        <v>67</v>
+      </c>
+      <c r="L12">
         <f>9</f>
         <v>9</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M12" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>496</v>
       </c>
       <c r="H13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I13">
+        <v>495</v>
+      </c>
+      <c r="I13" t="s">
+        <v>70</v>
+      </c>
+      <c r="J13">
         <v>2</v>
       </c>
-      <c r="J13" t="s">
-        <v>74</v>
-      </c>
-      <c r="K13">
+      <c r="K13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13">
         <v>16</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="N13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s">
-        <v>83</v>
-      </c>
-      <c r="I14">
+        <v>495</v>
+      </c>
+      <c r="I14" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14">
         <v>4</v>
       </c>
-      <c r="J14" t="s">
-        <v>84</v>
-      </c>
-      <c r="K14">
+      <c r="K14" t="s">
+        <v>77</v>
+      </c>
+      <c r="L14">
         <f>8*4</f>
         <v>32</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="N14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
-      </c>
-      <c r="I15">
+        <v>495</v>
+      </c>
+      <c r="I15" t="s">
+        <v>79</v>
+      </c>
+      <c r="J15">
         <v>2</v>
       </c>
-      <c r="J15" t="s">
-        <v>87</v>
-      </c>
-      <c r="K15">
+      <c r="K15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L15">
         <v>10</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="N15" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" t="s">
+        <v>495</v>
+      </c>
+      <c r="I16" t="s">
+        <v>70</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16" t="s">
+        <v>102</v>
+      </c>
+      <c r="L16">
         <v>9</v>
       </c>
-      <c r="G16" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I16">
-        <v>3</v>
-      </c>
-      <c r="J16" t="s">
-        <v>109</v>
-      </c>
-      <c r="K16">
-        <v>9</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M16" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>11</v>
+        <v>498</v>
       </c>
       <c r="H17" t="s">
-        <v>111</v>
-      </c>
-      <c r="I17">
+        <v>495</v>
+      </c>
+      <c r="I17" t="s">
+        <v>439</v>
+      </c>
+      <c r="J17">
         <v>2</v>
       </c>
-      <c r="J17" t="s">
-        <v>112</v>
-      </c>
-      <c r="K17">
+      <c r="K17" t="s">
+        <v>105</v>
+      </c>
+      <c r="L17">
         <v>46</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M17" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="H18" t="s">
-        <v>115</v>
-      </c>
-      <c r="I18">
+        <v>491</v>
+      </c>
+      <c r="I18" t="s">
+        <v>108</v>
+      </c>
+      <c r="J18">
         <v>2</v>
       </c>
-      <c r="J18" t="s">
-        <v>116</v>
-      </c>
-      <c r="K18">
+      <c r="K18" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18">
         <v>6</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M18" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="P18" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>11</v>
+        <v>497</v>
       </c>
       <c r="H19" t="s">
-        <v>39</v>
-      </c>
-      <c r="I19">
+        <v>491</v>
+      </c>
+      <c r="I19" t="s">
+        <v>129</v>
+      </c>
+      <c r="J19">
         <v>3</v>
       </c>
-      <c r="J19" t="s">
-        <v>119</v>
-      </c>
-      <c r="K19">
-        <f>I19*4</f>
+      <c r="K19" t="s">
+        <v>112</v>
+      </c>
+      <c r="L19">
+        <f>J19*4</f>
         <v>12</v>
       </c>
-      <c r="L19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M19" t="s">
+        <v>44</v>
+      </c>
+      <c r="O19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E20" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
+        <v>499</v>
       </c>
       <c r="H20" t="s">
-        <v>39</v>
-      </c>
-      <c r="I20">
+        <v>491</v>
+      </c>
+      <c r="I20" t="s">
+        <v>500</v>
+      </c>
+      <c r="J20">
         <v>2</v>
       </c>
-      <c r="J20" t="s">
-        <v>123</v>
-      </c>
-      <c r="K20">
+      <c r="K20" t="s">
+        <v>116</v>
+      </c>
+      <c r="L20">
         <v>6</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="N20" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M20" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="O20" t="s">
+        <v>118</v>
+      </c>
+      <c r="P20" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>152</v>
+      </c>
+      <c r="G21" t="s">
+        <v>501</v>
+      </c>
+      <c r="H21" t="s">
+        <v>491</v>
+      </c>
+      <c r="I21" t="s">
+        <v>501</v>
+      </c>
+      <c r="J21">
         <v>8</v>
       </c>
-      <c r="D21" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21" t="s">
-        <v>160</v>
-      </c>
-      <c r="H21" t="s">
-        <v>39</v>
-      </c>
-      <c r="I21">
-        <v>8</v>
-      </c>
-      <c r="J21" t="s">
-        <v>166</v>
-      </c>
-      <c r="K21">
-        <f>I21*4</f>
+      <c r="K21" t="s">
+        <v>158</v>
+      </c>
+      <c r="L21">
+        <f>J21*4</f>
         <v>32</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="N21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="O21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F22" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="H22" t="s">
-        <v>132</v>
-      </c>
-      <c r="I22">
+        <v>495</v>
+      </c>
+      <c r="I22" t="s">
+        <v>213</v>
+      </c>
+      <c r="J22">
         <v>2</v>
       </c>
-      <c r="J22" t="s">
-        <v>133</v>
-      </c>
-      <c r="K22">
-        <f>I22*11</f>
+      <c r="K22" t="s">
+        <v>126</v>
+      </c>
+      <c r="L22">
+        <f>J22*11</f>
         <v>22</v>
       </c>
-      <c r="L22" t="s">
-        <v>47</v>
-      </c>
       <c r="M22" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="N22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="E23" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F23" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>11</v>
+        <v>502</v>
       </c>
       <c r="H23" t="s">
-        <v>136</v>
-      </c>
-      <c r="I23">
+        <v>491</v>
+      </c>
+      <c r="I23" t="s">
+        <v>129</v>
+      </c>
+      <c r="J23">
         <v>4</v>
       </c>
-      <c r="J23" t="s">
-        <v>137</v>
-      </c>
-      <c r="K23">
+      <c r="K23" t="s">
+        <v>130</v>
+      </c>
+      <c r="L23">
         <f>19*2+16*2+1</f>
         <v>71</v>
       </c>
-      <c r="L23" t="s">
-        <v>47</v>
-      </c>
-      <c r="N23" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M23" t="s">
+        <v>44</v>
+      </c>
+      <c r="O23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>139</v>
+        <v>476</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F24" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G24" t="s">
-        <v>11</v>
+        <v>503</v>
       </c>
       <c r="H24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I24">
+        <v>491</v>
+      </c>
+      <c r="I24" t="s">
+        <v>504</v>
+      </c>
+      <c r="J24">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="J24" t="s">
-        <v>140</v>
-      </c>
-      <c r="K24">
-        <f>20</f>
-        <v>20</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K24" t="s">
+        <v>477</v>
+      </c>
+      <c r="L24">
+        <v>10</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="E25" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="F25" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="H25" t="s">
-        <v>144</v>
-      </c>
-      <c r="I25">
+        <v>495</v>
+      </c>
+      <c r="I25" t="s">
+        <v>136</v>
+      </c>
+      <c r="J25">
         <v>3</v>
       </c>
-      <c r="J25" t="s">
-        <v>145</v>
-      </c>
-      <c r="K25">
+      <c r="K25" t="s">
+        <v>137</v>
+      </c>
+      <c r="L25">
         <v>46</v>
       </c>
-      <c r="L25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="E26" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="F26" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="H26" t="s">
-        <v>115</v>
-      </c>
-      <c r="I26">
+        <v>495</v>
+      </c>
+      <c r="I26" t="s">
+        <v>108</v>
+      </c>
+      <c r="J26">
         <v>2</v>
       </c>
-      <c r="J26" t="s">
-        <v>147</v>
-      </c>
-      <c r="K26">
+      <c r="K26" t="s">
+        <v>139</v>
+      </c>
+      <c r="L26">
         <v>22</v>
       </c>
-      <c r="L26" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="F27" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>18</v>
+        <v>339</v>
       </c>
       <c r="H27" t="s">
-        <v>39</v>
-      </c>
-      <c r="I27">
+        <v>491</v>
+      </c>
+      <c r="I27" t="s">
+        <v>70</v>
+      </c>
+      <c r="J27">
         <v>5</v>
       </c>
-      <c r="J27" t="s">
-        <v>149</v>
-      </c>
-      <c r="K27">
-        <f>I27*4</f>
+      <c r="K27" t="s">
+        <v>141</v>
+      </c>
+      <c r="L27">
+        <f>J27*4</f>
         <v>20</v>
       </c>
-      <c r="L27" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>150</v>
+        <v>479</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="F28" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="G28" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="H28" t="s">
-        <v>132</v>
-      </c>
-      <c r="I28">
-        <v>3</v>
-      </c>
-      <c r="J28" t="s">
-        <v>151</v>
-      </c>
-      <c r="K28">
-        <f>I28*3</f>
-        <v>9</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+        <v>491</v>
+      </c>
+      <c r="I28" t="s">
+        <v>233</v>
+      </c>
+      <c r="J28">
+        <v>4</v>
+      </c>
+      <c r="K28" t="s">
+        <v>480</v>
+      </c>
+      <c r="L28">
+        <v>23</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C29" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="E29" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="F29" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>11</v>
+        <v>506</v>
       </c>
       <c r="H29" t="s">
-        <v>39</v>
-      </c>
-      <c r="I29">
+        <v>491</v>
+      </c>
+      <c r="I29" t="s">
+        <v>505</v>
+      </c>
+      <c r="J29">
         <v>4</v>
       </c>
-      <c r="J29" t="s">
-        <v>154</v>
-      </c>
-      <c r="K29">
-        <f>I29*3</f>
+      <c r="K29" t="s">
+        <v>146</v>
+      </c>
+      <c r="L29">
+        <f>J29*3</f>
         <v>12</v>
       </c>
-      <c r="L29" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="E30" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="F30" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>11</v>
+        <v>507</v>
       </c>
       <c r="H30" t="s">
-        <v>39</v>
-      </c>
-      <c r="I30">
+        <v>491</v>
+      </c>
+      <c r="I30" t="s">
+        <v>484</v>
+      </c>
+      <c r="J30">
         <v>3</v>
       </c>
-      <c r="J30" t="s">
-        <v>157</v>
-      </c>
-      <c r="K30">
-        <f>I30*4</f>
+      <c r="K30" t="s">
+        <v>149</v>
+      </c>
+      <c r="L30">
+        <f>J30*4</f>
         <v>12</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M30" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C31" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
-        <v>99</v>
+        <v>153</v>
       </c>
       <c r="E31" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="F31" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="G31" t="s">
-        <v>160</v>
+        <v>501</v>
       </c>
       <c r="H31" t="s">
-        <v>39</v>
-      </c>
-      <c r="I31">
+        <v>491</v>
+      </c>
+      <c r="I31" t="s">
+        <v>501</v>
+      </c>
+      <c r="J31">
         <v>4</v>
       </c>
-      <c r="J31" t="s">
-        <v>162</v>
-      </c>
-      <c r="K31">
-        <f>I31*4</f>
+      <c r="K31" t="s">
+        <v>154</v>
+      </c>
+      <c r="L31">
+        <f>J31*4</f>
         <v>16</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M31" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="E32" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="F32" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="G32" t="s">
-        <v>18</v>
+        <v>160</v>
       </c>
       <c r="H32" t="s">
-        <v>168</v>
-      </c>
-      <c r="I32">
+        <v>495</v>
+      </c>
+      <c r="I32" t="s">
+        <v>129</v>
+      </c>
+      <c r="J32">
         <v>4</v>
       </c>
-      <c r="J32" t="s">
-        <v>169</v>
-      </c>
-      <c r="K32">
-        <f>I32*4</f>
+      <c r="K32" t="s">
+        <v>161</v>
+      </c>
+      <c r="L32">
+        <f>J32*4</f>
         <v>16</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="M32" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M32" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="N32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D33" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="E33" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="F33" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G33" t="s">
-        <v>11</v>
+        <v>508</v>
       </c>
       <c r="H33" t="s">
-        <v>39</v>
-      </c>
-      <c r="I33">
+        <v>491</v>
+      </c>
+      <c r="I33" t="s">
+        <v>509</v>
+      </c>
+      <c r="J33">
         <f>3</f>
         <v>3</v>
       </c>
-      <c r="J33" t="s">
-        <v>174</v>
-      </c>
-      <c r="K33">
-        <f>I33*3</f>
+      <c r="K33" t="s">
+        <v>166</v>
+      </c>
+      <c r="L33">
+        <f>J33*3</f>
         <v>9</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M33" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="F34" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="G34" t="s">
-        <v>18</v>
+        <v>169</v>
       </c>
       <c r="H34" t="s">
-        <v>177</v>
-      </c>
-      <c r="I34">
+        <v>495</v>
+      </c>
+      <c r="I34" t="s">
+        <v>504</v>
+      </c>
+      <c r="J34">
         <v>4</v>
       </c>
-      <c r="J34" t="s">
-        <v>178</v>
-      </c>
-      <c r="K34">
+      <c r="K34" t="s">
+        <v>170</v>
+      </c>
+      <c r="L34">
         <f>11</f>
         <v>11</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M34" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C35" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D35" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="F35" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>11</v>
+        <v>173</v>
       </c>
       <c r="H35" t="s">
-        <v>181</v>
-      </c>
-      <c r="I35">
+        <v>495</v>
+      </c>
+      <c r="I35" t="s">
+        <v>500</v>
+      </c>
+      <c r="J35">
         <v>3</v>
       </c>
-      <c r="J35" t="s">
-        <v>182</v>
-      </c>
-      <c r="K35">
+      <c r="K35" t="s">
+        <v>174</v>
+      </c>
+      <c r="L35">
         <f>9</f>
         <v>9</v>
       </c>
-      <c r="L35" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M35" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C36" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="E36" t="s">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="F36" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>11</v>
+        <v>178</v>
       </c>
       <c r="H36" t="s">
-        <v>186</v>
-      </c>
-      <c r="I36">
+        <v>495</v>
+      </c>
+      <c r="I36" t="s">
+        <v>178</v>
+      </c>
+      <c r="J36">
         <v>2</v>
       </c>
-      <c r="J36" t="s">
-        <v>184</v>
-      </c>
-      <c r="K36">
+      <c r="K36" t="s">
+        <v>176</v>
+      </c>
+      <c r="L36">
         <f>8</f>
         <v>8</v>
       </c>
-      <c r="L36" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M36" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D37" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="E37" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="F37" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>11</v>
+        <v>510</v>
       </c>
       <c r="H37" t="s">
-        <v>136</v>
-      </c>
-      <c r="I37">
+        <v>495</v>
+      </c>
+      <c r="I37" t="s">
+        <v>129</v>
+      </c>
+      <c r="J37">
         <v>2</v>
       </c>
-      <c r="J37" t="s">
-        <v>189</v>
-      </c>
-      <c r="K37">
+      <c r="K37" t="s">
+        <v>181</v>
+      </c>
+      <c r="L37">
         <f>25*2</f>
         <v>50</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="M37" t="s">
-        <v>190</v>
+      <c r="M37" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="N37" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="O37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C38" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D38" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="E38" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="F38" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>18</v>
+        <v>511</v>
       </c>
       <c r="H38" t="s">
-        <v>39</v>
-      </c>
-      <c r="I38">
+        <v>491</v>
+      </c>
+      <c r="I38" t="s">
+        <v>79</v>
+      </c>
+      <c r="J38">
         <v>2</v>
       </c>
-      <c r="J38" t="s">
-        <v>194</v>
-      </c>
-      <c r="K38">
+      <c r="K38" t="s">
+        <v>186</v>
+      </c>
+      <c r="L38">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M38" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D39" t="s">
-        <v>99</v>
+        <v>189</v>
       </c>
       <c r="E39" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="F39" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G39" t="s">
-        <v>11</v>
+        <v>190</v>
       </c>
       <c r="H39" t="s">
-        <v>198</v>
-      </c>
-      <c r="I39">
+        <v>491</v>
+      </c>
+      <c r="I39" t="s">
+        <v>70</v>
+      </c>
+      <c r="J39">
         <v>4</v>
       </c>
-      <c r="J39" t="s">
-        <v>199</v>
-      </c>
-      <c r="K39">
-        <f>I39*3</f>
+      <c r="K39" t="s">
+        <v>191</v>
+      </c>
+      <c r="L39">
+        <f>J39*3</f>
         <v>12</v>
       </c>
-      <c r="L39" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M39" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D40" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="E40" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="F40" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="H40" t="s">
-        <v>144</v>
-      </c>
-      <c r="I40">
+        <v>495</v>
+      </c>
+      <c r="I40" t="s">
+        <v>136</v>
+      </c>
+      <c r="J40">
         <v>4</v>
       </c>
-      <c r="J40" t="s">
-        <v>202</v>
-      </c>
-      <c r="K40">
-        <f>I40*10</f>
+      <c r="K40" t="s">
+        <v>194</v>
+      </c>
+      <c r="L40">
+        <f>J40*10</f>
         <v>40</v>
       </c>
-      <c r="L40" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="M40" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M40" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="N40" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C41" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="F41" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="G41" t="s">
-        <v>18</v>
+        <v>512</v>
       </c>
       <c r="H41" t="s">
-        <v>77</v>
-      </c>
-      <c r="I41">
+        <v>495</v>
+      </c>
+      <c r="I41" t="s">
+        <v>70</v>
+      </c>
+      <c r="J41">
         <v>4</v>
       </c>
-      <c r="J41" t="s">
-        <v>206</v>
-      </c>
-      <c r="K41">
+      <c r="K41" t="s">
+        <v>198</v>
+      </c>
+      <c r="L41">
         <f>24</f>
         <v>24</v>
       </c>
-      <c r="L41" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="M41" t="s">
-        <v>208</v>
+      <c r="M41" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="N41" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="O41" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C42" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D42" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E42" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>11</v>
+        <v>499</v>
       </c>
       <c r="H42" t="s">
-        <v>39</v>
-      </c>
-      <c r="I42">
+        <v>491</v>
+      </c>
+      <c r="I42" t="s">
+        <v>500</v>
+      </c>
+      <c r="J42">
         <v>2</v>
       </c>
-      <c r="J42" t="s">
-        <v>127</v>
-      </c>
-      <c r="K42">
+      <c r="K42" t="s">
+        <v>120</v>
+      </c>
+      <c r="L42">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="N42" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M42" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="O42" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D43" t="s">
-        <v>99</v>
+        <v>203</v>
       </c>
       <c r="E43" t="s">
-        <v>211</v>
+        <v>124</v>
       </c>
       <c r="F43" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G43" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="H43" t="s">
-        <v>115</v>
-      </c>
-      <c r="I43">
+        <v>495</v>
+      </c>
+      <c r="I43" t="s">
+        <v>108</v>
+      </c>
+      <c r="J43">
         <v>2</v>
       </c>
-      <c r="J43" t="s">
-        <v>212</v>
-      </c>
-      <c r="K43">
+      <c r="K43" t="s">
+        <v>204</v>
+      </c>
+      <c r="L43">
         <f>35</f>
         <v>35</v>
       </c>
-      <c r="L43" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="M43" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M43" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="N43" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D44" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="E44" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F44" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>11</v>
+        <v>208</v>
       </c>
       <c r="H44" t="s">
-        <v>216</v>
-      </c>
-      <c r="I44">
+        <v>495</v>
+      </c>
+      <c r="I44" t="s">
+        <v>213</v>
+      </c>
+      <c r="J44">
         <v>3</v>
       </c>
-      <c r="J44" t="s">
-        <v>217</v>
-      </c>
-      <c r="K44">
+      <c r="K44" t="s">
+        <v>209</v>
+      </c>
+      <c r="L44">
         <v>29</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="M44" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M44" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="N44" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D45" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F45" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>11</v>
+        <v>513</v>
       </c>
       <c r="H45" t="s">
-        <v>221</v>
-      </c>
-      <c r="I45">
+        <v>495</v>
+      </c>
+      <c r="I45" t="s">
+        <v>213</v>
+      </c>
+      <c r="J45">
         <v>3</v>
       </c>
-      <c r="J45" t="s">
-        <v>217</v>
-      </c>
-      <c r="K45">
+      <c r="K45" t="s">
+        <v>209</v>
+      </c>
+      <c r="L45">
         <v>28</v>
       </c>
-      <c r="L45" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="M45" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M45" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="N45" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C46" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D46" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E46" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F46" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>11</v>
+        <v>514</v>
       </c>
       <c r="H46" t="s">
-        <v>39</v>
-      </c>
-      <c r="I46">
+        <v>491</v>
+      </c>
+      <c r="I46" t="s">
+        <v>515</v>
+      </c>
+      <c r="J46">
         <v>6</v>
       </c>
-      <c r="J46" t="s">
-        <v>224</v>
-      </c>
-      <c r="K46">
+      <c r="K46" t="s">
+        <v>216</v>
+      </c>
+      <c r="L46">
         <f>6*3</f>
         <v>18</v>
       </c>
-      <c r="L46" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="M46" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M46" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="N46" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F47" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>11</v>
+        <v>220</v>
       </c>
       <c r="H47" t="s">
-        <v>228</v>
-      </c>
-      <c r="I47">
+        <v>495</v>
+      </c>
+      <c r="I47" t="s">
+        <v>439</v>
+      </c>
+      <c r="J47">
         <v>2</v>
       </c>
-      <c r="J47" t="s">
-        <v>229</v>
-      </c>
-      <c r="K47">
+      <c r="K47" t="s">
+        <v>221</v>
+      </c>
+      <c r="L47">
         <v>21</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="M47" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M47" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="N47" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C48" t="s">
+        <v>92</v>
+      </c>
+      <c r="D48" t="s">
+        <v>225</v>
+      </c>
+      <c r="E48" t="s">
+        <v>124</v>
+      </c>
+      <c r="F48" t="s">
+        <v>17</v>
+      </c>
+      <c r="G48" t="s">
+        <v>226</v>
+      </c>
+      <c r="H48" t="s">
+        <v>495</v>
+      </c>
+      <c r="I48" t="s">
+        <v>108</v>
+      </c>
+      <c r="J48">
+        <v>2</v>
+      </c>
+      <c r="K48" t="s">
+        <v>67</v>
+      </c>
+      <c r="L48">
         <v>8</v>
       </c>
-      <c r="D48" t="s">
-        <v>99</v>
-      </c>
-      <c r="E48" t="s">
-        <v>233</v>
-      </c>
-      <c r="F48" t="s">
-        <v>131</v>
-      </c>
-      <c r="G48" t="s">
-        <v>18</v>
-      </c>
-      <c r="H48" t="s">
-        <v>234</v>
-      </c>
-      <c r="I48">
-        <v>2</v>
-      </c>
-      <c r="J48" t="s">
-        <v>74</v>
-      </c>
-      <c r="K48">
-        <v>8</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M48" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C49" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="E49" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="F49" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>11</v>
+        <v>516</v>
       </c>
       <c r="H49" t="s">
-        <v>39</v>
-      </c>
-      <c r="I49">
+        <v>491</v>
+      </c>
+      <c r="I49" t="s">
+        <v>108</v>
+      </c>
+      <c r="J49">
         <v>6</v>
       </c>
-      <c r="J49" t="s">
-        <v>237</v>
-      </c>
-      <c r="K49">
-        <f>I49*4</f>
+      <c r="K49" t="s">
+        <v>229</v>
+      </c>
+      <c r="L49">
+        <f>J49*4</f>
         <v>24</v>
       </c>
-      <c r="L49" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="M49" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M49" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="N49" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C50" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D50" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="E50" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F50" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="G50" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="H50" t="s">
-        <v>241</v>
-      </c>
-      <c r="I50">
+        <v>491</v>
+      </c>
+      <c r="I50" t="s">
+        <v>233</v>
+      </c>
+      <c r="J50">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="J50" t="s">
-        <v>242</v>
-      </c>
-      <c r="K50">
-        <f>I50*3</f>
+      <c r="K50" t="s">
+        <v>234</v>
+      </c>
+      <c r="L50">
+        <f>J50*3</f>
         <v>18</v>
       </c>
-      <c r="L50" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="M50" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M50" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="N50" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C51" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D51" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E51" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F51" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="G51" t="s">
-        <v>11</v>
+        <v>514</v>
       </c>
       <c r="H51" t="s">
-        <v>39</v>
-      </c>
-      <c r="I51">
+        <v>491</v>
+      </c>
+      <c r="I51" t="s">
+        <v>515</v>
+      </c>
+      <c r="J51">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="J51" t="s">
-        <v>246</v>
-      </c>
-      <c r="K51">
-        <f>I51*3</f>
+      <c r="K51" t="s">
+        <v>238</v>
+      </c>
+      <c r="L51">
+        <f>J51*3</f>
         <v>6</v>
       </c>
-      <c r="L51" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="M51" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M51" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="N51" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C52" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D52" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F52" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="G52" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="H52" t="s">
+        <v>491</v>
+      </c>
+      <c r="I52" t="s">
+        <v>233</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52" t="s">
         <v>241</v>
       </c>
-      <c r="I52">
-        <v>2</v>
-      </c>
-      <c r="J52" t="s">
-        <v>249</v>
-      </c>
-      <c r="K52">
+      <c r="L52">
         <v>6</v>
       </c>
-      <c r="L52" t="s">
-        <v>47</v>
-      </c>
       <c r="M52" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="N52" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C53" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D53" t="s">
-        <v>99</v>
+        <v>203</v>
       </c>
       <c r="E53" t="s">
-        <v>211</v>
+        <v>253</v>
       </c>
       <c r="F53" t="s">
-        <v>261</v>
+        <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>11</v>
+        <v>517</v>
       </c>
       <c r="H53" t="s">
-        <v>262</v>
-      </c>
-      <c r="I53">
+        <v>495</v>
+      </c>
+      <c r="I53" t="s">
+        <v>254</v>
+      </c>
+      <c r="J53">
         <v>3</v>
       </c>
-      <c r="J53" t="s">
-        <v>263</v>
-      </c>
-      <c r="K53">
+      <c r="K53" t="s">
+        <v>255</v>
+      </c>
+      <c r="L53">
         <v>69</v>
       </c>
-      <c r="L53" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="M53" t="s">
-        <v>265</v>
+      <c r="M53" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="N53" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="O53" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C54" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D54" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="E54" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="F54" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="G54" t="s">
-        <v>18</v>
+        <v>260</v>
       </c>
       <c r="H54" t="s">
-        <v>268</v>
-      </c>
-      <c r="I54">
+        <v>495</v>
+      </c>
+      <c r="I54" t="s">
+        <v>260</v>
+      </c>
+      <c r="J54">
         <v>3</v>
       </c>
-      <c r="J54" t="s">
-        <v>269</v>
-      </c>
-      <c r="K54">
+      <c r="K54" t="s">
+        <v>261</v>
+      </c>
+      <c r="L54">
         <f>14</f>
         <v>14</v>
       </c>
-      <c r="L54" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="M54" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M54" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="N54" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="C55" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="E55" t="s">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="F55" t="s">
-        <v>273</v>
+        <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="H55" t="s">
-        <v>115</v>
-      </c>
-      <c r="I55">
+        <v>495</v>
+      </c>
+      <c r="I55" t="s">
+        <v>108</v>
+      </c>
+      <c r="J55">
         <v>4</v>
       </c>
-      <c r="J55" t="s">
-        <v>274</v>
-      </c>
-      <c r="K55">
+      <c r="K55" t="s">
+        <v>266</v>
+      </c>
+      <c r="L55">
         <f>32</f>
         <v>32</v>
       </c>
-      <c r="L55" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="M55" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M55" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="N55" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C56" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D56" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="E56" t="s">
-        <v>50</v>
+        <v>265</v>
       </c>
       <c r="F56" t="s">
-        <v>273</v>
+        <v>11</v>
       </c>
       <c r="G56" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="H56" t="s">
-        <v>115</v>
-      </c>
-      <c r="I56">
+        <v>495</v>
+      </c>
+      <c r="I56" t="s">
+        <v>108</v>
+      </c>
+      <c r="J56">
         <v>2</v>
       </c>
-      <c r="J56" t="s">
-        <v>278</v>
-      </c>
-      <c r="K56">
+      <c r="K56" t="s">
+        <v>270</v>
+      </c>
+      <c r="L56">
         <f>27</f>
         <v>27</v>
       </c>
-      <c r="L56" t="s">
-        <v>279</v>
-      </c>
       <c r="M56" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+      <c r="N56" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C57" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D57" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="E57" t="s">
-        <v>122</v>
+        <v>265</v>
       </c>
       <c r="F57" t="s">
-        <v>273</v>
+        <v>11</v>
       </c>
       <c r="G57" t="s">
-        <v>11</v>
+        <v>173</v>
       </c>
       <c r="H57" t="s">
-        <v>181</v>
-      </c>
-      <c r="I57">
+        <v>495</v>
+      </c>
+      <c r="I57" t="s">
+        <v>500</v>
+      </c>
+      <c r="J57">
         <v>2</v>
       </c>
-      <c r="J57" t="s">
-        <v>282</v>
-      </c>
-      <c r="K57">
+      <c r="K57" t="s">
+        <v>274</v>
+      </c>
+      <c r="L57">
         <f>133</f>
         <v>133</v>
       </c>
-      <c r="L57" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="N57" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M57" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="O57" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C58" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D58" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="E58" t="s">
-        <v>50</v>
+        <v>265</v>
       </c>
       <c r="F58" t="s">
-        <v>273</v>
+        <v>11</v>
       </c>
       <c r="G58" t="s">
-        <v>11</v>
+        <v>518</v>
       </c>
       <c r="H58" t="s">
-        <v>39</v>
-      </c>
-      <c r="I58">
+        <v>491</v>
+      </c>
+      <c r="I58" t="s">
+        <v>108</v>
+      </c>
+      <c r="J58">
         <v>2</v>
       </c>
-      <c r="J58" t="s">
-        <v>286</v>
-      </c>
-      <c r="K58">
+      <c r="K58" t="s">
+        <v>278</v>
+      </c>
+      <c r="L58">
         <v>10</v>
       </c>
-      <c r="L58" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="N58" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M58" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="O58" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C59" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D59" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="E59" t="s">
-        <v>45</v>
+        <v>265</v>
       </c>
       <c r="F59" t="s">
-        <v>273</v>
+        <v>11</v>
       </c>
       <c r="G59" t="s">
-        <v>11</v>
+        <v>519</v>
       </c>
       <c r="H59" t="s">
-        <v>39</v>
-      </c>
-      <c r="I59">
+        <v>491</v>
+      </c>
+      <c r="I59" t="s">
+        <v>213</v>
+      </c>
+      <c r="J59">
         <v>2</v>
       </c>
-      <c r="J59" t="s">
-        <v>289</v>
-      </c>
-      <c r="K59">
+      <c r="K59" t="s">
+        <v>281</v>
+      </c>
+      <c r="L59">
         <v>7</v>
       </c>
-      <c r="L59" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="M59" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M59" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="N59" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C60" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D60" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="E60" t="s">
-        <v>31</v>
+        <v>265</v>
       </c>
       <c r="F60" t="s">
-        <v>273</v>
+        <v>11</v>
       </c>
       <c r="G60" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="H60" t="s">
-        <v>115</v>
-      </c>
-      <c r="I60">
+        <v>495</v>
+      </c>
+      <c r="I60" t="s">
+        <v>108</v>
+      </c>
+      <c r="J60">
         <v>2</v>
       </c>
-      <c r="J60" t="s">
-        <v>294</v>
-      </c>
-      <c r="K60">
+      <c r="K60" t="s">
+        <v>286</v>
+      </c>
+      <c r="L60">
         <v>48</v>
       </c>
-      <c r="L60" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="N60" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M60" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="O60" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C61" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D61" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="E61" t="s">
-        <v>50</v>
+        <v>265</v>
       </c>
       <c r="F61" t="s">
-        <v>273</v>
+        <v>11</v>
       </c>
       <c r="G61" t="s">
-        <v>11</v>
+        <v>173</v>
       </c>
       <c r="H61" t="s">
-        <v>181</v>
-      </c>
-      <c r="I61">
+        <v>495</v>
+      </c>
+      <c r="I61" t="s">
+        <v>500</v>
+      </c>
+      <c r="J61">
         <v>4</v>
       </c>
-      <c r="J61" t="s">
-        <v>301</v>
-      </c>
-      <c r="K61">
+      <c r="K61" t="s">
+        <v>293</v>
+      </c>
+      <c r="L61">
         <f>63+52</f>
         <v>115</v>
       </c>
-      <c r="L61" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="M61" t="s">
-        <v>475</v>
+      <c r="M61" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="N61" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+      <c r="O61" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C62" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D62" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="E62" t="s">
-        <v>50</v>
+        <v>265</v>
       </c>
       <c r="F62" t="s">
-        <v>273</v>
+        <v>11</v>
       </c>
       <c r="G62" t="s">
-        <v>11</v>
+        <v>173</v>
       </c>
       <c r="H62" t="s">
-        <v>181</v>
-      </c>
-      <c r="I62">
+        <v>495</v>
+      </c>
+      <c r="I62" t="s">
+        <v>500</v>
+      </c>
+      <c r="J62">
         <v>4</v>
       </c>
-      <c r="J62" t="s">
-        <v>301</v>
-      </c>
-      <c r="K62">
+      <c r="K62" t="s">
+        <v>293</v>
+      </c>
+      <c r="L62">
         <f>120</f>
         <v>120</v>
       </c>
-      <c r="L62" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="M62" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M62" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="N62" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C63" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D63" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="E63" t="s">
-        <v>45</v>
+        <v>265</v>
       </c>
       <c r="F63" t="s">
-        <v>273</v>
+        <v>17</v>
       </c>
       <c r="G63" t="s">
-        <v>18</v>
+        <v>260</v>
       </c>
       <c r="H63" t="s">
-        <v>268</v>
-      </c>
-      <c r="I63">
+        <v>495</v>
+      </c>
+      <c r="I63" t="s">
+        <v>260</v>
+      </c>
+      <c r="J63">
         <v>6</v>
       </c>
-      <c r="J63" t="s">
-        <v>303</v>
-      </c>
-      <c r="K63">
+      <c r="K63" t="s">
+        <v>295</v>
+      </c>
+      <c r="L63">
         <v>36</v>
       </c>
-      <c r="L63" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="M63" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M63" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="N63" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C64" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D64" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="E64" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="F64" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="G64" t="s">
-        <v>18</v>
+        <v>260</v>
       </c>
       <c r="H64" t="s">
-        <v>268</v>
-      </c>
-      <c r="I64">
+        <v>495</v>
+      </c>
+      <c r="I64" t="s">
+        <v>260</v>
+      </c>
+      <c r="J64">
         <v>5</v>
       </c>
-      <c r="J64" t="s">
-        <v>307</v>
-      </c>
-      <c r="K64">
+      <c r="K64" t="s">
+        <v>299</v>
+      </c>
+      <c r="L64">
         <v>35</v>
       </c>
-      <c r="L64" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="M64" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M64" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="N64" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C65" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D65" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="E65" t="s">
-        <v>50</v>
+        <v>265</v>
       </c>
       <c r="F65" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="G65" t="s">
-        <v>311</v>
+        <v>53</v>
       </c>
       <c r="H65" t="s">
-        <v>57</v>
-      </c>
-      <c r="I65">
+        <v>495</v>
+      </c>
+      <c r="I65" t="s">
+        <v>108</v>
+      </c>
+      <c r="J65">
         <v>3</v>
       </c>
-      <c r="J65" t="s">
-        <v>312</v>
-      </c>
-      <c r="K65">
+      <c r="K65" t="s">
+        <v>304</v>
+      </c>
+      <c r="L65">
         <v>9</v>
       </c>
-      <c r="L65" t="s">
-        <v>47</v>
-      </c>
-      <c r="N65" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M65" t="s">
+        <v>44</v>
+      </c>
+      <c r="O65" t="s">
+        <v>305</v>
+      </c>
+      <c r="P65" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="C66" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D66" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="E66" t="s">
-        <v>50</v>
+        <v>265</v>
       </c>
       <c r="F66" t="s">
-        <v>273</v>
+        <v>17</v>
       </c>
       <c r="G66" t="s">
+        <v>308</v>
+      </c>
+      <c r="H66" t="s">
+        <v>495</v>
+      </c>
+      <c r="I66" t="s">
+        <v>439</v>
+      </c>
+      <c r="J66">
+        <v>6</v>
+      </c>
+      <c r="K66" t="s">
+        <v>309</v>
+      </c>
+      <c r="L66">
+        <f>J66*3</f>
         <v>18</v>
       </c>
-      <c r="H66" t="s">
-        <v>316</v>
-      </c>
-      <c r="I66">
-        <v>6</v>
-      </c>
-      <c r="J66" t="s">
-        <v>317</v>
-      </c>
-      <c r="K66">
-        <f>I66*3</f>
-        <v>18</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M66" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="P66" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C67" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D67" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="E67" t="s">
-        <v>67</v>
+        <v>265</v>
       </c>
       <c r="F67" t="s">
-        <v>273</v>
+        <v>17</v>
       </c>
       <c r="G67" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="H67" t="s">
-        <v>77</v>
-      </c>
-      <c r="I67">
+        <v>495</v>
+      </c>
+      <c r="I67" t="s">
+        <v>70</v>
+      </c>
+      <c r="J67">
         <v>2</v>
       </c>
-      <c r="J67" t="s">
-        <v>321</v>
-      </c>
-      <c r="K67">
+      <c r="K67" t="s">
+        <v>313</v>
+      </c>
+      <c r="L67">
         <f>12</f>
         <v>12</v>
       </c>
-      <c r="L67" t="s">
-        <v>47</v>
-      </c>
       <c r="M67" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="N67" t="s">
+        <v>314</v>
+      </c>
+      <c r="P67" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="C68" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D68" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="E68" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="F68" t="s">
-        <v>9</v>
+        <v>316</v>
       </c>
       <c r="G68" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="H68" t="s">
-        <v>325</v>
-      </c>
-      <c r="I68">
+        <v>491</v>
+      </c>
+      <c r="I68" t="s">
+        <v>485</v>
+      </c>
+      <c r="J68">
         <v>2</v>
       </c>
-      <c r="J68" t="s">
-        <v>326</v>
-      </c>
-      <c r="K68">
+      <c r="K68" t="s">
+        <v>318</v>
+      </c>
+      <c r="L68">
         <v>12</v>
       </c>
-      <c r="L68" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M68" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="C69" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D69" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="E69" t="s">
-        <v>33</v>
+        <v>321</v>
       </c>
       <c r="F69" t="s">
-        <v>329</v>
+        <v>11</v>
       </c>
       <c r="G69" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="H69" t="s">
-        <v>115</v>
-      </c>
-      <c r="I69">
+        <v>495</v>
+      </c>
+      <c r="I69" t="s">
+        <v>108</v>
+      </c>
+      <c r="J69">
         <v>2</v>
       </c>
-      <c r="J69" t="s">
-        <v>330</v>
-      </c>
-      <c r="K69">
+      <c r="K69" t="s">
+        <v>322</v>
+      </c>
+      <c r="L69">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="L69" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M69" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C70" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D70" t="s">
-        <v>99</v>
+        <v>331</v>
       </c>
       <c r="E70" t="s">
-        <v>339</v>
+        <v>124</v>
       </c>
       <c r="F70" t="s">
-        <v>131</v>
+        <v>332</v>
       </c>
       <c r="G70" t="s">
-        <v>340</v>
+        <v>226</v>
       </c>
       <c r="H70" t="s">
-        <v>234</v>
-      </c>
-      <c r="I70">
+        <v>495</v>
+      </c>
+      <c r="I70" t="s">
+        <v>108</v>
+      </c>
+      <c r="J70">
         <v>2</v>
       </c>
-      <c r="J70" t="s">
-        <v>341</v>
-      </c>
-      <c r="K70">
+      <c r="K70" t="s">
+        <v>333</v>
+      </c>
+      <c r="L70">
         <v>10</v>
       </c>
-      <c r="L70" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="N70" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M70" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="O70" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C71" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D71" t="s">
-        <v>99</v>
+        <v>338</v>
       </c>
       <c r="E71" t="s">
-        <v>346</v>
+        <v>124</v>
       </c>
       <c r="F71" t="s">
-        <v>131</v>
+        <v>332</v>
       </c>
       <c r="G71" t="s">
+        <v>339</v>
+      </c>
+      <c r="H71" t="s">
+        <v>495</v>
+      </c>
+      <c r="I71" t="s">
+        <v>70</v>
+      </c>
+      <c r="J71">
+        <v>5</v>
+      </c>
+      <c r="K71" t="s">
         <v>340</v>
       </c>
-      <c r="H71" t="s">
-        <v>347</v>
-      </c>
-      <c r="I71">
-        <v>5</v>
-      </c>
-      <c r="J71" t="s">
-        <v>348</v>
-      </c>
-      <c r="K71">
-        <f>I71*4+4</f>
+      <c r="L71">
+        <f>J71*4+4</f>
         <v>24</v>
       </c>
-      <c r="L71" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="N71" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M71" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="O71" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C72" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D72" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F72" t="s">
-        <v>131</v>
+        <v>345</v>
       </c>
       <c r="G72" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="H72" t="s">
-        <v>354</v>
-      </c>
-      <c r="I72">
+        <v>495</v>
+      </c>
+      <c r="I72" t="s">
+        <v>346</v>
+      </c>
+      <c r="J72">
         <v>3</v>
       </c>
-      <c r="J72" t="s">
-        <v>351</v>
-      </c>
-      <c r="K72">
+      <c r="K72" t="s">
+        <v>343</v>
+      </c>
+      <c r="L72">
         <f>3*4</f>
         <v>12</v>
       </c>
-      <c r="L72" s="1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M72" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C73" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D73" t="s">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="E73" t="s">
-        <v>336</v>
+        <v>9</v>
       </c>
       <c r="F73" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G73" t="s">
-        <v>11</v>
+        <v>325</v>
       </c>
       <c r="H73" t="s">
-        <v>333</v>
-      </c>
-      <c r="I73">
+        <v>495</v>
+      </c>
+      <c r="I73" t="s">
+        <v>484</v>
+      </c>
+      <c r="J73">
         <v>4</v>
       </c>
-      <c r="J73" t="s">
-        <v>334</v>
-      </c>
-      <c r="K73">
+      <c r="K73" t="s">
+        <v>326</v>
+      </c>
+      <c r="L73">
         <v>23</v>
       </c>
-      <c r="L73" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="M73" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M73" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N73" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="C74" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D74" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E74" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="F74" t="s">
-        <v>9</v>
+        <v>332</v>
       </c>
       <c r="G74" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="H74" t="s">
-        <v>357</v>
-      </c>
-      <c r="I74">
+        <v>495</v>
+      </c>
+      <c r="I74" t="s">
+        <v>349</v>
+      </c>
+      <c r="J74">
         <v>12</v>
       </c>
-      <c r="J74" t="s">
-        <v>358</v>
-      </c>
-      <c r="K74">
-        <f>I74*6</f>
+      <c r="K74" t="s">
+        <v>350</v>
+      </c>
+      <c r="L74">
+        <f>J74*6</f>
         <v>72</v>
       </c>
-      <c r="L74" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="M74" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M74" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="N74" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C75" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D75" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E75" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="F75" t="s">
-        <v>9</v>
+        <v>332</v>
       </c>
       <c r="G75" t="s">
-        <v>340</v>
+        <v>129</v>
       </c>
       <c r="H75" t="s">
-        <v>136</v>
-      </c>
-      <c r="I75">
+        <v>495</v>
+      </c>
+      <c r="I75" t="s">
+        <v>129</v>
+      </c>
+      <c r="J75">
         <v>6</v>
       </c>
-      <c r="J75" t="s">
-        <v>363</v>
-      </c>
-      <c r="K75">
+      <c r="K75" t="s">
+        <v>355</v>
+      </c>
+      <c r="L75">
         <f>6*3</f>
         <v>18</v>
       </c>
-      <c r="L75" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M75" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C76" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D76" t="s">
-        <v>98</v>
+        <v>357</v>
       </c>
       <c r="E76" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="F76" t="s">
-        <v>366</v>
+        <v>316</v>
       </c>
       <c r="G76" t="s">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="H76" t="s">
-        <v>367</v>
-      </c>
-      <c r="I76">
+        <v>491</v>
+      </c>
+      <c r="I76" t="s">
+        <v>359</v>
+      </c>
+      <c r="J76">
         <v>3</v>
       </c>
-      <c r="J76" t="s">
-        <v>368</v>
-      </c>
-      <c r="K76">
-        <f>I76*3</f>
+      <c r="K76" t="s">
+        <v>360</v>
+      </c>
+      <c r="L76">
+        <f>J76*3</f>
         <v>9</v>
       </c>
-      <c r="L76" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M76" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C77" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D77" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="E77" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F77" t="s">
-        <v>9</v>
+        <v>345</v>
       </c>
       <c r="G77" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="H77" t="s">
-        <v>371</v>
-      </c>
-      <c r="I77">
+        <v>495</v>
+      </c>
+      <c r="I77" t="s">
+        <v>363</v>
+      </c>
+      <c r="J77">
         <f>3</f>
         <v>3</v>
       </c>
-      <c r="J77" t="s">
-        <v>370</v>
-      </c>
-      <c r="K77">
-        <f>I77*3</f>
+      <c r="K77" t="s">
+        <v>362</v>
+      </c>
+      <c r="L77">
+        <f>J77*3</f>
         <v>9</v>
       </c>
-      <c r="L77" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M77" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="C78" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D78" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="E78" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F78" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G78" t="s">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="H78" t="s">
-        <v>111</v>
-      </c>
-      <c r="I78">
+        <v>495</v>
+      </c>
+      <c r="I78" t="s">
+        <v>439</v>
+      </c>
+      <c r="J78">
         <v>2</v>
       </c>
-      <c r="J78" t="s">
-        <v>375</v>
-      </c>
-      <c r="K78">
+      <c r="K78" t="s">
+        <v>367</v>
+      </c>
+      <c r="L78">
         <v>15</v>
       </c>
-      <c r="L78" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M78" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C79" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D79" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="E79" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F79" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G79" t="s">
-        <v>18</v>
+        <v>371</v>
       </c>
       <c r="H79" t="s">
-        <v>379</v>
-      </c>
-      <c r="I79">
+        <v>491</v>
+      </c>
+      <c r="I79" t="s">
+        <v>492</v>
+      </c>
+      <c r="J79">
         <v>3</v>
       </c>
-      <c r="J79" t="s">
-        <v>378</v>
-      </c>
-      <c r="K79">
+      <c r="K79" t="s">
+        <v>370</v>
+      </c>
+      <c r="L79">
         <f>9</f>
         <v>9</v>
       </c>
-      <c r="L79" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M79" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C80" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D80" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="E80" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F80" t="s">
-        <v>9</v>
+        <v>373</v>
       </c>
       <c r="G80" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H80" t="s">
-        <v>382</v>
-      </c>
-      <c r="I80">
+        <v>491</v>
+      </c>
+      <c r="I80" t="s">
+        <v>374</v>
+      </c>
+      <c r="J80">
         <v>2</v>
       </c>
-      <c r="J80" t="s">
-        <v>383</v>
-      </c>
-      <c r="K80">
+      <c r="K80" t="s">
+        <v>375</v>
+      </c>
+      <c r="L80">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="L80" s="1" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M80" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C81" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D81" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="E81" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F81" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G81" t="s">
-        <v>11</v>
+        <v>520</v>
       </c>
       <c r="H81" t="s">
-        <v>39</v>
-      </c>
-      <c r="I81">
+        <v>491</v>
+      </c>
+      <c r="I81" t="s">
+        <v>260</v>
+      </c>
+      <c r="J81">
         <v>2</v>
       </c>
-      <c r="J81" t="s">
-        <v>286</v>
-      </c>
-      <c r="K81">
+      <c r="K81" t="s">
+        <v>278</v>
+      </c>
+      <c r="L81">
         <v>6</v>
       </c>
-      <c r="L81" s="1" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M81" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="C82" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D82" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="E82" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F82" t="s">
+        <v>17</v>
+      </c>
+      <c r="G82" t="s">
+        <v>349</v>
+      </c>
+      <c r="H82" t="s">
+        <v>495</v>
+      </c>
+      <c r="I82" t="s">
+        <v>349</v>
+      </c>
+      <c r="J82">
+        <v>3</v>
+      </c>
+      <c r="K82" t="s">
+        <v>381</v>
+      </c>
+      <c r="L82">
         <v>9</v>
       </c>
-      <c r="G82" t="s">
-        <v>18</v>
-      </c>
-      <c r="H82" t="s">
-        <v>357</v>
-      </c>
-      <c r="I82">
-        <v>3</v>
-      </c>
-      <c r="J82" t="s">
-        <v>389</v>
-      </c>
-      <c r="K82">
-        <v>9</v>
-      </c>
-      <c r="L82" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M82" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C83" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D83" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E83" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="F83" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G83" t="s">
-        <v>11</v>
+        <v>521</v>
       </c>
       <c r="H83" t="s">
-        <v>39</v>
-      </c>
-      <c r="I83">
+        <v>491</v>
+      </c>
+      <c r="I83" t="s">
+        <v>492</v>
+      </c>
+      <c r="J83">
         <v>7</v>
       </c>
-      <c r="J83" t="s">
-        <v>392</v>
-      </c>
-      <c r="K83">
-        <f>I83*3</f>
+      <c r="K83" t="s">
+        <v>384</v>
+      </c>
+      <c r="L83">
+        <f>J83*3</f>
         <v>21</v>
       </c>
-      <c r="L83" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="M83" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M83" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="N83" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C84" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D84" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E84" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="F84" t="s">
-        <v>9</v>
+        <v>332</v>
       </c>
       <c r="G84" t="s">
-        <v>340</v>
+        <v>522</v>
       </c>
       <c r="H84" t="s">
-        <v>39</v>
-      </c>
-      <c r="I84">
+        <v>491</v>
+      </c>
+      <c r="I84" t="s">
+        <v>523</v>
+      </c>
+      <c r="J84">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="J84" t="s">
-        <v>396</v>
-      </c>
-      <c r="K84">
+      <c r="K84" t="s">
+        <v>388</v>
+      </c>
+      <c r="L84">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="L84" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M84" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D85" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E85" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="F85" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G85" t="s">
-        <v>11</v>
+        <v>524</v>
       </c>
       <c r="H85" t="s">
-        <v>39</v>
-      </c>
-      <c r="I85">
+        <v>491</v>
+      </c>
+      <c r="I85" t="s">
+        <v>525</v>
+      </c>
+      <c r="J85">
         <v>4</v>
       </c>
-      <c r="J85" t="s">
-        <v>398</v>
-      </c>
-      <c r="K85">
-        <f>4*I85</f>
+      <c r="K85" t="s">
+        <v>390</v>
+      </c>
+      <c r="L85">
+        <f>4*J85</f>
         <v>16</v>
       </c>
-      <c r="L85" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M85" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C86" t="s">
+        <v>91</v>
+      </c>
+      <c r="D86" t="s">
+        <v>30</v>
+      </c>
+      <c r="E86" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" t="s">
+        <v>373</v>
+      </c>
+      <c r="G86" t="s">
+        <v>374</v>
+      </c>
+      <c r="H86" t="s">
+        <v>491</v>
+      </c>
+      <c r="I86" t="s">
+        <v>374</v>
+      </c>
+      <c r="J86">
         <v>8</v>
       </c>
-      <c r="D86" t="s">
-        <v>98</v>
-      </c>
-      <c r="E86" t="s">
-        <v>33</v>
-      </c>
-      <c r="F86" t="s">
-        <v>9</v>
-      </c>
-      <c r="G86" t="s">
-        <v>381</v>
-      </c>
-      <c r="H86" t="s">
-        <v>382</v>
-      </c>
-      <c r="I86">
-        <v>8</v>
-      </c>
-      <c r="J86" t="s">
-        <v>400</v>
-      </c>
-      <c r="K86">
+      <c r="K86" t="s">
+        <v>392</v>
+      </c>
+      <c r="L86">
         <f>8*4</f>
         <v>32</v>
       </c>
-      <c r="L86" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M86" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C87" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D87" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="E87" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F87" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G87" t="s">
-        <v>11</v>
+        <v>526</v>
       </c>
       <c r="H87" t="s">
-        <v>406</v>
-      </c>
-      <c r="I87">
+        <v>495</v>
+      </c>
+      <c r="I87" t="s">
+        <v>527</v>
+      </c>
+      <c r="J87">
         <v>4</v>
       </c>
-      <c r="J87" t="s">
-        <v>405</v>
-      </c>
-      <c r="K87">
+      <c r="K87" t="s">
+        <v>397</v>
+      </c>
+      <c r="L87">
         <f>4*4</f>
         <v>16</v>
       </c>
-      <c r="L87" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="M87" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M87" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="N87" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="C88" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D88" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="E88" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F88" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G88" t="s">
-        <v>18</v>
+        <v>528</v>
       </c>
       <c r="H88" t="s">
-        <v>39</v>
-      </c>
-      <c r="I88">
+        <v>491</v>
+      </c>
+      <c r="I88" t="s">
+        <v>493</v>
+      </c>
+      <c r="J88">
         <v>4</v>
       </c>
-      <c r="J88" t="s">
-        <v>409</v>
-      </c>
-      <c r="K88">
+      <c r="K88" t="s">
+        <v>400</v>
+      </c>
+      <c r="L88">
         <f>4*5</f>
         <v>20</v>
       </c>
-      <c r="L88" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="N88" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M88" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="O88" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="C89" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D89" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E89" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="F89" t="s">
-        <v>9</v>
+        <v>410</v>
       </c>
       <c r="G89" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="H89" t="s">
-        <v>420</v>
-      </c>
-      <c r="I89">
+        <v>495</v>
+      </c>
+      <c r="I89" t="s">
+        <v>411</v>
+      </c>
+      <c r="J89">
         <v>6</v>
       </c>
-      <c r="J89" t="s">
-        <v>421</v>
-      </c>
-      <c r="K89">
+      <c r="K89" t="s">
+        <v>412</v>
+      </c>
+      <c r="L89">
         <f>6*3</f>
         <v>18</v>
       </c>
-      <c r="L89" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="M89" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M89" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="N89" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="C90" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D90" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="E90" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F90" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G90" t="s">
-        <v>11</v>
+        <v>529</v>
       </c>
       <c r="H90" t="s">
-        <v>39</v>
-      </c>
-      <c r="I90">
+        <v>491</v>
+      </c>
+      <c r="I90" t="s">
+        <v>484</v>
+      </c>
+      <c r="J90">
         <v>3</v>
       </c>
-      <c r="J90" t="s">
-        <v>426</v>
-      </c>
-      <c r="K90">
+      <c r="K90" t="s">
+        <v>417</v>
+      </c>
+      <c r="L90">
         <f>3*4</f>
         <v>12</v>
       </c>
-      <c r="L90" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M90" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="C91" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D91" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E91" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="F91" t="s">
-        <v>9</v>
+        <v>420</v>
       </c>
       <c r="G91" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="H91" t="s">
-        <v>430</v>
-      </c>
-      <c r="I91">
+        <v>495</v>
+      </c>
+      <c r="I91" t="s">
+        <v>421</v>
+      </c>
+      <c r="J91">
         <v>3</v>
       </c>
-      <c r="J91" t="s">
-        <v>431</v>
-      </c>
-      <c r="K91">
+      <c r="K91" t="s">
+        <v>422</v>
+      </c>
+      <c r="L91">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="L91" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M91" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="C92" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D92" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E92" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="F92" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G92" t="s">
-        <v>11</v>
+        <v>425</v>
       </c>
       <c r="H92" t="s">
-        <v>434</v>
-      </c>
-      <c r="I92">
+        <v>495</v>
+      </c>
+      <c r="I92" t="s">
+        <v>492</v>
+      </c>
+      <c r="J92">
         <v>3</v>
       </c>
-      <c r="J92" t="s">
-        <v>433</v>
-      </c>
-      <c r="K92">
+      <c r="K92" t="s">
+        <v>424</v>
+      </c>
+      <c r="L92">
         <v>13</v>
       </c>
-      <c r="L92" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M92" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="C93" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D93" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F93" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G93" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="H93" t="s">
-        <v>39</v>
-      </c>
-      <c r="I93">
+        <v>495</v>
+      </c>
+      <c r="I93" t="s">
+        <v>108</v>
+      </c>
+      <c r="J93">
         <v>4</v>
       </c>
-      <c r="J93" t="s">
-        <v>437</v>
-      </c>
-      <c r="K93">
+      <c r="K93" t="s">
+        <v>428</v>
+      </c>
+      <c r="L93">
         <f>158</f>
         <v>158</v>
       </c>
-      <c r="L93" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M93" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="C94" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D94" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E94" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="F94" t="s">
-        <v>9</v>
+        <v>332</v>
       </c>
       <c r="G94" t="s">
-        <v>340</v>
+        <v>431</v>
       </c>
       <c r="H94" t="s">
-        <v>440</v>
-      </c>
-      <c r="I94">
+        <v>495</v>
+      </c>
+      <c r="I94" t="s">
+        <v>504</v>
+      </c>
+      <c r="J94">
         <v>2</v>
       </c>
-      <c r="J94" t="s">
-        <v>441</v>
-      </c>
-      <c r="K94">
+      <c r="K94" t="s">
+        <v>432</v>
+      </c>
+      <c r="L94">
         <f>16</f>
         <v>16</v>
       </c>
-      <c r="L94" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="M94" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M94" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="N94" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="C95" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D95" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="E95" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F95" t="s">
-        <v>9</v>
+        <v>436</v>
       </c>
       <c r="G95" t="s">
-        <v>445</v>
+        <v>506</v>
       </c>
       <c r="H95" t="s">
-        <v>39</v>
-      </c>
-      <c r="I95">
+        <v>491</v>
+      </c>
+      <c r="I95" t="s">
+        <v>530</v>
+      </c>
+      <c r="J95">
         <v>2</v>
       </c>
-      <c r="J95" t="s">
-        <v>444</v>
-      </c>
-      <c r="K95">
+      <c r="K95" t="s">
+        <v>435</v>
+      </c>
+      <c r="L95">
         <v>6</v>
       </c>
-      <c r="L95" t="s">
-        <v>47</v>
-      </c>
       <c r="M95" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="N95" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="C96" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D96" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E96" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="F96" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G96" t="s">
-        <v>18</v>
+        <v>439</v>
       </c>
       <c r="H96" t="s">
-        <v>448</v>
-      </c>
-      <c r="I96">
+        <v>495</v>
+      </c>
+      <c r="I96" t="s">
+        <v>439</v>
+      </c>
+      <c r="J96">
         <v>6</v>
       </c>
-      <c r="J96" t="s">
-        <v>447</v>
-      </c>
-      <c r="K96">
+      <c r="K96" t="s">
+        <v>438</v>
+      </c>
+      <c r="L96">
         <f>6*8</f>
         <v>48</v>
       </c>
-      <c r="L96" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="M96" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M96" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="N96" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="C97" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D97" t="s">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="E97" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="F97" t="s">
-        <v>9</v>
+        <v>420</v>
       </c>
       <c r="G97" t="s">
-        <v>429</v>
+        <v>531</v>
       </c>
       <c r="H97" t="s">
-        <v>39</v>
-      </c>
-      <c r="I97">
+        <v>491</v>
+      </c>
+      <c r="I97" t="s">
+        <v>531</v>
+      </c>
+      <c r="J97">
         <v>4</v>
       </c>
-      <c r="J97" t="s">
-        <v>451</v>
-      </c>
-      <c r="K97">
+      <c r="K97" t="s">
+        <v>442</v>
+      </c>
+      <c r="L97">
         <f>4*3</f>
         <v>12</v>
       </c>
-      <c r="L97" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="M97" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M97" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="N97" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="C98" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D98" t="s">
-        <v>98</v>
+        <v>203</v>
       </c>
       <c r="E98" t="s">
-        <v>211</v>
+        <v>9</v>
       </c>
       <c r="F98" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G98" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="H98" t="s">
-        <v>57</v>
-      </c>
-      <c r="I98">
+        <v>495</v>
+      </c>
+      <c r="I98" t="s">
+        <v>108</v>
+      </c>
+      <c r="J98">
         <v>3</v>
       </c>
-      <c r="J98" t="s">
-        <v>453</v>
-      </c>
-      <c r="K98">
+      <c r="K98" t="s">
+        <v>444</v>
+      </c>
+      <c r="L98">
         <f>30</f>
         <v>30</v>
       </c>
-      <c r="L98" s="1" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M98" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="C99" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D99" t="s">
-        <v>98</v>
+        <v>449</v>
       </c>
       <c r="E99" t="s">
-        <v>458</v>
+        <v>9</v>
       </c>
       <c r="F99" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G99" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="H99" t="s">
-        <v>57</v>
-      </c>
-      <c r="I99">
+        <v>495</v>
+      </c>
+      <c r="I99" t="s">
+        <v>108</v>
+      </c>
+      <c r="J99">
         <v>3</v>
       </c>
-      <c r="J99" t="s">
-        <v>456</v>
-      </c>
-      <c r="K99">
+      <c r="K99" t="s">
+        <v>447</v>
+      </c>
+      <c r="L99">
         <f>15</f>
         <v>15</v>
       </c>
-      <c r="L99" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="M99" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M99" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="N99" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="C100" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D100" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="E100" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="F100" t="s">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="G100" t="s">
-        <v>462</v>
+        <v>108</v>
       </c>
       <c r="H100" t="s">
-        <v>115</v>
-      </c>
-      <c r="I100">
+        <v>495</v>
+      </c>
+      <c r="I100" t="s">
+        <v>108</v>
+      </c>
+      <c r="J100">
         <v>3</v>
       </c>
-      <c r="J100" t="s">
-        <v>460</v>
-      </c>
-      <c r="K100">
+      <c r="K100" t="s">
+        <v>451</v>
+      </c>
+      <c r="L100">
         <f>60</f>
         <v>60</v>
       </c>
-      <c r="L100" t="s">
-        <v>47</v>
-      </c>
       <c r="M100" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="N100" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="C101" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D101" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E101" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="F101" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="G101" t="s">
-        <v>18</v>
+        <v>532</v>
       </c>
       <c r="H101" t="s">
-        <v>77</v>
-      </c>
-      <c r="I101">
+        <v>495</v>
+      </c>
+      <c r="I101" t="s">
+        <v>70</v>
+      </c>
+      <c r="J101">
         <v>3</v>
       </c>
-      <c r="J101" t="s">
-        <v>463</v>
-      </c>
-      <c r="K101">
+      <c r="K101" t="s">
+        <v>454</v>
+      </c>
+      <c r="L101">
         <f>3*4</f>
         <v>12</v>
       </c>
-      <c r="L101" s="1" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M101" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B102" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N101" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O101">
+    <sortCondition ref="A2:A101"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="L4" r:id="rId1" display="https://doi.org/10.1016/j.stemcr.2022.04.003" xr:uid="{A58B2C92-8135-4993-80B6-E01F7C4414D7}"/>
-    <hyperlink ref="L2" r:id="rId2" xr:uid="{ECF580C4-849C-4561-A481-5430106E5AFC}"/>
-    <hyperlink ref="L3" r:id="rId3" xr:uid="{56A4D8A2-3CDC-4C94-BF7F-C9AE6847D147}"/>
-    <hyperlink ref="L5" r:id="rId4" location="Sec9" xr:uid="{7F005011-D3D0-40EB-9669-AC279104458C}"/>
-    <hyperlink ref="L6" r:id="rId5" xr:uid="{A191089C-F484-4E45-8BCC-52AA445AD4F5}"/>
-    <hyperlink ref="L8" r:id="rId6" xr:uid="{C5BC7455-0EFA-4A23-B621-721339B38A6F}"/>
-    <hyperlink ref="L9" r:id="rId7" xr:uid="{B7CED74B-1E74-43D2-A36B-EAB3B1E178BC}"/>
-    <hyperlink ref="L10" r:id="rId8" location="sd" xr:uid="{52E8DACA-8996-4096-ACEA-71C8C40EA025}"/>
-    <hyperlink ref="L11" r:id="rId9" xr:uid="{27478232-A532-4DCE-809B-5DD99BA4CE49}"/>
-    <hyperlink ref="L12" r:id="rId10" xr:uid="{50937FCB-E158-45DA-96E3-555511B96735}"/>
-    <hyperlink ref="L13" r:id="rId11" location="Sec11" xr:uid="{EAAEE3D5-FD5F-4C5E-BEDE-E149007B61D7}"/>
-    <hyperlink ref="L14" r:id="rId12" xr:uid="{1466ACE4-040B-4872-B3E7-CB073BC90CE4}"/>
-    <hyperlink ref="L15" r:id="rId13" display="https://doi.org/10.1038/s42255-021-00420-9" xr:uid="{AA76EE2A-3D95-4B26-A3B2-D6961FCAA8B9}"/>
-    <hyperlink ref="L17" r:id="rId14" xr:uid="{73C3C164-1B9E-424D-B497-0A5C1413062E}"/>
-    <hyperlink ref="L18" r:id="rId15" xr:uid="{8E96941A-F27E-446D-BAAB-8817BA69407F}"/>
-    <hyperlink ref="L20" r:id="rId16" xr:uid="{612CAC31-BDF9-4217-882E-04BA9D317851}"/>
-    <hyperlink ref="L42" r:id="rId17" xr:uid="{A0AABACF-D49B-4ADE-969F-34674947E980}"/>
-    <hyperlink ref="L24" r:id="rId18" xr:uid="{45029A78-EC32-4653-B2C0-8A1C6AB739CD}"/>
-    <hyperlink ref="L28" r:id="rId19" xr:uid="{58E39B3E-0FD0-41D5-8918-94CB0DEBE92F}"/>
-    <hyperlink ref="L30" r:id="rId20" xr:uid="{798BD1EC-17B3-4197-8EAE-486722AEADF1}"/>
-    <hyperlink ref="L31" r:id="rId21" xr:uid="{AE40AA44-2798-47B6-B9FB-02DFCD819A98}"/>
-    <hyperlink ref="L21" r:id="rId22" xr:uid="{812AD498-467D-4930-99B1-0BD72991EB74}"/>
-    <hyperlink ref="L32" r:id="rId23" xr:uid="{0A4265F2-3C05-4E25-883C-F8A8F58C6D63}"/>
-    <hyperlink ref="L33" r:id="rId24" xr:uid="{DBE6CDEE-1512-471E-91A3-29DE9DCD40F4}"/>
-    <hyperlink ref="L34" r:id="rId25" xr:uid="{1530F3E7-5FB8-4C45-8815-BC53BEE62E5F}"/>
-    <hyperlink ref="L36" r:id="rId26" xr:uid="{81A03F1A-4A0B-4C2D-947D-86D4D18A30FC}"/>
-    <hyperlink ref="L37" r:id="rId27" xr:uid="{03A7BDDE-DDD3-4CE4-9A6A-3F28026978CD}"/>
-    <hyperlink ref="L38" r:id="rId28" xr:uid="{97D5A0D0-4F73-4447-98D7-176FE36E7E9F}"/>
-    <hyperlink ref="L39" r:id="rId29" xr:uid="{3FDDCA56-CB99-4846-8D3C-3F87979E1526}"/>
-    <hyperlink ref="L40" r:id="rId30" xr:uid="{7859E8C3-2333-43D3-B478-A44FA49BB177}"/>
-    <hyperlink ref="L41" r:id="rId31" xr:uid="{4AAB6572-69BF-4A8C-B9DD-0ECD744015A7}"/>
-    <hyperlink ref="L43" r:id="rId32" xr:uid="{AEFB8F3B-EA1A-47CE-B2E9-52C8FEE30E73}"/>
-    <hyperlink ref="L44" r:id="rId33" xr:uid="{CB2F7DF2-FC97-4B92-86B1-9479DA20F40F}"/>
-    <hyperlink ref="L45" r:id="rId34" xr:uid="{256ADA76-DDF3-43D7-9FF6-3D06B3102F1B}"/>
-    <hyperlink ref="L46" r:id="rId35" xr:uid="{8607D0FC-A3CA-4C2C-B9AF-EA3A5742473F}"/>
-    <hyperlink ref="L47" r:id="rId36" xr:uid="{CC518961-8295-4994-A3DF-84ED80F14808}"/>
-    <hyperlink ref="L48" r:id="rId37" xr:uid="{2FCAA5AF-4D5B-40D6-9710-958A63043040}"/>
-    <hyperlink ref="L49" r:id="rId38" xr:uid="{AE407C0D-97C6-498B-BFB4-71C4936A1365}"/>
-    <hyperlink ref="L50" r:id="rId39" xr:uid="{92FB0A8D-11DB-4567-8F9B-CF523A119E05}"/>
-    <hyperlink ref="L51" r:id="rId40" xr:uid="{207EE6F5-656D-4A38-9817-F2A00ABFCEEE}"/>
-    <hyperlink ref="L53" r:id="rId41" xr:uid="{E3F0AF35-4EFD-4690-93B1-C3CEFB35EC15}"/>
-    <hyperlink ref="L54" r:id="rId42" xr:uid="{7C683447-D985-423F-B5CD-03B9FB95AD65}"/>
-    <hyperlink ref="L55" r:id="rId43" xr:uid="{BDF4E4E0-765A-4F0B-BD68-C69115F0738F}"/>
-    <hyperlink ref="L57" r:id="rId44" xr:uid="{C0FA8537-4468-48BF-A054-0D7291F65AE0}"/>
-    <hyperlink ref="L58" r:id="rId45" xr:uid="{8D999E26-CBDB-4FE4-ADDB-E6B611D67331}"/>
-    <hyperlink ref="L59" r:id="rId46" xr:uid="{7A24ADCF-B6A2-404E-89EC-C398B7118D79}"/>
-    <hyperlink ref="L60" r:id="rId47" xr:uid="{0B450A65-6781-41DE-9BEF-0479DD4B3225}"/>
-    <hyperlink ref="L61" r:id="rId48" xr:uid="{13A1084D-B36D-4396-A3D3-56FA85A81598}"/>
-    <hyperlink ref="L63" r:id="rId49" xr:uid="{815FAA3B-87CE-4626-94FB-28BB0C9DC865}"/>
-    <hyperlink ref="L64" r:id="rId50" xr:uid="{87332800-52F9-415F-88A8-13B3218E1B95}"/>
-    <hyperlink ref="L62" r:id="rId51" xr:uid="{20655D6D-7A5B-4884-972D-A0B324AF2E09}"/>
-    <hyperlink ref="L66" r:id="rId52" xr:uid="{29C9B3AB-C1C5-4CD9-9B61-66EB2F5DB119}"/>
-    <hyperlink ref="L68" r:id="rId53" xr:uid="{A5A57614-CF6E-46F6-B6E8-5F616167FA0D}"/>
-    <hyperlink ref="L69" r:id="rId54" xr:uid="{01DF9558-6F69-4543-A8DD-1581956A8E01}"/>
-    <hyperlink ref="L73" r:id="rId55" xr:uid="{709E7BEA-314C-4B0F-A59A-6BF8CAABD75C}"/>
-    <hyperlink ref="L70" r:id="rId56" xr:uid="{9A7B274C-695B-4B24-B4F1-DD64F89BEC2F}"/>
-    <hyperlink ref="L71" r:id="rId57" xr:uid="{53F78946-D0F1-45CE-80F4-DCEF51325FA5}"/>
-    <hyperlink ref="L72" r:id="rId58" xr:uid="{8853D92F-CF28-4712-9231-7429D3BFBBFB}"/>
-    <hyperlink ref="L74" r:id="rId59" xr:uid="{44AE3EE4-BA3F-4C04-B457-C8BE8762DC83}"/>
-    <hyperlink ref="L75" r:id="rId60" xr:uid="{DB61579F-438D-4DF9-B387-7F2F5EA1AE5D}"/>
-    <hyperlink ref="L76" r:id="rId61" xr:uid="{9C641A84-E07C-4EF1-9FFC-12E3055FF46E}"/>
-    <hyperlink ref="L77" r:id="rId62" xr:uid="{35F7105D-4C78-45B1-8E0C-651E22400B24}"/>
-    <hyperlink ref="L78" r:id="rId63" xr:uid="{76FAEE4C-5466-4FB1-B104-402F652D0F82}"/>
-    <hyperlink ref="L80" r:id="rId64" xr:uid="{B222AC14-18AF-40AE-8D03-B1981FBE28A6}"/>
-    <hyperlink ref="L79" r:id="rId65" xr:uid="{B875AC8B-59AF-4BD2-9A20-40747F088572}"/>
-    <hyperlink ref="L81" r:id="rId66" xr:uid="{612059EE-8652-46E0-8015-99B298BDC96E}"/>
-    <hyperlink ref="L82" r:id="rId67" xr:uid="{2274C7CE-0848-479C-8E48-A92AFCD2DAF3}"/>
-    <hyperlink ref="L83" r:id="rId68" tooltip="Persistent link using digital object identifier" xr:uid="{27BFC4E4-9DCB-4C1D-B672-888C8D8E2732}"/>
-    <hyperlink ref="L84" r:id="rId69" xr:uid="{3593983D-93B4-45AC-8DAA-EEEB7814C6DA}"/>
-    <hyperlink ref="L85" r:id="rId70" xr:uid="{EC9CC085-AE00-427A-8A98-D6B7FAC40915}"/>
-    <hyperlink ref="L86" r:id="rId71" xr:uid="{37B11193-AEED-49A8-8DC8-B8B1A4B50E16}"/>
-    <hyperlink ref="L87" r:id="rId72" xr:uid="{A403A46C-980D-45D5-B1F3-6B41994824E5}"/>
-    <hyperlink ref="L88" r:id="rId73" xr:uid="{15C15D05-2BF6-429B-990B-D4D122B2135A}"/>
-    <hyperlink ref="L89" r:id="rId74" display="https://pubs.acs.org/doi/abs/10.1021/acs.jproteome.6b00211" xr:uid="{C8CA3592-D189-4484-9578-3CE6AA7AAAF0}"/>
-    <hyperlink ref="L90" r:id="rId75" xr:uid="{EA5E6D9D-EB0C-4CD0-A732-5E51418702BE}"/>
-    <hyperlink ref="L91" r:id="rId76" display="https://doi.org/10.1016/j.jbc.2021.100408" xr:uid="{B898DC3E-877C-48D3-B8DB-38527442C91C}"/>
-    <hyperlink ref="L92" r:id="rId77" xr:uid="{E631AF55-B593-4564-AD7B-C50AA064B385}"/>
-    <hyperlink ref="L93" r:id="rId78" xr:uid="{B2B70E0C-93B6-4E11-96C1-A5E9EACBC9AA}"/>
-    <hyperlink ref="L94" r:id="rId79" xr:uid="{9AE33C66-89B4-4F2A-8E68-CFB244668468}"/>
-    <hyperlink ref="L96" r:id="rId80" xr:uid="{DE49CA08-17FF-4C18-8C19-DF135E909D8E}"/>
-    <hyperlink ref="L98" r:id="rId81" xr:uid="{8925AE44-1384-4094-9B9F-CDCD372A1CA9}"/>
-    <hyperlink ref="L97" r:id="rId82" xr:uid="{69516E89-6753-4063-B3E0-FCDA495C291D}"/>
-    <hyperlink ref="L99" r:id="rId83" xr:uid="{58BA4A32-0915-4B17-956C-DBF2AC5940FA}"/>
-    <hyperlink ref="L101" r:id="rId84" xr:uid="{74804044-9702-465A-B0D4-A230294D0CE5}"/>
+    <hyperlink ref="M4" r:id="rId1" display="https://doi.org/10.1016/j.stemcr.2022.04.003" xr:uid="{A58B2C92-8135-4993-80B6-E01F7C4414D7}"/>
+    <hyperlink ref="M2" r:id="rId2" xr:uid="{ECF580C4-849C-4561-A481-5430106E5AFC}"/>
+    <hyperlink ref="M3" r:id="rId3" xr:uid="{56A4D8A2-3CDC-4C94-BF7F-C9AE6847D147}"/>
+    <hyperlink ref="M5" r:id="rId4" location="Sec9" xr:uid="{7F005011-D3D0-40EB-9669-AC279104458C}"/>
+    <hyperlink ref="M6" r:id="rId5" xr:uid="{A191089C-F484-4E45-8BCC-52AA445AD4F5}"/>
+    <hyperlink ref="M8" r:id="rId6" xr:uid="{C5BC7455-0EFA-4A23-B621-721339B38A6F}"/>
+    <hyperlink ref="M9" r:id="rId7" xr:uid="{B7CED74B-1E74-43D2-A36B-EAB3B1E178BC}"/>
+    <hyperlink ref="M10" r:id="rId8" location="sd" xr:uid="{52E8DACA-8996-4096-ACEA-71C8C40EA025}"/>
+    <hyperlink ref="M11" r:id="rId9" xr:uid="{27478232-A532-4DCE-809B-5DD99BA4CE49}"/>
+    <hyperlink ref="M12" r:id="rId10" xr:uid="{50937FCB-E158-45DA-96E3-555511B96735}"/>
+    <hyperlink ref="M13" r:id="rId11" location="Sec11" xr:uid="{EAAEE3D5-FD5F-4C5E-BEDE-E149007B61D7}"/>
+    <hyperlink ref="M14" r:id="rId12" xr:uid="{1466ACE4-040B-4872-B3E7-CB073BC90CE4}"/>
+    <hyperlink ref="M15" r:id="rId13" display="https://doi.org/10.1038/s42255-021-00420-9" xr:uid="{AA76EE2A-3D95-4B26-A3B2-D6961FCAA8B9}"/>
+    <hyperlink ref="M17" r:id="rId14" xr:uid="{73C3C164-1B9E-424D-B497-0A5C1413062E}"/>
+    <hyperlink ref="M18" r:id="rId15" xr:uid="{8E96941A-F27E-446D-BAAB-8817BA69407F}"/>
+    <hyperlink ref="M20" r:id="rId16" xr:uid="{612CAC31-BDF9-4217-882E-04BA9D317851}"/>
+    <hyperlink ref="M42" r:id="rId17" xr:uid="{A0AABACF-D49B-4ADE-969F-34674947E980}"/>
+    <hyperlink ref="M30" r:id="rId18" xr:uid="{798BD1EC-17B3-4197-8EAE-486722AEADF1}"/>
+    <hyperlink ref="M31" r:id="rId19" xr:uid="{AE40AA44-2798-47B6-B9FB-02DFCD819A98}"/>
+    <hyperlink ref="M21" r:id="rId20" xr:uid="{812AD498-467D-4930-99B1-0BD72991EB74}"/>
+    <hyperlink ref="M32" r:id="rId21" xr:uid="{0A4265F2-3C05-4E25-883C-F8A8F58C6D63}"/>
+    <hyperlink ref="M33" r:id="rId22" xr:uid="{DBE6CDEE-1512-471E-91A3-29DE9DCD40F4}"/>
+    <hyperlink ref="M34" r:id="rId23" xr:uid="{1530F3E7-5FB8-4C45-8815-BC53BEE62E5F}"/>
+    <hyperlink ref="M36" r:id="rId24" xr:uid="{81A03F1A-4A0B-4C2D-947D-86D4D18A30FC}"/>
+    <hyperlink ref="M37" r:id="rId25" xr:uid="{03A7BDDE-DDD3-4CE4-9A6A-3F28026978CD}"/>
+    <hyperlink ref="M38" r:id="rId26" xr:uid="{97D5A0D0-4F73-4447-98D7-176FE36E7E9F}"/>
+    <hyperlink ref="M39" r:id="rId27" xr:uid="{3FDDCA56-CB99-4846-8D3C-3F87979E1526}"/>
+    <hyperlink ref="M40" r:id="rId28" xr:uid="{7859E8C3-2333-43D3-B478-A44FA49BB177}"/>
+    <hyperlink ref="M41" r:id="rId29" xr:uid="{4AAB6572-69BF-4A8C-B9DD-0ECD744015A7}"/>
+    <hyperlink ref="M43" r:id="rId30" xr:uid="{AEFB8F3B-EA1A-47CE-B2E9-52C8FEE30E73}"/>
+    <hyperlink ref="M44" r:id="rId31" xr:uid="{CB2F7DF2-FC97-4B92-86B1-9479DA20F40F}"/>
+    <hyperlink ref="M45" r:id="rId32" xr:uid="{256ADA76-DDF3-43D7-9FF6-3D06B3102F1B}"/>
+    <hyperlink ref="M46" r:id="rId33" xr:uid="{8607D0FC-A3CA-4C2C-B9AF-EA3A5742473F}"/>
+    <hyperlink ref="M47" r:id="rId34" xr:uid="{CC518961-8295-4994-A3DF-84ED80F14808}"/>
+    <hyperlink ref="M48" r:id="rId35" xr:uid="{2FCAA5AF-4D5B-40D6-9710-958A63043040}"/>
+    <hyperlink ref="M49" r:id="rId36" xr:uid="{AE407C0D-97C6-498B-BFB4-71C4936A1365}"/>
+    <hyperlink ref="M50" r:id="rId37" xr:uid="{92FB0A8D-11DB-4567-8F9B-CF523A119E05}"/>
+    <hyperlink ref="M51" r:id="rId38" xr:uid="{207EE6F5-656D-4A38-9817-F2A00ABFCEEE}"/>
+    <hyperlink ref="M53" r:id="rId39" xr:uid="{E3F0AF35-4EFD-4690-93B1-C3CEFB35EC15}"/>
+    <hyperlink ref="M54" r:id="rId40" xr:uid="{7C683447-D985-423F-B5CD-03B9FB95AD65}"/>
+    <hyperlink ref="M55" r:id="rId41" xr:uid="{BDF4E4E0-765A-4F0B-BD68-C69115F0738F}"/>
+    <hyperlink ref="M57" r:id="rId42" xr:uid="{C0FA8537-4468-48BF-A054-0D7291F65AE0}"/>
+    <hyperlink ref="M58" r:id="rId43" xr:uid="{8D999E26-CBDB-4FE4-ADDB-E6B611D67331}"/>
+    <hyperlink ref="M59" r:id="rId44" xr:uid="{7A24ADCF-B6A2-404E-89EC-C398B7118D79}"/>
+    <hyperlink ref="M60" r:id="rId45" xr:uid="{0B450A65-6781-41DE-9BEF-0479DD4B3225}"/>
+    <hyperlink ref="M61" r:id="rId46" xr:uid="{13A1084D-B36D-4396-A3D3-56FA85A81598}"/>
+    <hyperlink ref="M63" r:id="rId47" xr:uid="{815FAA3B-87CE-4626-94FB-28BB0C9DC865}"/>
+    <hyperlink ref="M64" r:id="rId48" xr:uid="{87332800-52F9-415F-88A8-13B3218E1B95}"/>
+    <hyperlink ref="M62" r:id="rId49" xr:uid="{20655D6D-7A5B-4884-972D-A0B324AF2E09}"/>
+    <hyperlink ref="M66" r:id="rId50" xr:uid="{29C9B3AB-C1C5-4CD9-9B61-66EB2F5DB119}"/>
+    <hyperlink ref="M68" r:id="rId51" xr:uid="{A5A57614-CF6E-46F6-B6E8-5F616167FA0D}"/>
+    <hyperlink ref="M69" r:id="rId52" xr:uid="{01DF9558-6F69-4543-A8DD-1581956A8E01}"/>
+    <hyperlink ref="M73" r:id="rId53" xr:uid="{709E7BEA-314C-4B0F-A59A-6BF8CAABD75C}"/>
+    <hyperlink ref="M70" r:id="rId54" xr:uid="{9A7B274C-695B-4B24-B4F1-DD64F89BEC2F}"/>
+    <hyperlink ref="M71" r:id="rId55" xr:uid="{53F78946-D0F1-45CE-80F4-DCEF51325FA5}"/>
+    <hyperlink ref="M72" r:id="rId56" xr:uid="{8853D92F-CF28-4712-9231-7429D3BFBBFB}"/>
+    <hyperlink ref="M74" r:id="rId57" xr:uid="{44AE3EE4-BA3F-4C04-B457-C8BE8762DC83}"/>
+    <hyperlink ref="M75" r:id="rId58" xr:uid="{DB61579F-438D-4DF9-B387-7F2F5EA1AE5D}"/>
+    <hyperlink ref="M76" r:id="rId59" xr:uid="{9C641A84-E07C-4EF1-9FFC-12E3055FF46E}"/>
+    <hyperlink ref="M77" r:id="rId60" xr:uid="{35F7105D-4C78-45B1-8E0C-651E22400B24}"/>
+    <hyperlink ref="M78" r:id="rId61" xr:uid="{76FAEE4C-5466-4FB1-B104-402F652D0F82}"/>
+    <hyperlink ref="M80" r:id="rId62" xr:uid="{B222AC14-18AF-40AE-8D03-B1981FBE28A6}"/>
+    <hyperlink ref="M79" r:id="rId63" xr:uid="{B875AC8B-59AF-4BD2-9A20-40747F088572}"/>
+    <hyperlink ref="M81" r:id="rId64" xr:uid="{612059EE-8652-46E0-8015-99B298BDC96E}"/>
+    <hyperlink ref="M82" r:id="rId65" xr:uid="{2274C7CE-0848-479C-8E48-A92AFCD2DAF3}"/>
+    <hyperlink ref="M83" r:id="rId66" tooltip="Persistent link using digital object identifier" xr:uid="{27BFC4E4-9DCB-4C1D-B672-888C8D8E2732}"/>
+    <hyperlink ref="M84" r:id="rId67" xr:uid="{3593983D-93B4-45AC-8DAA-EEEB7814C6DA}"/>
+    <hyperlink ref="M85" r:id="rId68" xr:uid="{EC9CC085-AE00-427A-8A98-D6B7FAC40915}"/>
+    <hyperlink ref="M86" r:id="rId69" xr:uid="{37B11193-AEED-49A8-8DC8-B8B1A4B50E16}"/>
+    <hyperlink ref="M87" r:id="rId70" xr:uid="{A403A46C-980D-45D5-B1F3-6B41994824E5}"/>
+    <hyperlink ref="M88" r:id="rId71" xr:uid="{15C15D05-2BF6-429B-990B-D4D122B2135A}"/>
+    <hyperlink ref="M89" r:id="rId72" display="https://pubs.acs.org/doi/abs/10.1021/acs.jproteome.6b00211" xr:uid="{C8CA3592-D189-4484-9578-3CE6AA7AAAF0}"/>
+    <hyperlink ref="M90" r:id="rId73" xr:uid="{EA5E6D9D-EB0C-4CD0-A732-5E51418702BE}"/>
+    <hyperlink ref="M91" r:id="rId74" display="https://doi.org/10.1016/j.jbc.2021.100408" xr:uid="{B898DC3E-877C-48D3-B8DB-38527442C91C}"/>
+    <hyperlink ref="M92" r:id="rId75" xr:uid="{E631AF55-B593-4564-AD7B-C50AA064B385}"/>
+    <hyperlink ref="M93" r:id="rId76" xr:uid="{B2B70E0C-93B6-4E11-96C1-A5E9EACBC9AA}"/>
+    <hyperlink ref="M94" r:id="rId77" xr:uid="{9AE33C66-89B4-4F2A-8E68-CFB244668468}"/>
+    <hyperlink ref="M96" r:id="rId78" xr:uid="{DE49CA08-17FF-4C18-8C19-DF135E909D8E}"/>
+    <hyperlink ref="M98" r:id="rId79" xr:uid="{8925AE44-1384-4094-9B9F-CDCD372A1CA9}"/>
+    <hyperlink ref="M97" r:id="rId80" xr:uid="{69516E89-6753-4063-B3E0-FCDA495C291D}"/>
+    <hyperlink ref="M99" r:id="rId81" xr:uid="{58BA4A32-0915-4B17-956C-DBF2AC5940FA}"/>
+    <hyperlink ref="M101" r:id="rId82" xr:uid="{74804044-9702-465A-B0D4-A230294D0CE5}"/>
+    <hyperlink ref="M24" r:id="rId83" xr:uid="{DD198BDC-1A91-40C1-AB2A-6CA2254E3A80}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId85"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId84"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2087B5-F5A7-4715-8903-807F8D9032AE}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -6117,10 +6617,10 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
@@ -6138,7 +6638,7 @@
         <v>5</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>6</v>
@@ -6147,62 +6647,146 @@
         <v>13</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="J2">
         <v>7</v>
       </c>
       <c r="K2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L2">
         <v>365</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="N2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>476</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
         <v>92</v>
       </c>
-      <c r="O2" t="s">
-        <v>93</v>
+      <c r="F3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>132</v>
+      </c>
+      <c r="L3">
+        <v>20</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" t="s">
+        <v>124</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>125</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4" t="s">
+        <v>143</v>
+      </c>
+      <c r="L4">
+        <v>9</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" t="s">
+        <v>474</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1" xr:uid="{6B2D74F5-F272-4070-8CE0-D8DD58A4FA2E}"/>
+    <hyperlink ref="M3" r:id="rId2" xr:uid="{F34454E9-13F4-4934-B2C3-5A947F9A8BF5}"/>
+    <hyperlink ref="M4" r:id="rId3" xr:uid="{7AC1F143-25A4-4422-8D04-560DC3661B69}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6221,95 +6805,95 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B2" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B3" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B4" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B6" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="B7" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B8" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="B9" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="B10" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="B11" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="B12" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/goldStandard/_Index.xlsx
+++ b/goldStandard/_Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore\goldStandard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore-development\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96122E0-18C3-4F99-A61D-5ED559F6C78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8182AED-BB90-4B74-8208-B63CE6BE6FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22046" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
+    <workbookView xWindow="28140" yWindow="1065" windowWidth="20685" windowHeight="19155" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
   </bookViews>
   <sheets>
     <sheet name="In" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Possible" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">In!$A$1:$P$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">In!$A$1:$R$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Out!$B$3:$P$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="703">
   <si>
     <t>ID</t>
   </si>
@@ -681,9 +681,6 @@
     <t>PXD054270</t>
   </si>
   <si>
-    <t>RWPE1/KSFM;RWPE1/MEMa;22Rv;LNCaP;PC3"</t>
-  </si>
-  <si>
     <t>DOI: 10.3390/ANTIOX13111340</t>
   </si>
   <si>
@@ -1185,9 +1182,6 @@
     <t>PXD022038</t>
   </si>
   <si>
-    <t>DMSO;OXS008450;OXS008450.OXS008255.1uM;OXS008450.OXS008255.25uM;OXS008450.OXS008255.5uM;OXS008450.Paclitaxel;OXS008483"</t>
-  </si>
-  <si>
     <t>DOI:10.1016/j.isci.2022.104787</t>
   </si>
   <si>
@@ -1630,6 +1624,522 @@
   </si>
   <si>
     <t>Hippocampus</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <t>Edu</t>
+  </si>
+  <si>
+    <t>Nutlin</t>
+  </si>
+  <si>
+    <t>wt</t>
+  </si>
+  <si>
+    <t>WT</t>
+  </si>
+  <si>
+    <t>ND</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>BJAB</t>
+  </si>
+  <si>
+    <t>ARIDA</t>
+  </si>
+  <si>
+    <t>Ctl</t>
+  </si>
+  <si>
+    <t>TRPV2</t>
+  </si>
+  <si>
+    <t>Unfixed</t>
+  </si>
+  <si>
+    <t>Men</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>DMSO</t>
+  </si>
+  <si>
+    <t>ko</t>
+  </si>
+  <si>
+    <t>KO</t>
+  </si>
+  <si>
+    <t>PDR</t>
+  </si>
+  <si>
+    <t>T2D</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>MEC-1</t>
+  </si>
+  <si>
+    <t>IgG</t>
+  </si>
+  <si>
+    <t>LIM</t>
+  </si>
+  <si>
+    <t>Moyamoya</t>
+  </si>
+  <si>
+    <t>24h</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>Hom</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>fixed</t>
+  </si>
+  <si>
+    <t>Women</t>
+  </si>
+  <si>
+    <t>OLD</t>
+  </si>
+  <si>
+    <t>CTR</t>
+  </si>
+  <si>
+    <t>Con</t>
+  </si>
+  <si>
+    <t>0h</t>
+  </si>
+  <si>
+    <t>UW</t>
+  </si>
+  <si>
+    <t>CZ+</t>
+  </si>
+  <si>
+    <t>CTRL</t>
+  </si>
+  <si>
+    <t>siBPGMcontrol</t>
+  </si>
+  <si>
+    <t>CI3_M5</t>
+  </si>
+  <si>
+    <t>WT_No</t>
+  </si>
+  <si>
+    <t>Airway</t>
+  </si>
+  <si>
+    <t>Adult+Sperm</t>
+  </si>
+  <si>
+    <t>VEGFA</t>
+  </si>
+  <si>
+    <t>OSCC</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>WT_CTSB</t>
+  </si>
+  <si>
+    <t>Cntl</t>
+  </si>
+  <si>
+    <t>Responder</t>
+  </si>
+  <si>
+    <t>WT_D0</t>
+  </si>
+  <si>
+    <t>HC</t>
+  </si>
+  <si>
+    <t>ctrl</t>
+  </si>
+  <si>
+    <t>Minus</t>
+  </si>
+  <si>
+    <t>Cancer</t>
+  </si>
+  <si>
+    <t>Sham</t>
+  </si>
+  <si>
+    <t>CTL</t>
+  </si>
+  <si>
+    <t>mockcontrol</t>
+  </si>
+  <si>
+    <t>fl/fl_No</t>
+  </si>
+  <si>
+    <t>CI3_WT</t>
+  </si>
+  <si>
+    <t>IPL</t>
+  </si>
+  <si>
+    <t>AD_CTSB</t>
+  </si>
+  <si>
+    <t>Non-Responder</t>
+  </si>
+  <si>
+    <t>Mutant</t>
+  </si>
+  <si>
+    <t>depressed/SRI</t>
+  </si>
+  <si>
+    <t>SMA</t>
+  </si>
+  <si>
+    <t>LTPP</t>
+  </si>
+  <si>
+    <t>KO_D0</t>
+  </si>
+  <si>
+    <t>Plus</t>
+  </si>
+  <si>
+    <t>SNx</t>
+  </si>
+  <si>
+    <t>Ctrl</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>Sodium butyrate</t>
+  </si>
+  <si>
+    <t>XAV939</t>
+  </si>
+  <si>
+    <t>DMSO_24hr</t>
+  </si>
+  <si>
+    <t>ERCO_24hr</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Mock</t>
+  </si>
+  <si>
+    <t>MDD</t>
+  </si>
+  <si>
+    <t>Untreated</t>
+  </si>
+  <si>
+    <t>Crtl_antiFLAG</t>
+  </si>
+  <si>
+    <t>hangover_FLAG</t>
+  </si>
+  <si>
+    <t>Wild Control</t>
+  </si>
+  <si>
+    <t>SCR</t>
+  </si>
+  <si>
+    <t>acute</t>
+  </si>
+  <si>
+    <t>Severe</t>
+  </si>
+  <si>
+    <t>BrainPhys</t>
+  </si>
+  <si>
+    <t>IDMA</t>
+  </si>
+  <si>
+    <t>sgALAS1</t>
+  </si>
+  <si>
+    <t>recovery</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>SPI1OE</t>
+  </si>
+  <si>
+    <t>Mild</t>
+  </si>
+  <si>
+    <t>DOI: 10.1038/s44161-024-00471-7</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>SPI1KD</t>
+  </si>
+  <si>
+    <t>H_3rdT</t>
+  </si>
+  <si>
+    <t>Myc.M.aMum1</t>
+  </si>
+  <si>
+    <t>Myc.M.aMvc</t>
+  </si>
+  <si>
+    <t>Dex+Spi10</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>EV.VH</t>
+  </si>
+  <si>
+    <t>AR_3rdT</t>
+  </si>
+  <si>
+    <t>R1881</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>RWPE1/KSFM;RWPE1/MEMa;22Rv;LNCaP;PC3</t>
+  </si>
+  <si>
+    <t>PC3</t>
+  </si>
+  <si>
+    <t>22Rv</t>
+  </si>
+  <si>
+    <t>Veh</t>
+  </si>
+  <si>
+    <t>Healthy_F</t>
+  </si>
+  <si>
+    <t>AD_F</t>
+  </si>
+  <si>
+    <t>BPH</t>
+  </si>
+  <si>
+    <t>siPRDX6</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>PCA</t>
+  </si>
+  <si>
+    <t>siNC</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>PD-/LRRK2-</t>
+  </si>
+  <si>
+    <t>PD+/LRRK2+</t>
+  </si>
+  <si>
+    <t>fed_GRKO_Z18</t>
+  </si>
+  <si>
+    <t>fed_GFP_Z18</t>
+  </si>
+  <si>
+    <t>HFD_Veh_Insulin</t>
+  </si>
+  <si>
+    <t>HFD_612_Insulin</t>
+  </si>
+  <si>
+    <t>DOI: 10.3390/ijms27021047</t>
+  </si>
+  <si>
+    <t>FCV_BJ616</t>
+  </si>
+  <si>
+    <t>Duo_WT</t>
+  </si>
+  <si>
+    <t>Duo_KO</t>
+  </si>
+  <si>
+    <t>non-tumor contralateral breast tissues</t>
+  </si>
+  <si>
+    <t>SOG_D15</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>HI</t>
+  </si>
+  <si>
+    <t>GABI</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>M0</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>palbociclib</t>
+  </si>
+  <si>
+    <t>3T3L1_Co</t>
+  </si>
+  <si>
+    <t>HTLV1a</t>
+  </si>
+  <si>
+    <t>primary breast tumor tissues</t>
+  </si>
+  <si>
+    <t>D180_Ctrl</t>
+  </si>
+  <si>
+    <t>D180_1.5mg</t>
+  </si>
+  <si>
+    <t>NACL</t>
+  </si>
+  <si>
+    <t>MI_D15</t>
+  </si>
+  <si>
+    <t>3T3L1_Vas</t>
+  </si>
+  <si>
+    <t>xanthohumol C in DMSO</t>
+  </si>
+  <si>
+    <t>CON</t>
+  </si>
+  <si>
+    <t>Norm</t>
+  </si>
+  <si>
+    <t>Untreated_Ileum</t>
+  </si>
+  <si>
+    <t>Nash</t>
+  </si>
+  <si>
+    <t>DMSO;OXS008450;OXS008450.OXS008255.1uM;OXS008450.OXS008255.25uM;OXS008450.OXS008255.5uM;OXS008450.Paclitaxel;OXS008483</t>
+  </si>
+  <si>
+    <t>OXS008450.Paclitaxel</t>
+  </si>
+  <si>
+    <t>Hsp17_Solubl</t>
+  </si>
+  <si>
+    <t>Hsp17_Insolubl</t>
+  </si>
+  <si>
+    <t>vehicle</t>
+  </si>
+  <si>
+    <t>Treated_Ileum</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>V6</t>
+  </si>
+  <si>
+    <t>CCA</t>
+  </si>
+  <si>
+    <t>KYL</t>
+  </si>
+  <si>
+    <t>whi2</t>
+  </si>
+  <si>
+    <t>PXD076216</t>
+  </si>
+  <si>
+    <t>Cerbrospinal fluid</t>
+  </si>
+  <si>
+    <t>NoPOTS;POTS</t>
+  </si>
+  <si>
+    <t>NoPOTS</t>
+  </si>
+  <si>
+    <t>POTS</t>
+  </si>
+  <si>
+    <t>TSV: sdrf.tsv</t>
+  </si>
+  <si>
+    <t>Conditions assessed in volcanoplot from paper: POTS vs noPOTS. There are also information about severity of encephalomyelitis/chronic fatigue syndrome (three different groups)</t>
+  </si>
+  <si>
+    <t>DOI: 10.1038/s41598-026-46965-1</t>
   </si>
 </sst>
 </file>
@@ -2042,25 +2552,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}">
-  <dimension ref="A1:P102"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" customWidth="1"/>
     <col min="7" max="7" width="27.85546875" customWidth="1"/>
     <col min="8" max="8" width="12.140625" customWidth="1"/>
     <col min="9" max="9" width="27.85546875" customWidth="1"/>
-    <col min="11" max="11" width="24.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="38.28515625" customWidth="1"/>
-    <col min="14" max="14" width="40.7109375" customWidth="1"/>
-    <col min="15" max="15" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="116.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.140625" customWidth="1"/>
+    <col min="15" max="15" width="16.140625" customWidth="1"/>
+    <col min="16" max="16" width="40.7109375" customWidth="1"/>
+    <col min="17" max="17" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="116.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -2080,13 +2594,13 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>36</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>5</v>
@@ -2101,16 +2615,22 @@
         <v>13</v>
       </c>
       <c r="N1" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2130,13 +2650,13 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J2">
         <v>2</v>
@@ -2152,27 +2672,33 @@
         <v>15</v>
       </c>
       <c r="N2" t="s">
+        <v>546</v>
+      </c>
+      <c r="O2" t="s">
+        <v>533</v>
+      </c>
+      <c r="P2" t="s">
         <v>27</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>20</v>
       </c>
-      <c r="P2" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>695</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -2181,32 +2707,40 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>425</v>
+        <v>696</v>
       </c>
       <c r="H3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I3" t="s">
-        <v>492</v>
+        <v>70</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>697</v>
       </c>
       <c r="L3">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="N3" t="s">
+        <v>698</v>
       </c>
       <c r="O3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+      <c r="P3" t="s">
+        <v>700</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2226,10 +2760,10 @@
         <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I4" t="s">
         <v>70</v>
@@ -2238,7 +2772,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L4">
         <f>3*3</f>
@@ -2247,9 +2781,15 @@
       <c r="M4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="1"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N4" t="s">
+        <v>616</v>
+      </c>
+      <c r="O4" t="s">
+        <v>617</v>
+      </c>
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2269,13 +2809,13 @@
         <v>17</v>
       </c>
       <c r="G5" t="s">
+        <v>487</v>
+      </c>
+      <c r="H5" t="s">
         <v>489</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>491</v>
-      </c>
-      <c r="I5" t="s">
-        <v>493</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -2290,11 +2830,17 @@
       <c r="M5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5">
+        <v>6</v>
+      </c>
+      <c r="P5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2314,13 +2860,13 @@
         <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="H6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -2335,13 +2881,19 @@
         <v>38</v>
       </c>
       <c r="N6" t="s">
+        <v>613</v>
+      </c>
+      <c r="O6" t="s">
+        <v>618</v>
+      </c>
+      <c r="P6" t="s">
         <v>39</v>
       </c>
-      <c r="O6" t="s">
+      <c r="Q6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2361,13 +2913,13 @@
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="H7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -2383,13 +2935,19 @@
         <v>44</v>
       </c>
       <c r="N7" t="s">
+        <v>546</v>
+      </c>
+      <c r="O7" t="s">
+        <v>534</v>
+      </c>
+      <c r="P7" t="s">
         <v>45</v>
       </c>
-      <c r="O7" t="s">
+      <c r="Q7" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2409,13 +2967,13 @@
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H8" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I8" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J8">
         <v>2</v>
@@ -2431,11 +2989,17 @@
         <v>49</v>
       </c>
       <c r="N8" t="s">
+        <v>535</v>
+      </c>
+      <c r="O8" t="s">
+        <v>547</v>
+      </c>
+      <c r="P8" t="s">
         <v>50</v>
       </c>
-      <c r="O8" s="4"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q8" s="4"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2458,7 +3022,7 @@
         <v>53</v>
       </c>
       <c r="H9" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I9" t="s">
         <v>108</v>
@@ -2477,13 +3041,19 @@
         <v>55</v>
       </c>
       <c r="N9" t="s">
+        <v>563</v>
+      </c>
+      <c r="O9" t="s">
+        <v>567</v>
+      </c>
+      <c r="P9" t="s">
         <v>50</v>
       </c>
-      <c r="O9" t="s">
+      <c r="Q9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2503,13 +3073,13 @@
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H10" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J10">
         <v>7</v>
@@ -2523,11 +3093,17 @@
       <c r="M10" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="N10" t="s">
+        <v>531</v>
+      </c>
       <c r="O10" t="s">
+        <v>572</v>
+      </c>
+      <c r="Q10" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2550,7 +3126,7 @@
         <v>108</v>
       </c>
       <c r="H11" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I11" t="s">
         <v>108</v>
@@ -2568,10 +3144,16 @@
         <v>63</v>
       </c>
       <c r="N11" t="s">
+        <v>614</v>
+      </c>
+      <c r="O11" t="s">
+        <v>619</v>
+      </c>
+      <c r="P11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2591,10 +3173,10 @@
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H12" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I12" t="s">
         <v>129</v>
@@ -2612,8 +3194,14 @@
       <c r="M12" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N12" t="s">
+        <v>536</v>
+      </c>
+      <c r="O12" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2633,10 +3221,10 @@
         <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H13" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I13" t="s">
         <v>70</v>
@@ -2653,11 +3241,17 @@
       <c r="M13" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="N13" t="s">
+        <v>536</v>
+      </c>
       <c r="O13" t="s">
+        <v>548</v>
+      </c>
+      <c r="Q13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2680,7 +3274,7 @@
         <v>76</v>
       </c>
       <c r="H14" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I14" t="s">
         <v>76</v>
@@ -2698,11 +3292,17 @@
       <c r="M14" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="N14" t="s">
+        <v>568</v>
+      </c>
       <c r="O14" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2725,7 +3325,7 @@
         <v>79</v>
       </c>
       <c r="H15" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I15" t="s">
         <v>79</v>
@@ -2742,11 +3342,17 @@
       <c r="M15" s="1" t="s">
         <v>93</v>
       </c>
+      <c r="N15" t="s">
+        <v>537</v>
+      </c>
       <c r="O15" t="s">
+        <v>550</v>
+      </c>
+      <c r="Q15" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2769,7 +3375,7 @@
         <v>70</v>
       </c>
       <c r="H16" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I16" t="s">
         <v>70</v>
@@ -2786,8 +3392,14 @@
       <c r="M16" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N16" t="s">
+        <v>545</v>
+      </c>
+      <c r="O16" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2807,13 +3419,13 @@
         <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H17" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I17" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J17">
         <v>2</v>
@@ -2827,8 +3439,14 @@
       <c r="M17" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N17" t="s">
+        <v>538</v>
+      </c>
+      <c r="O17" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2851,7 +3469,7 @@
         <v>108</v>
       </c>
       <c r="H18" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I18" t="s">
         <v>108</v>
@@ -2868,11 +3486,17 @@
       <c r="M18" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="P18" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N18" t="s">
+        <v>552</v>
+      </c>
+      <c r="O18" t="s">
+        <v>539</v>
+      </c>
+      <c r="R18" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2892,10 +3516,10 @@
         <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H19" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I19" t="s">
         <v>129</v>
@@ -2913,11 +3537,17 @@
       <c r="M19" t="s">
         <v>44</v>
       </c>
+      <c r="N19" t="s">
+        <v>564</v>
+      </c>
       <c r="O19" t="s">
+        <v>574</v>
+      </c>
+      <c r="Q19" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2937,13 +3567,13 @@
         <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H20" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I20" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J20">
         <v>2</v>
@@ -2957,14 +3587,20 @@
       <c r="M20" s="1" t="s">
         <v>117</v>
       </c>
+      <c r="N20" t="s">
+        <v>540</v>
+      </c>
       <c r="O20" t="s">
+        <v>553</v>
+      </c>
+      <c r="Q20" t="s">
         <v>118</v>
       </c>
-      <c r="P20" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R20" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2984,13 +3620,13 @@
         <v>152</v>
       </c>
       <c r="G21" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H21" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I21" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="J21">
         <v>8</v>
@@ -3005,11 +3641,17 @@
       <c r="M21" s="1" t="s">
         <v>155</v>
       </c>
+      <c r="N21" t="s">
+        <v>536</v>
+      </c>
       <c r="O21" t="s">
+        <v>576</v>
+      </c>
+      <c r="Q21" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3032,7 +3674,7 @@
         <v>125</v>
       </c>
       <c r="H22" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I22" t="s">
         <v>213</v>
@@ -3051,10 +3693,16 @@
         <v>44</v>
       </c>
       <c r="N22" t="s">
+        <v>541</v>
+      </c>
+      <c r="O22" t="s">
+        <v>554</v>
+      </c>
+      <c r="P22" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3074,10 +3722,10 @@
         <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H23" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I23" t="s">
         <v>129</v>
@@ -3092,19 +3740,25 @@
         <f>19*2+16*2+1</f>
         <v>71</v>
       </c>
-      <c r="M23" t="s">
-        <v>44</v>
+      <c r="M23" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="N23" t="s">
+        <v>624</v>
       </c>
       <c r="O23" t="s">
+        <v>620</v>
+      </c>
+      <c r="Q23" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C24" t="s">
         <v>92</v>
@@ -3119,29 +3773,35 @@
         <v>11</v>
       </c>
       <c r="G24" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H24" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I24" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="J24">
         <f>2</f>
         <v>2</v>
       </c>
       <c r="K24" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L24">
         <v>10</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <v>476</v>
+      </c>
+      <c r="N24" t="s">
+        <v>536</v>
+      </c>
+      <c r="O24" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3164,7 +3824,7 @@
         <v>136</v>
       </c>
       <c r="H25" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I25" t="s">
         <v>136</v>
@@ -3181,8 +3841,14 @@
       <c r="M25" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N25" t="s">
+        <v>531</v>
+      </c>
+      <c r="O25" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3205,7 +3871,7 @@
         <v>108</v>
       </c>
       <c r="H26" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I26" t="s">
         <v>108</v>
@@ -3222,8 +3888,14 @@
       <c r="M26" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N26" t="s">
+        <v>531</v>
+      </c>
+      <c r="O26" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3243,10 +3915,10 @@
         <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H27" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I27" t="s">
         <v>70</v>
@@ -3264,13 +3936,19 @@
       <c r="M27" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N27" t="s">
+        <v>627</v>
+      </c>
+      <c r="O27" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C28" t="s">
         <v>92</v>
@@ -3285,28 +3963,34 @@
         <v>17</v>
       </c>
       <c r="G28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H28" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J28">
         <v>4</v>
       </c>
       <c r="K28" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="L28">
         <v>23</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+        <v>479</v>
+      </c>
+      <c r="N28" t="s">
+        <v>569</v>
+      </c>
+      <c r="O28" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3326,13 +4010,13 @@
         <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="H29" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I29" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="J29">
         <v>4</v>
@@ -3347,8 +4031,14 @@
       <c r="M29" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N29" t="s">
+        <v>629</v>
+      </c>
+      <c r="O29" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3368,13 +4058,13 @@
         <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H30" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I30" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J30">
         <v>3</v>
@@ -3389,8 +4079,14 @@
       <c r="M30" s="1" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N30" t="s">
+        <v>565</v>
+      </c>
+      <c r="O30" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3410,13 +4106,13 @@
         <v>152</v>
       </c>
       <c r="G31" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H31" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I31" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="J31">
         <v>4</v>
@@ -3431,8 +4127,14 @@
       <c r="M31" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N31" t="s">
+        <v>589</v>
+      </c>
+      <c r="O31" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3455,7 +4157,7 @@
         <v>160</v>
       </c>
       <c r="H32" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I32" t="s">
         <v>129</v>
@@ -3474,10 +4176,16 @@
         <v>162</v>
       </c>
       <c r="N32" t="s">
+        <v>571</v>
+      </c>
+      <c r="O32" t="s">
+        <v>588</v>
+      </c>
+      <c r="P32" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3497,13 +4205,13 @@
         <v>11</v>
       </c>
       <c r="G33" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H33" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I33" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="J33">
         <f>3</f>
@@ -3519,8 +4227,14 @@
       <c r="M33" s="1" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N33" t="s">
+        <v>536</v>
+      </c>
+      <c r="O33" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3543,10 +4257,10 @@
         <v>169</v>
       </c>
       <c r="H34" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I34" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="J34">
         <v>4</v>
@@ -3561,8 +4275,14 @@
       <c r="M34" s="1" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N34" t="s">
+        <v>536</v>
+      </c>
+      <c r="O34" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3585,10 +4305,10 @@
         <v>173</v>
       </c>
       <c r="H35" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I35" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J35">
         <v>3</v>
@@ -3603,8 +4323,14 @@
       <c r="M35" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N35" t="s">
+        <v>566</v>
+      </c>
+      <c r="O35" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3627,7 +4353,7 @@
         <v>178</v>
       </c>
       <c r="H36" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I36" t="s">
         <v>178</v>
@@ -3645,8 +4371,14 @@
       <c r="M36" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N36" t="s">
+        <v>543</v>
+      </c>
+      <c r="O36" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3666,10 +4398,10 @@
         <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="H37" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I37" t="s">
         <v>129</v>
@@ -3688,13 +4420,19 @@
         <v>184</v>
       </c>
       <c r="N37" t="s">
+        <v>544</v>
+      </c>
+      <c r="O37" t="s">
+        <v>561</v>
+      </c>
+      <c r="P37" t="s">
         <v>182</v>
       </c>
-      <c r="O37" t="s">
+      <c r="Q37" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3714,10 +4452,10 @@
         <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H38" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I38" t="s">
         <v>79</v>
@@ -3735,8 +4473,14 @@
       <c r="M38" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N38" t="s">
+        <v>545</v>
+      </c>
+      <c r="O38" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3759,7 +4503,7 @@
         <v>190</v>
       </c>
       <c r="H39" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I39" t="s">
         <v>70</v>
@@ -3777,8 +4521,14 @@
       <c r="M39" s="1" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N39" t="s">
+        <v>625</v>
+      </c>
+      <c r="O39" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3801,7 +4551,7 @@
         <v>136</v>
       </c>
       <c r="H40" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I40" t="s">
         <v>136</v>
@@ -3820,10 +4570,16 @@
         <v>195</v>
       </c>
       <c r="N40" t="s">
+        <v>628</v>
+      </c>
+      <c r="O40" t="s">
+        <v>634</v>
+      </c>
+      <c r="P40" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3843,10 +4599,10 @@
         <v>17</v>
       </c>
       <c r="G41" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="H41" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I41" t="s">
         <v>70</v>
@@ -3865,13 +4621,19 @@
         <v>199</v>
       </c>
       <c r="N41" t="s">
+        <v>577</v>
+      </c>
+      <c r="O41" t="s">
+        <v>591</v>
+      </c>
+      <c r="P41" t="s">
         <v>200</v>
       </c>
-      <c r="O41" t="s">
+      <c r="Q41" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3891,13 +4653,13 @@
         <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H42" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I42" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J42">
         <v>2</v>
@@ -3912,11 +4674,17 @@
       <c r="M42" s="1" t="s">
         <v>117</v>
       </c>
+      <c r="N42" t="s">
+        <v>578</v>
+      </c>
       <c r="O42" t="s">
+        <v>590</v>
+      </c>
+      <c r="Q42" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3939,7 +4707,7 @@
         <v>108</v>
       </c>
       <c r="H43" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I43" t="s">
         <v>108</v>
@@ -3958,10 +4726,16 @@
         <v>205</v>
       </c>
       <c r="N43" t="s">
+        <v>622</v>
+      </c>
+      <c r="O43" t="s">
+        <v>615</v>
+      </c>
+      <c r="P43" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3984,7 +4758,7 @@
         <v>208</v>
       </c>
       <c r="H44" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I44" t="s">
         <v>213</v>
@@ -4002,10 +4776,16 @@
         <v>210</v>
       </c>
       <c r="N44" t="s">
+        <v>636</v>
+      </c>
+      <c r="O44" t="s">
+        <v>626</v>
+      </c>
+      <c r="P44" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4025,10 +4805,10 @@
         <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="H45" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I45" t="s">
         <v>213</v>
@@ -4046,10 +4826,16 @@
         <v>210</v>
       </c>
       <c r="N45" t="s">
+        <v>636</v>
+      </c>
+      <c r="O45" t="s">
+        <v>626</v>
+      </c>
+      <c r="P45" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4069,37 +4855,43 @@
         <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H46" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I46" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="J46">
         <v>6</v>
       </c>
       <c r="K46" t="s">
-        <v>216</v>
+        <v>637</v>
       </c>
       <c r="L46">
         <f>6*3</f>
         <v>18</v>
       </c>
       <c r="M46" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="N46" t="s">
+        <v>639</v>
+      </c>
+      <c r="O46" t="s">
+        <v>638</v>
+      </c>
+      <c r="P46" t="s">
         <v>217</v>
       </c>
-      <c r="N46" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C47" t="s">
         <v>92</v>
@@ -4114,42 +4906,48 @@
         <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H47" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I47" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J47">
         <v>2</v>
       </c>
       <c r="K47" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L47">
         <v>21</v>
       </c>
       <c r="M47" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="N47" t="s">
+        <v>579</v>
+      </c>
+      <c r="O47" t="s">
+        <v>592</v>
+      </c>
+      <c r="P47" t="s">
         <v>222</v>
       </c>
-      <c r="N47" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C48" t="s">
         <v>92</v>
       </c>
       <c r="D48" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E48" t="s">
         <v>124</v>
@@ -4158,10 +4956,10 @@
         <v>17</v>
       </c>
       <c r="G48" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H48" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I48" t="s">
         <v>108</v>
@@ -4176,15 +4974,21 @@
         <v>8</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+      <c r="N48" t="s">
+        <v>536</v>
+      </c>
+      <c r="O48" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C49" t="s">
         <v>92</v>
@@ -4199,10 +5003,10 @@
         <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H49" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I49" t="s">
         <v>108</v>
@@ -4211,25 +5015,31 @@
         <v>6</v>
       </c>
       <c r="K49" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L49">
         <f>J49*4</f>
         <v>24</v>
       </c>
       <c r="M49" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="N49" t="s">
+        <v>640</v>
+      </c>
+      <c r="O49" t="s">
+        <v>631</v>
+      </c>
+      <c r="P49" t="s">
         <v>230</v>
       </c>
-      <c r="N49" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C50" t="s">
         <v>92</v>
@@ -4244,38 +5054,44 @@
         <v>17</v>
       </c>
       <c r="G50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H50" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J50">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="K50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L50">
         <f>J50*3</f>
         <v>18</v>
       </c>
       <c r="M50" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N50" t="s">
+        <v>580</v>
+      </c>
+      <c r="O50" t="s">
+        <v>597</v>
+      </c>
+      <c r="P50" t="s">
         <v>235</v>
       </c>
-      <c r="N50" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C51" t="s">
         <v>92</v>
@@ -4290,38 +5106,44 @@
         <v>11</v>
       </c>
       <c r="G51" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H51" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I51" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="J51">
         <f>2</f>
         <v>2</v>
       </c>
       <c r="K51" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L51">
         <f>J51*3</f>
         <v>6</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N51" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+        <v>632</v>
+      </c>
+      <c r="O51" t="s">
+        <v>635</v>
+      </c>
+      <c r="P51" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C52" t="s">
         <v>92</v>
@@ -4336,19 +5158,19 @@
         <v>17</v>
       </c>
       <c r="G52" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H52" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I52" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J52">
         <v>2</v>
       </c>
       <c r="K52" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L52">
         <v>6</v>
@@ -4357,15 +5179,21 @@
         <v>44</v>
       </c>
       <c r="N52" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+      <c r="O52" t="s">
+        <v>593</v>
+      </c>
+      <c r="P52" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C53" t="s">
         <v>92</v>
@@ -4374,45 +5202,51 @@
         <v>203</v>
       </c>
       <c r="E53" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F53" t="s">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H53" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I53" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J53">
         <v>3</v>
       </c>
       <c r="K53" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L53">
         <v>69</v>
       </c>
       <c r="M53" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="N53" t="s">
+        <v>531</v>
+      </c>
+      <c r="O53" t="s">
+        <v>594</v>
+      </c>
+      <c r="P53" t="s">
         <v>256</v>
       </c>
-      <c r="N53" t="s">
+      <c r="Q53" t="s">
         <v>257</v>
       </c>
-      <c r="O53" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C54" t="s">
         <v>92</v>
@@ -4427,37 +5261,43 @@
         <v>17</v>
       </c>
       <c r="G54" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H54" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I54" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J54">
         <v>3</v>
       </c>
       <c r="K54" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L54">
         <f>14</f>
         <v>14</v>
       </c>
       <c r="M54" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="N54" t="s">
+        <v>536</v>
+      </c>
+      <c r="O54" t="s">
+        <v>595</v>
+      </c>
+      <c r="P54" t="s">
         <v>262</v>
       </c>
-      <c r="N54" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C55" t="s">
         <v>92</v>
@@ -4466,7 +5306,7 @@
         <v>165</v>
       </c>
       <c r="E55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F55" t="s">
         <v>11</v>
@@ -4475,7 +5315,7 @@
         <v>108</v>
       </c>
       <c r="H55" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I55" t="s">
         <v>108</v>
@@ -4484,25 +5324,31 @@
         <v>4</v>
       </c>
       <c r="K55" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L55">
         <f>32</f>
         <v>32</v>
       </c>
       <c r="M55" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="N55" t="s">
+        <v>641</v>
+      </c>
+      <c r="O55" t="s">
+        <v>642</v>
+      </c>
+      <c r="P55" t="s">
         <v>267</v>
       </c>
-      <c r="N55" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C56" t="s">
         <v>92</v>
@@ -4511,7 +5357,7 @@
         <v>47</v>
       </c>
       <c r="E56" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F56" t="s">
         <v>11</v>
@@ -4520,7 +5366,7 @@
         <v>108</v>
       </c>
       <c r="H56" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I56" t="s">
         <v>108</v>
@@ -4529,25 +5375,31 @@
         <v>2</v>
       </c>
       <c r="K56" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L56">
         <f>27</f>
         <v>27</v>
       </c>
       <c r="M56" t="s">
+        <v>270</v>
+      </c>
+      <c r="N56" t="s">
+        <v>581</v>
+      </c>
+      <c r="O56" t="s">
+        <v>596</v>
+      </c>
+      <c r="P56" t="s">
         <v>271</v>
       </c>
-      <c r="N56" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C57" t="s">
         <v>92</v>
@@ -4556,7 +5408,7 @@
         <v>115</v>
       </c>
       <c r="E57" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F57" t="s">
         <v>11</v>
@@ -4565,34 +5417,40 @@
         <v>173</v>
       </c>
       <c r="H57" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I57" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J57">
         <v>2</v>
       </c>
       <c r="K57" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L57">
         <f>133</f>
         <v>133</v>
       </c>
       <c r="M57" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="N57" t="s">
+        <v>643</v>
+      </c>
+      <c r="O57" t="s">
+        <v>646</v>
+      </c>
+      <c r="Q57" t="s">
         <v>275</v>
       </c>
-      <c r="O57" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C58" t="s">
         <v>92</v>
@@ -4601,16 +5459,16 @@
         <v>47</v>
       </c>
       <c r="E58" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F58" t="s">
         <v>11</v>
       </c>
       <c r="G58" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H58" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I58" t="s">
         <v>108</v>
@@ -4619,24 +5477,30 @@
         <v>2</v>
       </c>
       <c r="K58" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L58">
         <v>10</v>
       </c>
       <c r="M58" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="N58" t="s">
+        <v>536</v>
+      </c>
+      <c r="O58" t="s">
+        <v>548</v>
+      </c>
+      <c r="Q58" t="s">
         <v>279</v>
       </c>
-      <c r="O58" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C59" t="s">
         <v>92</v>
@@ -4645,16 +5509,16 @@
         <v>42</v>
       </c>
       <c r="E59" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F59" t="s">
         <v>11</v>
       </c>
       <c r="G59" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H59" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I59" t="s">
         <v>213</v>
@@ -4663,24 +5527,30 @@
         <v>2</v>
       </c>
       <c r="K59" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L59">
         <v>7</v>
       </c>
       <c r="M59" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="N59" t="s">
+        <v>647</v>
+      </c>
+      <c r="O59" t="s">
+        <v>644</v>
+      </c>
+      <c r="P59" t="s">
         <v>283</v>
       </c>
-      <c r="N59" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C60" t="s">
         <v>92</v>
@@ -4689,7 +5559,7 @@
         <v>28</v>
       </c>
       <c r="E60" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F60" t="s">
         <v>11</v>
@@ -4698,7 +5568,7 @@
         <v>108</v>
       </c>
       <c r="H60" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I60" t="s">
         <v>108</v>
@@ -4707,24 +5577,30 @@
         <v>2</v>
       </c>
       <c r="K60" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L60">
         <v>48</v>
       </c>
       <c r="M60" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="N60" t="s">
+        <v>648</v>
+      </c>
+      <c r="O60" t="s">
+        <v>645</v>
+      </c>
+      <c r="Q60" t="s">
         <v>287</v>
       </c>
-      <c r="O60" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C61" t="s">
         <v>92</v>
@@ -4733,7 +5609,7 @@
         <v>47</v>
       </c>
       <c r="E61" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F61" t="s">
         <v>11</v>
@@ -4742,37 +5618,43 @@
         <v>173</v>
       </c>
       <c r="H61" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I61" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J61">
         <v>4</v>
       </c>
       <c r="K61" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L61">
         <f>63+52</f>
         <v>115</v>
       </c>
       <c r="M61" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="N61" t="s">
+        <v>649</v>
+      </c>
+      <c r="O61" t="s">
+        <v>650</v>
+      </c>
+      <c r="P61" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q61" t="s">
         <v>290</v>
       </c>
-      <c r="N61" t="s">
-        <v>466</v>
-      </c>
-      <c r="O61" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C62" t="s">
         <v>92</v>
@@ -4781,7 +5663,7 @@
         <v>47</v>
       </c>
       <c r="E62" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F62" t="s">
         <v>11</v>
@@ -4790,34 +5672,40 @@
         <v>173</v>
       </c>
       <c r="H62" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I62" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J62">
         <v>4</v>
       </c>
       <c r="K62" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L62">
         <f>120</f>
         <v>120</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N62" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+        <v>649</v>
+      </c>
+      <c r="O62" t="s">
+        <v>650</v>
+      </c>
+      <c r="P62" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C63" t="s">
         <v>92</v>
@@ -4826,42 +5714,48 @@
         <v>42</v>
       </c>
       <c r="E63" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F63" t="s">
         <v>17</v>
       </c>
       <c r="G63" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H63" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I63" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J63">
         <v>6</v>
       </c>
       <c r="K63" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L63">
         <v>36</v>
       </c>
       <c r="M63" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="N63" t="s">
+        <v>652</v>
+      </c>
+      <c r="O63" t="s">
+        <v>651</v>
+      </c>
+      <c r="P63" t="s">
         <v>296</v>
       </c>
-      <c r="N63" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C64" t="s">
         <v>92</v>
@@ -4876,36 +5770,42 @@
         <v>17</v>
       </c>
       <c r="G64" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H64" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I64" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J64">
         <v>5</v>
       </c>
       <c r="K64" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L64">
         <v>35</v>
       </c>
       <c r="M64" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="N64" t="s">
+        <v>653</v>
+      </c>
+      <c r="O64" t="s">
+        <v>654</v>
+      </c>
+      <c r="P64" t="s">
         <v>300</v>
       </c>
-      <c r="N64" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C65" t="s">
         <v>92</v>
@@ -4914,16 +5814,16 @@
         <v>47</v>
       </c>
       <c r="E65" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F65" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G65" t="s">
         <v>53</v>
       </c>
       <c r="H65" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I65" t="s">
         <v>108</v>
@@ -4932,27 +5832,33 @@
         <v>3</v>
       </c>
       <c r="K65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L65">
         <v>9</v>
       </c>
-      <c r="M65" t="s">
-        <v>44</v>
+      <c r="M65" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="N65" t="s">
+        <v>582</v>
       </c>
       <c r="O65" t="s">
-        <v>305</v>
-      </c>
-      <c r="P65" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+        <v>656</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>304</v>
+      </c>
+      <c r="R65" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C66" t="s">
         <v>92</v>
@@ -4961,43 +5867,49 @@
         <v>47</v>
       </c>
       <c r="E66" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F66" t="s">
         <v>17</v>
       </c>
       <c r="G66" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H66" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I66" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J66">
         <v>6</v>
       </c>
       <c r="K66" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L66">
         <f>J66*3</f>
         <v>18</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="P66" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+      <c r="N66" t="s">
+        <v>657</v>
+      </c>
+      <c r="O66" t="s">
+        <v>658</v>
+      </c>
+      <c r="R66" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C67" t="s">
         <v>92</v>
@@ -5006,7 +5918,7 @@
         <v>61</v>
       </c>
       <c r="E67" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F67" t="s">
         <v>17</v>
@@ -5015,7 +5927,7 @@
         <v>70</v>
       </c>
       <c r="H67" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I67" t="s">
         <v>70</v>
@@ -5024,7 +5936,7 @@
         <v>2</v>
       </c>
       <c r="K67" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L67">
         <f>12</f>
@@ -5034,18 +5946,24 @@
         <v>44</v>
       </c>
       <c r="N67" t="s">
-        <v>314</v>
+        <v>531</v>
+      </c>
+      <c r="O67" t="s">
+        <v>548</v>
       </c>
       <c r="P67" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+      <c r="R67" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C68" t="s">
         <v>92</v>
@@ -5057,36 +5975,42 @@
         <v>9</v>
       </c>
       <c r="F68" t="s">
+        <v>315</v>
+      </c>
+      <c r="G68" t="s">
         <v>316</v>
       </c>
-      <c r="G68" t="s">
-        <v>317</v>
-      </c>
       <c r="H68" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I68" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J68">
         <v>2</v>
       </c>
       <c r="K68" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L68">
         <v>12</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+      <c r="N68" t="s">
+        <v>583</v>
+      </c>
+      <c r="O68" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C69" t="s">
         <v>92</v>
@@ -5095,7 +6019,7 @@
         <v>30</v>
       </c>
       <c r="E69" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F69" t="s">
         <v>11</v>
@@ -5104,7 +6028,7 @@
         <v>108</v>
       </c>
       <c r="H69" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I69" t="s">
         <v>108</v>
@@ -5113,40 +6037,46 @@
         <v>2</v>
       </c>
       <c r="K69" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L69">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+      <c r="N69" t="s">
+        <v>531</v>
+      </c>
+      <c r="O69" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C70" t="s">
         <v>92</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E70" t="s">
         <v>124</v>
       </c>
       <c r="F70" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G70" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H70" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I70" t="s">
         <v>108</v>
@@ -5155,42 +6085,48 @@
         <v>2</v>
       </c>
       <c r="K70" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L70">
         <v>10</v>
       </c>
       <c r="M70" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="N70" t="s">
+        <v>585</v>
+      </c>
+      <c r="O70" t="s">
+        <v>599</v>
+      </c>
+      <c r="Q70" t="s">
         <v>334</v>
       </c>
-      <c r="O70" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C71" t="s">
         <v>92</v>
       </c>
       <c r="D71" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E71" t="s">
         <v>124</v>
       </c>
       <c r="F71" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G71" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H71" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I71" t="s">
         <v>70</v>
@@ -5199,25 +6135,31 @@
         <v>5</v>
       </c>
       <c r="K71" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L71">
         <f>J71*4+4</f>
         <v>24</v>
       </c>
       <c r="M71" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="N71" t="s">
+        <v>664</v>
+      </c>
+      <c r="O71" t="s">
+        <v>665</v>
+      </c>
+      <c r="Q71" t="s">
         <v>341</v>
       </c>
-      <c r="O71" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C72" t="s">
         <v>92</v>
@@ -5229,43 +6171,49 @@
         <v>124</v>
       </c>
       <c r="F72" t="s">
+        <v>344</v>
+      </c>
+      <c r="G72" t="s">
         <v>345</v>
       </c>
-      <c r="G72" t="s">
-        <v>346</v>
-      </c>
       <c r="H72" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I72" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J72">
         <v>3</v>
       </c>
       <c r="K72" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L72">
         <f>3*4</f>
         <v>12</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+      <c r="N72" t="s">
+        <v>536</v>
+      </c>
+      <c r="O72" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C73" t="s">
         <v>91</v>
       </c>
       <c r="D73" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E73" t="s">
         <v>9</v>
@@ -5274,36 +6222,42 @@
         <v>11</v>
       </c>
       <c r="G73" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H73" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I73" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J73">
         <v>4</v>
       </c>
       <c r="K73" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L73">
         <v>23</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N73" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+        <v>659</v>
+      </c>
+      <c r="O73" t="s">
+        <v>673</v>
+      </c>
+      <c r="P73" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C74" t="s">
         <v>91</v>
@@ -5315,40 +6269,46 @@
         <v>9</v>
       </c>
       <c r="F74" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G74" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H74" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I74" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J74">
         <v>12</v>
       </c>
       <c r="K74" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L74">
         <f>J74*6</f>
         <v>72</v>
       </c>
       <c r="M74" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="N74" t="s">
+        <v>674</v>
+      </c>
+      <c r="O74" t="s">
+        <v>675</v>
+      </c>
+      <c r="P74" t="s">
         <v>351</v>
       </c>
-      <c r="N74" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C75" t="s">
         <v>91</v>
@@ -5360,13 +6320,13 @@
         <v>9</v>
       </c>
       <c r="F75" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G75" t="s">
         <v>129</v>
       </c>
       <c r="H75" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I75" t="s">
         <v>129</v>
@@ -5375,64 +6335,76 @@
         <v>6</v>
       </c>
       <c r="K75" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L75">
         <f>6*3</f>
         <v>18</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+      <c r="N75" t="s">
+        <v>677</v>
+      </c>
+      <c r="O75" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C76" t="s">
         <v>91</v>
       </c>
       <c r="D76" t="s">
+        <v>356</v>
+      </c>
+      <c r="E76" t="s">
         <v>357</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
+        <v>315</v>
+      </c>
+      <c r="G76" t="s">
         <v>358</v>
       </c>
-      <c r="F76" t="s">
-        <v>316</v>
-      </c>
-      <c r="G76" t="s">
-        <v>359</v>
-      </c>
       <c r="H76" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I76" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J76">
         <v>3</v>
       </c>
       <c r="K76" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L76">
         <f>J76*3</f>
         <v>9</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+      <c r="N76" t="s">
+        <v>541</v>
+      </c>
+      <c r="O76" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C77" t="s">
         <v>91</v>
@@ -5444,38 +6416,44 @@
         <v>9</v>
       </c>
       <c r="F77" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G77" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H77" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I77" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J77">
         <f>3</f>
         <v>3</v>
       </c>
       <c r="K77" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L77">
         <f>J77*3</f>
         <v>9</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+      <c r="N77" t="s">
+        <v>586</v>
+      </c>
+      <c r="O77" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C78" t="s">
         <v>91</v>
@@ -5493,30 +6471,36 @@
         <v>104</v>
       </c>
       <c r="H78" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I78" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J78">
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="L78">
         <v>15</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+      <c r="N78" t="s">
+        <v>667</v>
+      </c>
+      <c r="O78" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C79" t="s">
         <v>91</v>
@@ -5531,34 +6515,40 @@
         <v>17</v>
       </c>
       <c r="G79" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H79" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I79" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J79">
         <v>3</v>
       </c>
       <c r="K79" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L79">
         <f>9</f>
         <v>9</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+      <c r="N79" t="s">
+        <v>668</v>
+      </c>
+      <c r="O79" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C80" t="s">
         <v>91</v>
@@ -5570,37 +6560,43 @@
         <v>9</v>
       </c>
       <c r="F80" t="s">
+        <v>372</v>
+      </c>
+      <c r="G80" t="s">
         <v>373</v>
       </c>
-      <c r="G80" t="s">
-        <v>374</v>
-      </c>
       <c r="H80" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I80" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J80">
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L80">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+      <c r="N80" t="s">
+        <v>669</v>
+      </c>
+      <c r="O80" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C81" t="s">
         <v>91</v>
@@ -5615,33 +6611,39 @@
         <v>11</v>
       </c>
       <c r="G81" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H81" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J81">
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L81">
         <v>6</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+      <c r="N81" t="s">
+        <v>536</v>
+      </c>
+      <c r="O81" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C82" t="s">
         <v>91</v>
@@ -5656,33 +6658,39 @@
         <v>17</v>
       </c>
       <c r="G82" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H82" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I82" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J82">
         <v>3</v>
       </c>
       <c r="K82" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L82">
         <v>9</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+      <c r="N82" t="s">
+        <v>538</v>
+      </c>
+      <c r="O82" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C83" t="s">
         <v>91</v>
@@ -5697,37 +6705,43 @@
         <v>11</v>
       </c>
       <c r="G83" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H83" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I83" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J83">
         <v>7</v>
       </c>
       <c r="K83" t="s">
-        <v>384</v>
+        <v>684</v>
       </c>
       <c r="L83">
         <f>J83*3</f>
         <v>21</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N83" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+        <v>546</v>
+      </c>
+      <c r="O83" t="s">
+        <v>685</v>
+      </c>
+      <c r="P83" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C84" t="s">
         <v>91</v>
@@ -5739,38 +6753,44 @@
         <v>9</v>
       </c>
       <c r="F84" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G84" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="H84" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I84" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J84">
         <f>2</f>
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="L84">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+      <c r="N84" t="s">
+        <v>600</v>
+      </c>
+      <c r="O84" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C85" t="s">
         <v>91</v>
@@ -5785,34 +6805,40 @@
         <v>11</v>
       </c>
       <c r="G85" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H85" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I85" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J85">
         <v>4</v>
       </c>
       <c r="K85" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L85">
         <f>4*J85</f>
         <v>16</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+      <c r="N85" t="s">
+        <v>604</v>
+      </c>
+      <c r="O85" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C86" t="s">
         <v>91</v>
@@ -5824,37 +6850,43 @@
         <v>9</v>
       </c>
       <c r="F86" t="s">
+        <v>372</v>
+      </c>
+      <c r="G86" t="s">
         <v>373</v>
       </c>
-      <c r="G86" t="s">
-        <v>374</v>
-      </c>
       <c r="H86" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I86" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J86">
         <v>8</v>
       </c>
       <c r="K86" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L86">
         <f>8*4</f>
         <v>32</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+      <c r="N86" t="s">
+        <v>686</v>
+      </c>
+      <c r="O86" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C87" t="s">
         <v>91</v>
@@ -5869,37 +6901,43 @@
         <v>11</v>
       </c>
       <c r="G87" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H87" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I87" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="J87">
         <v>4</v>
       </c>
       <c r="K87" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="L87">
         <f>4*4</f>
         <v>16</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="N87" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+        <v>688</v>
+      </c>
+      <c r="O87" t="s">
+        <v>670</v>
+      </c>
+      <c r="P87" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C88" t="s">
         <v>91</v>
@@ -5914,37 +6952,43 @@
         <v>17</v>
       </c>
       <c r="G88" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H88" t="s">
+        <v>489</v>
+      </c>
+      <c r="I88" t="s">
         <v>491</v>
-      </c>
-      <c r="I88" t="s">
-        <v>493</v>
       </c>
       <c r="J88">
         <v>4</v>
       </c>
       <c r="K88" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="L88">
         <f>4*5</f>
         <v>20</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
+      </c>
+      <c r="N88" t="s">
+        <v>671</v>
       </c>
       <c r="O88" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+        <v>678</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C89" t="s">
         <v>91</v>
@@ -5956,40 +7000,46 @@
         <v>9</v>
       </c>
       <c r="F89" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G89" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H89" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I89" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="J89">
         <v>6</v>
       </c>
       <c r="K89" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="L89">
         <f>6*3</f>
         <v>18</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="N89" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+        <v>690</v>
+      </c>
+      <c r="O89" t="s">
+        <v>691</v>
+      </c>
+      <c r="P89" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C90" t="s">
         <v>91</v>
@@ -6004,34 +7054,40 @@
         <v>11</v>
       </c>
       <c r="G90" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H90" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I90" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J90">
         <v>3</v>
       </c>
       <c r="K90" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L90">
         <f>3*4</f>
         <v>12</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+        <v>416</v>
+      </c>
+      <c r="N90" t="s">
+        <v>546</v>
+      </c>
+      <c r="O90" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C91" t="s">
         <v>91</v>
@@ -6043,37 +7099,43 @@
         <v>9</v>
       </c>
       <c r="F91" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G91" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H91" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I91" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J91">
         <v>3</v>
       </c>
       <c r="K91" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="L91">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+        <v>421</v>
+      </c>
+      <c r="N91" t="s">
+        <v>538</v>
+      </c>
+      <c r="O91" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C92" t="s">
         <v>91</v>
@@ -6088,33 +7150,39 @@
         <v>11</v>
       </c>
       <c r="G92" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H92" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I92" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J92">
         <v>3</v>
       </c>
       <c r="K92" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L92">
         <v>13</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+      <c r="N92" t="s">
+        <v>607</v>
+      </c>
+      <c r="O92" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C93" t="s">
         <v>91</v>
@@ -6132,7 +7200,7 @@
         <v>108</v>
       </c>
       <c r="H93" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I93" t="s">
         <v>108</v>
@@ -6141,22 +7209,28 @@
         <v>4</v>
       </c>
       <c r="K93" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L93">
         <f>158</f>
         <v>158</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+        <v>427</v>
+      </c>
+      <c r="N93" t="s">
+        <v>680</v>
+      </c>
+      <c r="O93" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C94" t="s">
         <v>91</v>
@@ -6168,40 +7242,46 @@
         <v>9</v>
       </c>
       <c r="F94" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G94" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H94" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I94" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="J94">
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="L94">
         <f>16</f>
         <v>16</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="N94" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+        <v>538</v>
+      </c>
+      <c r="O94" t="s">
+        <v>601</v>
+      </c>
+      <c r="P94" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C95" t="s">
         <v>91</v>
@@ -6213,22 +7293,22 @@
         <v>9</v>
       </c>
       <c r="F95" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="G95" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="H95" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I95" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="J95">
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L95">
         <v>6</v>
@@ -6237,15 +7317,21 @@
         <v>44</v>
       </c>
       <c r="N95" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+        <v>609</v>
+      </c>
+      <c r="O95" t="s">
+        <v>602</v>
+      </c>
+      <c r="P95" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C96" t="s">
         <v>91</v>
@@ -6260,37 +7346,43 @@
         <v>17</v>
       </c>
       <c r="G96" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H96" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I96" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J96">
         <v>6</v>
       </c>
       <c r="K96" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L96">
         <f>6*8</f>
         <v>48</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="N96" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+        <v>682</v>
+      </c>
+      <c r="O96" t="s">
+        <v>689</v>
+      </c>
+      <c r="P96" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C97" t="s">
         <v>91</v>
@@ -6302,40 +7394,46 @@
         <v>9</v>
       </c>
       <c r="F97" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G97" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H97" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I97" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="J97">
         <v>4</v>
       </c>
       <c r="K97" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="L97">
         <f>4*3</f>
         <v>12</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="N97" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+        <v>610</v>
+      </c>
+      <c r="O97" t="s">
+        <v>611</v>
+      </c>
+      <c r="P97" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C98" t="s">
         <v>91</v>
@@ -6353,7 +7451,7 @@
         <v>53</v>
       </c>
       <c r="H98" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I98" t="s">
         <v>108</v>
@@ -6362,28 +7460,34 @@
         <v>3</v>
       </c>
       <c r="K98" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="L98">
         <f>30</f>
         <v>30</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="N98" t="s">
+        <v>667</v>
+      </c>
+      <c r="O98" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C99" t="s">
         <v>91</v>
       </c>
       <c r="D99" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E99" t="s">
         <v>9</v>
@@ -6395,7 +7499,7 @@
         <v>53</v>
       </c>
       <c r="H99" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I99" t="s">
         <v>108</v>
@@ -6404,25 +7508,31 @@
         <v>3</v>
       </c>
       <c r="K99" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L99">
         <f>15</f>
         <v>15</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N99" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+        <v>681</v>
+      </c>
+      <c r="O99" t="s">
+        <v>683</v>
+      </c>
+      <c r="P99" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C100" t="s">
         <v>91</v>
@@ -6434,13 +7544,13 @@
         <v>52</v>
       </c>
       <c r="F100" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G100" t="s">
         <v>108</v>
       </c>
       <c r="H100" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I100" t="s">
         <v>108</v>
@@ -6449,7 +7559,7 @@
         <v>3</v>
       </c>
       <c r="K100" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="L100">
         <f>60</f>
@@ -6459,15 +7569,21 @@
         <v>44</v>
       </c>
       <c r="N100" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+        <v>612</v>
+      </c>
+      <c r="O100" t="s">
+        <v>532</v>
+      </c>
+      <c r="P100" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C101" t="s">
         <v>91</v>
@@ -6482,10 +7598,10 @@
         <v>17</v>
       </c>
       <c r="G101" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="H101" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I101" t="s">
         <v>70</v>
@@ -6494,119 +7610,127 @@
         <v>3</v>
       </c>
       <c r="K101" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L101">
         <f>3*4</f>
         <v>12</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+        <v>454</v>
+      </c>
+      <c r="N101" t="s">
+        <v>536</v>
+      </c>
+      <c r="O101" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B102" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O101">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q101">
     <sortCondition ref="A2:A101"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="M4" r:id="rId1" display="https://doi.org/10.1016/j.stemcr.2022.04.003" xr:uid="{A58B2C92-8135-4993-80B6-E01F7C4414D7}"/>
     <hyperlink ref="M2" r:id="rId2" xr:uid="{ECF580C4-849C-4561-A481-5430106E5AFC}"/>
-    <hyperlink ref="M3" r:id="rId3" xr:uid="{56A4D8A2-3CDC-4C94-BF7F-C9AE6847D147}"/>
-    <hyperlink ref="M5" r:id="rId4" location="Sec9" xr:uid="{7F005011-D3D0-40EB-9669-AC279104458C}"/>
-    <hyperlink ref="M6" r:id="rId5" xr:uid="{A191089C-F484-4E45-8BCC-52AA445AD4F5}"/>
-    <hyperlink ref="M8" r:id="rId6" xr:uid="{C5BC7455-0EFA-4A23-B621-721339B38A6F}"/>
-    <hyperlink ref="M9" r:id="rId7" xr:uid="{B7CED74B-1E74-43D2-A36B-EAB3B1E178BC}"/>
-    <hyperlink ref="M10" r:id="rId8" location="sd" xr:uid="{52E8DACA-8996-4096-ACEA-71C8C40EA025}"/>
-    <hyperlink ref="M11" r:id="rId9" xr:uid="{27478232-A532-4DCE-809B-5DD99BA4CE49}"/>
-    <hyperlink ref="M12" r:id="rId10" xr:uid="{50937FCB-E158-45DA-96E3-555511B96735}"/>
-    <hyperlink ref="M13" r:id="rId11" location="Sec11" xr:uid="{EAAEE3D5-FD5F-4C5E-BEDE-E149007B61D7}"/>
-    <hyperlink ref="M14" r:id="rId12" xr:uid="{1466ACE4-040B-4872-B3E7-CB073BC90CE4}"/>
-    <hyperlink ref="M15" r:id="rId13" display="https://doi.org/10.1038/s42255-021-00420-9" xr:uid="{AA76EE2A-3D95-4B26-A3B2-D6961FCAA8B9}"/>
-    <hyperlink ref="M17" r:id="rId14" xr:uid="{73C3C164-1B9E-424D-B497-0A5C1413062E}"/>
-    <hyperlink ref="M18" r:id="rId15" xr:uid="{8E96941A-F27E-446D-BAAB-8817BA69407F}"/>
-    <hyperlink ref="M20" r:id="rId16" xr:uid="{612CAC31-BDF9-4217-882E-04BA9D317851}"/>
-    <hyperlink ref="M42" r:id="rId17" xr:uid="{A0AABACF-D49B-4ADE-969F-34674947E980}"/>
-    <hyperlink ref="M30" r:id="rId18" xr:uid="{798BD1EC-17B3-4197-8EAE-486722AEADF1}"/>
-    <hyperlink ref="M31" r:id="rId19" xr:uid="{AE40AA44-2798-47B6-B9FB-02DFCD819A98}"/>
-    <hyperlink ref="M21" r:id="rId20" xr:uid="{812AD498-467D-4930-99B1-0BD72991EB74}"/>
-    <hyperlink ref="M32" r:id="rId21" xr:uid="{0A4265F2-3C05-4E25-883C-F8A8F58C6D63}"/>
-    <hyperlink ref="M33" r:id="rId22" xr:uid="{DBE6CDEE-1512-471E-91A3-29DE9DCD40F4}"/>
-    <hyperlink ref="M34" r:id="rId23" xr:uid="{1530F3E7-5FB8-4C45-8815-BC53BEE62E5F}"/>
-    <hyperlink ref="M36" r:id="rId24" xr:uid="{81A03F1A-4A0B-4C2D-947D-86D4D18A30FC}"/>
-    <hyperlink ref="M37" r:id="rId25" xr:uid="{03A7BDDE-DDD3-4CE4-9A6A-3F28026978CD}"/>
-    <hyperlink ref="M38" r:id="rId26" xr:uid="{97D5A0D0-4F73-4447-98D7-176FE36E7E9F}"/>
-    <hyperlink ref="M39" r:id="rId27" xr:uid="{3FDDCA56-CB99-4846-8D3C-3F87979E1526}"/>
-    <hyperlink ref="M40" r:id="rId28" xr:uid="{7859E8C3-2333-43D3-B478-A44FA49BB177}"/>
-    <hyperlink ref="M41" r:id="rId29" xr:uid="{4AAB6572-69BF-4A8C-B9DD-0ECD744015A7}"/>
-    <hyperlink ref="M43" r:id="rId30" xr:uid="{AEFB8F3B-EA1A-47CE-B2E9-52C8FEE30E73}"/>
-    <hyperlink ref="M44" r:id="rId31" xr:uid="{CB2F7DF2-FC97-4B92-86B1-9479DA20F40F}"/>
-    <hyperlink ref="M45" r:id="rId32" xr:uid="{256ADA76-DDF3-43D7-9FF6-3D06B3102F1B}"/>
-    <hyperlink ref="M46" r:id="rId33" xr:uid="{8607D0FC-A3CA-4C2C-B9AF-EA3A5742473F}"/>
-    <hyperlink ref="M47" r:id="rId34" xr:uid="{CC518961-8295-4994-A3DF-84ED80F14808}"/>
-    <hyperlink ref="M48" r:id="rId35" xr:uid="{2FCAA5AF-4D5B-40D6-9710-958A63043040}"/>
-    <hyperlink ref="M49" r:id="rId36" xr:uid="{AE407C0D-97C6-498B-BFB4-71C4936A1365}"/>
-    <hyperlink ref="M50" r:id="rId37" xr:uid="{92FB0A8D-11DB-4567-8F9B-CF523A119E05}"/>
-    <hyperlink ref="M51" r:id="rId38" xr:uid="{207EE6F5-656D-4A38-9817-F2A00ABFCEEE}"/>
-    <hyperlink ref="M53" r:id="rId39" xr:uid="{E3F0AF35-4EFD-4690-93B1-C3CEFB35EC15}"/>
-    <hyperlink ref="M54" r:id="rId40" xr:uid="{7C683447-D985-423F-B5CD-03B9FB95AD65}"/>
-    <hyperlink ref="M55" r:id="rId41" xr:uid="{BDF4E4E0-765A-4F0B-BD68-C69115F0738F}"/>
-    <hyperlink ref="M57" r:id="rId42" xr:uid="{C0FA8537-4468-48BF-A054-0D7291F65AE0}"/>
-    <hyperlink ref="M58" r:id="rId43" xr:uid="{8D999E26-CBDB-4FE4-ADDB-E6B611D67331}"/>
-    <hyperlink ref="M59" r:id="rId44" xr:uid="{7A24ADCF-B6A2-404E-89EC-C398B7118D79}"/>
-    <hyperlink ref="M60" r:id="rId45" xr:uid="{0B450A65-6781-41DE-9BEF-0479DD4B3225}"/>
-    <hyperlink ref="M61" r:id="rId46" xr:uid="{13A1084D-B36D-4396-A3D3-56FA85A81598}"/>
-    <hyperlink ref="M63" r:id="rId47" xr:uid="{815FAA3B-87CE-4626-94FB-28BB0C9DC865}"/>
-    <hyperlink ref="M64" r:id="rId48" xr:uid="{87332800-52F9-415F-88A8-13B3218E1B95}"/>
-    <hyperlink ref="M62" r:id="rId49" xr:uid="{20655D6D-7A5B-4884-972D-A0B324AF2E09}"/>
-    <hyperlink ref="M66" r:id="rId50" xr:uid="{29C9B3AB-C1C5-4CD9-9B61-66EB2F5DB119}"/>
-    <hyperlink ref="M68" r:id="rId51" xr:uid="{A5A57614-CF6E-46F6-B6E8-5F616167FA0D}"/>
-    <hyperlink ref="M69" r:id="rId52" xr:uid="{01DF9558-6F69-4543-A8DD-1581956A8E01}"/>
-    <hyperlink ref="M73" r:id="rId53" xr:uid="{709E7BEA-314C-4B0F-A59A-6BF8CAABD75C}"/>
-    <hyperlink ref="M70" r:id="rId54" xr:uid="{9A7B274C-695B-4B24-B4F1-DD64F89BEC2F}"/>
-    <hyperlink ref="M71" r:id="rId55" xr:uid="{53F78946-D0F1-45CE-80F4-DCEF51325FA5}"/>
-    <hyperlink ref="M72" r:id="rId56" xr:uid="{8853D92F-CF28-4712-9231-7429D3BFBBFB}"/>
-    <hyperlink ref="M74" r:id="rId57" xr:uid="{44AE3EE4-BA3F-4C04-B457-C8BE8762DC83}"/>
-    <hyperlink ref="M75" r:id="rId58" xr:uid="{DB61579F-438D-4DF9-B387-7F2F5EA1AE5D}"/>
-    <hyperlink ref="M76" r:id="rId59" xr:uid="{9C641A84-E07C-4EF1-9FFC-12E3055FF46E}"/>
-    <hyperlink ref="M77" r:id="rId60" xr:uid="{35F7105D-4C78-45B1-8E0C-651E22400B24}"/>
-    <hyperlink ref="M78" r:id="rId61" xr:uid="{76FAEE4C-5466-4FB1-B104-402F652D0F82}"/>
-    <hyperlink ref="M80" r:id="rId62" xr:uid="{B222AC14-18AF-40AE-8D03-B1981FBE28A6}"/>
-    <hyperlink ref="M79" r:id="rId63" xr:uid="{B875AC8B-59AF-4BD2-9A20-40747F088572}"/>
-    <hyperlink ref="M81" r:id="rId64" xr:uid="{612059EE-8652-46E0-8015-99B298BDC96E}"/>
-    <hyperlink ref="M82" r:id="rId65" xr:uid="{2274C7CE-0848-479C-8E48-A92AFCD2DAF3}"/>
-    <hyperlink ref="M83" r:id="rId66" tooltip="Persistent link using digital object identifier" xr:uid="{27BFC4E4-9DCB-4C1D-B672-888C8D8E2732}"/>
-    <hyperlink ref="M84" r:id="rId67" xr:uid="{3593983D-93B4-45AC-8DAA-EEEB7814C6DA}"/>
-    <hyperlink ref="M85" r:id="rId68" xr:uid="{EC9CC085-AE00-427A-8A98-D6B7FAC40915}"/>
-    <hyperlink ref="M86" r:id="rId69" xr:uid="{37B11193-AEED-49A8-8DC8-B8B1A4B50E16}"/>
-    <hyperlink ref="M87" r:id="rId70" xr:uid="{A403A46C-980D-45D5-B1F3-6B41994824E5}"/>
-    <hyperlink ref="M88" r:id="rId71" xr:uid="{15C15D05-2BF6-429B-990B-D4D122B2135A}"/>
-    <hyperlink ref="M89" r:id="rId72" display="https://pubs.acs.org/doi/abs/10.1021/acs.jproteome.6b00211" xr:uid="{C8CA3592-D189-4484-9578-3CE6AA7AAAF0}"/>
-    <hyperlink ref="M90" r:id="rId73" xr:uid="{EA5E6D9D-EB0C-4CD0-A732-5E51418702BE}"/>
-    <hyperlink ref="M91" r:id="rId74" display="https://doi.org/10.1016/j.jbc.2021.100408" xr:uid="{B898DC3E-877C-48D3-B8DB-38527442C91C}"/>
-    <hyperlink ref="M92" r:id="rId75" xr:uid="{E631AF55-B593-4564-AD7B-C50AA064B385}"/>
-    <hyperlink ref="M93" r:id="rId76" xr:uid="{B2B70E0C-93B6-4E11-96C1-A5E9EACBC9AA}"/>
-    <hyperlink ref="M94" r:id="rId77" xr:uid="{9AE33C66-89B4-4F2A-8E68-CFB244668468}"/>
-    <hyperlink ref="M96" r:id="rId78" xr:uid="{DE49CA08-17FF-4C18-8C19-DF135E909D8E}"/>
-    <hyperlink ref="M98" r:id="rId79" xr:uid="{8925AE44-1384-4094-9B9F-CDCD372A1CA9}"/>
-    <hyperlink ref="M97" r:id="rId80" xr:uid="{69516E89-6753-4063-B3E0-FCDA495C291D}"/>
-    <hyperlink ref="M99" r:id="rId81" xr:uid="{58BA4A32-0915-4B17-956C-DBF2AC5940FA}"/>
-    <hyperlink ref="M101" r:id="rId82" xr:uid="{74804044-9702-465A-B0D4-A230294D0CE5}"/>
-    <hyperlink ref="M24" r:id="rId83" xr:uid="{DD198BDC-1A91-40C1-AB2A-6CA2254E3A80}"/>
+    <hyperlink ref="M5" r:id="rId3" location="Sec9" xr:uid="{7F005011-D3D0-40EB-9669-AC279104458C}"/>
+    <hyperlink ref="M6" r:id="rId4" xr:uid="{A191089C-F484-4E45-8BCC-52AA445AD4F5}"/>
+    <hyperlink ref="M8" r:id="rId5" xr:uid="{C5BC7455-0EFA-4A23-B621-721339B38A6F}"/>
+    <hyperlink ref="M9" r:id="rId6" xr:uid="{B7CED74B-1E74-43D2-A36B-EAB3B1E178BC}"/>
+    <hyperlink ref="M10" r:id="rId7" location="sd" xr:uid="{52E8DACA-8996-4096-ACEA-71C8C40EA025}"/>
+    <hyperlink ref="M11" r:id="rId8" xr:uid="{27478232-A532-4DCE-809B-5DD99BA4CE49}"/>
+    <hyperlink ref="M12" r:id="rId9" xr:uid="{50937FCB-E158-45DA-96E3-555511B96735}"/>
+    <hyperlink ref="M13" r:id="rId10" location="Sec11" xr:uid="{EAAEE3D5-FD5F-4C5E-BEDE-E149007B61D7}"/>
+    <hyperlink ref="M14" r:id="rId11" xr:uid="{1466ACE4-040B-4872-B3E7-CB073BC90CE4}"/>
+    <hyperlink ref="M15" r:id="rId12" display="https://doi.org/10.1038/s42255-021-00420-9" xr:uid="{AA76EE2A-3D95-4B26-A3B2-D6961FCAA8B9}"/>
+    <hyperlink ref="M17" r:id="rId13" xr:uid="{73C3C164-1B9E-424D-B497-0A5C1413062E}"/>
+    <hyperlink ref="M18" r:id="rId14" xr:uid="{8E96941A-F27E-446D-BAAB-8817BA69407F}"/>
+    <hyperlink ref="M20" r:id="rId15" xr:uid="{612CAC31-BDF9-4217-882E-04BA9D317851}"/>
+    <hyperlink ref="M42" r:id="rId16" xr:uid="{A0AABACF-D49B-4ADE-969F-34674947E980}"/>
+    <hyperlink ref="M30" r:id="rId17" xr:uid="{798BD1EC-17B3-4197-8EAE-486722AEADF1}"/>
+    <hyperlink ref="M31" r:id="rId18" xr:uid="{AE40AA44-2798-47B6-B9FB-02DFCD819A98}"/>
+    <hyperlink ref="M21" r:id="rId19" xr:uid="{812AD498-467D-4930-99B1-0BD72991EB74}"/>
+    <hyperlink ref="M32" r:id="rId20" xr:uid="{0A4265F2-3C05-4E25-883C-F8A8F58C6D63}"/>
+    <hyperlink ref="M33" r:id="rId21" xr:uid="{DBE6CDEE-1512-471E-91A3-29DE9DCD40F4}"/>
+    <hyperlink ref="M34" r:id="rId22" xr:uid="{1530F3E7-5FB8-4C45-8815-BC53BEE62E5F}"/>
+    <hyperlink ref="M36" r:id="rId23" xr:uid="{81A03F1A-4A0B-4C2D-947D-86D4D18A30FC}"/>
+    <hyperlink ref="M37" r:id="rId24" xr:uid="{03A7BDDE-DDD3-4CE4-9A6A-3F28026978CD}"/>
+    <hyperlink ref="M38" r:id="rId25" xr:uid="{97D5A0D0-4F73-4447-98D7-176FE36E7E9F}"/>
+    <hyperlink ref="M39" r:id="rId26" xr:uid="{3FDDCA56-CB99-4846-8D3C-3F87979E1526}"/>
+    <hyperlink ref="M40" r:id="rId27" xr:uid="{7859E8C3-2333-43D3-B478-A44FA49BB177}"/>
+    <hyperlink ref="M41" r:id="rId28" xr:uid="{4AAB6572-69BF-4A8C-B9DD-0ECD744015A7}"/>
+    <hyperlink ref="M43" r:id="rId29" xr:uid="{AEFB8F3B-EA1A-47CE-B2E9-52C8FEE30E73}"/>
+    <hyperlink ref="M44" r:id="rId30" xr:uid="{CB2F7DF2-FC97-4B92-86B1-9479DA20F40F}"/>
+    <hyperlink ref="M45" r:id="rId31" xr:uid="{256ADA76-DDF3-43D7-9FF6-3D06B3102F1B}"/>
+    <hyperlink ref="M46" r:id="rId32" xr:uid="{8607D0FC-A3CA-4C2C-B9AF-EA3A5742473F}"/>
+    <hyperlink ref="M47" r:id="rId33" xr:uid="{CC518961-8295-4994-A3DF-84ED80F14808}"/>
+    <hyperlink ref="M48" r:id="rId34" xr:uid="{2FCAA5AF-4D5B-40D6-9710-958A63043040}"/>
+    <hyperlink ref="M49" r:id="rId35" xr:uid="{AE407C0D-97C6-498B-BFB4-71C4936A1365}"/>
+    <hyperlink ref="M50" r:id="rId36" xr:uid="{92FB0A8D-11DB-4567-8F9B-CF523A119E05}"/>
+    <hyperlink ref="M51" r:id="rId37" xr:uid="{207EE6F5-656D-4A38-9817-F2A00ABFCEEE}"/>
+    <hyperlink ref="M53" r:id="rId38" xr:uid="{E3F0AF35-4EFD-4690-93B1-C3CEFB35EC15}"/>
+    <hyperlink ref="M54" r:id="rId39" xr:uid="{7C683447-D985-423F-B5CD-03B9FB95AD65}"/>
+    <hyperlink ref="M55" r:id="rId40" xr:uid="{BDF4E4E0-765A-4F0B-BD68-C69115F0738F}"/>
+    <hyperlink ref="M57" r:id="rId41" xr:uid="{C0FA8537-4468-48BF-A054-0D7291F65AE0}"/>
+    <hyperlink ref="M58" r:id="rId42" xr:uid="{8D999E26-CBDB-4FE4-ADDB-E6B611D67331}"/>
+    <hyperlink ref="M59" r:id="rId43" xr:uid="{7A24ADCF-B6A2-404E-89EC-C398B7118D79}"/>
+    <hyperlink ref="M60" r:id="rId44" xr:uid="{0B450A65-6781-41DE-9BEF-0479DD4B3225}"/>
+    <hyperlink ref="M61" r:id="rId45" xr:uid="{13A1084D-B36D-4396-A3D3-56FA85A81598}"/>
+    <hyperlink ref="M63" r:id="rId46" xr:uid="{815FAA3B-87CE-4626-94FB-28BB0C9DC865}"/>
+    <hyperlink ref="M64" r:id="rId47" xr:uid="{87332800-52F9-415F-88A8-13B3218E1B95}"/>
+    <hyperlink ref="M62" r:id="rId48" xr:uid="{20655D6D-7A5B-4884-972D-A0B324AF2E09}"/>
+    <hyperlink ref="M66" r:id="rId49" xr:uid="{29C9B3AB-C1C5-4CD9-9B61-66EB2F5DB119}"/>
+    <hyperlink ref="M68" r:id="rId50" xr:uid="{A5A57614-CF6E-46F6-B6E8-5F616167FA0D}"/>
+    <hyperlink ref="M69" r:id="rId51" xr:uid="{01DF9558-6F69-4543-A8DD-1581956A8E01}"/>
+    <hyperlink ref="M73" r:id="rId52" xr:uid="{709E7BEA-314C-4B0F-A59A-6BF8CAABD75C}"/>
+    <hyperlink ref="M70" r:id="rId53" xr:uid="{9A7B274C-695B-4B24-B4F1-DD64F89BEC2F}"/>
+    <hyperlink ref="M71" r:id="rId54" xr:uid="{53F78946-D0F1-45CE-80F4-DCEF51325FA5}"/>
+    <hyperlink ref="M72" r:id="rId55" xr:uid="{8853D92F-CF28-4712-9231-7429D3BFBBFB}"/>
+    <hyperlink ref="M74" r:id="rId56" xr:uid="{44AE3EE4-BA3F-4C04-B457-C8BE8762DC83}"/>
+    <hyperlink ref="M75" r:id="rId57" xr:uid="{DB61579F-438D-4DF9-B387-7F2F5EA1AE5D}"/>
+    <hyperlink ref="M76" r:id="rId58" xr:uid="{9C641A84-E07C-4EF1-9FFC-12E3055FF46E}"/>
+    <hyperlink ref="M77" r:id="rId59" xr:uid="{35F7105D-4C78-45B1-8E0C-651E22400B24}"/>
+    <hyperlink ref="M78" r:id="rId60" xr:uid="{76FAEE4C-5466-4FB1-B104-402F652D0F82}"/>
+    <hyperlink ref="M80" r:id="rId61" xr:uid="{B222AC14-18AF-40AE-8D03-B1981FBE28A6}"/>
+    <hyperlink ref="M79" r:id="rId62" xr:uid="{B875AC8B-59AF-4BD2-9A20-40747F088572}"/>
+    <hyperlink ref="M81" r:id="rId63" xr:uid="{612059EE-8652-46E0-8015-99B298BDC96E}"/>
+    <hyperlink ref="M82" r:id="rId64" xr:uid="{2274C7CE-0848-479C-8E48-A92AFCD2DAF3}"/>
+    <hyperlink ref="M83" r:id="rId65" tooltip="Persistent link using digital object identifier" xr:uid="{27BFC4E4-9DCB-4C1D-B672-888C8D8E2732}"/>
+    <hyperlink ref="M84" r:id="rId66" xr:uid="{3593983D-93B4-45AC-8DAA-EEEB7814C6DA}"/>
+    <hyperlink ref="M85" r:id="rId67" xr:uid="{EC9CC085-AE00-427A-8A98-D6B7FAC40915}"/>
+    <hyperlink ref="M86" r:id="rId68" xr:uid="{37B11193-AEED-49A8-8DC8-B8B1A4B50E16}"/>
+    <hyperlink ref="M87" r:id="rId69" xr:uid="{A403A46C-980D-45D5-B1F3-6B41994824E5}"/>
+    <hyperlink ref="M88" r:id="rId70" xr:uid="{15C15D05-2BF6-429B-990B-D4D122B2135A}"/>
+    <hyperlink ref="M89" r:id="rId71" display="https://pubs.acs.org/doi/abs/10.1021/acs.jproteome.6b00211" xr:uid="{C8CA3592-D189-4484-9578-3CE6AA7AAAF0}"/>
+    <hyperlink ref="M90" r:id="rId72" xr:uid="{EA5E6D9D-EB0C-4CD0-A732-5E51418702BE}"/>
+    <hyperlink ref="M91" r:id="rId73" display="https://doi.org/10.1016/j.jbc.2021.100408" xr:uid="{B898DC3E-877C-48D3-B8DB-38527442C91C}"/>
+    <hyperlink ref="M92" r:id="rId74" xr:uid="{E631AF55-B593-4564-AD7B-C50AA064B385}"/>
+    <hyperlink ref="M93" r:id="rId75" xr:uid="{B2B70E0C-93B6-4E11-96C1-A5E9EACBC9AA}"/>
+    <hyperlink ref="M94" r:id="rId76" xr:uid="{9AE33C66-89B4-4F2A-8E68-CFB244668468}"/>
+    <hyperlink ref="M96" r:id="rId77" xr:uid="{DE49CA08-17FF-4C18-8C19-DF135E909D8E}"/>
+    <hyperlink ref="M98" r:id="rId78" xr:uid="{8925AE44-1384-4094-9B9F-CDCD372A1CA9}"/>
+    <hyperlink ref="M97" r:id="rId79" xr:uid="{69516E89-6753-4063-B3E0-FCDA495C291D}"/>
+    <hyperlink ref="M99" r:id="rId80" xr:uid="{58BA4A32-0915-4B17-956C-DBF2AC5940FA}"/>
+    <hyperlink ref="M101" r:id="rId81" xr:uid="{74804044-9702-465A-B0D4-A230294D0CE5}"/>
+    <hyperlink ref="M24" r:id="rId82" xr:uid="{DD198BDC-1A91-40C1-AB2A-6CA2254E3A80}"/>
+    <hyperlink ref="M23" r:id="rId83" xr:uid="{54EC2941-3A77-498F-9485-52BE0EAB6EE8}"/>
+    <hyperlink ref="M65" r:id="rId84" xr:uid="{2C672FCE-1691-4A02-BDA5-38F14F68F9A1}"/>
+    <hyperlink ref="M3" r:id="rId85" xr:uid="{A52741AB-5A3F-448A-85EE-A088C3461BE0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId84"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId86"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2087B5-F5A7-4715-8903-807F8D9032AE}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -6653,7 +7777,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>15</v>
       </c>
@@ -6700,12 +7824,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -6738,10 +7862,10 @@
         <v>133</v>
       </c>
       <c r="P3" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>27</v>
       </c>
@@ -6779,7 +7903,52 @@
         <v>144</v>
       </c>
       <c r="P4" t="s">
-        <v>474</v>
+        <v>472</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>423</v>
+      </c>
+      <c r="I5" t="s">
+        <v>489</v>
+      </c>
+      <c r="J5" t="s">
+        <v>490</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5">
+        <f>4*5</f>
+        <v>20</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R5" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -6787,6 +7956,7 @@
     <hyperlink ref="M2" r:id="rId1" xr:uid="{6B2D74F5-F272-4070-8CE0-D8DD58A4FA2E}"/>
     <hyperlink ref="M3" r:id="rId2" xr:uid="{F34454E9-13F4-4934-B2C3-5A947F9A8BF5}"/>
     <hyperlink ref="M4" r:id="rId3" xr:uid="{7AC1F143-25A4-4422-8D04-560DC3661B69}"/>
+    <hyperlink ref="N5" r:id="rId4" xr:uid="{7D228E1D-80DD-4B5E-A885-5940F2BD3467}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6805,95 +7975,95 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" t="s">
         <v>243</v>
-      </c>
-      <c r="B2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B3" t="s">
         <v>246</v>
-      </c>
-      <c r="B3" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B4" t="s">
         <v>248</v>
-      </c>
-      <c r="B4" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B5" t="s">
         <v>250</v>
-      </c>
-      <c r="B5" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B9" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B10" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B11" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B12" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>

--- a/goldStandard/_Index.xlsx
+++ b/goldStandard/_Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore-development\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8182AED-BB90-4B74-8208-B63CE6BE6FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A420EF3-2D76-4FDC-BB6A-9CBA71D7F8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28140" yWindow="1065" windowWidth="20685" windowHeight="19155" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
+    <workbookView xWindow="-22046" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
   </bookViews>
   <sheets>
     <sheet name="In" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="714">
   <si>
     <t>ID</t>
   </si>
@@ -105,9 +105,6 @@
     <t>(gap);L;M;H</t>
   </si>
   <si>
-    <t>Edu;DMSO</t>
-  </si>
-  <si>
     <t>More docs</t>
   </si>
   <si>
@@ -126,9 +123,6 @@
     <t>Orbitrap Fusion</t>
   </si>
   <si>
-    <t>1;2;3;4;5;6</t>
-  </si>
-  <si>
     <t>XLSX: Supplementary table (sheet sf6g)</t>
   </si>
   <si>
@@ -144,9 +138,6 @@
     <t>Cell culture</t>
   </si>
   <si>
-    <t>SCR;sgALAS1</t>
-  </si>
-  <si>
     <t>DOI: 10.1016/J.CELL.2025.10.028</t>
   </si>
   <si>
@@ -162,9 +153,6 @@
     <t>Orbitrap Exploris 480</t>
   </si>
   <si>
-    <t>Nutlin;DMSO</t>
-  </si>
-  <si>
     <t>Pending</t>
   </si>
   <si>
@@ -264,18 +252,12 @@
     <t>Tear</t>
   </si>
   <si>
-    <t>CTRL;T2D;NPDR;PDR</t>
-  </si>
-  <si>
     <t>PXD022561</t>
   </si>
   <si>
     <t>Pancreas</t>
   </si>
   <si>
-    <t>ND;T2D</t>
-  </si>
-  <si>
     <t>PXD064699</t>
   </si>
   <si>
@@ -330,27 +312,18 @@
     <t>Quedan poucas proteínas e teñen formas raras nas gráficas de evaluación… mais que raras, sin forma. Quizás hai que eliminar</t>
   </si>
   <si>
-    <t>Control;IPF X Alveoli;Airway;</t>
-  </si>
-  <si>
     <t>PXD022614</t>
   </si>
   <si>
     <t>LTQ Orbitrap;Q Exactive</t>
   </si>
   <si>
-    <t>Adult;Adult+Sperm;Young</t>
-  </si>
-  <si>
     <t>PXD019504</t>
   </si>
   <si>
     <t>Colon</t>
   </si>
   <si>
-    <t>C;T</t>
-  </si>
-  <si>
     <t>DOI: 10.18632/oncotarget.27491</t>
   </si>
   <si>
@@ -360,9 +333,6 @@
     <t>Blood</t>
   </si>
   <si>
-    <t>BJAB;MEC-1</t>
-  </si>
-  <si>
     <t>DOI: 10.1016/J.JBC.2025.108386</t>
   </si>
   <si>
@@ -381,9 +351,6 @@
     <t>Q Exactive</t>
   </si>
   <si>
-    <t>ARIDA;IgG</t>
-  </si>
-  <si>
     <t>DOI: 10.1002/1878-0261.70019</t>
   </si>
   <si>
@@ -393,9 +360,6 @@
     <t>Experiment 2</t>
   </si>
   <si>
-    <t>Cntl;IPL</t>
-  </si>
-  <si>
     <t>PXD054817.2</t>
   </si>
   <si>
@@ -411,9 +375,6 @@
     <t>Retina</t>
   </si>
   <si>
-    <t>Ctl;LIM</t>
-  </si>
-  <si>
     <t>TSV: sample info PXD046983.sdrf.tsv</t>
   </si>
   <si>
@@ -450,9 +411,6 @@
     <t>PXD063236</t>
   </si>
   <si>
-    <t>Control;Moyamoya</t>
-  </si>
-  <si>
     <t>PXD063383</t>
   </si>
   <si>
@@ -561,9 +519,6 @@
     <t>PXD064948</t>
   </si>
   <si>
-    <t>Unfixed;fixed</t>
-  </si>
-  <si>
     <t>DOI: 10.1016/j.ocarto.2025.100664</t>
   </si>
   <si>
@@ -576,9 +531,6 @@
     <t>PXD051201</t>
   </si>
   <si>
-    <t>Men;Women</t>
-  </si>
-  <si>
     <t>TXT: PXD051201_DM.xlsx</t>
   </si>
   <si>
@@ -591,9 +543,6 @@
     <t>PXD068597</t>
   </si>
   <si>
-    <t>Young;OLD</t>
-  </si>
-  <si>
     <t>DOI: 10.1158/0008-5472.can-25-1904</t>
   </si>
   <si>
@@ -795,9 +744,6 @@
     <t>Placenta</t>
   </si>
   <si>
-    <t>Control;depressed/no SRI;depressed/SRI</t>
-  </si>
-  <si>
     <t>DOI: 10.1371/journal.pone.0322090</t>
   </si>
   <si>
@@ -852,9 +798,6 @@
     <t>PXD035942</t>
   </si>
   <si>
-    <t>PCA;BPH</t>
-  </si>
-  <si>
     <t>DOI: 10.1021/acsomega.2c05487</t>
   </si>
   <si>
@@ -969,9 +912,6 @@
     <t>PXD052118</t>
   </si>
   <si>
-    <t>Control;KO</t>
-  </si>
-  <si>
     <t>XLSX: Samples_conditions_files.xlsx</t>
   </si>
   <si>
@@ -984,9 +924,6 @@
     <t>MCY1441, MCY1444 strains</t>
   </si>
   <si>
-    <t>Minus;Plus</t>
-  </si>
-  <si>
     <t>DOI: 10.1093/nar/gkae1321</t>
   </si>
   <si>
@@ -996,9 +933,6 @@
     <t>Skyline</t>
   </si>
   <si>
-    <t>Cancer;Control</t>
-  </si>
-  <si>
     <t>DOI:10.1039/d4mo00112e</t>
   </si>
   <si>
@@ -1389,9 +1323,6 @@
     <t>Enhydra lutris nereis</t>
   </si>
   <si>
-    <t>APP;KYL;WT</t>
-  </si>
-  <si>
     <t>PXD056771</t>
   </si>
   <si>
@@ -1632,30 +1563,18 @@
     <t>Case</t>
   </si>
   <si>
-    <t>Edu</t>
-  </si>
-  <si>
-    <t>Nutlin</t>
-  </si>
-  <si>
     <t>wt</t>
   </si>
   <si>
     <t>WT</t>
   </si>
   <si>
-    <t>ND</t>
-  </si>
-  <si>
     <t>C</t>
   </si>
   <si>
     <t>BJAB</t>
   </si>
   <si>
-    <t>ARIDA</t>
-  </si>
-  <si>
     <t>Ctl</t>
   </si>
   <si>
@@ -1665,9 +1584,6 @@
     <t>Unfixed</t>
   </si>
   <si>
-    <t>Men</t>
-  </si>
-  <si>
     <t>Young</t>
   </si>
   <si>
@@ -1680,27 +1596,15 @@
     <t>KO</t>
   </si>
   <si>
-    <t>PDR</t>
-  </si>
-  <si>
-    <t>T2D</t>
-  </si>
-  <si>
     <t>T</t>
   </si>
   <si>
-    <t>MEC-1</t>
-  </si>
-  <si>
     <t>IgG</t>
   </si>
   <si>
     <t>LIM</t>
   </si>
   <si>
-    <t>Moyamoya</t>
-  </si>
-  <si>
     <t>24h</t>
   </si>
   <si>
@@ -1713,15 +1617,9 @@
     <t>UP</t>
   </si>
   <si>
-    <t>fixed</t>
-  </si>
-  <si>
     <t>Women</t>
   </si>
   <si>
-    <t>OLD</t>
-  </si>
-  <si>
     <t>CTR</t>
   </si>
   <si>
@@ -1734,12 +1632,6 @@
     <t>UW</t>
   </si>
   <si>
-    <t>CZ+</t>
-  </si>
-  <si>
-    <t>CTRL</t>
-  </si>
-  <si>
     <t>siBPGMcontrol</t>
   </si>
   <si>
@@ -1749,12 +1641,6 @@
     <t>WT_No</t>
   </si>
   <si>
-    <t>Airway</t>
-  </si>
-  <si>
-    <t>Adult+Sperm</t>
-  </si>
-  <si>
     <t>VEGFA</t>
   </si>
   <si>
@@ -1767,9 +1653,6 @@
     <t>WT_CTSB</t>
   </si>
   <si>
-    <t>Cntl</t>
-  </si>
-  <si>
     <t>Responder</t>
   </si>
   <si>
@@ -1782,9 +1665,6 @@
     <t>ctrl</t>
   </si>
   <si>
-    <t>Minus</t>
-  </si>
-  <si>
     <t>Cancer</t>
   </si>
   <si>
@@ -1803,9 +1683,6 @@
     <t>CI3_WT</t>
   </si>
   <si>
-    <t>IPL</t>
-  </si>
-  <si>
     <t>AD_CTSB</t>
   </si>
   <si>
@@ -1827,9 +1704,6 @@
     <t>KO_D0</t>
   </si>
   <si>
-    <t>Plus</t>
-  </si>
-  <si>
     <t>SNx</t>
   </si>
   <si>
@@ -1872,9 +1746,6 @@
     <t>Wild Control</t>
   </si>
   <si>
-    <t>SCR</t>
-  </si>
-  <si>
     <t>acute</t>
   </si>
   <si>
@@ -1887,9 +1758,6 @@
     <t>IDMA</t>
   </si>
   <si>
-    <t>sgALAS1</t>
-  </si>
-  <si>
     <t>recovery</t>
   </si>
   <si>
@@ -1920,12 +1788,6 @@
     <t>H_3rdT</t>
   </si>
   <si>
-    <t>Myc.M.aMum1</t>
-  </si>
-  <si>
-    <t>Myc.M.aMvc</t>
-  </si>
-  <si>
     <t>Dex+Spi10</t>
   </si>
   <si>
@@ -1962,18 +1824,12 @@
     <t>AD_F</t>
   </si>
   <si>
-    <t>BPH</t>
-  </si>
-  <si>
     <t>siPRDX6</t>
   </si>
   <si>
     <t>D</t>
   </si>
   <si>
-    <t>PCA</t>
-  </si>
-  <si>
     <t>siNC</t>
   </si>
   <si>
@@ -2112,9 +1968,6 @@
     <t>CCA</t>
   </si>
   <si>
-    <t>KYL</t>
-  </si>
-  <si>
     <t>whi2</t>
   </si>
   <si>
@@ -2140,6 +1993,186 @@
   </si>
   <si>
     <t>DOI: 10.1038/s41598-026-46965-1</t>
+  </si>
+  <si>
+    <t>CZS+</t>
+  </si>
+  <si>
+    <t>AdultSperm</t>
+  </si>
+  <si>
+    <t>Adult;AdultSperm;Young</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Unfixed;Fixed</t>
+  </si>
+  <si>
+    <t>Control;cKO</t>
+  </si>
+  <si>
+    <t>cKO</t>
+  </si>
+  <si>
+    <t>BJAB;MEC1</t>
+  </si>
+  <si>
+    <t>MEC1</t>
+  </si>
+  <si>
+    <t>ARID1A</t>
+  </si>
+  <si>
+    <t>ARID1A;IgG</t>
+  </si>
+  <si>
+    <t>CTL;LIM</t>
+  </si>
+  <si>
+    <t>Man;Women</t>
+  </si>
+  <si>
+    <t>Man</t>
+  </si>
+  <si>
+    <t>control;depressed/no SRI;depressed/SRI</t>
+  </si>
+  <si>
+    <t>control</t>
+  </si>
+  <si>
+    <t>Cancer;Normal</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>E;D</t>
+  </si>
+  <si>
+    <t>G1;G2;G3;G4;G5;G6</t>
+  </si>
+  <si>
+    <t>G5</t>
+  </si>
+  <si>
+    <t>G6</t>
+  </si>
+  <si>
+    <t>Scr_d4;sgALAS1_d4;Scr_d6;sgALAS1_d6</t>
+  </si>
+  <si>
+    <t>Scr_d6</t>
+  </si>
+  <si>
+    <t>sgALAS1_d6</t>
+  </si>
+  <si>
+    <t>Nutlin_ER;DMSO_ER</t>
+  </si>
+  <si>
+    <t>DMSO_ER</t>
+  </si>
+  <si>
+    <t>Nutlin_ER</t>
+  </si>
+  <si>
+    <t>wt_mock;wt_LPS;ko_mock;ko_LPS</t>
+  </si>
+  <si>
+    <t>wt_LPS</t>
+  </si>
+  <si>
+    <t>ko_LPS</t>
+  </si>
+  <si>
+    <t>St-KO;St-WT;Un-KO;Un-WT</t>
+  </si>
+  <si>
+    <t>St-WT</t>
+  </si>
+  <si>
+    <t>St-KO</t>
+  </si>
+  <si>
+    <t>Group1;Group2;Group3;Group4</t>
+  </si>
+  <si>
+    <t>Group4</t>
+  </si>
+  <si>
+    <t>Group1</t>
+  </si>
+  <si>
+    <t>C;DM</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>IPFDistalAirway;IPFHCAirway;IPF_ABEC;IPF_Alveoli;IPF_Fibroblastic_Foci;NonFibroticControlAirway;Non_fibrotic_Control_Alveoli</t>
+  </si>
+  <si>
+    <t>Non_fibrotic_Control_Alveoli</t>
+  </si>
+  <si>
+    <t>IPFDistalAirway</t>
+  </si>
+  <si>
+    <t>A;B</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Myc.M.aMum1.</t>
+  </si>
+  <si>
+    <t>Myc.M.aMvc.</t>
+  </si>
+  <si>
+    <t>P11</t>
+  </si>
+  <si>
+    <t>P38</t>
+  </si>
+  <si>
+    <t>P11;P38</t>
+  </si>
+  <si>
+    <t>pca;bph</t>
+  </si>
+  <si>
+    <t>bph</t>
+  </si>
+  <si>
+    <t>pca</t>
+  </si>
+  <si>
+    <t>ctrl;IP</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>minus;plus</t>
+  </si>
+  <si>
+    <t>minus</t>
+  </si>
+  <si>
+    <t>plus</t>
+  </si>
+  <si>
+    <t>G1;G2;G3</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>G3</t>
   </si>
 </sst>
 </file>
@@ -2219,12 +2252,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2556,17 +2590,17 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" customWidth="1"/>
-    <col min="7" max="7" width="27.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="27.85546875" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="27.85546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="27.85546875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="32.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="38.28515625" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="38.28515625" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="19.140625" customWidth="1"/>
     <col min="15" max="15" width="16.140625" customWidth="1"/>
     <col min="16" max="16" width="40.7109375" customWidth="1"/>
@@ -2576,13 +2610,13 @@
   <sheetData>
     <row r="1" spans="1:18" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -2594,13 +2628,13 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>481</v>
+        <v>458</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>5</v>
@@ -2615,19 +2649,19 @@
         <v>13</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>532</v>
+        <v>509</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>19</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>467</v>
+        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -2638,7 +2672,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
@@ -2650,19 +2684,19 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="H2" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I2" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="J2">
         <v>2</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>672</v>
       </c>
       <c r="L2">
         <f>10</f>
@@ -2672,19 +2706,19 @@
         <v>15</v>
       </c>
       <c r="N2" t="s">
-        <v>546</v>
+        <v>598</v>
       </c>
       <c r="O2" t="s">
-        <v>533</v>
+        <v>564</v>
       </c>
       <c r="P2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q2" t="s">
         <v>20</v>
       </c>
       <c r="R2" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -2692,13 +2726,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>695</v>
+        <v>646</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -2707,37 +2741,37 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>696</v>
+        <v>647</v>
       </c>
       <c r="H3" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>697</v>
+        <v>648</v>
       </c>
       <c r="L3">
         <v>30</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>702</v>
+        <v>653</v>
       </c>
       <c r="N3" t="s">
-        <v>698</v>
+        <v>649</v>
       </c>
       <c r="O3" t="s">
-        <v>699</v>
+        <v>650</v>
       </c>
       <c r="P3" t="s">
-        <v>700</v>
+        <v>651</v>
       </c>
       <c r="Q3" t="s">
-        <v>701</v>
+        <v>652</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -2748,7 +2782,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -2760,19 +2794,19 @@
         <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>485</v>
+        <v>462</v>
       </c>
       <c r="H4" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J4">
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>473</v>
+        <v>450</v>
       </c>
       <c r="L4">
         <f>3*3</f>
@@ -2782,10 +2816,10 @@
         <v>14</v>
       </c>
       <c r="N4" t="s">
-        <v>616</v>
+        <v>573</v>
       </c>
       <c r="O4" t="s">
-        <v>617</v>
+        <v>574</v>
       </c>
       <c r="P4" s="1"/>
     </row>
@@ -2794,13 +2828,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" t="s">
         <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -2809,35 +2843,35 @@
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>487</v>
+        <v>464</v>
       </c>
       <c r="H5" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I5" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="J5">
         <v>6</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>673</v>
       </c>
       <c r="L5">
         <f>6*3</f>
         <v>18</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5">
-        <v>5</v>
-      </c>
-      <c r="O5">
-        <v>6</v>
+        <v>31</v>
+      </c>
+      <c r="N5" t="s">
+        <v>674</v>
+      </c>
+      <c r="O5" t="s">
+        <v>675</v>
       </c>
       <c r="P5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -2845,13 +2879,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -2860,37 +2894,37 @@
         <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>486</v>
+        <v>463</v>
       </c>
       <c r="H6" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I6" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>37</v>
+        <v>676</v>
       </c>
       <c r="L6">
         <v>16</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N6" t="s">
-        <v>613</v>
+        <v>677</v>
       </c>
       <c r="O6" t="s">
-        <v>618</v>
+        <v>678</v>
       </c>
       <c r="P6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Q6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -2898,13 +2932,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -2913,38 +2947,38 @@
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="H7" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I7" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="J7">
         <v>4</v>
       </c>
       <c r="K7" t="s">
-        <v>43</v>
+        <v>679</v>
       </c>
       <c r="L7">
         <f>J7*4</f>
         <v>16</v>
       </c>
       <c r="M7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N7" t="s">
-        <v>546</v>
+        <v>680</v>
       </c>
       <c r="O7" t="s">
-        <v>534</v>
+        <v>681</v>
       </c>
       <c r="P7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -2952,13 +2986,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -2967,35 +3001,35 @@
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="H8" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I8" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="J8">
         <v>2</v>
       </c>
       <c r="K8" t="s">
-        <v>48</v>
+        <v>682</v>
       </c>
       <c r="L8">
         <f>24</f>
         <v>24</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N8" t="s">
-        <v>535</v>
+        <v>683</v>
       </c>
       <c r="O8" t="s">
-        <v>547</v>
+        <v>684</v>
       </c>
       <c r="P8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Q8" s="4"/>
     </row>
@@ -3004,53 +3038,53 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H9" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I9" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J9">
         <v>3</v>
       </c>
       <c r="K9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L9">
         <f>29</f>
         <v>29</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="N9" t="s">
-        <v>563</v>
+        <v>529</v>
       </c>
       <c r="O9" t="s">
-        <v>567</v>
+        <v>654</v>
       </c>
       <c r="P9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Q9" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -3058,49 +3092,49 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="H10" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I10" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="J10">
         <v>7</v>
       </c>
       <c r="K10" t="s">
-        <v>99</v>
+        <v>693</v>
       </c>
       <c r="L10">
         <v>24</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="N10" t="s">
-        <v>531</v>
-      </c>
-      <c r="O10" t="s">
-        <v>572</v>
+        <v>694</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>695</v>
       </c>
       <c r="Q10" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3108,49 +3142,49 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H11" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I11" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J11">
         <v>2</v>
       </c>
       <c r="K11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L11">
         <v>33</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="N11" t="s">
-        <v>614</v>
+        <v>571</v>
       </c>
       <c r="O11" t="s">
-        <v>619</v>
+        <v>575</v>
       </c>
       <c r="P11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -3158,47 +3192,47 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="H12" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I12" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="J12">
         <v>2</v>
       </c>
       <c r="K12" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="L12">
         <f>9</f>
         <v>9</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="N12" t="s">
-        <v>536</v>
+        <v>510</v>
       </c>
       <c r="O12" t="s">
-        <v>548</v>
+        <v>519</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -3206,13 +3240,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -3221,34 +3255,34 @@
         <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
       <c r="H13" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J13">
         <v>2</v>
       </c>
       <c r="K13" t="s">
-        <v>67</v>
+        <v>685</v>
       </c>
       <c r="L13">
         <v>16</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="N13" t="s">
-        <v>536</v>
+        <v>686</v>
       </c>
       <c r="O13" t="s">
-        <v>548</v>
+        <v>687</v>
       </c>
       <c r="Q13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -3256,13 +3290,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -3271,35 +3305,35 @@
         <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H14" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J14">
         <v>4</v>
       </c>
       <c r="K14" t="s">
-        <v>77</v>
+        <v>688</v>
       </c>
       <c r="L14">
         <f>8*4</f>
         <v>32</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N14" t="s">
-        <v>568</v>
+        <v>690</v>
       </c>
       <c r="O14" t="s">
-        <v>549</v>
+        <v>689</v>
       </c>
       <c r="Q14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -3307,13 +3341,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -3322,34 +3356,34 @@
         <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H15" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I15" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="J15">
         <v>2</v>
       </c>
       <c r="K15" t="s">
-        <v>80</v>
+        <v>691</v>
       </c>
       <c r="L15">
         <v>10</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="N15" t="s">
-        <v>537</v>
+        <v>512</v>
       </c>
       <c r="O15" t="s">
-        <v>550</v>
+        <v>692</v>
       </c>
       <c r="Q15" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -3357,13 +3391,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -3372,31 +3406,31 @@
         <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H16" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I16" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J16">
         <v>3</v>
       </c>
       <c r="K16" t="s">
-        <v>102</v>
+        <v>656</v>
       </c>
       <c r="L16">
         <v>9</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N16" t="s">
-        <v>545</v>
+        <v>517</v>
       </c>
       <c r="O16" t="s">
-        <v>573</v>
+        <v>655</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -3404,13 +3438,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -3419,31 +3453,31 @@
         <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="H17" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I17" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="J17">
         <v>2</v>
       </c>
       <c r="K17" t="s">
-        <v>105</v>
+        <v>344</v>
       </c>
       <c r="L17">
         <v>46</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="N17" t="s">
-        <v>538</v>
+        <v>619</v>
       </c>
       <c r="O17" t="s">
-        <v>551</v>
+        <v>521</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -3451,13 +3485,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -3466,34 +3500,34 @@
         <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H18" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I18" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J18">
         <v>2</v>
       </c>
       <c r="K18" t="s">
-        <v>109</v>
+        <v>661</v>
       </c>
       <c r="L18">
         <v>6</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="N18" t="s">
-        <v>552</v>
+        <v>662</v>
       </c>
       <c r="O18" t="s">
-        <v>539</v>
+        <v>513</v>
       </c>
       <c r="R18" t="s">
-        <v>470</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -3501,13 +3535,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -3516,35 +3550,35 @@
         <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
       <c r="H19" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I19" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="J19">
         <v>3</v>
       </c>
       <c r="K19" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L19">
         <f>J19*4</f>
         <v>12</v>
       </c>
       <c r="M19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N19" t="s">
-        <v>564</v>
+        <v>530</v>
       </c>
       <c r="O19" t="s">
-        <v>574</v>
+        <v>536</v>
       </c>
       <c r="Q19" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -3552,13 +3586,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -3567,37 +3601,37 @@
         <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>497</v>
+        <v>474</v>
       </c>
       <c r="H20" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I20" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="J20">
         <v>2</v>
       </c>
       <c r="K20" t="s">
-        <v>116</v>
+        <v>664</v>
       </c>
       <c r="L20">
         <v>6</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>540</v>
+        <v>663</v>
       </c>
       <c r="O20" t="s">
-        <v>553</v>
+        <v>522</v>
       </c>
       <c r="Q20" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="R20" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -3605,50 +3639,50 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="G21" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="H21" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I21" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="J21">
         <v>8</v>
       </c>
       <c r="K21" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="L21">
         <f>J21*4</f>
         <v>32</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="N21" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="O21" t="s">
-        <v>576</v>
+        <v>538</v>
       </c>
       <c r="Q21" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -3656,50 +3690,50 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E22" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F22" t="s">
         <v>17</v>
       </c>
       <c r="G22" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="H22" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I22" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="J22">
         <v>2</v>
       </c>
       <c r="K22" t="s">
-        <v>126</v>
+        <v>665</v>
       </c>
       <c r="L22">
         <f>J22*11</f>
         <v>22</v>
       </c>
       <c r="M22" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N22" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="O22" t="s">
-        <v>554</v>
+        <v>523</v>
       </c>
       <c r="P22" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -3707,50 +3741,50 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F23" t="s">
         <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="H23" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I23" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="J23">
         <v>4</v>
       </c>
       <c r="K23" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="L23">
         <f>19*2+16*2+1</f>
         <v>71</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>623</v>
+        <v>579</v>
       </c>
       <c r="N23" t="s">
-        <v>624</v>
+        <v>580</v>
       </c>
       <c r="O23" t="s">
-        <v>620</v>
+        <v>576</v>
       </c>
       <c r="Q23" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -3758,47 +3792,47 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>474</v>
+        <v>451</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F24" t="s">
         <v>11</v>
       </c>
       <c r="G24" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="H24" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I24" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="J24">
         <f>2</f>
         <v>2</v>
       </c>
       <c r="K24" t="s">
-        <v>475</v>
+        <v>452</v>
       </c>
       <c r="L24">
         <v>10</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="N24" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="O24" t="s">
-        <v>542</v>
+        <v>515</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -3806,46 +3840,46 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E25" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F25" t="s">
         <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="H25" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I25" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="J25">
         <v>3</v>
       </c>
       <c r="K25" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="L25">
         <v>46</v>
       </c>
       <c r="M25" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N25" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="O25" t="s">
-        <v>575</v>
+        <v>537</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -3853,46 +3887,46 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E26" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F26" t="s">
         <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H26" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I26" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J26">
         <v>2</v>
       </c>
       <c r="K26" t="s">
-        <v>139</v>
+        <v>696</v>
       </c>
       <c r="L26">
         <v>22</v>
       </c>
       <c r="M26" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N26" t="s">
-        <v>531</v>
+        <v>600</v>
       </c>
       <c r="O26" t="s">
-        <v>555</v>
+        <v>697</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -3900,47 +3934,47 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F27" t="s">
         <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="H27" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I27" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J27">
         <v>5</v>
       </c>
       <c r="K27" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="L27">
         <f>J27*4</f>
         <v>20</v>
       </c>
       <c r="M27" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N27" t="s">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="O27" t="s">
-        <v>621</v>
+        <v>577</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -3948,46 +3982,46 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F28" t="s">
         <v>17</v>
       </c>
       <c r="G28" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="H28" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I28" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="J28">
         <v>4</v>
       </c>
       <c r="K28" t="s">
-        <v>478</v>
+        <v>455</v>
       </c>
       <c r="L28">
         <v>23</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>479</v>
+        <v>456</v>
       </c>
       <c r="N28" t="s">
-        <v>569</v>
+        <v>533</v>
       </c>
       <c r="O28" t="s">
-        <v>587</v>
+        <v>547</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -3995,47 +4029,47 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E29" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="H29" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I29" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="J29">
         <v>4</v>
       </c>
       <c r="K29" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="L29">
         <f>J29*3</f>
         <v>12</v>
       </c>
       <c r="M29" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N29" t="s">
-        <v>629</v>
+        <v>698</v>
       </c>
       <c r="O29" t="s">
-        <v>630</v>
+        <v>699</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -4043,47 +4077,47 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F30" t="s">
         <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="H30" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I30" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="J30">
         <v>3</v>
       </c>
       <c r="K30" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="L30">
         <f>J30*4</f>
         <v>12</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="N30" t="s">
-        <v>565</v>
+        <v>531</v>
       </c>
       <c r="O30" t="s">
-        <v>556</v>
+        <v>524</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -4091,47 +4125,47 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D31" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="E31" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F31" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="G31" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="H31" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I31" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="J31">
         <v>4</v>
       </c>
       <c r="K31" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="L31">
         <f>J31*4</f>
         <v>16</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="N31" t="s">
-        <v>589</v>
+        <v>549</v>
       </c>
       <c r="O31" t="s">
-        <v>570</v>
+        <v>534</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -4139,50 +4173,50 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D32" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E32" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F32" t="s">
         <v>17</v>
       </c>
       <c r="G32" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="H32" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I32" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="J32">
         <v>4</v>
       </c>
       <c r="K32" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="L32">
         <f>J32*4</f>
         <v>16</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="N32" t="s">
-        <v>571</v>
+        <v>535</v>
       </c>
       <c r="O32" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="P32" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -4190,48 +4224,48 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E33" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F33" t="s">
         <v>11</v>
       </c>
       <c r="G33" t="s">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="H33" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I33" t="s">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="J33">
         <f>3</f>
         <v>3</v>
       </c>
       <c r="K33" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="L33">
         <f>J33*3</f>
         <v>9</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="N33" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="O33" t="s">
-        <v>557</v>
+        <v>525</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -4239,47 +4273,47 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F34" t="s">
         <v>17</v>
       </c>
       <c r="G34" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="H34" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I34" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="J34">
         <v>4</v>
       </c>
       <c r="K34" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="L34">
         <f>11</f>
         <v>11</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="N34" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="O34" t="s">
-        <v>558</v>
+        <v>526</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -4287,47 +4321,47 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="C35" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F35" t="s">
         <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="H35" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I35" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="J35">
         <v>3</v>
       </c>
       <c r="K35" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="L35">
         <f>9</f>
         <v>9</v>
       </c>
       <c r="M35" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N35" t="s">
-        <v>566</v>
+        <v>532</v>
       </c>
       <c r="O35" t="s">
-        <v>559</v>
+        <v>527</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -4335,47 +4369,47 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D36" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E36" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="H36" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I36" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="J36">
         <v>2</v>
       </c>
       <c r="K36" t="s">
-        <v>176</v>
+        <v>658</v>
       </c>
       <c r="L36">
         <f>8</f>
         <v>8</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="N36" t="s">
-        <v>543</v>
+        <v>516</v>
       </c>
       <c r="O36" t="s">
-        <v>560</v>
+        <v>657</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -4383,53 +4417,53 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C37" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E37" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F37" t="s">
         <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="H37" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I37" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="J37">
         <v>2</v>
       </c>
       <c r="K37" t="s">
-        <v>181</v>
+        <v>666</v>
       </c>
       <c r="L37">
         <f>25*2</f>
         <v>50</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="N37" t="s">
-        <v>544</v>
+        <v>667</v>
       </c>
       <c r="O37" t="s">
-        <v>561</v>
+        <v>528</v>
       </c>
       <c r="P37" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="Q37" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -4437,47 +4471,47 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="C38" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E38" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F38" t="s">
         <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="H38" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I38" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="J38">
         <v>2</v>
       </c>
       <c r="K38" t="s">
-        <v>186</v>
+        <v>702</v>
       </c>
       <c r="L38">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="N38" t="s">
-        <v>545</v>
+        <v>700</v>
       </c>
       <c r="O38" t="s">
-        <v>562</v>
+        <v>701</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -4485,47 +4519,47 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D39" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="E39" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F39" t="s">
         <v>11</v>
       </c>
       <c r="G39" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="H39" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I39" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J39">
         <v>4</v>
       </c>
       <c r="K39" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="L39">
         <f>J39*3</f>
         <v>12</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="N39" t="s">
-        <v>625</v>
+        <v>581</v>
       </c>
       <c r="O39" t="s">
-        <v>633</v>
+        <v>587</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -4533,50 +4567,50 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="C40" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E40" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F40" t="s">
         <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="H40" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I40" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="J40">
         <v>4</v>
       </c>
       <c r="K40" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="L40">
         <f>J40*10</f>
         <v>40</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="N40" t="s">
-        <v>628</v>
+        <v>584</v>
       </c>
       <c r="O40" t="s">
-        <v>634</v>
+        <v>588</v>
       </c>
       <c r="P40" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -4584,53 +4618,53 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D41" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E41" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F41" t="s">
         <v>17</v>
       </c>
       <c r="G41" t="s">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="H41" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I41" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J41">
         <v>4</v>
       </c>
       <c r="K41" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="L41">
         <f>24</f>
         <v>24</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="N41" t="s">
-        <v>577</v>
+        <v>539</v>
       </c>
       <c r="O41" t="s">
-        <v>591</v>
+        <v>550</v>
       </c>
       <c r="P41" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="Q41" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -4638,13 +4672,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D42" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
@@ -4653,35 +4687,35 @@
         <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>497</v>
+        <v>474</v>
       </c>
       <c r="H42" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I42" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="J42">
         <v>2</v>
       </c>
       <c r="K42" t="s">
-        <v>120</v>
+        <v>706</v>
       </c>
       <c r="L42">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="N42" t="s">
-        <v>578</v>
+        <v>543</v>
       </c>
       <c r="O42" t="s">
-        <v>590</v>
+        <v>707</v>
       </c>
       <c r="Q42" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -4689,50 +4723,50 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="C43" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D43" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="E43" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F43" t="s">
         <v>11</v>
       </c>
       <c r="G43" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H43" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I43" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J43">
         <v>2</v>
       </c>
       <c r="K43" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="L43">
         <f>35</f>
         <v>35</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="N43" t="s">
-        <v>622</v>
+        <v>578</v>
       </c>
       <c r="O43" t="s">
-        <v>615</v>
+        <v>572</v>
       </c>
       <c r="P43" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -4740,49 +4774,49 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="C44" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
       </c>
       <c r="E44" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F44" t="s">
         <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="H44" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I44" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="J44">
         <v>3</v>
       </c>
       <c r="K44" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="L44">
         <v>29</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="N44" t="s">
-        <v>636</v>
+        <v>590</v>
       </c>
       <c r="O44" t="s">
-        <v>626</v>
+        <v>582</v>
       </c>
       <c r="P44" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -4790,49 +4824,49 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="H45" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I45" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="J45">
         <v>3</v>
       </c>
       <c r="K45" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="L45">
         <v>28</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="N45" t="s">
-        <v>636</v>
+        <v>590</v>
       </c>
       <c r="O45" t="s">
-        <v>626</v>
+        <v>582</v>
       </c>
       <c r="P45" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -4840,50 +4874,50 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D46" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E46" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F46" t="s">
         <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="H46" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I46" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="J46">
         <v>6</v>
       </c>
       <c r="K46" t="s">
-        <v>637</v>
+        <v>591</v>
       </c>
       <c r="L46">
         <f>6*3</f>
         <v>18</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="N46" t="s">
-        <v>639</v>
+        <v>593</v>
       </c>
       <c r="O46" t="s">
-        <v>638</v>
+        <v>592</v>
       </c>
       <c r="P46" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -4891,49 +4925,49 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="C47" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F47" t="s">
         <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="H47" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I47" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="J47">
         <v>2</v>
       </c>
       <c r="K47" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="L47">
         <v>21</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="N47" t="s">
-        <v>579</v>
+        <v>540</v>
       </c>
       <c r="O47" t="s">
-        <v>592</v>
+        <v>551</v>
       </c>
       <c r="P47" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -4941,46 +4975,46 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="C48" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D48" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="E48" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F48" t="s">
         <v>17</v>
       </c>
       <c r="G48" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="H48" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I48" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J48">
         <v>2</v>
       </c>
       <c r="K48" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L48">
         <v>8</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="N48" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="O48" t="s">
-        <v>548</v>
+        <v>520</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -4988,50 +5022,50 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D49" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E49" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F49" t="s">
         <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>514</v>
+        <v>491</v>
       </c>
       <c r="H49" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I49" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J49">
         <v>6</v>
       </c>
       <c r="K49" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="L49">
         <f>J49*4</f>
         <v>24</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="N49" t="s">
-        <v>640</v>
+        <v>594</v>
       </c>
       <c r="O49" t="s">
-        <v>631</v>
+        <v>585</v>
       </c>
       <c r="P49" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -5039,51 +5073,51 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="C50" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
       </c>
       <c r="E50" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F50" t="s">
         <v>17</v>
       </c>
       <c r="G50" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="H50" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I50" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="J50">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="K50" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="L50">
         <f>J50*3</f>
         <v>18</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="N50" t="s">
-        <v>580</v>
+        <v>541</v>
       </c>
       <c r="O50" t="s">
-        <v>597</v>
+        <v>556</v>
       </c>
       <c r="P50" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -5091,51 +5125,51 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="C51" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D51" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E51" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F51" t="s">
         <v>11</v>
       </c>
       <c r="G51" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="H51" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I51" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="J51">
         <f>2</f>
         <v>2</v>
       </c>
       <c r="K51" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="L51">
         <f>J51*3</f>
         <v>6</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="N51" t="s">
-        <v>632</v>
+        <v>586</v>
       </c>
       <c r="O51" t="s">
-        <v>635</v>
+        <v>589</v>
       </c>
       <c r="P51" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -5143,49 +5177,49 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="C52" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F52" t="s">
         <v>17</v>
       </c>
       <c r="G52" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="H52" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I52" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="J52">
         <v>2</v>
       </c>
       <c r="K52" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="L52">
         <v>6</v>
       </c>
       <c r="M52" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N52" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="O52" t="s">
-        <v>593</v>
+        <v>552</v>
       </c>
       <c r="P52" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -5193,52 +5227,52 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="C53" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D53" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="E53" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="F53" t="s">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="H53" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I53" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="J53">
         <v>3</v>
       </c>
       <c r="K53" t="s">
-        <v>254</v>
+        <v>668</v>
       </c>
       <c r="L53">
         <v>69</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="N53" t="s">
-        <v>531</v>
+        <v>669</v>
       </c>
       <c r="O53" t="s">
-        <v>594</v>
+        <v>553</v>
       </c>
       <c r="P53" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="Q53" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -5246,50 +5280,50 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="C54" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D54" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E54" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F54" t="s">
         <v>17</v>
       </c>
       <c r="G54" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="H54" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I54" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="J54">
         <v>3</v>
       </c>
       <c r="K54" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="L54">
         <f>14</f>
         <v>14</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="N54" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="O54" t="s">
-        <v>595</v>
+        <v>554</v>
       </c>
       <c r="P54" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -5297,50 +5331,50 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="C55" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D55" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E55" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F55" t="s">
         <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H55" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I55" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J55">
         <v>4</v>
       </c>
       <c r="K55" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="L55">
         <f>32</f>
         <v>32</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="N55" t="s">
-        <v>641</v>
+        <v>595</v>
       </c>
       <c r="O55" t="s">
-        <v>642</v>
+        <v>596</v>
       </c>
       <c r="P55" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -5348,50 +5382,50 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="C56" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D56" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E56" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F56" t="s">
         <v>11</v>
       </c>
       <c r="G56" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H56" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I56" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J56">
         <v>2</v>
       </c>
       <c r="K56" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="L56">
         <f>27</f>
         <v>27</v>
       </c>
       <c r="M56" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="N56" t="s">
-        <v>581</v>
+        <v>542</v>
       </c>
       <c r="O56" t="s">
-        <v>596</v>
+        <v>555</v>
       </c>
       <c r="P56" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -5399,50 +5433,50 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="C57" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D57" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E57" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F57" t="s">
         <v>11</v>
       </c>
       <c r="G57" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="H57" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I57" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="J57">
         <v>2</v>
       </c>
       <c r="K57" t="s">
-        <v>273</v>
+        <v>703</v>
       </c>
       <c r="L57">
         <f>133</f>
         <v>133</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="N57" t="s">
-        <v>643</v>
+        <v>704</v>
       </c>
       <c r="O57" t="s">
-        <v>646</v>
+        <v>705</v>
       </c>
       <c r="Q57" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -5450,49 +5484,49 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="C58" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D58" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E58" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F58" t="s">
         <v>11</v>
       </c>
       <c r="G58" t="s">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="H58" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I58" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J58">
         <v>2</v>
       </c>
       <c r="K58" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="L58">
         <v>10</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="N58" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="O58" t="s">
-        <v>548</v>
+        <v>520</v>
       </c>
       <c r="Q58" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -5500,49 +5534,49 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="C59" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D59" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E59" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F59" t="s">
         <v>11</v>
       </c>
       <c r="G59" t="s">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="H59" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I59" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="J59">
         <v>2</v>
       </c>
       <c r="K59" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="L59">
         <v>7</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="N59" t="s">
-        <v>647</v>
+        <v>599</v>
       </c>
       <c r="O59" t="s">
-        <v>644</v>
+        <v>597</v>
       </c>
       <c r="P59" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -5550,49 +5584,49 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="C60" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E60" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F60" t="s">
         <v>11</v>
       </c>
       <c r="G60" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H60" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I60" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J60">
         <v>2</v>
       </c>
       <c r="K60" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="L60">
         <v>48</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="N60" t="s">
-        <v>648</v>
+        <v>600</v>
       </c>
       <c r="O60" t="s">
-        <v>645</v>
+        <v>598</v>
       </c>
       <c r="Q60" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -5600,53 +5634,53 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="C61" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D61" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E61" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F61" t="s">
         <v>11</v>
       </c>
       <c r="G61" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="H61" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I61" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="J61">
         <v>4</v>
       </c>
       <c r="K61" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="L61">
         <f>63+52</f>
         <v>115</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="N61" t="s">
-        <v>649</v>
+        <v>601</v>
       </c>
       <c r="O61" t="s">
-        <v>650</v>
+        <v>602</v>
       </c>
       <c r="P61" t="s">
-        <v>464</v>
+        <v>441</v>
       </c>
       <c r="Q61" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -5654,50 +5688,50 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="C62" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D62" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E62" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F62" t="s">
         <v>11</v>
       </c>
       <c r="G62" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="H62" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I62" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="J62">
         <v>4</v>
       </c>
       <c r="K62" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="L62">
         <f>120</f>
         <v>120</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="N62" t="s">
-        <v>649</v>
+        <v>601</v>
       </c>
       <c r="O62" t="s">
-        <v>650</v>
+        <v>602</v>
       </c>
       <c r="P62" t="s">
-        <v>464</v>
+        <v>441</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -5705,49 +5739,49 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="C63" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D63" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E63" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F63" t="s">
         <v>17</v>
       </c>
       <c r="G63" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="H63" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I63" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="J63">
         <v>6</v>
       </c>
       <c r="K63" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="L63">
         <v>36</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="N63" t="s">
-        <v>652</v>
+        <v>604</v>
       </c>
       <c r="O63" t="s">
-        <v>651</v>
+        <v>603</v>
       </c>
       <c r="P63" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -5755,49 +5789,49 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="C64" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D64" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E64" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F64" t="s">
         <v>17</v>
       </c>
       <c r="G64" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="H64" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I64" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="J64">
         <v>5</v>
       </c>
       <c r="K64" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="L64">
         <v>35</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="N64" t="s">
-        <v>653</v>
+        <v>605</v>
       </c>
       <c r="O64" t="s">
-        <v>654</v>
+        <v>606</v>
       </c>
       <c r="P64" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -5805,52 +5839,52 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="C65" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D65" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E65" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F65" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="G65" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H65" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I65" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J65">
         <v>3</v>
       </c>
       <c r="K65" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="L65">
         <v>9</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>655</v>
+        <v>607</v>
       </c>
       <c r="N65" t="s">
-        <v>582</v>
+        <v>543</v>
       </c>
       <c r="O65" t="s">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="Q65" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="R65" t="s">
-        <v>470</v>
+        <v>447</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
@@ -5858,50 +5892,50 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="C66" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D66" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E66" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F66" t="s">
         <v>17</v>
       </c>
       <c r="G66" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="H66" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I66" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="J66">
         <v>6</v>
       </c>
       <c r="K66" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="L66">
         <f>J66*3</f>
         <v>18</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="N66" t="s">
-        <v>657</v>
+        <v>609</v>
       </c>
       <c r="O66" t="s">
-        <v>658</v>
+        <v>610</v>
       </c>
       <c r="R66" t="s">
-        <v>468</v>
+        <v>445</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
@@ -5909,53 +5943,53 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="C67" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D67" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E67" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F67" t="s">
         <v>17</v>
       </c>
       <c r="G67" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H67" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I67" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J67">
         <v>2</v>
       </c>
       <c r="K67" t="s">
-        <v>312</v>
+        <v>659</v>
       </c>
       <c r="L67">
         <f>12</f>
         <v>12</v>
       </c>
       <c r="M67" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N67" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="O67" t="s">
-        <v>548</v>
+        <v>660</v>
       </c>
       <c r="P67" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="R67" t="s">
-        <v>469</v>
+        <v>446</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
@@ -5963,46 +5997,46 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="C68" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D68" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E68" t="s">
         <v>9</v>
       </c>
       <c r="F68" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="G68" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="H68" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I68" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="J68">
         <v>2</v>
       </c>
       <c r="K68" t="s">
-        <v>317</v>
+        <v>708</v>
       </c>
       <c r="L68">
         <v>12</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="N68" t="s">
-        <v>583</v>
+        <v>709</v>
       </c>
       <c r="O68" t="s">
-        <v>598</v>
+        <v>710</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -6010,47 +6044,47 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="C69" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D69" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E69" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="F69" t="s">
         <v>11</v>
       </c>
       <c r="G69" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H69" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I69" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J69">
         <v>2</v>
       </c>
       <c r="K69" t="s">
-        <v>321</v>
+        <v>670</v>
       </c>
       <c r="L69">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="N69" t="s">
-        <v>531</v>
+        <v>671</v>
       </c>
       <c r="O69" t="s">
-        <v>584</v>
+        <v>544</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -6058,49 +6092,49 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="C70" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="E70" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F70" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="G70" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="H70" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I70" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J70">
         <v>2</v>
       </c>
       <c r="K70" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="L70">
         <v>10</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="N70" t="s">
-        <v>585</v>
+        <v>545</v>
       </c>
       <c r="O70" t="s">
-        <v>599</v>
+        <v>557</v>
       </c>
       <c r="Q70" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
@@ -6108,50 +6142,50 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="C71" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D71" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="E71" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F71" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="G71" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="H71" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I71" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J71">
         <v>5</v>
       </c>
       <c r="K71" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="L71">
         <f>J71*4+4</f>
         <v>24</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="N71" t="s">
-        <v>664</v>
+        <v>616</v>
       </c>
       <c r="O71" t="s">
-        <v>665</v>
+        <v>617</v>
       </c>
       <c r="Q71" t="s">
-        <v>341</v>
+        <v>319</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -6159,47 +6193,47 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="C72" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F72" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="G72" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="H72" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I72" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="J72">
         <v>3</v>
       </c>
       <c r="K72" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="L72">
         <f>3*4</f>
         <v>12</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="N72" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="O72" t="s">
-        <v>666</v>
+        <v>618</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
@@ -6207,13 +6241,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="C73" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D73" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="E73" t="s">
         <v>9</v>
@@ -6222,34 +6256,34 @@
         <v>11</v>
       </c>
       <c r="G73" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="H73" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I73" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="J73">
         <v>4</v>
       </c>
       <c r="K73" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="L73">
         <v>23</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="N73" t="s">
-        <v>659</v>
+        <v>611</v>
       </c>
       <c r="O73" t="s">
-        <v>673</v>
+        <v>625</v>
       </c>
       <c r="P73" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
@@ -6257,50 +6291,50 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="C74" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D74" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E74" t="s">
         <v>9</v>
       </c>
       <c r="F74" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="G74" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="H74" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I74" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="J74">
         <v>12</v>
       </c>
       <c r="K74" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="L74">
         <f>J74*6</f>
         <v>72</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="N74" t="s">
-        <v>674</v>
+        <v>626</v>
       </c>
       <c r="O74" t="s">
-        <v>675</v>
+        <v>627</v>
       </c>
       <c r="P74" t="s">
-        <v>351</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -6308,47 +6342,47 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="C75" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D75" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E75" t="s">
         <v>9</v>
       </c>
       <c r="F75" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="G75" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="H75" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I75" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="J75">
         <v>6</v>
       </c>
       <c r="K75" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="L75">
         <f>6*3</f>
         <v>18</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="N75" t="s">
-        <v>677</v>
+        <v>629</v>
       </c>
       <c r="O75" t="s">
-        <v>660</v>
+        <v>612</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
@@ -6356,47 +6390,47 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="C76" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D76" t="s">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="E76" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="F76" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="G76" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="H76" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I76" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="J76">
         <v>3</v>
       </c>
       <c r="K76" t="s">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="L76">
         <f>J76*3</f>
         <v>9</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="N76" t="s">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="O76" t="s">
-        <v>694</v>
+        <v>645</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
@@ -6404,48 +6438,48 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="C77" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D77" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E77" t="s">
         <v>9</v>
       </c>
       <c r="F77" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="G77" t="s">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="H77" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I77" t="s">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="J77">
         <f>3</f>
         <v>3</v>
       </c>
       <c r="K77" t="s">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="L77">
         <f>J77*3</f>
         <v>9</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="N77" t="s">
-        <v>586</v>
+        <v>546</v>
       </c>
       <c r="O77" t="s">
-        <v>676</v>
+        <v>628</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
@@ -6453,13 +6487,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="C78" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D78" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E78" t="s">
         <v>9</v>
@@ -6468,31 +6502,31 @@
         <v>11</v>
       </c>
       <c r="G78" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="H78" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I78" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="J78">
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="L78">
         <v>15</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="N78" t="s">
-        <v>667</v>
+        <v>619</v>
       </c>
       <c r="O78" t="s">
-        <v>551</v>
+        <v>521</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
@@ -6500,13 +6534,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="C79" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D79" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E79" t="s">
         <v>9</v>
@@ -6515,32 +6549,32 @@
         <v>17</v>
       </c>
       <c r="G79" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="H79" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I79" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="J79">
         <v>3</v>
       </c>
       <c r="K79" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="L79">
         <f>9</f>
         <v>9</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="N79" t="s">
-        <v>668</v>
+        <v>620</v>
       </c>
       <c r="O79" t="s">
-        <v>661</v>
+        <v>613</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
@@ -6548,47 +6582,47 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="C80" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D80" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E80" t="s">
         <v>9</v>
       </c>
       <c r="F80" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="G80" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="H80" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I80" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="J80">
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
       <c r="L80">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="N80" t="s">
-        <v>669</v>
+        <v>621</v>
       </c>
       <c r="O80" t="s">
-        <v>662</v>
+        <v>614</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -6596,13 +6630,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="C81" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D81" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E81" t="s">
         <v>9</v>
@@ -6611,31 +6645,31 @@
         <v>11</v>
       </c>
       <c r="G81" t="s">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="H81" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I81" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="J81">
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="L81">
         <v>6</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="N81" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="O81" t="s">
-        <v>548</v>
+        <v>520</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -6643,13 +6677,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="C82" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D82" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E82" t="s">
         <v>9</v>
@@ -6658,31 +6692,31 @@
         <v>17</v>
       </c>
       <c r="G82" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="H82" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I82" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="J82">
         <v>3</v>
       </c>
       <c r="K82" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="L82">
         <v>9</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="N82" t="s">
-        <v>538</v>
+        <v>512</v>
       </c>
       <c r="O82" t="s">
-        <v>663</v>
+        <v>615</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -6690,13 +6724,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="C83" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D83" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E83" t="s">
         <v>9</v>
@@ -6705,35 +6739,35 @@
         <v>11</v>
       </c>
       <c r="G83" t="s">
-        <v>519</v>
+        <v>496</v>
       </c>
       <c r="H83" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I83" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="J83">
         <v>7</v>
       </c>
       <c r="K83" t="s">
-        <v>684</v>
+        <v>636</v>
       </c>
       <c r="L83">
         <f>J83*3</f>
         <v>21</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="N83" t="s">
-        <v>546</v>
+        <v>518</v>
       </c>
       <c r="O83" t="s">
-        <v>685</v>
+        <v>637</v>
       </c>
       <c r="P83" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -6741,48 +6775,48 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="C84" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D84" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E84" t="s">
         <v>9</v>
       </c>
       <c r="F84" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="G84" t="s">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="H84" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I84" t="s">
-        <v>521</v>
+        <v>498</v>
       </c>
       <c r="J84">
         <f>2</f>
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="L84">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="N84" t="s">
-        <v>600</v>
+        <v>558</v>
       </c>
       <c r="O84" t="s">
-        <v>603</v>
+        <v>561</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -6790,13 +6824,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="C85" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D85" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E85" t="s">
         <v>9</v>
@@ -6805,32 +6839,32 @@
         <v>11</v>
       </c>
       <c r="G85" t="s">
-        <v>522</v>
+        <v>499</v>
       </c>
       <c r="H85" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I85" t="s">
-        <v>523</v>
+        <v>500</v>
       </c>
       <c r="J85">
         <v>4</v>
       </c>
       <c r="K85" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="L85">
         <f>4*J85</f>
         <v>16</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>389</v>
+        <v>367</v>
       </c>
       <c r="N85" t="s">
-        <v>604</v>
+        <v>562</v>
       </c>
       <c r="O85" t="s">
-        <v>605</v>
+        <v>563</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -6838,47 +6872,47 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="C86" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E86" t="s">
         <v>9</v>
       </c>
       <c r="F86" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="G86" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="H86" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I86" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="J86">
         <v>8</v>
       </c>
       <c r="K86" t="s">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="L86">
         <f>8*4</f>
         <v>32</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>392</v>
+        <v>370</v>
       </c>
       <c r="N86" t="s">
-        <v>686</v>
+        <v>638</v>
       </c>
       <c r="O86" t="s">
-        <v>687</v>
+        <v>639</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -6886,13 +6920,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="C87" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D87" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E87" t="s">
         <v>9</v>
@@ -6901,35 +6935,35 @@
         <v>11</v>
       </c>
       <c r="G87" t="s">
-        <v>524</v>
+        <v>501</v>
       </c>
       <c r="H87" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I87" t="s">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="J87">
         <v>4</v>
       </c>
       <c r="K87" t="s">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="L87">
         <f>4*4</f>
         <v>16</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>396</v>
+        <v>374</v>
       </c>
       <c r="N87" t="s">
-        <v>688</v>
+        <v>640</v>
       </c>
       <c r="O87" t="s">
-        <v>670</v>
+        <v>622</v>
       </c>
       <c r="P87" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -6937,13 +6971,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>397</v>
+        <v>375</v>
       </c>
       <c r="C88" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D88" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E88" t="s">
         <v>9</v>
@@ -6952,35 +6986,35 @@
         <v>17</v>
       </c>
       <c r="G88" t="s">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="H88" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I88" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="J88">
         <v>4</v>
       </c>
       <c r="K88" t="s">
-        <v>398</v>
+        <v>376</v>
       </c>
       <c r="L88">
         <f>4*5</f>
         <v>20</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="N88" t="s">
-        <v>671</v>
+        <v>623</v>
       </c>
       <c r="O88" t="s">
-        <v>678</v>
+        <v>630</v>
       </c>
       <c r="Q88" t="s">
-        <v>400</v>
+        <v>378</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -6988,50 +7022,50 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>407</v>
+        <v>385</v>
       </c>
       <c r="C89" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D89" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E89" t="s">
         <v>9</v>
       </c>
       <c r="F89" t="s">
-        <v>408</v>
+        <v>386</v>
       </c>
       <c r="G89" t="s">
-        <v>409</v>
+        <v>387</v>
       </c>
       <c r="H89" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I89" t="s">
-        <v>409</v>
+        <v>387</v>
       </c>
       <c r="J89">
         <v>6</v>
       </c>
       <c r="K89" t="s">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="L89">
         <f>6*3</f>
         <v>18</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>411</v>
+        <v>389</v>
       </c>
       <c r="N89" t="s">
-        <v>690</v>
+        <v>642</v>
       </c>
       <c r="O89" t="s">
-        <v>691</v>
+        <v>643</v>
       </c>
       <c r="P89" t="s">
-        <v>461</v>
+        <v>438</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -7039,13 +7073,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>414</v>
+        <v>392</v>
       </c>
       <c r="C90" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D90" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
@@ -7054,32 +7088,32 @@
         <v>11</v>
       </c>
       <c r="G90" t="s">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="H90" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I90" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="J90">
         <v>3</v>
       </c>
       <c r="K90" t="s">
-        <v>415</v>
+        <v>393</v>
       </c>
       <c r="L90">
         <f>3*4</f>
         <v>12</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>416</v>
+        <v>394</v>
       </c>
       <c r="N90" t="s">
-        <v>546</v>
+        <v>518</v>
       </c>
       <c r="O90" t="s">
-        <v>679</v>
+        <v>631</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -7087,47 +7121,47 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>417</v>
+        <v>395</v>
       </c>
       <c r="C91" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D91" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E91" t="s">
         <v>9</v>
       </c>
       <c r="F91" t="s">
-        <v>418</v>
+        <v>396</v>
       </c>
       <c r="G91" t="s">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="H91" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I91" t="s">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="J91">
         <v>3</v>
       </c>
       <c r="K91" t="s">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="L91">
         <f>6</f>
         <v>6</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>421</v>
+        <v>399</v>
       </c>
       <c r="N91" t="s">
-        <v>538</v>
+        <v>512</v>
       </c>
       <c r="O91" t="s">
-        <v>606</v>
+        <v>564</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -7135,13 +7169,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>463</v>
+        <v>440</v>
       </c>
       <c r="C92" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D92" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E92" t="s">
         <v>9</v>
@@ -7150,31 +7184,31 @@
         <v>11</v>
       </c>
       <c r="G92" t="s">
-        <v>423</v>
+        <v>401</v>
       </c>
       <c r="H92" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I92" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="J92">
         <v>3</v>
       </c>
       <c r="K92" t="s">
-        <v>422</v>
+        <v>400</v>
       </c>
       <c r="L92">
         <v>13</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>424</v>
+        <v>402</v>
       </c>
       <c r="N92" t="s">
-        <v>607</v>
+        <v>565</v>
       </c>
       <c r="O92" t="s">
-        <v>672</v>
+        <v>624</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -7182,10 +7216,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="C93" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D93" t="s">
         <v>12</v>
@@ -7197,32 +7231,32 @@
         <v>11</v>
       </c>
       <c r="G93" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H93" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I93" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J93">
         <v>4</v>
       </c>
       <c r="K93" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="L93">
         <f>158</f>
         <v>158</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="N93" t="s">
-        <v>680</v>
+        <v>632</v>
       </c>
       <c r="O93" t="s">
-        <v>608</v>
+        <v>566</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -7230,50 +7264,50 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>428</v>
+        <v>406</v>
       </c>
       <c r="C94" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D94" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E94" t="s">
         <v>9</v>
       </c>
       <c r="F94" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="G94" t="s">
-        <v>429</v>
+        <v>407</v>
       </c>
       <c r="H94" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I94" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="J94">
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>430</v>
+        <v>408</v>
       </c>
       <c r="L94">
         <f>16</f>
         <v>16</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>431</v>
+        <v>409</v>
       </c>
       <c r="N94" t="s">
-        <v>538</v>
+        <v>512</v>
       </c>
       <c r="O94" t="s">
-        <v>601</v>
+        <v>559</v>
       </c>
       <c r="P94" t="s">
-        <v>460</v>
+        <v>437</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -7281,49 +7315,49 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>432</v>
+        <v>410</v>
       </c>
       <c r="C95" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D95" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E95" t="s">
         <v>9</v>
       </c>
       <c r="F95" t="s">
-        <v>434</v>
+        <v>412</v>
       </c>
       <c r="G95" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="H95" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I95" t="s">
-        <v>528</v>
+        <v>505</v>
       </c>
       <c r="J95">
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="L95">
         <v>6</v>
       </c>
       <c r="M95" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N95" t="s">
-        <v>609</v>
+        <v>567</v>
       </c>
       <c r="O95" t="s">
-        <v>602</v>
+        <v>560</v>
       </c>
       <c r="P95" t="s">
-        <v>459</v>
+        <v>436</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -7331,13 +7365,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>435</v>
+        <v>413</v>
       </c>
       <c r="C96" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D96" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E96" t="s">
         <v>9</v>
@@ -7346,35 +7380,35 @@
         <v>17</v>
       </c>
       <c r="G96" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="H96" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I96" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="J96">
         <v>6</v>
       </c>
       <c r="K96" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="L96">
         <f>6*8</f>
         <v>48</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="N96" t="s">
-        <v>682</v>
+        <v>634</v>
       </c>
       <c r="O96" t="s">
-        <v>689</v>
+        <v>641</v>
       </c>
       <c r="P96" t="s">
-        <v>458</v>
+        <v>435</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
@@ -7382,50 +7416,50 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>439</v>
+        <v>417</v>
       </c>
       <c r="C97" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D97" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E97" t="s">
         <v>9</v>
       </c>
       <c r="F97" t="s">
-        <v>418</v>
+        <v>396</v>
       </c>
       <c r="G97" t="s">
-        <v>529</v>
+        <v>506</v>
       </c>
       <c r="H97" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I97" t="s">
-        <v>529</v>
+        <v>506</v>
       </c>
       <c r="J97">
         <v>4</v>
       </c>
       <c r="K97" t="s">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="L97">
         <f>4*3</f>
         <v>12</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>444</v>
+        <v>422</v>
       </c>
       <c r="N97" t="s">
-        <v>610</v>
+        <v>568</v>
       </c>
       <c r="O97" t="s">
-        <v>611</v>
+        <v>569</v>
       </c>
       <c r="P97" t="s">
-        <v>457</v>
+        <v>434</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
@@ -7433,13 +7467,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>441</v>
+        <v>419</v>
       </c>
       <c r="C98" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D98" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="E98" t="s">
         <v>9</v>
@@ -7448,32 +7482,32 @@
         <v>11</v>
       </c>
       <c r="G98" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H98" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I98" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J98">
         <v>3</v>
       </c>
       <c r="K98" t="s">
-        <v>442</v>
+        <v>420</v>
       </c>
       <c r="L98">
         <f>30</f>
         <v>30</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="N98" t="s">
-        <v>667</v>
+        <v>619</v>
       </c>
       <c r="O98" t="s">
-        <v>692</v>
+        <v>644</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.25">
@@ -7481,13 +7515,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="C99" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D99" t="s">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="E99" t="s">
         <v>9</v>
@@ -7496,35 +7530,35 @@
         <v>11</v>
       </c>
       <c r="G99" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H99" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I99" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J99">
         <v>3</v>
       </c>
       <c r="K99" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="L99">
         <f>15</f>
         <v>15</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="N99" t="s">
-        <v>681</v>
+        <v>633</v>
       </c>
       <c r="O99" t="s">
-        <v>683</v>
+        <v>635</v>
       </c>
       <c r="P99" t="s">
-        <v>456</v>
+        <v>433</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
@@ -7532,50 +7566,50 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="C100" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D100" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E100" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F100" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="G100" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H100" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I100" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J100">
         <v>3</v>
       </c>
       <c r="K100" t="s">
-        <v>449</v>
+        <v>427</v>
       </c>
       <c r="L100">
         <f>60</f>
         <v>60</v>
       </c>
       <c r="M100" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N100" t="s">
-        <v>612</v>
+        <v>570</v>
       </c>
       <c r="O100" t="s">
-        <v>532</v>
+        <v>509</v>
       </c>
       <c r="P100" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.25">
@@ -7583,53 +7617,55 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="C101" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D101" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E101" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F101" t="s">
         <v>17</v>
       </c>
       <c r="G101" t="s">
-        <v>530</v>
+        <v>507</v>
       </c>
       <c r="H101" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I101" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J101">
         <v>3</v>
       </c>
       <c r="K101" t="s">
-        <v>452</v>
+        <v>711</v>
       </c>
       <c r="L101">
         <f>3*4</f>
         <v>12</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>454</v>
+        <v>431</v>
       </c>
       <c r="N101" t="s">
-        <v>536</v>
+        <v>712</v>
       </c>
       <c r="O101" t="s">
-        <v>693</v>
+        <v>713</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B102" s="1"/>
+      <c r="K102" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R101" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q101">
     <sortCondition ref="A2:A101"/>
   </sortState>
@@ -7732,7 +7768,7 @@
   <sheetData>
     <row r="1" spans="1:18" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -7741,10 +7777,10 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
@@ -7771,7 +7807,7 @@
         <v>13</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>19</v>
@@ -7782,46 +7818,46 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J2">
         <v>7</v>
       </c>
       <c r="K2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L2">
         <v>365</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="N2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="O2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -7829,40 +7865,40 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>474</v>
+        <v>451</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="G3" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
       </c>
       <c r="I3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="L3">
         <v>20</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="P3" t="s">
-        <v>471</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -7870,40 +7906,40 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="J4">
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="L4">
         <v>9</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="P4" t="s">
-        <v>472</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -7914,7 +7950,7 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>18</v>
@@ -7926,13 +7962,13 @@
         <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>423</v>
+        <v>401</v>
       </c>
       <c r="I5" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="J5" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="K5">
         <v>4</v>
@@ -7945,10 +7981,10 @@
         <v>20</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -7975,95 +8011,95 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="B4" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="B5" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="B6" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="B7" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
       <c r="B8" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>403</v>
+        <v>381</v>
       </c>
       <c r="B9" t="s">
-        <v>404</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>405</v>
+        <v>383</v>
       </c>
       <c r="B10" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>412</v>
+        <v>390</v>
       </c>
       <c r="B11" t="s">
-        <v>413</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="B12" t="s">
-        <v>466</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>

--- a/goldStandard/_Index.xlsx
+++ b/goldStandard/_Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore-development\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A420EF3-2D76-4FDC-BB6A-9CBA71D7F8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB851249-1EA9-41A9-BDBA-C9A7AC4626CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22046" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
+    <workbookView xWindow="10485" yWindow="4200" windowWidth="37380" windowHeight="12765" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
   </bookViews>
   <sheets>
     <sheet name="In" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Possible" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">In!$A$1:$R$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">In!$A$1:$S$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Out!$B$3:$P$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="718">
   <si>
     <t>ID</t>
   </si>
@@ -1038,9 +1038,6 @@
     <t>LTQ Orbitrap</t>
   </si>
   <si>
-    <t>MaxQuant </t>
-  </si>
-  <si>
     <t>Colonies</t>
   </si>
   <si>
@@ -2173,6 +2170,21 @@
   </si>
   <si>
     <t>G3</t>
+  </si>
+  <si>
+    <t>MS instrument (summary)</t>
+  </si>
+  <si>
+    <t>Orbitrap</t>
+  </si>
+  <si>
+    <t>Orbitrap;Q Exactive</t>
+  </si>
+  <si>
+    <t>TripleTOF</t>
+  </si>
+  <si>
+    <t>ZenoTOF</t>
   </si>
 </sst>
 </file>
@@ -2252,13 +2264,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2586,29 +2597,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}">
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:S102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="27.85546875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="27.85546875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="32.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="38.28515625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="19.140625" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" customWidth="1"/>
-    <col min="16" max="16" width="40.7109375" customWidth="1"/>
-    <col min="17" max="17" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="116.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" customWidth="1"/>
+    <col min="4" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="27.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" customWidth="1"/>
+    <col min="10" max="10" width="27.85546875" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" customWidth="1"/>
+    <col min="12" max="12" width="32.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.140625" customWidth="1"/>
+    <col min="14" max="14" width="38.28515625" customWidth="1"/>
+    <col min="15" max="15" width="19.140625" customWidth="1"/>
+    <col min="16" max="16" width="16.140625" customWidth="1"/>
+    <col min="17" max="17" width="40.7109375" customWidth="1"/>
+    <col min="18" max="18" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="116.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>37</v>
       </c>
@@ -2622,49 +2633,52 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>461</v>
-      </c>
       <c r="H1" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>458</v>
-      </c>
       <c r="J1" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S1" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2678,55 +2692,58 @@
         <v>18</v>
       </c>
       <c r="E2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>215</v>
       </c>
-      <c r="H2" t="s">
-        <v>466</v>
-      </c>
       <c r="I2" t="s">
+        <v>465</v>
+      </c>
+      <c r="J2" t="s">
         <v>215</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>2</v>
       </c>
-      <c r="K2" t="s">
-        <v>672</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>671</v>
+      </c>
+      <c r="M2">
         <f>10</f>
         <v>10</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N2" t="s">
-        <v>598</v>
-      </c>
       <c r="O2" t="s">
-        <v>564</v>
+        <v>597</v>
       </c>
       <c r="P2" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q2" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>20</v>
       </c>
-      <c r="R2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C3" t="s">
         <v>85</v>
@@ -2735,46 +2752,49 @@
         <v>105</v>
       </c>
       <c r="E3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>646</v>
+      </c>
+      <c r="I3" t="s">
+        <v>465</v>
+      </c>
+      <c r="J3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3" t="s">
         <v>647</v>
       </c>
-      <c r="H3" t="s">
-        <v>466</v>
-      </c>
-      <c r="I3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="M3">
+        <v>30</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="O3" t="s">
         <v>648</v>
       </c>
-      <c r="L3">
-        <v>30</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>649</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
         <v>650</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>651</v>
       </c>
-      <c r="Q3" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2788,42 +2808,45 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>11</v>
       </c>
-      <c r="G4" t="s">
-        <v>462</v>
-      </c>
       <c r="H4" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="I4" t="s">
+        <v>465</v>
+      </c>
+      <c r="J4" t="s">
         <v>66</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>3</v>
       </c>
-      <c r="K4" t="s">
-        <v>450</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>449</v>
+      </c>
+      <c r="M4">
         <f>3*3</f>
         <v>9</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
+        <v>572</v>
+      </c>
+      <c r="P4" t="s">
         <v>573</v>
       </c>
-      <c r="O4" t="s">
-        <v>574</v>
-      </c>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2837,44 +2860,47 @@
         <v>29</v>
       </c>
       <c r="E5" t="s">
+        <v>714</v>
+      </c>
+      <c r="F5" t="s">
         <v>9</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>17</v>
       </c>
-      <c r="G5" t="s">
-        <v>464</v>
-      </c>
       <c r="H5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I5" t="s">
-        <v>468</v>
-      </c>
-      <c r="J5">
+        <v>465</v>
+      </c>
+      <c r="J5" t="s">
+        <v>467</v>
+      </c>
+      <c r="K5">
         <v>6</v>
       </c>
-      <c r="K5" t="s">
-        <v>673</v>
-      </c>
-      <c r="L5">
+      <c r="L5" t="s">
+        <v>672</v>
+      </c>
+      <c r="M5">
         <f>6*3</f>
         <v>18</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
+        <v>673</v>
+      </c>
+      <c r="P5" t="s">
         <v>674</v>
       </c>
-      <c r="O5" t="s">
-        <v>675</v>
-      </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2888,46 +2914,49 @@
         <v>33</v>
       </c>
       <c r="E6" t="s">
+        <v>714</v>
+      </c>
+      <c r="F6" t="s">
         <v>9</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>11</v>
       </c>
-      <c r="G6" t="s">
-        <v>463</v>
-      </c>
       <c r="H6" t="s">
+        <v>462</v>
+      </c>
+      <c r="I6" t="s">
+        <v>465</v>
+      </c>
+      <c r="J6" t="s">
         <v>466</v>
       </c>
-      <c r="I6" t="s">
-        <v>467</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6" t="s">
+        <v>675</v>
+      </c>
+      <c r="M6">
+        <v>16</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O6" t="s">
         <v>676</v>
       </c>
-      <c r="L6">
-        <v>16</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="N6" t="s">
+      <c r="P6" t="s">
         <v>677</v>
       </c>
-      <c r="O6" t="s">
-        <v>678</v>
-      </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>36</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2941,47 +2970,50 @@
         <v>39</v>
       </c>
       <c r="E7" t="s">
+        <v>714</v>
+      </c>
+      <c r="F7" t="s">
         <v>9</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>11</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
+        <v>464</v>
+      </c>
+      <c r="I7" t="s">
         <v>465</v>
       </c>
-      <c r="H7" t="s">
-        <v>466</v>
-      </c>
-      <c r="I7" t="s">
-        <v>459</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="J7" t="s">
+        <v>458</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7" t="s">
+        <v>678</v>
+      </c>
+      <c r="M7">
+        <f>K7*4</f>
+        <v>8</v>
+      </c>
+      <c r="N7" t="s">
+        <v>40</v>
+      </c>
+      <c r="O7" t="s">
         <v>679</v>
       </c>
-      <c r="L7">
-        <f>J7*4</f>
-        <v>16</v>
-      </c>
-      <c r="M7" t="s">
-        <v>40</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="P7" t="s">
         <v>680</v>
       </c>
-      <c r="O7" t="s">
-        <v>681</v>
-      </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>41</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2995,45 +3027,48 @@
         <v>43</v>
       </c>
       <c r="E8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s">
         <v>9</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>17</v>
       </c>
-      <c r="G8" t="s">
-        <v>348</v>
-      </c>
       <c r="H8" t="s">
+        <v>347</v>
+      </c>
+      <c r="I8" t="s">
+        <v>465</v>
+      </c>
+      <c r="J8" t="s">
         <v>466</v>
       </c>
-      <c r="I8" t="s">
-        <v>467</v>
-      </c>
-      <c r="J8">
-        <v>2</v>
-      </c>
-      <c r="K8" t="s">
-        <v>682</v>
-      </c>
-      <c r="L8">
+      <c r="K8">
+        <v>4</v>
+      </c>
+      <c r="L8" t="s">
+        <v>681</v>
+      </c>
+      <c r="M8">
         <f>24</f>
         <v>24</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N8" t="s">
+      <c r="O8" t="s">
+        <v>682</v>
+      </c>
+      <c r="P8" t="s">
         <v>683</v>
       </c>
-      <c r="O8" t="s">
-        <v>684</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>46</v>
       </c>
-      <c r="Q8" s="4"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R8" s="4"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3047,47 +3082,50 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F9" t="s">
         <v>48</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>11</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>49</v>
       </c>
-      <c r="H9" t="s">
-        <v>470</v>
-      </c>
       <c r="I9" t="s">
+        <v>469</v>
+      </c>
+      <c r="J9" t="s">
         <v>99</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>3</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>50</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <f>29</f>
         <v>29</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N9" t="s">
-        <v>529</v>
-      </c>
       <c r="O9" t="s">
-        <v>654</v>
+        <v>528</v>
       </c>
       <c r="P9" t="s">
+        <v>653</v>
+      </c>
+      <c r="Q9" t="s">
         <v>46</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3101,43 +3139,46 @@
         <v>53</v>
       </c>
       <c r="E10" t="s">
+        <v>315</v>
+      </c>
+      <c r="F10" t="s">
         <v>48</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>11</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>326</v>
       </c>
-      <c r="H10" t="s">
-        <v>470</v>
-      </c>
       <c r="I10" t="s">
+        <v>469</v>
+      </c>
+      <c r="J10" t="s">
         <v>326</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>7</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
+        <v>692</v>
+      </c>
+      <c r="M10">
+        <v>24</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O10" t="s">
         <v>693</v>
       </c>
-      <c r="L10">
-        <v>24</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="P10" t="s">
         <v>694</v>
       </c>
-      <c r="O10" s="5" t="s">
-        <v>695</v>
-      </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3151,43 +3192,46 @@
         <v>57</v>
       </c>
       <c r="E11" t="s">
+        <v>315</v>
+      </c>
+      <c r="F11" t="s">
         <v>48</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>11</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>99</v>
       </c>
-      <c r="H11" t="s">
-        <v>470</v>
-      </c>
       <c r="I11" t="s">
+        <v>469</v>
+      </c>
+      <c r="J11" t="s">
         <v>99</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>2</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>58</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>33</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="N11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N11" t="s">
-        <v>571</v>
-      </c>
       <c r="O11" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="P11" t="s">
+        <v>574</v>
+      </c>
+      <c r="Q11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3201,41 +3245,44 @@
         <v>61</v>
       </c>
       <c r="E12" t="s">
+        <v>714</v>
+      </c>
+      <c r="F12" t="s">
         <v>48</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>17</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
+        <v>468</v>
+      </c>
+      <c r="I12" t="s">
         <v>469</v>
       </c>
-      <c r="H12" t="s">
-        <v>470</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>116</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>2</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>44</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <f>9</f>
         <v>9</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="N12" t="s">
-        <v>510</v>
-      </c>
       <c r="O12" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+        <v>509</v>
+      </c>
+      <c r="P12" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3249,43 +3296,46 @@
         <v>27</v>
       </c>
       <c r="E13" t="s">
+        <v>714</v>
+      </c>
+      <c r="F13" t="s">
         <v>9</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>17</v>
-      </c>
-      <c r="G13" t="s">
-        <v>471</v>
       </c>
       <c r="H13" t="s">
         <v>470</v>
       </c>
       <c r="I13" t="s">
+        <v>469</v>
+      </c>
+      <c r="J13" t="s">
         <v>66</v>
       </c>
-      <c r="J13">
-        <v>2</v>
-      </c>
-      <c r="K13" t="s">
+      <c r="K13">
+        <v>4</v>
+      </c>
+      <c r="L13" t="s">
+        <v>684</v>
+      </c>
+      <c r="M13">
+        <v>16</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O13" t="s">
         <v>685</v>
       </c>
-      <c r="L13">
-        <v>16</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="P13" t="s">
         <v>686</v>
       </c>
-      <c r="O13" t="s">
-        <v>687</v>
-      </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3299,44 +3349,47 @@
         <v>43</v>
       </c>
       <c r="E14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F14" t="s">
         <v>9</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>11</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>72</v>
       </c>
-      <c r="H14" t="s">
-        <v>470</v>
-      </c>
       <c r="I14" t="s">
+        <v>469</v>
+      </c>
+      <c r="J14" t="s">
         <v>72</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>4</v>
       </c>
-      <c r="K14" t="s">
-        <v>688</v>
-      </c>
-      <c r="L14">
+      <c r="L14" t="s">
+        <v>687</v>
+      </c>
+      <c r="M14">
         <f>8*4</f>
         <v>32</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="N14" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="N14" t="s">
-        <v>690</v>
       </c>
       <c r="O14" t="s">
         <v>689</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="P14" t="s">
+        <v>688</v>
+      </c>
+      <c r="R14" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3350,43 +3403,46 @@
         <v>57</v>
       </c>
       <c r="E15" t="s">
+        <v>315</v>
+      </c>
+      <c r="F15" t="s">
         <v>9</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>11</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>74</v>
       </c>
-      <c r="H15" t="s">
-        <v>470</v>
-      </c>
       <c r="I15" t="s">
+        <v>469</v>
+      </c>
+      <c r="J15" t="s">
         <v>74</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>2</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
+        <v>690</v>
+      </c>
+      <c r="M15">
+        <v>10</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O15" t="s">
+        <v>511</v>
+      </c>
+      <c r="P15" t="s">
         <v>691</v>
       </c>
-      <c r="L15">
-        <v>10</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="N15" t="s">
-        <v>512</v>
-      </c>
-      <c r="O15" t="s">
-        <v>692</v>
-      </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3400,40 +3456,43 @@
         <v>94</v>
       </c>
       <c r="E16" t="s">
+        <v>715</v>
+      </c>
+      <c r="F16" t="s">
         <v>9</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>11</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>66</v>
       </c>
-      <c r="H16" t="s">
-        <v>470</v>
-      </c>
       <c r="I16" t="s">
+        <v>469</v>
+      </c>
+      <c r="J16" t="s">
         <v>66</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>3</v>
       </c>
-      <c r="K16" t="s">
-        <v>656</v>
-      </c>
-      <c r="L16">
+      <c r="L16" t="s">
+        <v>655</v>
+      </c>
+      <c r="M16">
         <v>9</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N16" t="s">
-        <v>517</v>
-      </c>
       <c r="O16" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+        <v>516</v>
+      </c>
+      <c r="P16" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3447,40 +3506,43 @@
         <v>27</v>
       </c>
       <c r="E17" t="s">
+        <v>714</v>
+      </c>
+      <c r="F17" t="s">
         <v>9</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>11</v>
       </c>
-      <c r="G17" t="s">
-        <v>473</v>
-      </c>
       <c r="H17" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="I17" t="s">
-        <v>415</v>
-      </c>
-      <c r="J17">
+        <v>469</v>
+      </c>
+      <c r="J17" t="s">
+        <v>414</v>
+      </c>
+      <c r="K17">
         <v>2</v>
       </c>
-      <c r="K17" t="s">
-        <v>344</v>
-      </c>
-      <c r="L17">
+      <c r="L17" t="s">
+        <v>343</v>
+      </c>
+      <c r="M17">
         <v>46</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="N17" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="N17" t="s">
-        <v>619</v>
-      </c>
       <c r="O17" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+      <c r="P17" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3494,43 +3556,46 @@
         <v>61</v>
       </c>
       <c r="E18" t="s">
+        <v>714</v>
+      </c>
+      <c r="F18" t="s">
         <v>9</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>11</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>99</v>
       </c>
-      <c r="H18" t="s">
-        <v>466</v>
-      </c>
       <c r="I18" t="s">
+        <v>465</v>
+      </c>
+      <c r="J18" t="s">
         <v>99</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>2</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
+        <v>660</v>
+      </c>
+      <c r="M18">
+        <v>6</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="O18" t="s">
         <v>661</v>
       </c>
-      <c r="L18">
-        <v>6</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="N18" t="s">
-        <v>662</v>
-      </c>
-      <c r="O18" t="s">
-        <v>513</v>
-      </c>
-      <c r="R18" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="P18" t="s">
+        <v>512</v>
+      </c>
+      <c r="S18" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3544,44 +3609,47 @@
         <v>27</v>
       </c>
       <c r="E19" t="s">
+        <v>714</v>
+      </c>
+      <c r="F19" t="s">
         <v>9</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>11</v>
       </c>
-      <c r="G19" t="s">
-        <v>472</v>
-      </c>
       <c r="H19" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="I19" t="s">
+        <v>465</v>
+      </c>
+      <c r="J19" t="s">
         <v>116</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>3</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>102</v>
       </c>
-      <c r="L19">
-        <f>J19*4</f>
+      <c r="M19">
+        <f>K19*4</f>
         <v>12</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>40</v>
       </c>
-      <c r="N19" t="s">
-        <v>530</v>
-      </c>
       <c r="O19" t="s">
-        <v>536</v>
-      </c>
-      <c r="Q19" t="s">
+        <v>529</v>
+      </c>
+      <c r="P19" t="s">
+        <v>535</v>
+      </c>
+      <c r="R19" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3595,46 +3663,49 @@
         <v>105</v>
       </c>
       <c r="E20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" t="s">
         <v>9</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>11</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
+        <v>473</v>
+      </c>
+      <c r="I20" t="s">
+        <v>465</v>
+      </c>
+      <c r="J20" t="s">
         <v>474</v>
       </c>
-      <c r="H20" t="s">
-        <v>466</v>
-      </c>
-      <c r="I20" t="s">
-        <v>475</v>
-      </c>
-      <c r="J20">
+      <c r="K20">
         <v>2</v>
       </c>
-      <c r="K20" t="s">
-        <v>664</v>
-      </c>
-      <c r="L20">
+      <c r="L20" t="s">
+        <v>663</v>
+      </c>
+      <c r="M20">
         <v>6</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="N20" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="N20" t="s">
-        <v>663</v>
-      </c>
       <c r="O20" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q20" t="s">
+        <v>662</v>
+      </c>
+      <c r="P20" t="s">
+        <v>521</v>
+      </c>
+      <c r="R20" t="s">
         <v>107</v>
       </c>
-      <c r="R20" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S20" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3648,44 +3719,47 @@
         <v>29</v>
       </c>
       <c r="E21" t="s">
+        <v>714</v>
+      </c>
+      <c r="F21" t="s">
         <v>9</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>138</v>
       </c>
-      <c r="G21" t="s">
-        <v>476</v>
-      </c>
       <c r="H21" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="I21" t="s">
-        <v>476</v>
-      </c>
-      <c r="J21">
+        <v>465</v>
+      </c>
+      <c r="J21" t="s">
+        <v>475</v>
+      </c>
+      <c r="K21">
         <v>8</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>144</v>
       </c>
-      <c r="L21">
-        <f>J21*4</f>
+      <c r="M21">
+        <f>K21*4</f>
         <v>32</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="N21" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="N21" t="s">
-        <v>511</v>
-      </c>
       <c r="O21" t="s">
-        <v>538</v>
-      </c>
-      <c r="Q21" t="s">
+        <v>510</v>
+      </c>
+      <c r="P21" t="s">
+        <v>537</v>
+      </c>
+      <c r="R21" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3699,44 +3773,47 @@
         <v>111</v>
       </c>
       <c r="E22" t="s">
+        <v>717</v>
+      </c>
+      <c r="F22" t="s">
         <v>112</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>17</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>113</v>
       </c>
-      <c r="H22" t="s">
-        <v>470</v>
-      </c>
       <c r="I22" t="s">
+        <v>469</v>
+      </c>
+      <c r="J22" t="s">
         <v>196</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>2</v>
       </c>
-      <c r="K22" t="s">
-        <v>665</v>
-      </c>
-      <c r="L22">
-        <f>J22*11</f>
+      <c r="L22" t="s">
+        <v>664</v>
+      </c>
+      <c r="M22">
+        <f>K22*11</f>
         <v>22</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>40</v>
       </c>
-      <c r="N22" t="s">
-        <v>546</v>
-      </c>
       <c r="O22" t="s">
-        <v>523</v>
+        <v>545</v>
       </c>
       <c r="P22" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q22" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3750,49 +3827,52 @@
         <v>105</v>
       </c>
       <c r="E23" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" t="s">
         <v>112</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>11</v>
       </c>
-      <c r="G23" t="s">
-        <v>477</v>
-      </c>
       <c r="H23" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="I23" t="s">
+        <v>465</v>
+      </c>
+      <c r="J23" t="s">
         <v>116</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>4</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>117</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <f>19*2+16*2+1</f>
         <v>71</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="N23" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="O23" t="s">
         <v>579</v>
       </c>
-      <c r="N23" t="s">
-        <v>580</v>
-      </c>
-      <c r="O23" t="s">
-        <v>576</v>
-      </c>
-      <c r="Q23" t="s">
+      <c r="P23" t="s">
+        <v>575</v>
+      </c>
+      <c r="R23" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C24" t="s">
         <v>86</v>
@@ -3801,41 +3881,44 @@
         <v>43</v>
       </c>
       <c r="E24" t="s">
+        <v>105</v>
+      </c>
+      <c r="F24" t="s">
         <v>112</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>11</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
+        <v>477</v>
+      </c>
+      <c r="I24" t="s">
+        <v>465</v>
+      </c>
+      <c r="J24" t="s">
         <v>478</v>
       </c>
-      <c r="H24" t="s">
-        <v>466</v>
-      </c>
-      <c r="I24" t="s">
-        <v>479</v>
-      </c>
-      <c r="J24">
+      <c r="K24">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
+        <v>451</v>
+      </c>
+      <c r="M24">
+        <v>10</v>
+      </c>
+      <c r="N24" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="L24">
-        <v>10</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="N24" t="s">
-        <v>511</v>
-      </c>
       <c r="O24" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+      <c r="P24" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3849,40 +3932,43 @@
         <v>122</v>
       </c>
       <c r="E25" t="s">
+        <v>315</v>
+      </c>
+      <c r="F25" t="s">
         <v>112</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>11</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>123</v>
       </c>
-      <c r="H25" t="s">
-        <v>470</v>
-      </c>
       <c r="I25" t="s">
+        <v>469</v>
+      </c>
+      <c r="J25" t="s">
         <v>123</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>3</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>124</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>46</v>
       </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>40</v>
       </c>
-      <c r="N25" t="s">
-        <v>508</v>
-      </c>
       <c r="O25" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+        <v>507</v>
+      </c>
+      <c r="P25" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3896,40 +3982,43 @@
         <v>53</v>
       </c>
       <c r="E26" t="s">
+        <v>315</v>
+      </c>
+      <c r="F26" t="s">
         <v>112</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>11</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>99</v>
       </c>
-      <c r="H26" t="s">
-        <v>470</v>
-      </c>
       <c r="I26" t="s">
+        <v>469</v>
+      </c>
+      <c r="J26" t="s">
         <v>99</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>2</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
+        <v>695</v>
+      </c>
+      <c r="M26">
+        <v>22</v>
+      </c>
+      <c r="N26" t="s">
+        <v>40</v>
+      </c>
+      <c r="O26" t="s">
+        <v>599</v>
+      </c>
+      <c r="P26" t="s">
         <v>696</v>
       </c>
-      <c r="L26">
-        <v>22</v>
-      </c>
-      <c r="M26" t="s">
-        <v>40</v>
-      </c>
-      <c r="N26" t="s">
-        <v>600</v>
-      </c>
-      <c r="O26" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3943,46 +4032,49 @@
         <v>39</v>
       </c>
       <c r="E27" t="s">
+        <v>714</v>
+      </c>
+      <c r="F27" t="s">
         <v>112</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>17</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>316</v>
       </c>
-      <c r="H27" t="s">
-        <v>466</v>
-      </c>
       <c r="I27" t="s">
+        <v>465</v>
+      </c>
+      <c r="J27" t="s">
         <v>66</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>5</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>127</v>
       </c>
-      <c r="L27">
-        <f>J27*4</f>
+      <c r="M27">
+        <f>K27*4</f>
         <v>20</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" t="s">
         <v>40</v>
       </c>
-      <c r="N27" t="s">
-        <v>583</v>
-      </c>
       <c r="O27" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+        <v>582</v>
+      </c>
+      <c r="P27" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C28" t="s">
         <v>86</v>
@@ -3991,40 +4083,43 @@
         <v>105</v>
       </c>
       <c r="E28" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" t="s">
         <v>112</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>17</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>215</v>
       </c>
-      <c r="H28" t="s">
-        <v>466</v>
-      </c>
       <c r="I28" t="s">
+        <v>465</v>
+      </c>
+      <c r="J28" t="s">
         <v>215</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>4</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
+        <v>454</v>
+      </c>
+      <c r="M28">
+        <v>23</v>
+      </c>
+      <c r="N28" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="L28">
-        <v>23</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="N28" t="s">
-        <v>533</v>
-      </c>
       <c r="O28" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+        <v>532</v>
+      </c>
+      <c r="P28" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4038,41 +4133,44 @@
         <v>57</v>
       </c>
       <c r="E29" t="s">
+        <v>315</v>
+      </c>
+      <c r="F29" t="s">
         <v>112</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>11</v>
       </c>
-      <c r="G29" t="s">
-        <v>481</v>
-      </c>
       <c r="H29" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="I29" t="s">
-        <v>480</v>
-      </c>
-      <c r="J29">
+        <v>465</v>
+      </c>
+      <c r="J29" t="s">
+        <v>479</v>
+      </c>
+      <c r="K29">
         <v>4</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>132</v>
       </c>
-      <c r="L29">
-        <f>J29*3</f>
+      <c r="M29">
+        <f>K29*3</f>
         <v>12</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
         <v>40</v>
       </c>
-      <c r="N29" t="s">
+      <c r="O29" t="s">
+        <v>697</v>
+      </c>
+      <c r="P29" t="s">
         <v>698</v>
       </c>
-      <c r="O29" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4086,41 +4184,44 @@
         <v>134</v>
       </c>
       <c r="E30" t="s">
+        <v>714</v>
+      </c>
+      <c r="F30" t="s">
         <v>112</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>11</v>
       </c>
-      <c r="G30" t="s">
-        <v>482</v>
-      </c>
       <c r="H30" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="I30" t="s">
-        <v>459</v>
-      </c>
-      <c r="J30">
+        <v>465</v>
+      </c>
+      <c r="J30" t="s">
+        <v>458</v>
+      </c>
+      <c r="K30">
         <v>3</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>135</v>
       </c>
-      <c r="L30">
-        <f>J30*4</f>
+      <c r="M30">
+        <f>K30*4</f>
         <v>12</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="N30" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="N30" t="s">
-        <v>531</v>
-      </c>
       <c r="O30" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+        <v>530</v>
+      </c>
+      <c r="P30" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4134,41 +4235,44 @@
         <v>139</v>
       </c>
       <c r="E31" t="s">
+        <v>139</v>
+      </c>
+      <c r="F31" t="s">
         <v>112</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>138</v>
       </c>
-      <c r="G31" t="s">
-        <v>476</v>
-      </c>
       <c r="H31" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="I31" t="s">
-        <v>476</v>
-      </c>
-      <c r="J31">
+        <v>465</v>
+      </c>
+      <c r="J31" t="s">
+        <v>475</v>
+      </c>
+      <c r="K31">
         <v>4</v>
       </c>
-      <c r="K31" t="s">
+      <c r="L31" t="s">
         <v>140</v>
       </c>
-      <c r="L31">
-        <f>J31*4</f>
+      <c r="M31">
+        <f>K31*4</f>
         <v>16</v>
       </c>
-      <c r="M31" s="1" t="s">
+      <c r="N31" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="N31" t="s">
-        <v>549</v>
-      </c>
       <c r="O31" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+      <c r="P31" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4182,44 +4286,47 @@
         <v>57</v>
       </c>
       <c r="E32" t="s">
+        <v>315</v>
+      </c>
+      <c r="F32" t="s">
         <v>112</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>17</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>146</v>
       </c>
-      <c r="H32" t="s">
-        <v>470</v>
-      </c>
       <c r="I32" t="s">
+        <v>469</v>
+      </c>
+      <c r="J32" t="s">
         <v>116</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>4</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" t="s">
         <v>147</v>
       </c>
-      <c r="L32">
-        <f>J32*4</f>
+      <c r="M32">
+        <f>K32*4</f>
         <v>16</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="N32" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="N32" t="s">
-        <v>535</v>
-      </c>
       <c r="O32" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
       <c r="P32" t="s">
+        <v>547</v>
+      </c>
+      <c r="Q32" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4233,42 +4340,45 @@
         <v>151</v>
       </c>
       <c r="E33" t="s">
+        <v>714</v>
+      </c>
+      <c r="F33" t="s">
         <v>112</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>11</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
+        <v>482</v>
+      </c>
+      <c r="I33" t="s">
+        <v>465</v>
+      </c>
+      <c r="J33" t="s">
         <v>483</v>
       </c>
-      <c r="H33" t="s">
-        <v>466</v>
-      </c>
-      <c r="I33" t="s">
-        <v>484</v>
-      </c>
-      <c r="J33">
+      <c r="K33">
         <f>3</f>
         <v>3</v>
       </c>
-      <c r="K33" t="s">
+      <c r="L33" t="s">
         <v>152</v>
       </c>
-      <c r="L33">
-        <f>J33*3</f>
+      <c r="M33">
+        <f>K33*3</f>
         <v>9</v>
       </c>
-      <c r="M33" s="1" t="s">
+      <c r="N33" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="N33" t="s">
-        <v>511</v>
-      </c>
       <c r="O33" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+      <c r="P33" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4282,41 +4392,44 @@
         <v>27</v>
       </c>
       <c r="E34" t="s">
+        <v>714</v>
+      </c>
+      <c r="F34" t="s">
         <v>112</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>17</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>155</v>
       </c>
-      <c r="H34" t="s">
-        <v>470</v>
-      </c>
       <c r="I34" t="s">
-        <v>479</v>
-      </c>
-      <c r="J34">
+        <v>469</v>
+      </c>
+      <c r="J34" t="s">
+        <v>478</v>
+      </c>
+      <c r="K34">
         <v>4</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L34" t="s">
         <v>156</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <f>11</f>
         <v>11</v>
       </c>
-      <c r="M34" s="1" t="s">
+      <c r="N34" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="N34" t="s">
-        <v>511</v>
-      </c>
       <c r="O34" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+      <c r="P34" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4330,41 +4443,44 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
+        <v>105</v>
+      </c>
+      <c r="F35" t="s">
         <v>112</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>11</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>159</v>
       </c>
-      <c r="H35" t="s">
-        <v>470</v>
-      </c>
       <c r="I35" t="s">
-        <v>475</v>
-      </c>
-      <c r="J35">
+        <v>469</v>
+      </c>
+      <c r="J35" t="s">
+        <v>474</v>
+      </c>
+      <c r="K35">
         <v>3</v>
       </c>
-      <c r="K35" t="s">
+      <c r="L35" t="s">
         <v>160</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <f>9</f>
         <v>9</v>
       </c>
-      <c r="M35" t="s">
+      <c r="N35" t="s">
         <v>40</v>
       </c>
-      <c r="N35" t="s">
-        <v>532</v>
-      </c>
       <c r="O35" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+      <c r="P35" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4378,41 +4494,44 @@
         <v>164</v>
       </c>
       <c r="E36" t="s">
+        <v>315</v>
+      </c>
+      <c r="F36" t="s">
         <v>112</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>11</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>163</v>
       </c>
-      <c r="H36" t="s">
-        <v>470</v>
-      </c>
       <c r="I36" t="s">
+        <v>469</v>
+      </c>
+      <c r="J36" t="s">
         <v>163</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>2</v>
       </c>
-      <c r="K36" t="s">
-        <v>658</v>
-      </c>
-      <c r="L36">
+      <c r="L36" t="s">
+        <v>657</v>
+      </c>
+      <c r="M36">
         <f>8</f>
         <v>8</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="N36" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="N36" t="s">
-        <v>516</v>
-      </c>
       <c r="O36" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+      <c r="P36" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4426,47 +4545,50 @@
         <v>61</v>
       </c>
       <c r="E37" t="s">
+        <v>714</v>
+      </c>
+      <c r="F37" t="s">
         <v>112</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>11</v>
       </c>
-      <c r="G37" t="s">
-        <v>485</v>
-      </c>
       <c r="H37" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="I37" t="s">
+        <v>469</v>
+      </c>
+      <c r="J37" t="s">
         <v>116</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>2</v>
       </c>
-      <c r="K37" t="s">
-        <v>666</v>
-      </c>
-      <c r="L37">
+      <c r="L37" t="s">
+        <v>665</v>
+      </c>
+      <c r="M37">
         <f>25*2</f>
         <v>50</v>
       </c>
-      <c r="M37" s="1" t="s">
+      <c r="N37" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="N37" t="s">
-        <v>667</v>
-      </c>
       <c r="O37" t="s">
-        <v>528</v>
+        <v>666</v>
       </c>
       <c r="P37" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q37" t="s">
         <v>166</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="R37" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4480,41 +4602,44 @@
         <v>27</v>
       </c>
       <c r="E38" t="s">
+        <v>714</v>
+      </c>
+      <c r="F38" t="s">
         <v>112</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>17</v>
       </c>
-      <c r="G38" t="s">
-        <v>486</v>
-      </c>
       <c r="H38" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="I38" t="s">
+        <v>465</v>
+      </c>
+      <c r="J38" t="s">
         <v>74</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>2</v>
       </c>
-      <c r="K38" t="s">
-        <v>702</v>
-      </c>
-      <c r="L38">
+      <c r="L38" t="s">
+        <v>701</v>
+      </c>
+      <c r="M38">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="M38" s="1" t="s">
+      <c r="N38" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="N38" t="s">
+      <c r="O38" t="s">
+        <v>699</v>
+      </c>
+      <c r="P38" t="s">
         <v>700</v>
       </c>
-      <c r="O38" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4528,41 +4653,44 @@
         <v>172</v>
       </c>
       <c r="E39" t="s">
+        <v>315</v>
+      </c>
+      <c r="F39" t="s">
         <v>112</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>11</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>173</v>
       </c>
-      <c r="H39" t="s">
-        <v>466</v>
-      </c>
       <c r="I39" t="s">
+        <v>465</v>
+      </c>
+      <c r="J39" t="s">
         <v>66</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>4</v>
       </c>
-      <c r="K39" t="s">
+      <c r="L39" t="s">
         <v>174</v>
       </c>
-      <c r="L39">
-        <f>J39*3</f>
+      <c r="M39">
+        <f>K39*3</f>
         <v>12</v>
       </c>
-      <c r="M39" s="1" t="s">
+      <c r="N39" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="N39" t="s">
-        <v>581</v>
-      </c>
       <c r="O39" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+        <v>580</v>
+      </c>
+      <c r="P39" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4576,44 +4704,47 @@
         <v>53</v>
       </c>
       <c r="E40" t="s">
+        <v>315</v>
+      </c>
+      <c r="F40" t="s">
         <v>112</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>11</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>123</v>
       </c>
-      <c r="H40" t="s">
-        <v>470</v>
-      </c>
       <c r="I40" t="s">
+        <v>469</v>
+      </c>
+      <c r="J40" t="s">
         <v>123</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>4</v>
       </c>
-      <c r="K40" t="s">
+      <c r="L40" t="s">
         <v>177</v>
       </c>
-      <c r="L40">
-        <f>J40*10</f>
+      <c r="M40">
+        <f>K40*10</f>
         <v>40</v>
       </c>
-      <c r="M40" s="1" t="s">
+      <c r="N40" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="N40" t="s">
-        <v>584</v>
-      </c>
       <c r="O40" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="P40" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q40" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4627,47 +4758,50 @@
         <v>57</v>
       </c>
       <c r="E41" t="s">
+        <v>315</v>
+      </c>
+      <c r="F41" t="s">
         <v>112</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>17</v>
       </c>
-      <c r="G41" t="s">
-        <v>487</v>
-      </c>
       <c r="H41" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="I41" t="s">
+        <v>469</v>
+      </c>
+      <c r="J41" t="s">
         <v>66</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>4</v>
       </c>
-      <c r="K41" t="s">
+      <c r="L41" t="s">
         <v>181</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <f>24</f>
         <v>24</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="N41" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="N41" t="s">
-        <v>539</v>
-      </c>
       <c r="O41" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="P41" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q41" t="s">
         <v>183</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="R41" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4681,44 +4815,47 @@
         <v>105</v>
       </c>
       <c r="E42" t="s">
+        <v>105</v>
+      </c>
+      <c r="F42" t="s">
         <v>9</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>11</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
+        <v>473</v>
+      </c>
+      <c r="I42" t="s">
+        <v>465</v>
+      </c>
+      <c r="J42" t="s">
         <v>474</v>
       </c>
-      <c r="H42" t="s">
-        <v>466</v>
-      </c>
-      <c r="I42" t="s">
-        <v>475</v>
-      </c>
-      <c r="J42">
+      <c r="K42">
         <v>2</v>
       </c>
-      <c r="K42" t="s">
-        <v>706</v>
-      </c>
-      <c r="L42">
+      <c r="L42" t="s">
+        <v>705</v>
+      </c>
+      <c r="M42">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="M42" s="1" t="s">
+      <c r="N42" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="N42" t="s">
-        <v>543</v>
-      </c>
       <c r="O42" t="s">
-        <v>707</v>
-      </c>
-      <c r="Q42" t="s">
+        <v>542</v>
+      </c>
+      <c r="P42" t="s">
+        <v>706</v>
+      </c>
+      <c r="R42" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4732,44 +4869,47 @@
         <v>186</v>
       </c>
       <c r="E43" t="s">
+        <v>716</v>
+      </c>
+      <c r="F43" t="s">
         <v>112</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>11</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>99</v>
       </c>
-      <c r="H43" t="s">
-        <v>470</v>
-      </c>
       <c r="I43" t="s">
+        <v>469</v>
+      </c>
+      <c r="J43" t="s">
         <v>99</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>2</v>
       </c>
-      <c r="K43" t="s">
+      <c r="L43" t="s">
         <v>187</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <f>35</f>
         <v>35</v>
       </c>
-      <c r="M43" s="1" t="s">
+      <c r="N43" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="N43" t="s">
-        <v>578</v>
-      </c>
       <c r="O43" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="P43" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q43" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4783,43 +4923,46 @@
         <v>18</v>
       </c>
       <c r="E44" t="s">
+        <v>105</v>
+      </c>
+      <c r="F44" t="s">
         <v>112</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>11</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>191</v>
       </c>
-      <c r="H44" t="s">
-        <v>470</v>
-      </c>
       <c r="I44" t="s">
+        <v>469</v>
+      </c>
+      <c r="J44" t="s">
         <v>196</v>
       </c>
-      <c r="J44">
+      <c r="K44">
         <v>3</v>
       </c>
-      <c r="K44" t="s">
+      <c r="L44" t="s">
         <v>192</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>29</v>
       </c>
-      <c r="M44" s="1" t="s">
+      <c r="N44" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="N44" t="s">
-        <v>590</v>
-      </c>
       <c r="O44" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="P44" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q44" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4833,43 +4976,46 @@
         <v>18</v>
       </c>
       <c r="E45" t="s">
+        <v>105</v>
+      </c>
+      <c r="F45" t="s">
         <v>112</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>11</v>
       </c>
-      <c r="G45" t="s">
-        <v>488</v>
-      </c>
       <c r="H45" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="I45" t="s">
+        <v>469</v>
+      </c>
+      <c r="J45" t="s">
         <v>196</v>
       </c>
-      <c r="J45">
+      <c r="K45">
         <v>3</v>
       </c>
-      <c r="K45" t="s">
+      <c r="L45" t="s">
         <v>192</v>
       </c>
-      <c r="L45">
+      <c r="M45">
         <v>28</v>
       </c>
-      <c r="M45" s="1" t="s">
+      <c r="N45" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="N45" t="s">
-        <v>590</v>
-      </c>
       <c r="O45" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="P45" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q45" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4883,44 +5029,47 @@
         <v>111</v>
       </c>
       <c r="E46" t="s">
+        <v>717</v>
+      </c>
+      <c r="F46" t="s">
         <v>112</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>11</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
+        <v>488</v>
+      </c>
+      <c r="I46" t="s">
+        <v>465</v>
+      </c>
+      <c r="J46" t="s">
         <v>489</v>
       </c>
-      <c r="H46" t="s">
-        <v>466</v>
-      </c>
-      <c r="I46" t="s">
-        <v>490</v>
-      </c>
-      <c r="J46">
+      <c r="K46">
         <v>6</v>
       </c>
-      <c r="K46" t="s">
-        <v>591</v>
-      </c>
-      <c r="L46">
+      <c r="L46" t="s">
+        <v>590</v>
+      </c>
+      <c r="M46">
         <f>6*3</f>
         <v>18</v>
       </c>
-      <c r="M46" s="1" t="s">
+      <c r="N46" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="N46" t="s">
-        <v>593</v>
       </c>
       <c r="O46" t="s">
         <v>592</v>
       </c>
       <c r="P46" t="s">
+        <v>591</v>
+      </c>
+      <c r="Q46" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4934,43 +5083,46 @@
         <v>18</v>
       </c>
       <c r="E47" t="s">
+        <v>105</v>
+      </c>
+      <c r="F47" t="s">
         <v>112</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>11</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>202</v>
       </c>
-      <c r="H47" t="s">
-        <v>470</v>
-      </c>
       <c r="I47" t="s">
-        <v>415</v>
-      </c>
-      <c r="J47">
+        <v>469</v>
+      </c>
+      <c r="J47" t="s">
+        <v>414</v>
+      </c>
+      <c r="K47">
         <v>2</v>
       </c>
-      <c r="K47" t="s">
+      <c r="L47" t="s">
         <v>203</v>
       </c>
-      <c r="L47">
+      <c r="M47">
         <v>21</v>
       </c>
-      <c r="M47" s="1" t="s">
+      <c r="N47" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="N47" t="s">
-        <v>540</v>
-      </c>
       <c r="O47" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="P47" t="s">
+        <v>550</v>
+      </c>
+      <c r="Q47" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4984,40 +5136,43 @@
         <v>207</v>
       </c>
       <c r="E48" t="s">
+        <v>105</v>
+      </c>
+      <c r="F48" t="s">
         <v>112</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>17</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>208</v>
       </c>
-      <c r="H48" t="s">
-        <v>470</v>
-      </c>
       <c r="I48" t="s">
+        <v>469</v>
+      </c>
+      <c r="J48" t="s">
         <v>99</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>2</v>
       </c>
-      <c r="K48" t="s">
+      <c r="L48" t="s">
         <v>63</v>
       </c>
-      <c r="L48">
+      <c r="M48">
         <v>8</v>
       </c>
-      <c r="M48" s="1" t="s">
+      <c r="N48" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="N48" t="s">
-        <v>511</v>
-      </c>
       <c r="O48" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+      <c r="P48" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5031,44 +5186,47 @@
         <v>39</v>
       </c>
       <c r="E49" t="s">
+        <v>714</v>
+      </c>
+      <c r="F49" t="s">
         <v>112</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>11</v>
       </c>
-      <c r="G49" t="s">
-        <v>491</v>
-      </c>
       <c r="H49" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="I49" t="s">
+        <v>465</v>
+      </c>
+      <c r="J49" t="s">
         <v>99</v>
       </c>
-      <c r="J49">
+      <c r="K49">
         <v>6</v>
       </c>
-      <c r="K49" t="s">
+      <c r="L49" t="s">
         <v>211</v>
       </c>
-      <c r="L49">
-        <f>J49*4</f>
+      <c r="M49">
+        <f>K49*4</f>
         <v>24</v>
       </c>
-      <c r="M49" s="1" t="s">
+      <c r="N49" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="N49" t="s">
-        <v>594</v>
-      </c>
       <c r="O49" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="P49" t="s">
+        <v>584</v>
+      </c>
+      <c r="Q49" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5082,45 +5240,48 @@
         <v>18</v>
       </c>
       <c r="E50" t="s">
+        <v>105</v>
+      </c>
+      <c r="F50" t="s">
         <v>112</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>17</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>215</v>
       </c>
-      <c r="H50" t="s">
-        <v>466</v>
-      </c>
       <c r="I50" t="s">
+        <v>465</v>
+      </c>
+      <c r="J50" t="s">
         <v>215</v>
       </c>
-      <c r="J50">
+      <c r="K50">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="K50" t="s">
+      <c r="L50" t="s">
         <v>216</v>
       </c>
-      <c r="L50">
-        <f>J50*3</f>
+      <c r="M50">
+        <f>K50*3</f>
         <v>18</v>
       </c>
-      <c r="M50" s="1" t="s">
+      <c r="N50" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="N50" t="s">
-        <v>541</v>
-      </c>
       <c r="O50" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="P50" t="s">
+        <v>555</v>
+      </c>
+      <c r="Q50" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5134,45 +5295,48 @@
         <v>111</v>
       </c>
       <c r="E51" t="s">
+        <v>717</v>
+      </c>
+      <c r="F51" t="s">
         <v>112</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>11</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
+        <v>488</v>
+      </c>
+      <c r="I51" t="s">
+        <v>465</v>
+      </c>
+      <c r="J51" t="s">
         <v>489</v>
       </c>
-      <c r="H51" t="s">
-        <v>466</v>
-      </c>
-      <c r="I51" t="s">
-        <v>490</v>
-      </c>
-      <c r="J51">
+      <c r="K51">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="K51" t="s">
+      <c r="L51" t="s">
         <v>220</v>
       </c>
-      <c r="L51">
-        <f>J51*3</f>
+      <c r="M51">
+        <f>K51*3</f>
         <v>6</v>
       </c>
-      <c r="M51" s="1" t="s">
+      <c r="N51" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="N51" t="s">
-        <v>586</v>
-      </c>
       <c r="O51" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="P51" t="s">
+        <v>588</v>
+      </c>
+      <c r="Q51" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5186,43 +5350,46 @@
         <v>18</v>
       </c>
       <c r="E52" t="s">
+        <v>105</v>
+      </c>
+      <c r="F52" t="s">
         <v>112</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>17</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>215</v>
       </c>
-      <c r="H52" t="s">
-        <v>466</v>
-      </c>
       <c r="I52" t="s">
+        <v>465</v>
+      </c>
+      <c r="J52" t="s">
         <v>215</v>
       </c>
-      <c r="J52">
+      <c r="K52">
         <v>2</v>
       </c>
-      <c r="K52" t="s">
+      <c r="L52" t="s">
         <v>223</v>
       </c>
-      <c r="L52">
+      <c r="M52">
         <v>6</v>
       </c>
-      <c r="M52" t="s">
+      <c r="N52" t="s">
         <v>40</v>
       </c>
-      <c r="N52" t="s">
-        <v>508</v>
-      </c>
       <c r="O52" t="s">
-        <v>552</v>
+        <v>507</v>
       </c>
       <c r="P52" t="s">
+        <v>551</v>
+      </c>
+      <c r="Q52" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5236,46 +5403,49 @@
         <v>186</v>
       </c>
       <c r="E53" t="s">
+        <v>716</v>
+      </c>
+      <c r="F53" t="s">
         <v>235</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>11</v>
       </c>
-      <c r="G53" t="s">
-        <v>492</v>
-      </c>
       <c r="H53" t="s">
-        <v>470</v>
+        <v>491</v>
       </c>
       <c r="I53" t="s">
+        <v>469</v>
+      </c>
+      <c r="J53" t="s">
         <v>236</v>
       </c>
-      <c r="J53">
+      <c r="K53">
         <v>3</v>
       </c>
-      <c r="K53" t="s">
+      <c r="L53" t="s">
+        <v>667</v>
+      </c>
+      <c r="M53">
+        <v>69</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="O53" t="s">
         <v>668</v>
       </c>
-      <c r="L53">
-        <v>69</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="N53" t="s">
-        <v>669</v>
-      </c>
-      <c r="O53" t="s">
-        <v>553</v>
-      </c>
       <c r="P53" t="s">
+        <v>552</v>
+      </c>
+      <c r="Q53" t="s">
         <v>238</v>
       </c>
-      <c r="Q53" t="s">
+      <c r="R53" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5289,44 +5459,47 @@
         <v>39</v>
       </c>
       <c r="E54" t="s">
+        <v>714</v>
+      </c>
+      <c r="F54" t="s">
         <v>112</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>17</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>241</v>
       </c>
-      <c r="H54" t="s">
-        <v>470</v>
-      </c>
       <c r="I54" t="s">
+        <v>469</v>
+      </c>
+      <c r="J54" t="s">
         <v>241</v>
       </c>
-      <c r="J54">
+      <c r="K54">
         <v>3</v>
       </c>
-      <c r="K54" t="s">
+      <c r="L54" t="s">
         <v>242</v>
       </c>
-      <c r="L54">
+      <c r="M54">
         <f>14</f>
         <v>14</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="N54" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="N54" t="s">
-        <v>511</v>
-      </c>
       <c r="O54" t="s">
-        <v>554</v>
+        <v>510</v>
       </c>
       <c r="P54" t="s">
+        <v>553</v>
+      </c>
+      <c r="Q54" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5340,44 +5513,47 @@
         <v>151</v>
       </c>
       <c r="E55" t="s">
+        <v>714</v>
+      </c>
+      <c r="F55" t="s">
         <v>246</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>11</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>99</v>
       </c>
-      <c r="H55" t="s">
-        <v>470</v>
-      </c>
       <c r="I55" t="s">
+        <v>469</v>
+      </c>
+      <c r="J55" t="s">
         <v>99</v>
       </c>
-      <c r="J55">
+      <c r="K55">
         <v>4</v>
       </c>
-      <c r="K55" t="s">
+      <c r="L55" t="s">
         <v>247</v>
       </c>
-      <c r="L55">
+      <c r="M55">
         <f>32</f>
         <v>32</v>
       </c>
-      <c r="M55" s="1" t="s">
+      <c r="N55" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="N55" t="s">
+      <c r="O55" t="s">
+        <v>594</v>
+      </c>
+      <c r="P55" t="s">
         <v>595</v>
       </c>
-      <c r="O55" t="s">
-        <v>596</v>
-      </c>
-      <c r="P55" t="s">
+      <c r="Q55" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5391,44 +5567,47 @@
         <v>43</v>
       </c>
       <c r="E56" t="s">
+        <v>105</v>
+      </c>
+      <c r="F56" t="s">
         <v>246</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>11</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>99</v>
       </c>
-      <c r="H56" t="s">
-        <v>470</v>
-      </c>
       <c r="I56" t="s">
+        <v>469</v>
+      </c>
+      <c r="J56" t="s">
         <v>99</v>
       </c>
-      <c r="J56">
+      <c r="K56">
         <v>2</v>
       </c>
-      <c r="K56" t="s">
+      <c r="L56" t="s">
         <v>251</v>
       </c>
-      <c r="L56">
+      <c r="M56">
         <f>27</f>
         <v>27</v>
       </c>
-      <c r="M56" t="s">
+      <c r="N56" t="s">
         <v>252</v>
       </c>
-      <c r="N56" t="s">
-        <v>542</v>
-      </c>
       <c r="O56" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="P56" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q56" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5442,44 +5621,47 @@
         <v>105</v>
       </c>
       <c r="E57" t="s">
+        <v>105</v>
+      </c>
+      <c r="F57" t="s">
         <v>246</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>11</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>159</v>
       </c>
-      <c r="H57" t="s">
-        <v>470</v>
-      </c>
       <c r="I57" t="s">
-        <v>475</v>
-      </c>
-      <c r="J57">
+        <v>469</v>
+      </c>
+      <c r="J57" t="s">
+        <v>474</v>
+      </c>
+      <c r="K57">
         <v>2</v>
       </c>
-      <c r="K57" t="s">
-        <v>703</v>
-      </c>
-      <c r="L57">
+      <c r="L57" t="s">
+        <v>702</v>
+      </c>
+      <c r="M57">
         <f>133</f>
         <v>133</v>
       </c>
-      <c r="M57" s="1" t="s">
+      <c r="N57" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="N57" t="s">
+      <c r="O57" t="s">
+        <v>703</v>
+      </c>
+      <c r="P57" t="s">
         <v>704</v>
       </c>
-      <c r="O57" t="s">
-        <v>705</v>
-      </c>
-      <c r="Q57" t="s">
+      <c r="R57" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5493,43 +5675,46 @@
         <v>43</v>
       </c>
       <c r="E58" t="s">
+        <v>105</v>
+      </c>
+      <c r="F58" t="s">
         <v>246</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>11</v>
       </c>
-      <c r="G58" t="s">
-        <v>493</v>
-      </c>
       <c r="H58" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
       <c r="I58" t="s">
+        <v>465</v>
+      </c>
+      <c r="J58" t="s">
         <v>99</v>
       </c>
-      <c r="J58">
+      <c r="K58">
         <v>2</v>
       </c>
-      <c r="K58" t="s">
+      <c r="L58" t="s">
         <v>258</v>
       </c>
-      <c r="L58">
+      <c r="M58">
         <v>10</v>
       </c>
-      <c r="M58" s="1" t="s">
+      <c r="N58" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="N58" t="s">
-        <v>511</v>
-      </c>
       <c r="O58" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q58" t="s">
+        <v>510</v>
+      </c>
+      <c r="P58" t="s">
+        <v>519</v>
+      </c>
+      <c r="R58" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5543,43 +5728,46 @@
         <v>39</v>
       </c>
       <c r="E59" t="s">
+        <v>714</v>
+      </c>
+      <c r="F59" t="s">
         <v>246</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>11</v>
       </c>
-      <c r="G59" t="s">
-        <v>494</v>
-      </c>
       <c r="H59" t="s">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="I59" t="s">
+        <v>465</v>
+      </c>
+      <c r="J59" t="s">
         <v>196</v>
       </c>
-      <c r="J59">
+      <c r="K59">
         <v>2</v>
       </c>
-      <c r="K59" t="s">
+      <c r="L59" t="s">
         <v>261</v>
       </c>
-      <c r="L59">
+      <c r="M59">
         <v>7</v>
       </c>
-      <c r="M59" s="1" t="s">
+      <c r="N59" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="N59" t="s">
-        <v>599</v>
-      </c>
       <c r="O59" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P59" t="s">
+        <v>596</v>
+      </c>
+      <c r="Q59" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5593,43 +5781,46 @@
         <v>27</v>
       </c>
       <c r="E60" t="s">
+        <v>714</v>
+      </c>
+      <c r="F60" t="s">
         <v>246</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>11</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>99</v>
       </c>
-      <c r="H60" t="s">
-        <v>470</v>
-      </c>
       <c r="I60" t="s">
+        <v>469</v>
+      </c>
+      <c r="J60" t="s">
         <v>99</v>
       </c>
-      <c r="J60">
+      <c r="K60">
         <v>2</v>
       </c>
-      <c r="K60" t="s">
+      <c r="L60" t="s">
         <v>266</v>
       </c>
-      <c r="L60">
+      <c r="M60">
         <v>48</v>
       </c>
-      <c r="M60" s="1" t="s">
+      <c r="N60" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="N60" t="s">
-        <v>600</v>
-      </c>
       <c r="O60" t="s">
-        <v>598</v>
-      </c>
-      <c r="Q60" t="s">
+        <v>599</v>
+      </c>
+      <c r="P60" t="s">
+        <v>597</v>
+      </c>
+      <c r="R60" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5643,47 +5834,50 @@
         <v>43</v>
       </c>
       <c r="E61" t="s">
+        <v>105</v>
+      </c>
+      <c r="F61" t="s">
         <v>246</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>11</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>159</v>
       </c>
-      <c r="H61" t="s">
-        <v>470</v>
-      </c>
       <c r="I61" t="s">
-        <v>475</v>
-      </c>
-      <c r="J61">
+        <v>469</v>
+      </c>
+      <c r="J61" t="s">
+        <v>474</v>
+      </c>
+      <c r="K61">
         <v>4</v>
       </c>
-      <c r="K61" t="s">
+      <c r="L61" t="s">
         <v>273</v>
       </c>
-      <c r="L61">
+      <c r="M61">
         <f>63+52</f>
         <v>115</v>
       </c>
-      <c r="M61" s="1" t="s">
+      <c r="N61" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="N61" t="s">
+      <c r="O61" t="s">
+        <v>600</v>
+      </c>
+      <c r="P61" t="s">
         <v>601</v>
       </c>
-      <c r="O61" t="s">
-        <v>602</v>
-      </c>
-      <c r="P61" t="s">
-        <v>441</v>
-      </c>
       <c r="Q61" t="s">
+        <v>440</v>
+      </c>
+      <c r="R61" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5697,44 +5891,47 @@
         <v>43</v>
       </c>
       <c r="E62" t="s">
+        <v>105</v>
+      </c>
+      <c r="F62" t="s">
         <v>246</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>11</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>159</v>
       </c>
-      <c r="H62" t="s">
-        <v>470</v>
-      </c>
       <c r="I62" t="s">
-        <v>475</v>
-      </c>
-      <c r="J62">
+        <v>469</v>
+      </c>
+      <c r="J62" t="s">
+        <v>474</v>
+      </c>
+      <c r="K62">
         <v>4</v>
       </c>
-      <c r="K62" t="s">
+      <c r="L62" t="s">
         <v>273</v>
       </c>
-      <c r="L62">
+      <c r="M62">
         <f>120</f>
         <v>120</v>
       </c>
-      <c r="M62" s="1" t="s">
+      <c r="N62" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="N62" t="s">
+      <c r="O62" t="s">
+        <v>600</v>
+      </c>
+      <c r="P62" t="s">
         <v>601</v>
       </c>
-      <c r="O62" t="s">
-        <v>602</v>
-      </c>
-      <c r="P62" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q62" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5748,43 +5945,46 @@
         <v>39</v>
       </c>
       <c r="E63" t="s">
+        <v>714</v>
+      </c>
+      <c r="F63" t="s">
         <v>246</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>17</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>241</v>
       </c>
-      <c r="H63" t="s">
-        <v>470</v>
-      </c>
       <c r="I63" t="s">
+        <v>469</v>
+      </c>
+      <c r="J63" t="s">
         <v>241</v>
       </c>
-      <c r="J63">
+      <c r="K63">
         <v>6</v>
       </c>
-      <c r="K63" t="s">
+      <c r="L63" t="s">
         <v>275</v>
       </c>
-      <c r="L63">
+      <c r="M63">
         <v>36</v>
       </c>
-      <c r="M63" s="1" t="s">
+      <c r="N63" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="N63" t="s">
-        <v>604</v>
       </c>
       <c r="O63" t="s">
         <v>603</v>
       </c>
       <c r="P63" t="s">
+        <v>602</v>
+      </c>
+      <c r="Q63" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5798,43 +5998,46 @@
         <v>39</v>
       </c>
       <c r="E64" t="s">
+        <v>714</v>
+      </c>
+      <c r="F64" t="s">
         <v>112</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>17</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>241</v>
       </c>
-      <c r="H64" t="s">
-        <v>470</v>
-      </c>
       <c r="I64" t="s">
+        <v>469</v>
+      </c>
+      <c r="J64" t="s">
         <v>241</v>
       </c>
-      <c r="J64">
+      <c r="K64">
         <v>5</v>
       </c>
-      <c r="K64" t="s">
+      <c r="L64" t="s">
         <v>279</v>
       </c>
-      <c r="L64">
+      <c r="M64">
         <v>35</v>
       </c>
-      <c r="M64" s="1" t="s">
+      <c r="N64" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="N64" t="s">
+      <c r="O64" t="s">
+        <v>604</v>
+      </c>
+      <c r="P64" t="s">
         <v>605</v>
       </c>
-      <c r="O64" t="s">
-        <v>606</v>
-      </c>
-      <c r="P64" t="s">
+      <c r="Q64" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5848,46 +6051,49 @@
         <v>43</v>
       </c>
       <c r="E65" t="s">
+        <v>105</v>
+      </c>
+      <c r="F65" t="s">
         <v>246</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>283</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>49</v>
       </c>
-      <c r="H65" t="s">
-        <v>470</v>
-      </c>
       <c r="I65" t="s">
+        <v>469</v>
+      </c>
+      <c r="J65" t="s">
         <v>99</v>
       </c>
-      <c r="J65">
+      <c r="K65">
         <v>3</v>
       </c>
-      <c r="K65" t="s">
+      <c r="L65" t="s">
         <v>284</v>
       </c>
-      <c r="L65">
+      <c r="M65">
         <v>9</v>
       </c>
-      <c r="M65" s="1" t="s">
+      <c r="N65" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="O65" t="s">
+        <v>542</v>
+      </c>
+      <c r="P65" t="s">
         <v>607</v>
       </c>
-      <c r="N65" t="s">
-        <v>543</v>
-      </c>
-      <c r="O65" t="s">
-        <v>608</v>
-      </c>
-      <c r="Q65" t="s">
+      <c r="R65" t="s">
         <v>285</v>
       </c>
-      <c r="R65" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S65" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5901,44 +6107,47 @@
         <v>43</v>
       </c>
       <c r="E66" t="s">
+        <v>105</v>
+      </c>
+      <c r="F66" t="s">
         <v>246</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>17</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>288</v>
       </c>
-      <c r="H66" t="s">
-        <v>470</v>
-      </c>
       <c r="I66" t="s">
-        <v>415</v>
-      </c>
-      <c r="J66">
+        <v>469</v>
+      </c>
+      <c r="J66" t="s">
+        <v>414</v>
+      </c>
+      <c r="K66">
         <v>6</v>
       </c>
-      <c r="K66" t="s">
+      <c r="L66" t="s">
         <v>289</v>
       </c>
-      <c r="L66">
-        <f>J66*3</f>
+      <c r="M66">
+        <f>K66*3</f>
         <v>18</v>
       </c>
-      <c r="M66" s="1" t="s">
+      <c r="N66" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="N66" t="s">
+      <c r="O66" t="s">
+        <v>608</v>
+      </c>
+      <c r="P66" t="s">
         <v>609</v>
       </c>
-      <c r="O66" t="s">
-        <v>610</v>
-      </c>
-      <c r="R66" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S66" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5952,47 +6161,50 @@
         <v>57</v>
       </c>
       <c r="E67" t="s">
+        <v>315</v>
+      </c>
+      <c r="F67" t="s">
         <v>246</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>17</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>66</v>
       </c>
-      <c r="H67" t="s">
-        <v>470</v>
-      </c>
       <c r="I67" t="s">
+        <v>469</v>
+      </c>
+      <c r="J67" t="s">
         <v>66</v>
       </c>
-      <c r="J67">
+      <c r="K67">
         <v>2</v>
       </c>
-      <c r="K67" t="s">
-        <v>659</v>
-      </c>
-      <c r="L67">
+      <c r="L67" t="s">
+        <v>658</v>
+      </c>
+      <c r="M67">
         <f>12</f>
         <v>12</v>
       </c>
-      <c r="M67" t="s">
+      <c r="N67" t="s">
         <v>40</v>
       </c>
-      <c r="N67" t="s">
-        <v>508</v>
-      </c>
       <c r="O67" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
       <c r="P67" t="s">
+        <v>659</v>
+      </c>
+      <c r="Q67" t="s">
         <v>293</v>
       </c>
-      <c r="R67" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S67" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6006,40 +6218,43 @@
         <v>57</v>
       </c>
       <c r="E68" t="s">
+        <v>315</v>
+      </c>
+      <c r="F68" t="s">
         <v>9</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
         <v>295</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>296</v>
       </c>
-      <c r="H68" t="s">
-        <v>466</v>
-      </c>
       <c r="I68" t="s">
-        <v>460</v>
-      </c>
-      <c r="J68">
+        <v>465</v>
+      </c>
+      <c r="J68" t="s">
+        <v>459</v>
+      </c>
+      <c r="K68">
         <v>2</v>
       </c>
-      <c r="K68" t="s">
+      <c r="L68" t="s">
+        <v>707</v>
+      </c>
+      <c r="M68">
+        <v>12</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="O68" t="s">
         <v>708</v>
       </c>
-      <c r="L68">
-        <v>12</v>
-      </c>
-      <c r="M68" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="N68" t="s">
+      <c r="P68" t="s">
         <v>709</v>
       </c>
-      <c r="O68" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6053,41 +6268,44 @@
         <v>29</v>
       </c>
       <c r="E69" t="s">
+        <v>714</v>
+      </c>
+      <c r="F69" t="s">
         <v>299</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>11</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>99</v>
       </c>
-      <c r="H69" t="s">
-        <v>470</v>
-      </c>
       <c r="I69" t="s">
+        <v>469</v>
+      </c>
+      <c r="J69" t="s">
         <v>99</v>
       </c>
-      <c r="J69">
+      <c r="K69">
         <v>2</v>
       </c>
-      <c r="K69" t="s">
-        <v>670</v>
-      </c>
-      <c r="L69">
+      <c r="L69" t="s">
+        <v>669</v>
+      </c>
+      <c r="M69">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="M69" s="1" t="s">
+      <c r="N69" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="N69" t="s">
-        <v>671</v>
-      </c>
       <c r="O69" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+        <v>670</v>
+      </c>
+      <c r="P69" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6101,43 +6319,46 @@
         <v>308</v>
       </c>
       <c r="E70" t="s">
+        <v>716</v>
+      </c>
+      <c r="F70" t="s">
         <v>112</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>309</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>208</v>
       </c>
-      <c r="H70" t="s">
-        <v>470</v>
-      </c>
       <c r="I70" t="s">
+        <v>469</v>
+      </c>
+      <c r="J70" t="s">
         <v>99</v>
       </c>
-      <c r="J70">
+      <c r="K70">
         <v>2</v>
       </c>
-      <c r="K70" t="s">
+      <c r="L70" t="s">
         <v>310</v>
       </c>
-      <c r="L70">
+      <c r="M70">
         <v>10</v>
       </c>
-      <c r="M70" s="1" t="s">
+      <c r="N70" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="N70" t="s">
-        <v>545</v>
-      </c>
       <c r="O70" t="s">
-        <v>557</v>
-      </c>
-      <c r="Q70" t="s">
+        <v>544</v>
+      </c>
+      <c r="P70" t="s">
+        <v>556</v>
+      </c>
+      <c r="R70" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6151,44 +6372,47 @@
         <v>315</v>
       </c>
       <c r="E71" t="s">
+        <v>315</v>
+      </c>
+      <c r="F71" t="s">
         <v>112</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>309</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>316</v>
       </c>
-      <c r="H71" t="s">
-        <v>470</v>
-      </c>
       <c r="I71" t="s">
+        <v>469</v>
+      </c>
+      <c r="J71" t="s">
         <v>66</v>
       </c>
-      <c r="J71">
+      <c r="K71">
         <v>5</v>
       </c>
-      <c r="K71" t="s">
+      <c r="L71" t="s">
         <v>317</v>
       </c>
-      <c r="L71">
-        <f>J71*4+4</f>
+      <c r="M71">
+        <f>K71*4+4</f>
         <v>24</v>
       </c>
-      <c r="M71" s="1" t="s">
+      <c r="N71" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="N71" t="s">
+      <c r="O71" t="s">
+        <v>615</v>
+      </c>
+      <c r="P71" t="s">
         <v>616</v>
       </c>
-      <c r="O71" t="s">
-        <v>617</v>
-      </c>
-      <c r="Q71" t="s">
+      <c r="R71" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6202,41 +6426,44 @@
         <v>18</v>
       </c>
       <c r="E72" t="s">
+        <v>105</v>
+      </c>
+      <c r="F72" t="s">
         <v>112</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>322</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>323</v>
       </c>
-      <c r="H72" t="s">
-        <v>470</v>
-      </c>
       <c r="I72" t="s">
+        <v>469</v>
+      </c>
+      <c r="J72" t="s">
         <v>323</v>
       </c>
-      <c r="J72">
+      <c r="K72">
         <v>3</v>
       </c>
-      <c r="K72" t="s">
+      <c r="L72" t="s">
         <v>320</v>
       </c>
-      <c r="L72">
+      <c r="M72">
         <f>3*4</f>
         <v>12</v>
       </c>
-      <c r="M72" s="1" t="s">
+      <c r="N72" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="N72" t="s">
-        <v>511</v>
-      </c>
       <c r="O72" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+      <c r="P72" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6250,43 +6477,46 @@
         <v>305</v>
       </c>
       <c r="E73" t="s">
+        <v>714</v>
+      </c>
+      <c r="F73" t="s">
         <v>9</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>11</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>302</v>
       </c>
-      <c r="H73" t="s">
-        <v>470</v>
-      </c>
       <c r="I73" t="s">
-        <v>459</v>
-      </c>
-      <c r="J73">
+        <v>469</v>
+      </c>
+      <c r="J73" t="s">
+        <v>458</v>
+      </c>
+      <c r="K73">
         <v>4</v>
       </c>
-      <c r="K73" t="s">
+      <c r="L73" t="s">
         <v>303</v>
       </c>
-      <c r="L73">
+      <c r="M73">
         <v>23</v>
       </c>
-      <c r="M73" s="1" t="s">
+      <c r="N73" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="N73" t="s">
-        <v>611</v>
-      </c>
       <c r="O73" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="P73" t="s">
+        <v>624</v>
+      </c>
+      <c r="Q73" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6300,44 +6530,47 @@
         <v>105</v>
       </c>
       <c r="E74" t="s">
+        <v>105</v>
+      </c>
+      <c r="F74" t="s">
         <v>9</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>309</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>326</v>
       </c>
-      <c r="H74" t="s">
-        <v>470</v>
-      </c>
       <c r="I74" t="s">
+        <v>469</v>
+      </c>
+      <c r="J74" t="s">
         <v>326</v>
       </c>
-      <c r="J74">
+      <c r="K74">
         <v>12</v>
       </c>
-      <c r="K74" t="s">
+      <c r="L74" t="s">
         <v>327</v>
       </c>
-      <c r="L74">
-        <f>J74*6</f>
+      <c r="M74">
+        <f>K74*6</f>
         <v>72</v>
       </c>
-      <c r="M74" s="1" t="s">
+      <c r="N74" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="N74" t="s">
+      <c r="O74" t="s">
+        <v>625</v>
+      </c>
+      <c r="P74" t="s">
         <v>626</v>
       </c>
-      <c r="O74" t="s">
-        <v>627</v>
-      </c>
-      <c r="P74" t="s">
+      <c r="Q74" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6351,41 +6584,44 @@
         <v>105</v>
       </c>
       <c r="E75" t="s">
+        <v>105</v>
+      </c>
+      <c r="F75" t="s">
         <v>9</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>309</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>116</v>
       </c>
-      <c r="H75" t="s">
-        <v>470</v>
-      </c>
       <c r="I75" t="s">
+        <v>469</v>
+      </c>
+      <c r="J75" t="s">
         <v>116</v>
       </c>
-      <c r="J75">
+      <c r="K75">
         <v>6</v>
       </c>
-      <c r="K75" t="s">
+      <c r="L75" t="s">
         <v>332</v>
       </c>
-      <c r="L75">
+      <c r="M75">
         <f>6*3</f>
         <v>18</v>
       </c>
-      <c r="M75" s="1" t="s">
+      <c r="N75" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="N75" t="s">
-        <v>629</v>
-      </c>
       <c r="O75" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+      <c r="P75" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6399,46 +6635,49 @@
         <v>334</v>
       </c>
       <c r="E76" t="s">
+        <v>714</v>
+      </c>
+      <c r="F76" t="s">
+        <v>9</v>
+      </c>
+      <c r="G76" t="s">
+        <v>295</v>
+      </c>
+      <c r="H76" t="s">
         <v>335</v>
       </c>
-      <c r="F76" t="s">
-        <v>295</v>
-      </c>
-      <c r="G76" t="s">
+      <c r="I76" t="s">
+        <v>465</v>
+      </c>
+      <c r="J76" t="s">
+        <v>335</v>
+      </c>
+      <c r="K76">
+        <v>3</v>
+      </c>
+      <c r="L76" t="s">
         <v>336</v>
       </c>
-      <c r="H76" t="s">
-        <v>466</v>
-      </c>
-      <c r="I76" t="s">
-        <v>336</v>
-      </c>
-      <c r="J76">
-        <v>3</v>
-      </c>
-      <c r="K76" t="s">
+      <c r="M76">
+        <f>K76*3</f>
+        <v>9</v>
+      </c>
+      <c r="N76" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="L76">
-        <f>J76*3</f>
-        <v>9</v>
-      </c>
-      <c r="M76" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="N76" t="s">
-        <v>514</v>
-      </c>
       <c r="O76" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+      <c r="P76" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C77" t="s">
         <v>85</v>
@@ -6447,47 +6686,50 @@
         <v>29</v>
       </c>
       <c r="E77" t="s">
+        <v>714</v>
+      </c>
+      <c r="F77" t="s">
         <v>9</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>322</v>
       </c>
-      <c r="G77" t="s">
-        <v>340</v>
-      </c>
       <c r="H77" t="s">
-        <v>470</v>
+        <v>339</v>
       </c>
       <c r="I77" t="s">
-        <v>340</v>
-      </c>
-      <c r="J77">
+        <v>469</v>
+      </c>
+      <c r="J77" t="s">
+        <v>339</v>
+      </c>
+      <c r="K77">
         <f>3</f>
         <v>3</v>
       </c>
-      <c r="K77" t="s">
-        <v>339</v>
-      </c>
-      <c r="L77">
-        <f>J77*3</f>
+      <c r="L77" t="s">
+        <v>338</v>
+      </c>
+      <c r="M77">
+        <f>K77*3</f>
         <v>9</v>
       </c>
-      <c r="M77" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="N77" t="s">
-        <v>546</v>
+      <c r="N77" s="1" t="s">
+        <v>341</v>
       </c>
       <c r="O77" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+        <v>545</v>
+      </c>
+      <c r="P77" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C78" t="s">
         <v>85</v>
@@ -6496,45 +6738,48 @@
         <v>27</v>
       </c>
       <c r="E78" t="s">
+        <v>714</v>
+      </c>
+      <c r="F78" t="s">
         <v>9</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>11</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>96</v>
       </c>
-      <c r="H78" t="s">
-        <v>470</v>
-      </c>
       <c r="I78" t="s">
-        <v>415</v>
-      </c>
-      <c r="J78">
+        <v>469</v>
+      </c>
+      <c r="J78" t="s">
+        <v>414</v>
+      </c>
+      <c r="K78">
         <v>2</v>
       </c>
-      <c r="K78" t="s">
+      <c r="L78" t="s">
+        <v>343</v>
+      </c>
+      <c r="M78">
+        <v>15</v>
+      </c>
+      <c r="N78" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="L78">
-        <v>15</v>
-      </c>
-      <c r="M78" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="N78" t="s">
-        <v>619</v>
-      </c>
       <c r="O78" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+      <c r="P78" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C79" t="s">
         <v>85</v>
@@ -6543,46 +6788,49 @@
         <v>43</v>
       </c>
       <c r="E79" t="s">
+        <v>105</v>
+      </c>
+      <c r="F79" t="s">
         <v>9</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>17</v>
       </c>
-      <c r="G79" t="s">
-        <v>348</v>
-      </c>
       <c r="H79" t="s">
+        <v>347</v>
+      </c>
+      <c r="I79" t="s">
+        <v>465</v>
+      </c>
+      <c r="J79" t="s">
         <v>466</v>
       </c>
-      <c r="I79" t="s">
-        <v>467</v>
-      </c>
-      <c r="J79">
+      <c r="K79">
         <v>3</v>
       </c>
-      <c r="K79" t="s">
-        <v>347</v>
-      </c>
-      <c r="L79">
+      <c r="L79" t="s">
+        <v>346</v>
+      </c>
+      <c r="M79">
         <f>9</f>
         <v>9</v>
       </c>
-      <c r="M79" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="N79" t="s">
-        <v>620</v>
+      <c r="N79" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="O79" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+        <v>619</v>
+      </c>
+      <c r="P79" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C80" t="s">
         <v>85</v>
@@ -6591,46 +6839,49 @@
         <v>29</v>
       </c>
       <c r="E80" t="s">
+        <v>714</v>
+      </c>
+      <c r="F80" t="s">
         <v>9</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
+        <v>349</v>
+      </c>
+      <c r="H80" t="s">
         <v>350</v>
       </c>
-      <c r="G80" t="s">
+      <c r="I80" t="s">
+        <v>465</v>
+      </c>
+      <c r="J80" t="s">
+        <v>350</v>
+      </c>
+      <c r="K80">
+        <v>2</v>
+      </c>
+      <c r="L80" t="s">
         <v>351</v>
       </c>
-      <c r="H80" t="s">
-        <v>466</v>
-      </c>
-      <c r="I80" t="s">
-        <v>351</v>
-      </c>
-      <c r="J80">
-        <v>2</v>
-      </c>
-      <c r="K80" t="s">
-        <v>352</v>
-      </c>
-      <c r="L80">
+      <c r="M80">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="M80" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="N80" t="s">
-        <v>621</v>
+      <c r="N80" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="O80" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+        <v>620</v>
+      </c>
+      <c r="P80" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C81" t="s">
         <v>85</v>
@@ -6639,45 +6890,48 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
+        <v>714</v>
+      </c>
+      <c r="F81" t="s">
         <v>9</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>11</v>
       </c>
-      <c r="G81" t="s">
-        <v>495</v>
-      </c>
       <c r="H81" t="s">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="I81" t="s">
+        <v>465</v>
+      </c>
+      <c r="J81" t="s">
         <v>241</v>
       </c>
-      <c r="J81">
+      <c r="K81">
         <v>2</v>
       </c>
-      <c r="K81" t="s">
+      <c r="L81" t="s">
         <v>258</v>
       </c>
-      <c r="L81">
+      <c r="M81">
         <v>6</v>
       </c>
-      <c r="M81" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="N81" t="s">
-        <v>511</v>
+      <c r="N81" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="O81" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+      <c r="P81" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C82" t="s">
         <v>85</v>
@@ -6686,45 +6940,48 @@
         <v>43</v>
       </c>
       <c r="E82" t="s">
+        <v>105</v>
+      </c>
+      <c r="F82" t="s">
         <v>9</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>17</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>326</v>
       </c>
-      <c r="H82" t="s">
-        <v>470</v>
-      </c>
       <c r="I82" t="s">
+        <v>469</v>
+      </c>
+      <c r="J82" t="s">
         <v>326</v>
       </c>
-      <c r="J82">
+      <c r="K82">
         <v>3</v>
       </c>
-      <c r="K82" t="s">
+      <c r="L82" t="s">
+        <v>357</v>
+      </c>
+      <c r="M82">
+        <v>9</v>
+      </c>
+      <c r="N82" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="L82">
-        <v>9</v>
-      </c>
-      <c r="M82" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="N82" t="s">
-        <v>512</v>
-      </c>
       <c r="O82" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+      <c r="P82" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C83" t="s">
         <v>85</v>
@@ -6733,49 +6990,52 @@
         <v>105</v>
       </c>
       <c r="E83" t="s">
+        <v>105</v>
+      </c>
+      <c r="F83" t="s">
         <v>9</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>11</v>
       </c>
-      <c r="G83" t="s">
-        <v>496</v>
-      </c>
       <c r="H83" t="s">
+        <v>495</v>
+      </c>
+      <c r="I83" t="s">
+        <v>465</v>
+      </c>
+      <c r="J83" t="s">
         <v>466</v>
       </c>
-      <c r="I83" t="s">
-        <v>467</v>
-      </c>
-      <c r="J83">
+      <c r="K83">
         <v>7</v>
       </c>
-      <c r="K83" t="s">
+      <c r="L83" t="s">
+        <v>635</v>
+      </c>
+      <c r="M83">
+        <f>K83*3</f>
+        <v>21</v>
+      </c>
+      <c r="N83" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="O83" t="s">
+        <v>517</v>
+      </c>
+      <c r="P83" t="s">
         <v>636</v>
       </c>
-      <c r="L83">
-        <f>J83*3</f>
-        <v>21</v>
-      </c>
-      <c r="M83" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="N83" t="s">
-        <v>518</v>
-      </c>
-      <c r="O83" t="s">
-        <v>637</v>
-      </c>
-      <c r="P83" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q83" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C84" t="s">
         <v>85</v>
@@ -6784,47 +7044,50 @@
         <v>105</v>
       </c>
       <c r="E84" t="s">
+        <v>105</v>
+      </c>
+      <c r="F84" t="s">
         <v>9</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>309</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
+        <v>496</v>
+      </c>
+      <c r="I84" t="s">
+        <v>465</v>
+      </c>
+      <c r="J84" t="s">
         <v>497</v>
       </c>
-      <c r="H84" t="s">
-        <v>466</v>
-      </c>
-      <c r="I84" t="s">
-        <v>498</v>
-      </c>
-      <c r="J84">
+      <c r="K84">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="K84" t="s">
-        <v>364</v>
-      </c>
-      <c r="L84">
+      <c r="L84" t="s">
+        <v>363</v>
+      </c>
+      <c r="M84">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="M84" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="N84" t="s">
-        <v>558</v>
+      <c r="N84" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="O84" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+        <v>557</v>
+      </c>
+      <c r="P84" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C85" t="s">
         <v>85</v>
@@ -6833,46 +7096,49 @@
         <v>105</v>
       </c>
       <c r="E85" t="s">
+        <v>105</v>
+      </c>
+      <c r="F85" t="s">
         <v>9</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>11</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
+        <v>498</v>
+      </c>
+      <c r="I85" t="s">
+        <v>465</v>
+      </c>
+      <c r="J85" t="s">
         <v>499</v>
       </c>
-      <c r="H85" t="s">
-        <v>466</v>
-      </c>
-      <c r="I85" t="s">
-        <v>500</v>
-      </c>
-      <c r="J85">
+      <c r="K85">
         <v>4</v>
       </c>
-      <c r="K85" t="s">
+      <c r="L85" t="s">
+        <v>365</v>
+      </c>
+      <c r="M85">
+        <f>4*K85</f>
+        <v>16</v>
+      </c>
+      <c r="N85" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="L85">
-        <f>4*J85</f>
-        <v>16</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="N85" t="s">
+      <c r="O85" t="s">
+        <v>561</v>
+      </c>
+      <c r="P85" t="s">
         <v>562</v>
       </c>
-      <c r="O85" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C86" t="s">
         <v>85</v>
@@ -6881,46 +7147,49 @@
         <v>29</v>
       </c>
       <c r="E86" t="s">
+        <v>714</v>
+      </c>
+      <c r="F86" t="s">
         <v>9</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
+        <v>349</v>
+      </c>
+      <c r="H86" t="s">
         <v>350</v>
       </c>
-      <c r="G86" t="s">
-        <v>351</v>
-      </c>
-      <c r="H86" t="s">
-        <v>466</v>
-      </c>
       <c r="I86" t="s">
-        <v>351</v>
-      </c>
-      <c r="J86">
+        <v>465</v>
+      </c>
+      <c r="J86" t="s">
+        <v>350</v>
+      </c>
+      <c r="K86">
         <v>8</v>
       </c>
-      <c r="K86" t="s">
-        <v>368</v>
-      </c>
-      <c r="L86">
+      <c r="L86" t="s">
+        <v>367</v>
+      </c>
+      <c r="M86">
         <f>8*4</f>
         <v>32</v>
       </c>
-      <c r="M86" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="N86" t="s">
+      <c r="N86" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="O86" t="s">
+        <v>637</v>
+      </c>
+      <c r="P86" t="s">
         <v>638</v>
       </c>
-      <c r="O86" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C87" t="s">
         <v>85</v>
@@ -6929,49 +7198,52 @@
         <v>43</v>
       </c>
       <c r="E87" t="s">
+        <v>105</v>
+      </c>
+      <c r="F87" t="s">
         <v>9</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>11</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
+        <v>500</v>
+      </c>
+      <c r="I87" t="s">
+        <v>469</v>
+      </c>
+      <c r="J87" t="s">
         <v>501</v>
       </c>
-      <c r="H87" t="s">
-        <v>470</v>
-      </c>
-      <c r="I87" t="s">
-        <v>502</v>
-      </c>
-      <c r="J87">
+      <c r="K87">
         <v>4</v>
       </c>
-      <c r="K87" t="s">
-        <v>373</v>
-      </c>
-      <c r="L87">
+      <c r="L87" t="s">
+        <v>372</v>
+      </c>
+      <c r="M87">
         <f>4*4</f>
         <v>16</v>
       </c>
-      <c r="M87" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="N87" t="s">
-        <v>640</v>
+      <c r="N87" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="O87" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="P87" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+        <v>621</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C88" t="s">
         <v>85</v>
@@ -6980,49 +7252,52 @@
         <v>43</v>
       </c>
       <c r="E88" t="s">
+        <v>105</v>
+      </c>
+      <c r="F88" t="s">
         <v>9</v>
       </c>
-      <c r="F88" t="s">
+      <c r="G88" t="s">
         <v>17</v>
       </c>
-      <c r="G88" t="s">
-        <v>503</v>
-      </c>
       <c r="H88" t="s">
-        <v>466</v>
+        <v>502</v>
       </c>
       <c r="I88" t="s">
-        <v>468</v>
-      </c>
-      <c r="J88">
+        <v>465</v>
+      </c>
+      <c r="J88" t="s">
+        <v>467</v>
+      </c>
+      <c r="K88">
         <v>4</v>
       </c>
-      <c r="K88" t="s">
-        <v>376</v>
-      </c>
-      <c r="L88">
+      <c r="L88" t="s">
+        <v>375</v>
+      </c>
+      <c r="M88">
         <f>4*5</f>
         <v>20</v>
       </c>
-      <c r="M88" s="1" t="s">
+      <c r="N88" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="O88" t="s">
+        <v>622</v>
+      </c>
+      <c r="P88" t="s">
+        <v>629</v>
+      </c>
+      <c r="R88" t="s">
         <v>377</v>
       </c>
-      <c r="N88" t="s">
-        <v>623</v>
-      </c>
-      <c r="O88" t="s">
-        <v>630</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C89" t="s">
         <v>85</v>
@@ -7031,49 +7306,52 @@
         <v>105</v>
       </c>
       <c r="E89" t="s">
+        <v>105</v>
+      </c>
+      <c r="F89" t="s">
         <v>9</v>
       </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
+        <v>385</v>
+      </c>
+      <c r="H89" t="s">
         <v>386</v>
       </c>
-      <c r="G89" t="s">
+      <c r="I89" t="s">
+        <v>469</v>
+      </c>
+      <c r="J89" t="s">
+        <v>386</v>
+      </c>
+      <c r="K89">
+        <v>6</v>
+      </c>
+      <c r="L89" t="s">
         <v>387</v>
       </c>
-      <c r="H89" t="s">
-        <v>470</v>
-      </c>
-      <c r="I89" t="s">
-        <v>387</v>
-      </c>
-      <c r="J89">
-        <v>6</v>
-      </c>
-      <c r="K89" t="s">
-        <v>388</v>
-      </c>
-      <c r="L89">
+      <c r="M89">
         <f>6*3</f>
         <v>18</v>
       </c>
-      <c r="M89" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="N89" t="s">
+      <c r="N89" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="O89" t="s">
+        <v>641</v>
+      </c>
+      <c r="P89" t="s">
         <v>642</v>
       </c>
-      <c r="O89" t="s">
-        <v>643</v>
-      </c>
-      <c r="P89" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q89" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C90" t="s">
         <v>85</v>
@@ -7082,46 +7360,49 @@
         <v>43</v>
       </c>
       <c r="E90" t="s">
+        <v>105</v>
+      </c>
+      <c r="F90" t="s">
         <v>9</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>11</v>
       </c>
-      <c r="G90" t="s">
-        <v>504</v>
-      </c>
       <c r="H90" t="s">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="I90" t="s">
-        <v>459</v>
-      </c>
-      <c r="J90">
+        <v>465</v>
+      </c>
+      <c r="J90" t="s">
+        <v>458</v>
+      </c>
+      <c r="K90">
         <v>3</v>
       </c>
-      <c r="K90" t="s">
-        <v>393</v>
-      </c>
-      <c r="L90">
+      <c r="L90" t="s">
+        <v>392</v>
+      </c>
+      <c r="M90">
         <f>3*4</f>
         <v>12</v>
       </c>
-      <c r="M90" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="N90" t="s">
-        <v>518</v>
+      <c r="N90" s="1" t="s">
+        <v>393</v>
       </c>
       <c r="O90" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+      <c r="P90" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C91" t="s">
         <v>85</v>
@@ -7130,46 +7411,49 @@
         <v>105</v>
       </c>
       <c r="E91" t="s">
+        <v>105</v>
+      </c>
+      <c r="F91" t="s">
         <v>9</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
+        <v>395</v>
+      </c>
+      <c r="H91" t="s">
         <v>396</v>
       </c>
-      <c r="G91" t="s">
+      <c r="I91" t="s">
+        <v>469</v>
+      </c>
+      <c r="J91" t="s">
+        <v>396</v>
+      </c>
+      <c r="K91">
+        <v>3</v>
+      </c>
+      <c r="L91" t="s">
         <v>397</v>
       </c>
-      <c r="H91" t="s">
-        <v>470</v>
-      </c>
-      <c r="I91" t="s">
-        <v>397</v>
-      </c>
-      <c r="J91">
-        <v>3</v>
-      </c>
-      <c r="K91" t="s">
-        <v>398</v>
-      </c>
-      <c r="L91">
+      <c r="M91">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="M91" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="N91" t="s">
-        <v>512</v>
+      <c r="N91" s="1" t="s">
+        <v>398</v>
       </c>
       <c r="O91" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+      <c r="P91" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C92" t="s">
         <v>85</v>
@@ -7178,45 +7462,48 @@
         <v>57</v>
       </c>
       <c r="E92" t="s">
+        <v>315</v>
+      </c>
+      <c r="F92" t="s">
         <v>9</v>
       </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>11</v>
       </c>
-      <c r="G92" t="s">
+      <c r="H92" t="s">
+        <v>400</v>
+      </c>
+      <c r="I92" t="s">
+        <v>469</v>
+      </c>
+      <c r="J92" t="s">
+        <v>466</v>
+      </c>
+      <c r="K92">
+        <v>3</v>
+      </c>
+      <c r="L92" t="s">
+        <v>399</v>
+      </c>
+      <c r="M92">
+        <v>13</v>
+      </c>
+      <c r="N92" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="H92" t="s">
-        <v>470</v>
-      </c>
-      <c r="I92" t="s">
-        <v>467</v>
-      </c>
-      <c r="J92">
-        <v>3</v>
-      </c>
-      <c r="K92" t="s">
-        <v>400</v>
-      </c>
-      <c r="L92">
-        <v>13</v>
-      </c>
-      <c r="M92" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="N92" t="s">
-        <v>565</v>
-      </c>
       <c r="O92" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+        <v>564</v>
+      </c>
+      <c r="P92" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C93" t="s">
         <v>85</v>
@@ -7225,46 +7512,49 @@
         <v>12</v>
       </c>
       <c r="E93" t="s">
+        <v>105</v>
+      </c>
+      <c r="F93" t="s">
         <v>9</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>11</v>
       </c>
-      <c r="G93" t="s">
+      <c r="H93" t="s">
         <v>99</v>
       </c>
-      <c r="H93" t="s">
-        <v>470</v>
-      </c>
       <c r="I93" t="s">
+        <v>469</v>
+      </c>
+      <c r="J93" t="s">
         <v>99</v>
       </c>
-      <c r="J93">
+      <c r="K93">
         <v>4</v>
       </c>
-      <c r="K93" t="s">
-        <v>404</v>
-      </c>
-      <c r="L93">
+      <c r="L93" t="s">
+        <v>403</v>
+      </c>
+      <c r="M93">
         <f>158</f>
         <v>158</v>
       </c>
-      <c r="M93" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="N93" t="s">
-        <v>632</v>
+      <c r="N93" s="1" t="s">
+        <v>404</v>
       </c>
       <c r="O93" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+        <v>631</v>
+      </c>
+      <c r="P93" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C94" t="s">
         <v>85</v>
@@ -7273,49 +7563,52 @@
         <v>105</v>
       </c>
       <c r="E94" t="s">
+        <v>105</v>
+      </c>
+      <c r="F94" t="s">
         <v>9</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>309</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
+        <v>406</v>
+      </c>
+      <c r="I94" t="s">
+        <v>469</v>
+      </c>
+      <c r="J94" t="s">
+        <v>478</v>
+      </c>
+      <c r="K94">
+        <v>2</v>
+      </c>
+      <c r="L94" t="s">
         <v>407</v>
       </c>
-      <c r="H94" t="s">
-        <v>470</v>
-      </c>
-      <c r="I94" t="s">
-        <v>479</v>
-      </c>
-      <c r="J94">
-        <v>2</v>
-      </c>
-      <c r="K94" t="s">
-        <v>408</v>
-      </c>
-      <c r="L94">
+      <c r="M94">
         <f>16</f>
         <v>16</v>
       </c>
-      <c r="M94" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="N94" t="s">
-        <v>512</v>
+      <c r="N94" s="1" t="s">
+        <v>408</v>
       </c>
       <c r="O94" t="s">
-        <v>559</v>
+        <v>511</v>
       </c>
       <c r="P94" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+        <v>558</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C95" t="s">
         <v>85</v>
@@ -7324,48 +7617,51 @@
         <v>43</v>
       </c>
       <c r="E95" t="s">
+        <v>105</v>
+      </c>
+      <c r="F95" t="s">
         <v>9</v>
       </c>
-      <c r="F95" t="s">
-        <v>412</v>
-      </c>
       <c r="G95" t="s">
-        <v>481</v>
+        <v>411</v>
       </c>
       <c r="H95" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="I95" t="s">
-        <v>505</v>
-      </c>
-      <c r="J95">
+        <v>465</v>
+      </c>
+      <c r="J95" t="s">
+        <v>504</v>
+      </c>
+      <c r="K95">
         <v>2</v>
       </c>
-      <c r="K95" t="s">
-        <v>411</v>
-      </c>
-      <c r="L95">
+      <c r="L95" t="s">
+        <v>410</v>
+      </c>
+      <c r="M95">
         <v>6</v>
       </c>
-      <c r="M95" t="s">
+      <c r="N95" t="s">
         <v>40</v>
       </c>
-      <c r="N95" t="s">
-        <v>567</v>
-      </c>
       <c r="O95" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="P95" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+        <v>559</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C96" t="s">
         <v>85</v>
@@ -7374,49 +7670,52 @@
         <v>105</v>
       </c>
       <c r="E96" t="s">
+        <v>105</v>
+      </c>
+      <c r="F96" t="s">
         <v>9</v>
       </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>17</v>
       </c>
-      <c r="G96" t="s">
-        <v>415</v>
-      </c>
       <c r="H96" t="s">
-        <v>470</v>
+        <v>414</v>
       </c>
       <c r="I96" t="s">
-        <v>415</v>
-      </c>
-      <c r="J96">
+        <v>469</v>
+      </c>
+      <c r="J96" t="s">
+        <v>414</v>
+      </c>
+      <c r="K96">
         <v>6</v>
       </c>
-      <c r="K96" t="s">
-        <v>414</v>
-      </c>
-      <c r="L96">
+      <c r="L96" t="s">
+        <v>413</v>
+      </c>
+      <c r="M96">
         <f>6*8</f>
         <v>48</v>
       </c>
-      <c r="M96" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="N96" t="s">
-        <v>634</v>
+      <c r="N96" s="1" t="s">
+        <v>415</v>
       </c>
       <c r="O96" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="P96" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C97" t="s">
         <v>85</v>
@@ -7425,49 +7724,52 @@
         <v>39</v>
       </c>
       <c r="E97" t="s">
+        <v>714</v>
+      </c>
+      <c r="F97" t="s">
         <v>9</v>
       </c>
-      <c r="F97" t="s">
-        <v>396</v>
-      </c>
       <c r="G97" t="s">
-        <v>506</v>
+        <v>395</v>
       </c>
       <c r="H97" t="s">
-        <v>466</v>
+        <v>505</v>
       </c>
       <c r="I97" t="s">
-        <v>506</v>
-      </c>
-      <c r="J97">
+        <v>465</v>
+      </c>
+      <c r="J97" t="s">
+        <v>505</v>
+      </c>
+      <c r="K97">
         <v>4</v>
       </c>
-      <c r="K97" t="s">
-        <v>418</v>
-      </c>
-      <c r="L97">
+      <c r="L97" t="s">
+        <v>417</v>
+      </c>
+      <c r="M97">
         <f>4*3</f>
         <v>12</v>
       </c>
-      <c r="M97" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="N97" t="s">
+      <c r="N97" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="O97" t="s">
+        <v>567</v>
+      </c>
+      <c r="P97" t="s">
         <v>568</v>
       </c>
-      <c r="O97" t="s">
-        <v>569</v>
-      </c>
-      <c r="P97" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q97" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C98" t="s">
         <v>85</v>
@@ -7476,97 +7778,103 @@
         <v>186</v>
       </c>
       <c r="E98" t="s">
+        <v>716</v>
+      </c>
+      <c r="F98" t="s">
         <v>9</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>11</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
         <v>49</v>
       </c>
-      <c r="H98" t="s">
-        <v>470</v>
-      </c>
       <c r="I98" t="s">
+        <v>469</v>
+      </c>
+      <c r="J98" t="s">
         <v>99</v>
       </c>
-      <c r="J98">
+      <c r="K98">
         <v>3</v>
       </c>
-      <c r="K98" t="s">
-        <v>420</v>
-      </c>
-      <c r="L98">
+      <c r="L98" t="s">
+        <v>419</v>
+      </c>
+      <c r="M98">
         <f>30</f>
         <v>30</v>
       </c>
-      <c r="M98" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="N98" t="s">
-        <v>619</v>
+      <c r="N98" s="1" t="s">
+        <v>420</v>
       </c>
       <c r="O98" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+      <c r="P98" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C99" t="s">
         <v>85</v>
       </c>
       <c r="D99" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E99" t="s">
+        <v>714</v>
+      </c>
+      <c r="F99" t="s">
         <v>9</v>
       </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>11</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
         <v>49</v>
       </c>
-      <c r="H99" t="s">
-        <v>470</v>
-      </c>
       <c r="I99" t="s">
+        <v>469</v>
+      </c>
+      <c r="J99" t="s">
         <v>99</v>
       </c>
-      <c r="J99">
+      <c r="K99">
         <v>3</v>
       </c>
-      <c r="K99" t="s">
-        <v>423</v>
-      </c>
-      <c r="L99">
+      <c r="L99" t="s">
+        <v>422</v>
+      </c>
+      <c r="M99">
         <f>15</f>
         <v>15</v>
       </c>
-      <c r="M99" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="N99" t="s">
-        <v>633</v>
+      <c r="N99" s="1" t="s">
+        <v>425</v>
       </c>
       <c r="O99" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="P99" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+        <v>634</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C100" t="s">
         <v>85</v>
@@ -7575,49 +7883,52 @@
         <v>27</v>
       </c>
       <c r="E100" t="s">
+        <v>714</v>
+      </c>
+      <c r="F100" t="s">
         <v>48</v>
       </c>
-      <c r="F100" t="s">
-        <v>429</v>
-      </c>
       <c r="G100" t="s">
+        <v>428</v>
+      </c>
+      <c r="H100" t="s">
         <v>99</v>
       </c>
-      <c r="H100" t="s">
-        <v>470</v>
-      </c>
       <c r="I100" t="s">
+        <v>469</v>
+      </c>
+      <c r="J100" t="s">
         <v>99</v>
       </c>
-      <c r="J100">
+      <c r="K100">
         <v>3</v>
       </c>
-      <c r="K100" t="s">
-        <v>427</v>
-      </c>
-      <c r="L100">
+      <c r="L100" t="s">
+        <v>426</v>
+      </c>
+      <c r="M100">
         <f>60</f>
         <v>60</v>
       </c>
-      <c r="M100" t="s">
+      <c r="N100" t="s">
         <v>40</v>
       </c>
-      <c r="N100" t="s">
-        <v>570</v>
-      </c>
       <c r="O100" t="s">
-        <v>509</v>
+        <v>569</v>
       </c>
       <c r="P100" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C101" t="s">
         <v>85</v>
@@ -7626,135 +7937,138 @@
         <v>57</v>
       </c>
       <c r="E101" t="s">
+        <v>315</v>
+      </c>
+      <c r="F101" t="s">
         <v>48</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>17</v>
       </c>
-      <c r="G101" t="s">
-        <v>507</v>
-      </c>
       <c r="H101" t="s">
-        <v>470</v>
+        <v>506</v>
       </c>
       <c r="I101" t="s">
+        <v>469</v>
+      </c>
+      <c r="J101" t="s">
         <v>66</v>
       </c>
-      <c r="J101">
+      <c r="K101">
         <v>3</v>
       </c>
-      <c r="K101" t="s">
-        <v>711</v>
-      </c>
-      <c r="L101">
+      <c r="L101" t="s">
+        <v>710</v>
+      </c>
+      <c r="M101">
         <f>3*4</f>
         <v>12</v>
       </c>
-      <c r="M101" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="N101" t="s">
+      <c r="N101" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="O101" t="s">
+        <v>711</v>
+      </c>
+      <c r="P101" t="s">
         <v>712</v>
       </c>
-      <c r="O101" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B102" s="1"/>
-      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R101" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q101">
+  <autoFilter ref="A1:S101" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R101">
     <sortCondition ref="A2:A101"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="M4" r:id="rId1" display="https://doi.org/10.1016/j.stemcr.2022.04.003" xr:uid="{A58B2C92-8135-4993-80B6-E01F7C4414D7}"/>
-    <hyperlink ref="M2" r:id="rId2" xr:uid="{ECF580C4-849C-4561-A481-5430106E5AFC}"/>
-    <hyperlink ref="M5" r:id="rId3" location="Sec9" xr:uid="{7F005011-D3D0-40EB-9669-AC279104458C}"/>
-    <hyperlink ref="M6" r:id="rId4" xr:uid="{A191089C-F484-4E45-8BCC-52AA445AD4F5}"/>
-    <hyperlink ref="M8" r:id="rId5" xr:uid="{C5BC7455-0EFA-4A23-B621-721339B38A6F}"/>
-    <hyperlink ref="M9" r:id="rId6" xr:uid="{B7CED74B-1E74-43D2-A36B-EAB3B1E178BC}"/>
-    <hyperlink ref="M10" r:id="rId7" location="sd" xr:uid="{52E8DACA-8996-4096-ACEA-71C8C40EA025}"/>
-    <hyperlink ref="M11" r:id="rId8" xr:uid="{27478232-A532-4DCE-809B-5DD99BA4CE49}"/>
-    <hyperlink ref="M12" r:id="rId9" xr:uid="{50937FCB-E158-45DA-96E3-555511B96735}"/>
-    <hyperlink ref="M13" r:id="rId10" location="Sec11" xr:uid="{EAAEE3D5-FD5F-4C5E-BEDE-E149007B61D7}"/>
-    <hyperlink ref="M14" r:id="rId11" xr:uid="{1466ACE4-040B-4872-B3E7-CB073BC90CE4}"/>
-    <hyperlink ref="M15" r:id="rId12" display="https://doi.org/10.1038/s42255-021-00420-9" xr:uid="{AA76EE2A-3D95-4B26-A3B2-D6961FCAA8B9}"/>
-    <hyperlink ref="M17" r:id="rId13" xr:uid="{73C3C164-1B9E-424D-B497-0A5C1413062E}"/>
-    <hyperlink ref="M18" r:id="rId14" xr:uid="{8E96941A-F27E-446D-BAAB-8817BA69407F}"/>
-    <hyperlink ref="M20" r:id="rId15" xr:uid="{612CAC31-BDF9-4217-882E-04BA9D317851}"/>
-    <hyperlink ref="M42" r:id="rId16" xr:uid="{A0AABACF-D49B-4ADE-969F-34674947E980}"/>
-    <hyperlink ref="M30" r:id="rId17" xr:uid="{798BD1EC-17B3-4197-8EAE-486722AEADF1}"/>
-    <hyperlink ref="M31" r:id="rId18" xr:uid="{AE40AA44-2798-47B6-B9FB-02DFCD819A98}"/>
-    <hyperlink ref="M21" r:id="rId19" xr:uid="{812AD498-467D-4930-99B1-0BD72991EB74}"/>
-    <hyperlink ref="M32" r:id="rId20" xr:uid="{0A4265F2-3C05-4E25-883C-F8A8F58C6D63}"/>
-    <hyperlink ref="M33" r:id="rId21" xr:uid="{DBE6CDEE-1512-471E-91A3-29DE9DCD40F4}"/>
-    <hyperlink ref="M34" r:id="rId22" xr:uid="{1530F3E7-5FB8-4C45-8815-BC53BEE62E5F}"/>
-    <hyperlink ref="M36" r:id="rId23" xr:uid="{81A03F1A-4A0B-4C2D-947D-86D4D18A30FC}"/>
-    <hyperlink ref="M37" r:id="rId24" xr:uid="{03A7BDDE-DDD3-4CE4-9A6A-3F28026978CD}"/>
-    <hyperlink ref="M38" r:id="rId25" xr:uid="{97D5A0D0-4F73-4447-98D7-176FE36E7E9F}"/>
-    <hyperlink ref="M39" r:id="rId26" xr:uid="{3FDDCA56-CB99-4846-8D3C-3F87979E1526}"/>
-    <hyperlink ref="M40" r:id="rId27" xr:uid="{7859E8C3-2333-43D3-B478-A44FA49BB177}"/>
-    <hyperlink ref="M41" r:id="rId28" xr:uid="{4AAB6572-69BF-4A8C-B9DD-0ECD744015A7}"/>
-    <hyperlink ref="M43" r:id="rId29" xr:uid="{AEFB8F3B-EA1A-47CE-B2E9-52C8FEE30E73}"/>
-    <hyperlink ref="M44" r:id="rId30" xr:uid="{CB2F7DF2-FC97-4B92-86B1-9479DA20F40F}"/>
-    <hyperlink ref="M45" r:id="rId31" xr:uid="{256ADA76-DDF3-43D7-9FF6-3D06B3102F1B}"/>
-    <hyperlink ref="M46" r:id="rId32" xr:uid="{8607D0FC-A3CA-4C2C-B9AF-EA3A5742473F}"/>
-    <hyperlink ref="M47" r:id="rId33" xr:uid="{CC518961-8295-4994-A3DF-84ED80F14808}"/>
-    <hyperlink ref="M48" r:id="rId34" xr:uid="{2FCAA5AF-4D5B-40D6-9710-958A63043040}"/>
-    <hyperlink ref="M49" r:id="rId35" xr:uid="{AE407C0D-97C6-498B-BFB4-71C4936A1365}"/>
-    <hyperlink ref="M50" r:id="rId36" xr:uid="{92FB0A8D-11DB-4567-8F9B-CF523A119E05}"/>
-    <hyperlink ref="M51" r:id="rId37" xr:uid="{207EE6F5-656D-4A38-9817-F2A00ABFCEEE}"/>
-    <hyperlink ref="M53" r:id="rId38" xr:uid="{E3F0AF35-4EFD-4690-93B1-C3CEFB35EC15}"/>
-    <hyperlink ref="M54" r:id="rId39" xr:uid="{7C683447-D985-423F-B5CD-03B9FB95AD65}"/>
-    <hyperlink ref="M55" r:id="rId40" xr:uid="{BDF4E4E0-765A-4F0B-BD68-C69115F0738F}"/>
-    <hyperlink ref="M57" r:id="rId41" xr:uid="{C0FA8537-4468-48BF-A054-0D7291F65AE0}"/>
-    <hyperlink ref="M58" r:id="rId42" xr:uid="{8D999E26-CBDB-4FE4-ADDB-E6B611D67331}"/>
-    <hyperlink ref="M59" r:id="rId43" xr:uid="{7A24ADCF-B6A2-404E-89EC-C398B7118D79}"/>
-    <hyperlink ref="M60" r:id="rId44" xr:uid="{0B450A65-6781-41DE-9BEF-0479DD4B3225}"/>
-    <hyperlink ref="M61" r:id="rId45" xr:uid="{13A1084D-B36D-4396-A3D3-56FA85A81598}"/>
-    <hyperlink ref="M63" r:id="rId46" xr:uid="{815FAA3B-87CE-4626-94FB-28BB0C9DC865}"/>
-    <hyperlink ref="M64" r:id="rId47" xr:uid="{87332800-52F9-415F-88A8-13B3218E1B95}"/>
-    <hyperlink ref="M62" r:id="rId48" xr:uid="{20655D6D-7A5B-4884-972D-A0B324AF2E09}"/>
-    <hyperlink ref="M66" r:id="rId49" xr:uid="{29C9B3AB-C1C5-4CD9-9B61-66EB2F5DB119}"/>
-    <hyperlink ref="M68" r:id="rId50" xr:uid="{A5A57614-CF6E-46F6-B6E8-5F616167FA0D}"/>
-    <hyperlink ref="M69" r:id="rId51" xr:uid="{01DF9558-6F69-4543-A8DD-1581956A8E01}"/>
-    <hyperlink ref="M73" r:id="rId52" xr:uid="{709E7BEA-314C-4B0F-A59A-6BF8CAABD75C}"/>
-    <hyperlink ref="M70" r:id="rId53" xr:uid="{9A7B274C-695B-4B24-B4F1-DD64F89BEC2F}"/>
-    <hyperlink ref="M71" r:id="rId54" xr:uid="{53F78946-D0F1-45CE-80F4-DCEF51325FA5}"/>
-    <hyperlink ref="M72" r:id="rId55" xr:uid="{8853D92F-CF28-4712-9231-7429D3BFBBFB}"/>
-    <hyperlink ref="M74" r:id="rId56" xr:uid="{44AE3EE4-BA3F-4C04-B457-C8BE8762DC83}"/>
-    <hyperlink ref="M75" r:id="rId57" xr:uid="{DB61579F-438D-4DF9-B387-7F2F5EA1AE5D}"/>
-    <hyperlink ref="M76" r:id="rId58" xr:uid="{9C641A84-E07C-4EF1-9FFC-12E3055FF46E}"/>
-    <hyperlink ref="M77" r:id="rId59" xr:uid="{35F7105D-4C78-45B1-8E0C-651E22400B24}"/>
-    <hyperlink ref="M78" r:id="rId60" xr:uid="{76FAEE4C-5466-4FB1-B104-402F652D0F82}"/>
-    <hyperlink ref="M80" r:id="rId61" xr:uid="{B222AC14-18AF-40AE-8D03-B1981FBE28A6}"/>
-    <hyperlink ref="M79" r:id="rId62" xr:uid="{B875AC8B-59AF-4BD2-9A20-40747F088572}"/>
-    <hyperlink ref="M81" r:id="rId63" xr:uid="{612059EE-8652-46E0-8015-99B298BDC96E}"/>
-    <hyperlink ref="M82" r:id="rId64" xr:uid="{2274C7CE-0848-479C-8E48-A92AFCD2DAF3}"/>
-    <hyperlink ref="M83" r:id="rId65" tooltip="Persistent link using digital object identifier" xr:uid="{27BFC4E4-9DCB-4C1D-B672-888C8D8E2732}"/>
-    <hyperlink ref="M84" r:id="rId66" xr:uid="{3593983D-93B4-45AC-8DAA-EEEB7814C6DA}"/>
-    <hyperlink ref="M85" r:id="rId67" xr:uid="{EC9CC085-AE00-427A-8A98-D6B7FAC40915}"/>
-    <hyperlink ref="M86" r:id="rId68" xr:uid="{37B11193-AEED-49A8-8DC8-B8B1A4B50E16}"/>
-    <hyperlink ref="M87" r:id="rId69" xr:uid="{A403A46C-980D-45D5-B1F3-6B41994824E5}"/>
-    <hyperlink ref="M88" r:id="rId70" xr:uid="{15C15D05-2BF6-429B-990B-D4D122B2135A}"/>
-    <hyperlink ref="M89" r:id="rId71" display="https://pubs.acs.org/doi/abs/10.1021/acs.jproteome.6b00211" xr:uid="{C8CA3592-D189-4484-9578-3CE6AA7AAAF0}"/>
-    <hyperlink ref="M90" r:id="rId72" xr:uid="{EA5E6D9D-EB0C-4CD0-A732-5E51418702BE}"/>
-    <hyperlink ref="M91" r:id="rId73" display="https://doi.org/10.1016/j.jbc.2021.100408" xr:uid="{B898DC3E-877C-48D3-B8DB-38527442C91C}"/>
-    <hyperlink ref="M92" r:id="rId74" xr:uid="{E631AF55-B593-4564-AD7B-C50AA064B385}"/>
-    <hyperlink ref="M93" r:id="rId75" xr:uid="{B2B70E0C-93B6-4E11-96C1-A5E9EACBC9AA}"/>
-    <hyperlink ref="M94" r:id="rId76" xr:uid="{9AE33C66-89B4-4F2A-8E68-CFB244668468}"/>
-    <hyperlink ref="M96" r:id="rId77" xr:uid="{DE49CA08-17FF-4C18-8C19-DF135E909D8E}"/>
-    <hyperlink ref="M98" r:id="rId78" xr:uid="{8925AE44-1384-4094-9B9F-CDCD372A1CA9}"/>
-    <hyperlink ref="M97" r:id="rId79" xr:uid="{69516E89-6753-4063-B3E0-FCDA495C291D}"/>
-    <hyperlink ref="M99" r:id="rId80" xr:uid="{58BA4A32-0915-4B17-956C-DBF2AC5940FA}"/>
-    <hyperlink ref="M101" r:id="rId81" xr:uid="{74804044-9702-465A-B0D4-A230294D0CE5}"/>
-    <hyperlink ref="M24" r:id="rId82" xr:uid="{DD198BDC-1A91-40C1-AB2A-6CA2254E3A80}"/>
-    <hyperlink ref="M23" r:id="rId83" xr:uid="{54EC2941-3A77-498F-9485-52BE0EAB6EE8}"/>
-    <hyperlink ref="M65" r:id="rId84" xr:uid="{2C672FCE-1691-4A02-BDA5-38F14F68F9A1}"/>
-    <hyperlink ref="M3" r:id="rId85" xr:uid="{A52741AB-5A3F-448A-85EE-A088C3461BE0}"/>
+    <hyperlink ref="N4" r:id="rId1" display="https://doi.org/10.1016/j.stemcr.2022.04.003" xr:uid="{A58B2C92-8135-4993-80B6-E01F7C4414D7}"/>
+    <hyperlink ref="N2" r:id="rId2" xr:uid="{ECF580C4-849C-4561-A481-5430106E5AFC}"/>
+    <hyperlink ref="N5" r:id="rId3" location="Sec9" xr:uid="{7F005011-D3D0-40EB-9669-AC279104458C}"/>
+    <hyperlink ref="N6" r:id="rId4" xr:uid="{A191089C-F484-4E45-8BCC-52AA445AD4F5}"/>
+    <hyperlink ref="N8" r:id="rId5" xr:uid="{C5BC7455-0EFA-4A23-B621-721339B38A6F}"/>
+    <hyperlink ref="N9" r:id="rId6" xr:uid="{B7CED74B-1E74-43D2-A36B-EAB3B1E178BC}"/>
+    <hyperlink ref="N10" r:id="rId7" location="sd" xr:uid="{52E8DACA-8996-4096-ACEA-71C8C40EA025}"/>
+    <hyperlink ref="N11" r:id="rId8" xr:uid="{27478232-A532-4DCE-809B-5DD99BA4CE49}"/>
+    <hyperlink ref="N12" r:id="rId9" xr:uid="{50937FCB-E158-45DA-96E3-555511B96735}"/>
+    <hyperlink ref="N13" r:id="rId10" location="Sec11" xr:uid="{EAAEE3D5-FD5F-4C5E-BEDE-E149007B61D7}"/>
+    <hyperlink ref="N14" r:id="rId11" xr:uid="{1466ACE4-040B-4872-B3E7-CB073BC90CE4}"/>
+    <hyperlink ref="N15" r:id="rId12" display="https://doi.org/10.1038/s42255-021-00420-9" xr:uid="{AA76EE2A-3D95-4B26-A3B2-D6961FCAA8B9}"/>
+    <hyperlink ref="N17" r:id="rId13" xr:uid="{73C3C164-1B9E-424D-B497-0A5C1413062E}"/>
+    <hyperlink ref="N18" r:id="rId14" xr:uid="{8E96941A-F27E-446D-BAAB-8817BA69407F}"/>
+    <hyperlink ref="N20" r:id="rId15" xr:uid="{612CAC31-BDF9-4217-882E-04BA9D317851}"/>
+    <hyperlink ref="N42" r:id="rId16" xr:uid="{A0AABACF-D49B-4ADE-969F-34674947E980}"/>
+    <hyperlink ref="N30" r:id="rId17" xr:uid="{798BD1EC-17B3-4197-8EAE-486722AEADF1}"/>
+    <hyperlink ref="N31" r:id="rId18" xr:uid="{AE40AA44-2798-47B6-B9FB-02DFCD819A98}"/>
+    <hyperlink ref="N21" r:id="rId19" xr:uid="{812AD498-467D-4930-99B1-0BD72991EB74}"/>
+    <hyperlink ref="N32" r:id="rId20" xr:uid="{0A4265F2-3C05-4E25-883C-F8A8F58C6D63}"/>
+    <hyperlink ref="N33" r:id="rId21" xr:uid="{DBE6CDEE-1512-471E-91A3-29DE9DCD40F4}"/>
+    <hyperlink ref="N34" r:id="rId22" xr:uid="{1530F3E7-5FB8-4C45-8815-BC53BEE62E5F}"/>
+    <hyperlink ref="N36" r:id="rId23" xr:uid="{81A03F1A-4A0B-4C2D-947D-86D4D18A30FC}"/>
+    <hyperlink ref="N37" r:id="rId24" xr:uid="{03A7BDDE-DDD3-4CE4-9A6A-3F28026978CD}"/>
+    <hyperlink ref="N38" r:id="rId25" xr:uid="{97D5A0D0-4F73-4447-98D7-176FE36E7E9F}"/>
+    <hyperlink ref="N39" r:id="rId26" xr:uid="{3FDDCA56-CB99-4846-8D3C-3F87979E1526}"/>
+    <hyperlink ref="N40" r:id="rId27" xr:uid="{7859E8C3-2333-43D3-B478-A44FA49BB177}"/>
+    <hyperlink ref="N41" r:id="rId28" xr:uid="{4AAB6572-69BF-4A8C-B9DD-0ECD744015A7}"/>
+    <hyperlink ref="N43" r:id="rId29" xr:uid="{AEFB8F3B-EA1A-47CE-B2E9-52C8FEE30E73}"/>
+    <hyperlink ref="N44" r:id="rId30" xr:uid="{CB2F7DF2-FC97-4B92-86B1-9479DA20F40F}"/>
+    <hyperlink ref="N45" r:id="rId31" xr:uid="{256ADA76-DDF3-43D7-9FF6-3D06B3102F1B}"/>
+    <hyperlink ref="N46" r:id="rId32" xr:uid="{8607D0FC-A3CA-4C2C-B9AF-EA3A5742473F}"/>
+    <hyperlink ref="N47" r:id="rId33" xr:uid="{CC518961-8295-4994-A3DF-84ED80F14808}"/>
+    <hyperlink ref="N48" r:id="rId34" xr:uid="{2FCAA5AF-4D5B-40D6-9710-958A63043040}"/>
+    <hyperlink ref="N49" r:id="rId35" xr:uid="{AE407C0D-97C6-498B-BFB4-71C4936A1365}"/>
+    <hyperlink ref="N50" r:id="rId36" xr:uid="{92FB0A8D-11DB-4567-8F9B-CF523A119E05}"/>
+    <hyperlink ref="N51" r:id="rId37" xr:uid="{207EE6F5-656D-4A38-9817-F2A00ABFCEEE}"/>
+    <hyperlink ref="N53" r:id="rId38" xr:uid="{E3F0AF35-4EFD-4690-93B1-C3CEFB35EC15}"/>
+    <hyperlink ref="N54" r:id="rId39" xr:uid="{7C683447-D985-423F-B5CD-03B9FB95AD65}"/>
+    <hyperlink ref="N55" r:id="rId40" xr:uid="{BDF4E4E0-765A-4F0B-BD68-C69115F0738F}"/>
+    <hyperlink ref="N57" r:id="rId41" xr:uid="{C0FA8537-4468-48BF-A054-0D7291F65AE0}"/>
+    <hyperlink ref="N58" r:id="rId42" xr:uid="{8D999E26-CBDB-4FE4-ADDB-E6B611D67331}"/>
+    <hyperlink ref="N59" r:id="rId43" xr:uid="{7A24ADCF-B6A2-404E-89EC-C398B7118D79}"/>
+    <hyperlink ref="N60" r:id="rId44" xr:uid="{0B450A65-6781-41DE-9BEF-0479DD4B3225}"/>
+    <hyperlink ref="N61" r:id="rId45" xr:uid="{13A1084D-B36D-4396-A3D3-56FA85A81598}"/>
+    <hyperlink ref="N63" r:id="rId46" xr:uid="{815FAA3B-87CE-4626-94FB-28BB0C9DC865}"/>
+    <hyperlink ref="N64" r:id="rId47" xr:uid="{87332800-52F9-415F-88A8-13B3218E1B95}"/>
+    <hyperlink ref="N62" r:id="rId48" xr:uid="{20655D6D-7A5B-4884-972D-A0B324AF2E09}"/>
+    <hyperlink ref="N66" r:id="rId49" xr:uid="{29C9B3AB-C1C5-4CD9-9B61-66EB2F5DB119}"/>
+    <hyperlink ref="N68" r:id="rId50" xr:uid="{A5A57614-CF6E-46F6-B6E8-5F616167FA0D}"/>
+    <hyperlink ref="N69" r:id="rId51" xr:uid="{01DF9558-6F69-4543-A8DD-1581956A8E01}"/>
+    <hyperlink ref="N73" r:id="rId52" xr:uid="{709E7BEA-314C-4B0F-A59A-6BF8CAABD75C}"/>
+    <hyperlink ref="N70" r:id="rId53" xr:uid="{9A7B274C-695B-4B24-B4F1-DD64F89BEC2F}"/>
+    <hyperlink ref="N71" r:id="rId54" xr:uid="{53F78946-D0F1-45CE-80F4-DCEF51325FA5}"/>
+    <hyperlink ref="N72" r:id="rId55" xr:uid="{8853D92F-CF28-4712-9231-7429D3BFBBFB}"/>
+    <hyperlink ref="N74" r:id="rId56" xr:uid="{44AE3EE4-BA3F-4C04-B457-C8BE8762DC83}"/>
+    <hyperlink ref="N75" r:id="rId57" xr:uid="{DB61579F-438D-4DF9-B387-7F2F5EA1AE5D}"/>
+    <hyperlink ref="N76" r:id="rId58" xr:uid="{9C641A84-E07C-4EF1-9FFC-12E3055FF46E}"/>
+    <hyperlink ref="N77" r:id="rId59" xr:uid="{35F7105D-4C78-45B1-8E0C-651E22400B24}"/>
+    <hyperlink ref="N78" r:id="rId60" xr:uid="{76FAEE4C-5466-4FB1-B104-402F652D0F82}"/>
+    <hyperlink ref="N80" r:id="rId61" xr:uid="{B222AC14-18AF-40AE-8D03-B1981FBE28A6}"/>
+    <hyperlink ref="N79" r:id="rId62" xr:uid="{B875AC8B-59AF-4BD2-9A20-40747F088572}"/>
+    <hyperlink ref="N81" r:id="rId63" xr:uid="{612059EE-8652-46E0-8015-99B298BDC96E}"/>
+    <hyperlink ref="N82" r:id="rId64" xr:uid="{2274C7CE-0848-479C-8E48-A92AFCD2DAF3}"/>
+    <hyperlink ref="N83" r:id="rId65" tooltip="Persistent link using digital object identifier" xr:uid="{27BFC4E4-9DCB-4C1D-B672-888C8D8E2732}"/>
+    <hyperlink ref="N84" r:id="rId66" xr:uid="{3593983D-93B4-45AC-8DAA-EEEB7814C6DA}"/>
+    <hyperlink ref="N85" r:id="rId67" xr:uid="{EC9CC085-AE00-427A-8A98-D6B7FAC40915}"/>
+    <hyperlink ref="N86" r:id="rId68" xr:uid="{37B11193-AEED-49A8-8DC8-B8B1A4B50E16}"/>
+    <hyperlink ref="N87" r:id="rId69" xr:uid="{A403A46C-980D-45D5-B1F3-6B41994824E5}"/>
+    <hyperlink ref="N88" r:id="rId70" xr:uid="{15C15D05-2BF6-429B-990B-D4D122B2135A}"/>
+    <hyperlink ref="N89" r:id="rId71" display="https://pubs.acs.org/doi/abs/10.1021/acs.jproteome.6b00211" xr:uid="{C8CA3592-D189-4484-9578-3CE6AA7AAAF0}"/>
+    <hyperlink ref="N90" r:id="rId72" xr:uid="{EA5E6D9D-EB0C-4CD0-A732-5E51418702BE}"/>
+    <hyperlink ref="N91" r:id="rId73" display="https://doi.org/10.1016/j.jbc.2021.100408" xr:uid="{B898DC3E-877C-48D3-B8DB-38527442C91C}"/>
+    <hyperlink ref="N92" r:id="rId74" xr:uid="{E631AF55-B593-4564-AD7B-C50AA064B385}"/>
+    <hyperlink ref="N93" r:id="rId75" xr:uid="{B2B70E0C-93B6-4E11-96C1-A5E9EACBC9AA}"/>
+    <hyperlink ref="N94" r:id="rId76" xr:uid="{9AE33C66-89B4-4F2A-8E68-CFB244668468}"/>
+    <hyperlink ref="N96" r:id="rId77" xr:uid="{DE49CA08-17FF-4C18-8C19-DF135E909D8E}"/>
+    <hyperlink ref="N98" r:id="rId78" xr:uid="{8925AE44-1384-4094-9B9F-CDCD372A1CA9}"/>
+    <hyperlink ref="N97" r:id="rId79" xr:uid="{69516E89-6753-4063-B3E0-FCDA495C291D}"/>
+    <hyperlink ref="N99" r:id="rId80" xr:uid="{58BA4A32-0915-4B17-956C-DBF2AC5940FA}"/>
+    <hyperlink ref="N101" r:id="rId81" xr:uid="{74804044-9702-465A-B0D4-A230294D0CE5}"/>
+    <hyperlink ref="N24" r:id="rId82" xr:uid="{DD198BDC-1A91-40C1-AB2A-6CA2254E3A80}"/>
+    <hyperlink ref="N23" r:id="rId83" xr:uid="{54EC2941-3A77-498F-9485-52BE0EAB6EE8}"/>
+    <hyperlink ref="N65" r:id="rId84" xr:uid="{2C672FCE-1691-4A02-BDA5-38F14F68F9A1}"/>
+    <hyperlink ref="N3" r:id="rId85" xr:uid="{A52741AB-5A3F-448A-85EE-A088C3461BE0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId86"/>
@@ -7865,7 +8179,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -7898,7 +8212,7 @@
         <v>120</v>
       </c>
       <c r="P3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -7939,7 +8253,7 @@
         <v>130</v>
       </c>
       <c r="P4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -7962,13 +8276,13 @@
         <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I5" t="s">
+        <v>465</v>
+      </c>
+      <c r="J5" t="s">
         <v>466</v>
-      </c>
-      <c r="J5" t="s">
-        <v>467</v>
       </c>
       <c r="K5">
         <v>4</v>
@@ -8064,42 +8378,42 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>378</v>
+      </c>
+      <c r="B8" t="s">
         <v>379</v>
-      </c>
-      <c r="B8" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>380</v>
+      </c>
+      <c r="B9" t="s">
         <v>381</v>
-      </c>
-      <c r="B9" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>382</v>
+      </c>
+      <c r="B10" t="s">
         <v>383</v>
-      </c>
-      <c r="B10" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>389</v>
+      </c>
+      <c r="B11" t="s">
         <v>390</v>
-      </c>
-      <c r="B11" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>441</v>
+      </c>
+      <c r="B12" t="s">
         <v>442</v>
-      </c>
-      <c r="B12" t="s">
-        <v>443</v>
       </c>
     </row>
   </sheetData>

--- a/goldStandard/_Index.xlsx
+++ b/goldStandard/_Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore-development\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB851249-1EA9-41A9-BDBA-C9A7AC4626CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC13A02-D14B-45E8-8F5E-5FEA36084C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10485" yWindow="4200" windowWidth="37380" windowHeight="12765" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
+    <workbookView xWindow="930" yWindow="1065" windowWidth="29700" windowHeight="19665" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
   </bookViews>
   <sheets>
     <sheet name="In" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="716">
   <si>
     <t>ID</t>
   </si>
@@ -2175,16 +2175,10 @@
     <t>MS instrument (summary)</t>
   </si>
   <si>
-    <t>Orbitrap</t>
-  </si>
-  <si>
-    <t>Orbitrap;Q Exactive</t>
-  </si>
-  <si>
-    <t>TripleTOF</t>
-  </si>
-  <si>
-    <t>ZenoTOF</t>
+    <t>TOF-based</t>
+  </si>
+  <si>
+    <t>Orbitrap-based</t>
   </si>
 </sst>
 </file>
@@ -2692,7 +2686,7 @@
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -2752,7 +2746,7 @@
         <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
@@ -2808,7 +2802,7 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -2860,7 +2854,7 @@
         <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
@@ -2914,7 +2908,7 @@
         <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
@@ -2970,7 +2964,7 @@
         <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
@@ -3027,7 +3021,7 @@
         <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -3082,7 +3076,7 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F9" t="s">
         <v>48</v>
@@ -3139,7 +3133,7 @@
         <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F10" t="s">
         <v>48</v>
@@ -3192,7 +3186,7 @@
         <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F11" t="s">
         <v>48</v>
@@ -3245,7 +3239,7 @@
         <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F12" t="s">
         <v>48</v>
@@ -3296,7 +3290,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -3349,7 +3343,7 @@
         <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
@@ -3403,7 +3397,7 @@
         <v>57</v>
       </c>
       <c r="E15" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
@@ -3506,7 +3500,7 @@
         <v>27</v>
       </c>
       <c r="E17" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
@@ -3556,7 +3550,7 @@
         <v>61</v>
       </c>
       <c r="E18" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F18" t="s">
         <v>9</v>
@@ -3609,7 +3603,7 @@
         <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
@@ -3663,7 +3657,7 @@
         <v>105</v>
       </c>
       <c r="E20" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
@@ -3719,7 +3713,7 @@
         <v>29</v>
       </c>
       <c r="E21" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
@@ -3773,7 +3767,7 @@
         <v>111</v>
       </c>
       <c r="E22" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="F22" t="s">
         <v>112</v>
@@ -3827,7 +3821,7 @@
         <v>105</v>
       </c>
       <c r="E23" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F23" t="s">
         <v>112</v>
@@ -3881,7 +3875,7 @@
         <v>43</v>
       </c>
       <c r="E24" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F24" t="s">
         <v>112</v>
@@ -3932,7 +3926,7 @@
         <v>122</v>
       </c>
       <c r="E25" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F25" t="s">
         <v>112</v>
@@ -3982,7 +3976,7 @@
         <v>53</v>
       </c>
       <c r="E26" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F26" t="s">
         <v>112</v>
@@ -4032,7 +4026,7 @@
         <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F27" t="s">
         <v>112</v>
@@ -4083,7 +4077,7 @@
         <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F28" t="s">
         <v>112</v>
@@ -4133,7 +4127,7 @@
         <v>57</v>
       </c>
       <c r="E29" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F29" t="s">
         <v>112</v>
@@ -4184,7 +4178,7 @@
         <v>134</v>
       </c>
       <c r="E30" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F30" t="s">
         <v>112</v>
@@ -4235,7 +4229,7 @@
         <v>139</v>
       </c>
       <c r="E31" t="s">
-        <v>139</v>
+        <v>714</v>
       </c>
       <c r="F31" t="s">
         <v>112</v>
@@ -4253,13 +4247,12 @@
         <v>475</v>
       </c>
       <c r="K31">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L31" t="s">
         <v>140</v>
       </c>
       <c r="M31">
-        <f>K31*4</f>
         <v>16</v>
       </c>
       <c r="N31" s="1" t="s">
@@ -4286,7 +4279,7 @@
         <v>57</v>
       </c>
       <c r="E32" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F32" t="s">
         <v>112</v>
@@ -4340,7 +4333,7 @@
         <v>151</v>
       </c>
       <c r="E33" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F33" t="s">
         <v>112</v>
@@ -4392,7 +4385,7 @@
         <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F34" t="s">
         <v>112</v>
@@ -4410,7 +4403,7 @@
         <v>478</v>
       </c>
       <c r="K34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L34" t="s">
         <v>156</v>
@@ -4443,7 +4436,7 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F35" t="s">
         <v>112</v>
@@ -4494,7 +4487,7 @@
         <v>164</v>
       </c>
       <c r="E36" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F36" t="s">
         <v>112</v>
@@ -4545,7 +4538,7 @@
         <v>61</v>
       </c>
       <c r="E37" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F37" t="s">
         <v>112</v>
@@ -4602,7 +4595,7 @@
         <v>27</v>
       </c>
       <c r="E38" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F38" t="s">
         <v>112</v>
@@ -4653,7 +4646,7 @@
         <v>172</v>
       </c>
       <c r="E39" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F39" t="s">
         <v>112</v>
@@ -4704,7 +4697,7 @@
         <v>53</v>
       </c>
       <c r="E40" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F40" t="s">
         <v>112</v>
@@ -4758,7 +4751,7 @@
         <v>57</v>
       </c>
       <c r="E41" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F41" t="s">
         <v>112</v>
@@ -4815,7 +4808,7 @@
         <v>105</v>
       </c>
       <c r="E42" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
@@ -4869,7 +4862,7 @@
         <v>186</v>
       </c>
       <c r="E43" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="F43" t="s">
         <v>112</v>
@@ -4923,7 +4916,7 @@
         <v>18</v>
       </c>
       <c r="E44" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F44" t="s">
         <v>112</v>
@@ -4976,7 +4969,7 @@
         <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F45" t="s">
         <v>112</v>
@@ -5029,7 +5022,7 @@
         <v>111</v>
       </c>
       <c r="E46" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="F46" t="s">
         <v>112</v>
@@ -5047,7 +5040,7 @@
         <v>489</v>
       </c>
       <c r="K46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L46" t="s">
         <v>590</v>
@@ -5083,7 +5076,7 @@
         <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F47" t="s">
         <v>112</v>
@@ -5136,7 +5129,7 @@
         <v>207</v>
       </c>
       <c r="E48" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F48" t="s">
         <v>112</v>
@@ -5186,7 +5179,7 @@
         <v>39</v>
       </c>
       <c r="E49" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F49" t="s">
         <v>112</v>
@@ -5240,7 +5233,7 @@
         <v>18</v>
       </c>
       <c r="E50" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F50" t="s">
         <v>112</v>
@@ -5295,7 +5288,7 @@
         <v>111</v>
       </c>
       <c r="E51" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="F51" t="s">
         <v>112</v>
@@ -5350,7 +5343,7 @@
         <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F52" t="s">
         <v>112</v>
@@ -5403,7 +5396,7 @@
         <v>186</v>
       </c>
       <c r="E53" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="F53" t="s">
         <v>235</v>
@@ -5459,7 +5452,7 @@
         <v>39</v>
       </c>
       <c r="E54" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F54" t="s">
         <v>112</v>
@@ -5513,7 +5506,7 @@
         <v>151</v>
       </c>
       <c r="E55" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F55" t="s">
         <v>246</v>
@@ -5567,7 +5560,7 @@
         <v>43</v>
       </c>
       <c r="E56" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F56" t="s">
         <v>246</v>
@@ -5621,7 +5614,7 @@
         <v>105</v>
       </c>
       <c r="E57" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F57" t="s">
         <v>246</v>
@@ -5675,7 +5668,7 @@
         <v>43</v>
       </c>
       <c r="E58" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F58" t="s">
         <v>246</v>
@@ -5728,7 +5721,7 @@
         <v>39</v>
       </c>
       <c r="E59" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F59" t="s">
         <v>246</v>
@@ -5781,7 +5774,7 @@
         <v>27</v>
       </c>
       <c r="E60" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F60" t="s">
         <v>246</v>
@@ -5834,7 +5827,7 @@
         <v>43</v>
       </c>
       <c r="E61" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F61" t="s">
         <v>246</v>
@@ -5891,7 +5884,7 @@
         <v>43</v>
       </c>
       <c r="E62" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F62" t="s">
         <v>246</v>
@@ -5945,7 +5938,7 @@
         <v>39</v>
       </c>
       <c r="E63" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F63" t="s">
         <v>246</v>
@@ -5998,7 +5991,7 @@
         <v>39</v>
       </c>
       <c r="E64" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F64" t="s">
         <v>112</v>
@@ -6051,7 +6044,7 @@
         <v>43</v>
       </c>
       <c r="E65" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F65" t="s">
         <v>246</v>
@@ -6107,7 +6100,7 @@
         <v>43</v>
       </c>
       <c r="E66" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F66" t="s">
         <v>246</v>
@@ -6161,7 +6154,7 @@
         <v>57</v>
       </c>
       <c r="E67" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F67" t="s">
         <v>246</v>
@@ -6218,7 +6211,7 @@
         <v>57</v>
       </c>
       <c r="E68" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F68" t="s">
         <v>9</v>
@@ -6268,7 +6261,7 @@
         <v>29</v>
       </c>
       <c r="E69" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F69" t="s">
         <v>299</v>
@@ -6319,7 +6312,7 @@
         <v>308</v>
       </c>
       <c r="E70" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="F70" t="s">
         <v>112</v>
@@ -6372,7 +6365,7 @@
         <v>315</v>
       </c>
       <c r="E71" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F71" t="s">
         <v>112</v>
@@ -6426,7 +6419,7 @@
         <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F72" t="s">
         <v>112</v>
@@ -6477,7 +6470,7 @@
         <v>305</v>
       </c>
       <c r="E73" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F73" t="s">
         <v>9</v>
@@ -6530,7 +6523,7 @@
         <v>105</v>
       </c>
       <c r="E74" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F74" t="s">
         <v>9</v>
@@ -6584,7 +6577,7 @@
         <v>105</v>
       </c>
       <c r="E75" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F75" t="s">
         <v>9</v>
@@ -6635,7 +6628,7 @@
         <v>334</v>
       </c>
       <c r="E76" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F76" t="s">
         <v>9</v>
@@ -6686,7 +6679,7 @@
         <v>29</v>
       </c>
       <c r="E77" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F77" t="s">
         <v>9</v>
@@ -6738,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="E78" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F78" t="s">
         <v>9</v>
@@ -6788,7 +6781,7 @@
         <v>43</v>
       </c>
       <c r="E79" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F79" t="s">
         <v>9</v>
@@ -6839,7 +6832,7 @@
         <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F80" t="s">
         <v>9</v>
@@ -6890,7 +6883,7 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F81" t="s">
         <v>9</v>
@@ -6940,7 +6933,7 @@
         <v>43</v>
       </c>
       <c r="E82" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
@@ -6990,7 +6983,7 @@
         <v>105</v>
       </c>
       <c r="E83" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F83" t="s">
         <v>9</v>
@@ -7044,7 +7037,7 @@
         <v>105</v>
       </c>
       <c r="E84" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F84" t="s">
         <v>9</v>
@@ -7096,7 +7089,7 @@
         <v>105</v>
       </c>
       <c r="E85" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F85" t="s">
         <v>9</v>
@@ -7147,7 +7140,7 @@
         <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F86" t="s">
         <v>9</v>
@@ -7198,7 +7191,7 @@
         <v>43</v>
       </c>
       <c r="E87" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F87" t="s">
         <v>9</v>
@@ -7252,7 +7245,7 @@
         <v>43</v>
       </c>
       <c r="E88" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F88" t="s">
         <v>9</v>
@@ -7306,7 +7299,7 @@
         <v>105</v>
       </c>
       <c r="E89" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F89" t="s">
         <v>9</v>
@@ -7324,7 +7317,7 @@
         <v>386</v>
       </c>
       <c r="K89">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L89" t="s">
         <v>387</v>
@@ -7360,7 +7353,7 @@
         <v>43</v>
       </c>
       <c r="E90" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F90" t="s">
         <v>9</v>
@@ -7411,7 +7404,7 @@
         <v>105</v>
       </c>
       <c r="E91" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F91" t="s">
         <v>9</v>
@@ -7429,7 +7422,7 @@
         <v>396</v>
       </c>
       <c r="K91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L91" t="s">
         <v>397</v>
@@ -7462,7 +7455,7 @@
         <v>57</v>
       </c>
       <c r="E92" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F92" t="s">
         <v>9</v>
@@ -7512,7 +7505,7 @@
         <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F93" t="s">
         <v>9</v>
@@ -7563,7 +7556,7 @@
         <v>105</v>
       </c>
       <c r="E94" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F94" t="s">
         <v>9</v>
@@ -7617,7 +7610,7 @@
         <v>43</v>
       </c>
       <c r="E95" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F95" t="s">
         <v>9</v>
@@ -7670,7 +7663,7 @@
         <v>105</v>
       </c>
       <c r="E96" t="s">
-        <v>105</v>
+        <v>715</v>
       </c>
       <c r="F96" t="s">
         <v>9</v>
@@ -7724,7 +7717,7 @@
         <v>39</v>
       </c>
       <c r="E97" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F97" t="s">
         <v>9</v>
@@ -7778,7 +7771,7 @@
         <v>186</v>
       </c>
       <c r="E98" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="F98" t="s">
         <v>9</v>
@@ -7829,7 +7822,7 @@
         <v>424</v>
       </c>
       <c r="E99" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F99" t="s">
         <v>9</v>
@@ -7883,7 +7876,7 @@
         <v>27</v>
       </c>
       <c r="E100" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F100" t="s">
         <v>48</v>
@@ -7937,7 +7930,7 @@
         <v>57</v>
       </c>
       <c r="E101" t="s">
-        <v>315</v>
+        <v>714</v>
       </c>
       <c r="F101" t="s">
         <v>48</v>

--- a/goldStandard/_Index.xlsx
+++ b/goldStandard/_Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore-development\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC13A02-D14B-45E8-8F5E-5FEA36084C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9220C87C-FFFA-48F0-BA5E-EAC8A76FB1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="1065" windowWidth="29700" windowHeight="19665" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="15240" windowHeight="19365" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
   </bookViews>
   <sheets>
     <sheet name="In" sheetId="1" r:id="rId1"/>
@@ -3893,7 +3893,6 @@
         <v>478</v>
       </c>
       <c r="K24">
-        <f>2</f>
         <v>2</v>
       </c>
       <c r="L24" t="s">
@@ -4351,7 +4350,6 @@
         <v>483</v>
       </c>
       <c r="K33">
-        <f>3</f>
         <v>3</v>
       </c>
       <c r="L33" t="s">
@@ -5251,7 +5249,6 @@
         <v>215</v>
       </c>
       <c r="K50">
-        <f>6</f>
         <v>6</v>
       </c>
       <c r="L50" t="s">
@@ -5306,7 +5303,6 @@
         <v>489</v>
       </c>
       <c r="K51">
-        <f>2</f>
         <v>2</v>
       </c>
       <c r="L51" t="s">
@@ -6697,7 +6693,6 @@
         <v>339</v>
       </c>
       <c r="K77">
-        <f>3</f>
         <v>3</v>
       </c>
       <c r="L77" t="s">
@@ -7055,7 +7050,6 @@
         <v>497</v>
       </c>
       <c r="K84">
-        <f>2</f>
         <v>2</v>
       </c>
       <c r="L84" t="s">

--- a/goldStandard/_Index.xlsx
+++ b/goldStandard/_Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore-development\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9220C87C-FFFA-48F0-BA5E-EAC8A76FB1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6C4FF0-7C14-454B-BF4A-CD46A9675EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="15240" windowHeight="19365" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{F827C457-048B-4104-BF2A-59E43A6422D6}"/>
   </bookViews>
   <sheets>
     <sheet name="In" sheetId="1" r:id="rId1"/>
@@ -2592,28 +2592,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BCF4AC8-88B5-4543-8C52-FD30450BEA57}">
   <dimension ref="A1:S102"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" customWidth="1"/>
-    <col min="4" max="5" width="22.85546875" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="27.85546875" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" customWidth="1"/>
-    <col min="10" max="10" width="27.85546875" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" customWidth="1"/>
-    <col min="12" max="12" width="32.42578125" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" customWidth="1"/>
-    <col min="14" max="14" width="38.28515625" customWidth="1"/>
-    <col min="15" max="15" width="19.140625" customWidth="1"/>
-    <col min="16" max="16" width="16.140625" customWidth="1"/>
-    <col min="17" max="17" width="40.7109375" customWidth="1"/>
-    <col min="18" max="18" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="116.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3828125" customWidth="1"/>
+    <col min="4" max="5" width="22.84375" customWidth="1"/>
+    <col min="6" max="6" width="15.3046875" customWidth="1"/>
+    <col min="7" max="7" width="17.69140625" customWidth="1"/>
+    <col min="8" max="8" width="27.84375" customWidth="1"/>
+    <col min="9" max="9" width="12.15234375" customWidth="1"/>
+    <col min="10" max="10" width="27.84375" customWidth="1"/>
+    <col min="11" max="11" width="9.84375" customWidth="1"/>
+    <col min="12" max="12" width="32.3828125" customWidth="1"/>
+    <col min="13" max="13" width="12.15234375" customWidth="1"/>
+    <col min="14" max="14" width="38.3046875" customWidth="1"/>
+    <col min="15" max="15" width="19.15234375" customWidth="1"/>
+    <col min="16" max="16" width="16.15234375" customWidth="1"/>
+    <col min="17" max="17" width="40.69140625" customWidth="1"/>
+    <col min="18" max="18" width="38.3828125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="116.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="2" customFormat="1" ht="15.9" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>37</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="R8" s="4"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4846,7 +4846,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4900,7 +4900,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4953,7 +4953,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5217,7 +5217,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5271,7 +5271,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5596,7 +5596,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5866,7 +5866,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5920,7 +5920,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6082,7 +6082,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6193,7 +6193,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6347,7 +6347,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6401,7 +6401,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6452,7 +6452,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6610,7 +6610,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6661,7 +6661,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6712,7 +6712,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6864,7 +6864,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6914,7 +6914,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6964,7 +6964,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7069,7 +7069,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7120,7 +7120,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7171,7 +7171,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7225,7 +7225,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7279,7 +7279,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>88</v>
       </c>
@@ -7333,7 +7333,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>89</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>90</v>
       </c>
@@ -7435,7 +7435,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>91</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>92</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>93</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>94</v>
       </c>
@@ -7643,7 +7643,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>95</v>
       </c>
@@ -7697,7 +7697,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7751,7 +7751,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7802,7 +7802,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7856,7 +7856,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7910,7 +7910,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7961,7 +7961,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
       <c r="B102" s="1"/>
       <c r="L102" s="4"/>
     </row>
@@ -8065,9 +8065,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2087B5-F5A7-4715-8903-807F8D9032AE}">
   <dimension ref="A1:R5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.9" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>37</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>15</v>
       </c>
@@ -8161,7 +8161,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B3">
         <v>23</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B4">
         <v>27</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B5">
         <v>2</v>
       </c>
@@ -8302,12 +8302,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5412E459-6599-4D39-A6E4-9FCCBAA2B3FA}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="65.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8315,7 +8315,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>225</v>
       </c>
@@ -8323,7 +8323,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>228</v>
       </c>
@@ -8331,7 +8331,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>230</v>
       </c>
@@ -8339,7 +8339,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>232</v>
       </c>
@@ -8347,7 +8347,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>286</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>307</v>
       </c>
@@ -8363,7 +8363,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>378</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>380</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>382</v>
       </c>
@@ -8387,7 +8387,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>389</v>
       </c>
@@ -8395,7 +8395,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>441</v>
       </c>
